--- a/annual_returns.xlsx
+++ b/annual_returns.xlsx
@@ -647,88 +647,88 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.01803992067502702</v>
+        <v>0.01803952075481896</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.6513732909974028</v>
+        <v>0.6513744111128561</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.4187936651965184</v>
+        <v>-0.4187936408010601</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-0.2335325165071439</v>
+        <v>-0.2335329311907193</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-0.3816688809762329</v>
+        <v>-0.3816686421017804</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.3867549207900416</v>
+        <v>0.3867546812667546</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.0563767917020912</v>
+        <v>0.05637629349675133</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>-0.00316561175750818</v>
+        <v>-0.003164434207204803</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.1215728748157219</v>
+        <v>0.1215718423100096</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.1545696111103672</v>
+        <v>0.1545700655431392</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>-0.4150722509601843</v>
+        <v>-0.4150723121444779</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.5132505564593477</v>
+        <v>0.5132504383083232</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.1139458972839671</v>
+        <v>0.1139455877081046</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.0261385686988409</v>
+        <v>0.02613866859943337</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0.1529619698522731</v>
+        <v>0.1529623585769933</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>0.2624123609728033</v>
+        <v>0.2624122415793257</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0.178424146027728</v>
+        <v>0.1784239488892811</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>0.05469239239899926</v>
+        <v>0.054691977092445</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.1501179771507288</v>
+        <v>0.1501186509088253</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.3425647587099354</v>
+        <v>0.3425644686421785</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>-0.01677226276428645</v>
+        <v>-0.0167723295700094</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0.4985585170297733</v>
+        <v>0.4985590755363654</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>0.4361880571348353</v>
+        <v>0.4361878051190067</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.3474410958649705</v>
+        <v>0.3474409736835209</v>
       </c>
       <c r="AA2" s="3" t="n">
-        <v>-0.2772629560389609</v>
+        <v>-0.2772628905035783</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>0.5601838106118116</v>
+        <v>0.5601836851489554</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>0.2163062554200001</v>
+        <v>0.2163062728143625</v>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>0.2460593797775963</v>
+        <v>0.246059462160146</v>
       </c>
       <c r="AE2" s="2" t="n">
         <v>0.3284539365995716</v>
@@ -746,61 +746,61 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.005361732641899986</v>
+        <v>0.005361817612089537</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.02667707524854079</v>
+        <v>0.02667758055064984</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.258565010403939</v>
+        <v>0.2585638460275983</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0.09430593678772425</v>
+        <v>-0.09430596159440918</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.147360826192943</v>
+        <v>-0.1473600702967638</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.3049182701110027</v>
+        <v>0.304918088348616</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.108597267350536</v>
+        <v>0.1085963693772423</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.06204445689790661</v>
+        <v>0.06204518520594093</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.1888860473208651</v>
+        <v>0.1888858736499601</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.1917571613777176</v>
+        <v>-0.1917574985869139</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>-0.5490219484912907</v>
+        <v>-0.5490219021199552</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1756542421827549</v>
+        <v>0.1756542646497079</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.1190395993587232</v>
+        <v>0.1190399386922694</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>-0.1714256381299488</v>
+        <v>-0.1714257020186396</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>0.2841540941827474</v>
+        <v>0.2841542955121223</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.3552735093481487</v>
+        <v>0.35527304647557</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0.1505356335750723</v>
+        <v>0.1505361156598604</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-0.01770036738767533</v>
+        <v>-0.01770047836089927</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2241518952515822</v>
+        <v>0.2241516031486177</v>
       </c>
       <c r="V3" s="2" t="n">
         <v>0.2199987992677872</v>
@@ -812,22 +812,22 @@
         <v>0.3187401384967818</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.01736349374523927</v>
+        <v>-0.01736370276096533</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.347978827503485</v>
+        <v>0.3479789724248119</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>-0.105864835446098</v>
+        <v>-0.1058646361848936</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>0.1203094972364134</v>
+        <v>0.120309247772477</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>0.3055622184685867</v>
+        <v>0.3055624605979379</v>
       </c>
       <c r="AD3" s="2" t="n">
-        <v>0.149023536793333</v>
+        <v>0.1490234443656935</v>
       </c>
       <c r="AE3" s="3" t="n">
         <v>-0.05340256693391532</v>
@@ -845,88 +845,88 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.003358024847339047</v>
+        <v>0.00335810824795435</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.1794925069482742</v>
+        <v>0.1794926726348633</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.2440086604277087</v>
+        <v>0.2440082047328644</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.1813304621680309</v>
+        <v>-0.1813296562234216</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-0.146816406716054</v>
+        <v>-0.1468169160251814</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.2581168462434773</v>
+        <v>0.2581170470132406</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.3393517554187964</v>
+        <v>0.3393520961468641</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.4017889642704118</v>
+        <v>0.4017882532812593</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.1806885801220079</v>
+        <v>0.1806887730798334</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.3688834801416352</v>
+        <v>0.368883162739104</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>-0.3895530419990055</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2176376812690042</v>
+        <v>0.2176375425296744</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.2177692281222847</v>
+        <v>0.2177695947594247</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.02839091099369462</v>
+        <v>0.02839062498391831</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.05212601743553935</v>
+        <v>0.05212611316069626</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.2624634459402024</v>
+        <v>0.2624643106901163</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.08678217000496058</v>
+        <v>-0.08678272703460688</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.2149819542513006</v>
+        <v>-0.2149817881138687</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.2802540942427307</v>
+        <v>0.2802537272689836</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>-0.008874343728888623</v>
+        <v>-0.008874791517217262</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>-0.1821762931336006</v>
+        <v>-0.1821757730432199</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.1174149315247217</v>
+        <v>0.1174147257568852</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.3267132970044401</v>
+        <v>-0.3267132146060674</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.5327987307487294</v>
+        <v>0.532798543161324</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.6432490833895357</v>
+        <v>0.6432489237047789</v>
       </c>
       <c r="AB4" s="3" t="n">
-        <v>-0.006302364628161916</v>
+        <v>-0.006302462416845067</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>0.0555921354051403</v>
+        <v>0.05559224407071373</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>0.07876269073095488</v>
+        <v>0.07876279067009717</v>
       </c>
       <c r="AE4" s="2" t="n">
         <v>0.2672284657221249</v>
@@ -944,85 +944,85 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.03870222444779592</v>
+        <v>0.03870118005450363</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.1950531798369732</v>
+        <v>0.1950534839045193</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-0.1176956600523846</v>
+        <v>-0.1176955900772207</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0.008258118399936287</v>
+        <v>-0.008258015530844598</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.007389657429019647</v>
+        <v>-0.007389552839648483</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1493007726530409</v>
+        <v>0.1493004408175376</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.01273033134195001</v>
+        <v>0.01273060871652332</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.06416029404828683</v>
+        <v>0.06416065035056828</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.07051441393112734</v>
+        <v>0.07051404365989167</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.07159589856602699</v>
+        <v>0.07159589287658363</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-0.2331011807161925</v>
+        <v>-0.2331012375869043</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1951880140709463</v>
+        <v>0.1951875305864386</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.03299232339289149</v>
+        <v>0.03299282217042321</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.1239683338061321</v>
+        <v>0.1239683240967866</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.1737183499296693</v>
+        <v>0.1737184075072267</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.414092872916408</v>
+        <v>0.4140928237476809</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>0.2513638907100595</v>
+        <v>0.2513637856356619</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.06831181590837154</v>
+        <v>0.06831174880726087</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>-0.02761698659990008</v>
+        <v>-0.02761711395537636</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.2177281946056253</v>
+        <v>0.2177284305806353</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.06279969064191793</v>
+        <v>0.06279990282167236</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.2045177451043221</v>
+        <v>0.2045172051683384</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.1329521760605166</v>
+        <v>0.1329522919869854</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.260385477002445</v>
+        <v>0.2603859539786966</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>-0.02079229250305614</v>
+        <v>-0.02079263588970737</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>0.02066576816531485</v>
+        <v>0.02066577061494845</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>0.02474435034350631</v>
+        <v>0.02474446935298791</v>
       </c>
       <c r="AD5" s="2" t="n">
         <v>0.1450372837805922</v>
@@ -1043,88 +1043,88 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.05503403291252407</v>
+        <v>0.0550327889218114</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.2185885454093244</v>
+        <v>0.2185888996478762</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.06708688400122442</v>
+        <v>0.06708708269741015</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.1054061219185554</v>
+        <v>-0.1054060914561338</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-0.2457298682172888</v>
+        <v>-0.245730165727913</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.3185762837353254</v>
+        <v>0.3185766633911398</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.1775144462983154</v>
+        <v>0.1775139747672461</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.02748651755823062</v>
+        <v>0.02748652261301809</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.1351585042520074</v>
+        <v>0.1351585284428192</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.1349317444350193</v>
+        <v>0.1349320810508552</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.3872759606914191</v>
+        <v>-0.3872765320519624</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2203112235608824</v>
+        <v>0.2203119652272059</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.278206660457857</v>
+        <v>0.2782066192486943</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-0.01099653694957359</v>
+        <v>-0.01099617594782742</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.1492438049814122</v>
+        <v>0.1492434890942747</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.4054860793474986</v>
+        <v>0.405485747536932</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>0.1036573148389617</v>
+        <v>0.1036579895179757</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.04323382069785209</v>
+        <v>-0.04323389245108999</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2000552191916678</v>
+        <v>0.2000550985409917</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.2397923228921761</v>
+        <v>0.2397922338665117</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.1324741663180937</v>
+        <v>-0.1324741083995854</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.2908455363050775</v>
+        <v>0.2908457171759737</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.1090499899042059</v>
+        <v>0.1090497604628506</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.2108201735539803</v>
+        <v>0.2108200802845017</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>-0.0556872212236138</v>
+        <v>-0.05568722551320082</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.1812931957237058</v>
+        <v>0.1812930473671437</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0.1730970761048023</v>
+        <v>0.1730971810173545</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.1934699418008137</v>
+        <v>0.1934700823065034</v>
       </c>
       <c r="AE6" s="2" t="n">
         <v>0.1192398410686544</v>
@@ -1142,79 +1142,79 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.02576712616945254</v>
+        <v>0.02576640656980622</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.1950851427252809</v>
+        <v>0.195085814813508</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-0.1687405959051582</v>
+        <v>-0.1687403190870383</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1273011534054376</v>
+        <v>0.1273004912217963</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-0.1866003645430745</v>
+        <v>-0.1866002925479232</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.3720000887943684</v>
+        <v>0.3720006328775078</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.1288069161686904</v>
+        <v>0.1288059133402859</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0.06573495302588539</v>
+        <v>-0.0657343529969564</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.1841202041446521</v>
+        <v>0.1841200260392537</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.1366818832873591</v>
+        <v>-0.1366820738232629</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>-0.3297120083654829</v>
+        <v>-0.3297114190278582</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4056913758239289</v>
+        <v>0.4056904501368093</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.2746240133471074</v>
+        <v>0.2746236229529586</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.05994296420147593</v>
+        <v>0.05994279879177911</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.2359901184703994</v>
+        <v>0.2359909210833071</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.4273270308859325</v>
+        <v>0.4273263898695028</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>0.09461615530790946</v>
+        <v>0.09461683528367182</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.09902902486735887</v>
+        <v>0.0990287498844804</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.05968985729575382</v>
+        <v>0.05968963294838892</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.2282244883673816</v>
+        <v>0.2282245118260144</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.0158204439324976</v>
+        <v>0.01582044525647741</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.283895552882635</v>
+        <v>0.283895493886696</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.2963027059298144</v>
+        <v>0.2963031289617502</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.2792814269766639</v>
+        <v>0.2792812726774123</v>
       </c>
       <c r="AA7" s="3" t="n">
-        <v>-0.3627218558503452</v>
+        <v>-0.3627219051680074</v>
       </c>
       <c r="AB7" s="2" t="n">
         <v>0.3963927927258393</v>
@@ -1241,88 +1241,88 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.02476404013850808</v>
+        <v>0.02476405027011852</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>-0.1425784835613021</v>
+        <v>-0.1425782743247919</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.2554236476181333</v>
+        <v>0.2554236096576419</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-0.09927232713573753</v>
+        <v>-0.09927185102178471</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-0.2009403455025104</v>
+        <v>-0.2009410314629944</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.1117328521405891</v>
+        <v>0.1117335968099722</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.07645508098281328</v>
+        <v>0.07645429662482828</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.02841785633290939</v>
+        <v>0.02841866209191535</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.1448979476478855</v>
+        <v>0.1448981266661893</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.1268631885095755</v>
+        <v>0.1268626544939686</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>-0.1502360884577426</v>
+        <v>-0.1502359965295582</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1427767030596885</v>
+        <v>0.1427774669013104</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.137798754910992</v>
+        <v>0.1377986628051993</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.1408682074242102</v>
+        <v>0.140867537212966</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.1072598607892614</v>
+        <v>0.1072596891487678</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.2630882364567206</v>
+        <v>0.2630887422803145</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>0.1571981118853485</v>
+        <v>0.1571983187526724</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0.06873047869467364</v>
+        <v>0.068730025320483</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.04980684593689766</v>
+        <v>0.04980654823483022</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.1298197143765132</v>
+        <v>0.1298198457165398</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>-0.08071138051875104</v>
+        <v>-0.08071122669478692</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.274339477402936</v>
+        <v>0.2743393863927162</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.1011073435966086</v>
+        <v>0.1011073508174491</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1720549888866036</v>
+        <v>0.172055064905819</v>
       </c>
       <c r="AA8" s="3" t="n">
         <v>-0.008093919615959622</v>
       </c>
       <c r="AB8" s="3" t="n">
-        <v>-0.008181947006138057</v>
+        <v>-0.008182281746496711</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>0.1220214061629175</v>
+        <v>0.1220216723466361</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.01516152200171828</v>
+        <v>0.01516162378790931</v>
       </c>
       <c r="AE8" s="2" t="n">
         <v>0.07333522705498763</v>
@@ -1340,88 +1340,88 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.01361997562631911</v>
+        <v>0.01361923201037873</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>-0.04408559088839448</v>
+        <v>-0.04408551734084065</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.2247931652779243</v>
+        <v>0.2247935217629804</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-0.1300514008293301</v>
+        <v>-0.130051580628567</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-0.2877550436975667</v>
+        <v>-0.2877549645058982</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.2646585956007257</v>
+        <v>0.2646583438024208</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.2358588395325198</v>
+        <v>0.2358591240221342</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1638563074105315</v>
+        <v>0.1638559284022751</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.2089273880329623</v>
+        <v>0.2089276097148078</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0.1842055953705508</v>
+        <v>0.1842057976111542</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>-0.2891022340888914</v>
+        <v>-0.2891020993247209</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1170576982107447</v>
+        <v>0.11705777614579</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.0530864522775063</v>
+        <v>0.05308599932535896</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>0.1964010420846758</v>
+        <v>0.1964014505210934</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.0103702441834177</v>
+        <v>0.01036989925571574</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1306574809627925</v>
+        <v>0.1306570586082776</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>0.2874722332647077</v>
+        <v>0.2874721165206318</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>-0.04929061832169324</v>
+        <v>-0.04929029303497912</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1607640294638379</v>
+        <v>0.160764049088824</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.1204807949560573</v>
+        <v>0.1204809127928579</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.03935172540404541</v>
+        <v>0.03935163154587973</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.2593131509940452</v>
+        <v>0.2593132647157335</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.005105275420193456</v>
+        <v>0.005105132001494761</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1770402579782209</v>
+        <v>0.177040425930385</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>0.01442964654766921</v>
+        <v>0.01442928286369605</v>
       </c>
       <c r="AB9" s="3" t="n">
-        <v>-0.07174786796621246</v>
+        <v>-0.07174759492950844</v>
       </c>
       <c r="AC9" s="2" t="n">
-        <v>0.2331222397645389</v>
+        <v>0.2331221904004421</v>
       </c>
       <c r="AD9" s="2" t="n">
-        <v>0.1602436283709976</v>
+        <v>0.1602437495027853</v>
       </c>
       <c r="AE9" s="2" t="n">
         <v>0.04779942464971931</v>
@@ -1456,37 +1456,37 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" s="2" t="n">
-        <v>0.04365450000321758</v>
+        <v>0.04365440936752507</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.02755229799765146</v>
+        <v>0.02755238723496345</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.1069551623555232</v>
+        <v>0.1069553313873823</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>-0.02387637361127148</v>
+        <v>-0.02387675171485693</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>0.2868379018979388</v>
+        <v>0.2868381256401122</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.02186268048962159</v>
+        <v>-0.02186249947043084</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.4610099644750854</v>
+        <v>0.461009534332109</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>-0.2624927534259335</v>
+        <v>-0.2624927130182646</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.1236000985950436</v>
+        <v>0.1236003435370987</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>0.05094259590719852</v>
+        <v>0.05094228271366008</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.02629910698238502</v>
+        <v>0.02629930747751974</v>
       </c>
       <c r="AE10" s="2" t="n">
         <v>0.09753848165712986</v>
@@ -1504,88 +1504,88 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.05251350069823868</v>
+        <v>0.05251334267320451</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.2292270786509465</v>
+        <v>0.2292273097605726</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.1622410997937925</v>
+        <v>-0.162241120708603</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.02140514858871256</v>
+        <v>0.02140561351379522</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.05328445468143883</v>
+        <v>-0.05328428797428542</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.3741289435293715</v>
+        <v>0.37412749187017</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.1349245539232911</v>
+        <v>0.1349253268812689</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.04080162681215649</v>
+        <v>0.04080182672480936</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.1836473192813666</v>
+        <v>0.183647069192475</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0.2208557249072047</v>
+        <v>0.2208555409605291</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.4404888981819203</v>
+        <v>-0.4404887923794544</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.4815800166434201</v>
+        <v>0.4815794732308456</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>0.2055492942277286</v>
+        <v>0.2055499175856104</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.1092180965529751</v>
+        <v>-0.1092184742185512</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>0.1469340124842606</v>
+        <v>0.1469343397238727</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>0.259879780515917</v>
+        <v>0.2598798788741881</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>0.07182985621497462</v>
+        <v>0.07182952461460479</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-0.08693357005008251</v>
+        <v>-0.08693348019220903</v>
       </c>
       <c r="U11" s="2" t="n">
         <v>0.1679637304995818</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>0.2401266123580859</v>
+        <v>0.2401267969242056</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.1487742005289214</v>
+        <v>-0.1487743272155176</v>
       </c>
       <c r="X11" s="2" t="n">
-        <v>0.2412909497491917</v>
+        <v>0.2412907749090394</v>
       </c>
       <c r="Y11" s="2" t="n">
-        <v>0.2046063032496588</v>
+        <v>0.2046064729226749</v>
       </c>
       <c r="Z11" s="2" t="n">
         <v>0.2743797673439119</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>-0.1229692268181752</v>
+        <v>-0.1229691350644748</v>
       </c>
       <c r="AB11" s="2" t="n">
-        <v>0.1245592812202458</v>
+        <v>0.1245590589519272</v>
       </c>
       <c r="AC11" s="2" t="n">
-        <v>0.001492305847436759</v>
+        <v>0.001492305986267262</v>
       </c>
       <c r="AD11" s="2" t="n">
-        <v>0.09943337676348696</v>
+        <v>0.09943347889217247</v>
       </c>
       <c r="AE11" s="2" t="n">
         <v>0.1329100790530531</v>
@@ -1623,28 +1623,28 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="3" t="n">
-        <v>-0.1688051523266501</v>
+        <v>-0.168805357667382</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>0.310478454399072</v>
+        <v>0.3104787516132539</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>0.2690435472995627</v>
+        <v>0.2690435618803686</v>
       </c>
       <c r="Z12" s="2" t="n">
-        <v>0.1596198403686027</v>
+        <v>0.1596196831892627</v>
       </c>
       <c r="AA12" s="3" t="n">
-        <v>-0.3762951644385958</v>
+        <v>-0.3762952285204823</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>0.5282086517733859</v>
+        <v>0.5282084870417123</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>0.3470661769802317</v>
+        <v>0.3470664299798338</v>
       </c>
       <c r="AD12" s="2" t="n">
-        <v>0.2307845086793088</v>
+        <v>0.2307844101903578</v>
       </c>
       <c r="AE12" s="3" t="n">
         <v>-0.01410818769531763</v>
@@ -1664,70 +1664,70 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" s="3" t="n">
-        <v>-0.5034831628843297</v>
+        <v>-0.5034832084045648</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0.1459186235807726</v>
+        <v>-0.1459185452793216</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>-0.4707286422990851</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8731378722645653</v>
+        <v>0.8731374666412881</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0.1957099238294255</v>
+        <v>-0.1957098037992829</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.09799197057470388</v>
+        <v>0.0979923810313581</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0.08160444245196286</v>
+        <v>-0.08160472395358687</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0.03536423423761381</v>
+        <v>-0.03536416748758087</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0.4574861441383279</v>
+        <v>-0.4574861124815988</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.5854628500584176</v>
+        <v>0.5854626478341343</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>0.1651144682165293</v>
+        <v>0.1651145486656349</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-0.06455568699271985</v>
+        <v>-0.06455568253526345</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>0.08549913889391636</v>
+        <v>0.08549891114302643</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>0.3332986082966907</v>
+        <v>0.3332985176260639</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>0.3022333290832591</v>
+        <v>0.3022335947435613</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>-0.003373053638469292</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>0.3554260562586045</v>
+        <v>0.3554262134454997</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>0.384776357986794</v>
+        <v>0.3847761973962032</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>-0.09052264403933452</v>
+        <v>-0.09052272778471604</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>0.6445059544034408</v>
+        <v>0.6445061058308408</v>
       </c>
       <c r="Y13" s="2" t="n">
-        <v>0.555344462048635</v>
+        <v>0.5553443500626898</v>
       </c>
       <c r="Z13" s="2" t="n">
-        <v>0.4213154001581281</v>
+        <v>0.4213155024938897</v>
       </c>
       <c r="AA13" s="3" t="n">
         <v>-0.3353174142831742</v>
@@ -1760,76 +1760,76 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>-0.08465273671220253</v>
+        <v>-0.08465226546337168</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-0.4784963693128591</v>
+        <v>-0.4784965354310255</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.8095312406483315</v>
+        <v>0.8095300547282183</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>-0.1426299210378611</v>
+        <v>-0.1426295562277158</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.133838151244589</v>
+        <v>0.1338384274803734</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.002272519943063767</v>
+        <v>0.002271834639484105</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>-0.02148644927933285</v>
+        <v>-0.02148543628049482</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>-0.5170984750015861</v>
+        <v>-0.517098728976493</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.7494308921235686</v>
+        <v>0.7494305154061585</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>0.1364558987383497</v>
+        <v>0.1364560741497178</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>-0.1059531292089432</v>
+        <v>-0.1059526570285552</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>0.06621205823799925</v>
+        <v>0.06621162441647321</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>0.4157918540841044</v>
+        <v>0.4157923629025317</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>0.2985082887422825</v>
+        <v>0.2985073728396304</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>-0.02018544406745326</v>
+        <v>-0.0201852434734372</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>0.3834407372791557</v>
+        <v>0.3834405089630728</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>0.3978625365036439</v>
+        <v>0.3978633729892809</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>-0.06488538914231379</v>
+        <v>-0.06488544322028011</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>0.6241722301702706</v>
+        <v>0.6241712248178986</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>0.5271725080823733</v>
+        <v>0.5271730955732352</v>
       </c>
       <c r="Z14" s="2" t="n">
-        <v>0.4408978602648632</v>
+        <v>0.440897356468823</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>-0.3508613433864259</v>
+        <v>-0.3508610290111565</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>0.671178142019403</v>
+        <v>0.6711776476751496</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>0.1292433312749057</v>
+        <v>0.129243513252929</v>
       </c>
       <c r="AD14" s="2" t="n">
         <v>0.4073726610134432</v>
@@ -1853,61 +1853,61 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>-0.1013034969556823</v>
+        <v>-0.1013029494777429</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.4469348305230357</v>
+        <v>-0.4469350598499733</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.5001987959237533</v>
+        <v>0.5001987959628915</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.1380484839640503</v>
+        <v>0.1380483142886109</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0.05531084530855512</v>
+        <v>-0.05531034552742631</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.1076024970820095</v>
+        <v>0.1076018060166009</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0.1574696664856325</v>
+        <v>0.1574703971483575</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>-0.3843023643867032</v>
+        <v>-0.3843025292400264</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.4752910793402871</v>
+        <v>0.4752913480573846</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>0.2464264809595409</v>
+        <v>0.2464263503054593</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>-0.07322438672857345</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>0.167748086130741</v>
+        <v>0.1677481768741509</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>0.3068085760453167</v>
+        <v>0.3068083190797379</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>0.1342318419609221</v>
+        <v>0.1342319768528115</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>0.1211962629444023</v>
+        <v>0.1211964726510082</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>0.05785953968573265</v>
+        <v>0.05785934182555486</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>0.4215574841993119</v>
+        <v>0.4215573957951999</v>
       </c>
       <c r="W15" s="2" t="n">
-        <v>0.1244063280481442</v>
+        <v>0.124406522349386</v>
       </c>
       <c r="X15" s="2" t="n">
-        <v>0.3432289679050036</v>
+        <v>0.3432288193234976</v>
       </c>
       <c r="Y15" s="2" t="n">
         <v>0.5286013805189052</v>
@@ -1960,34 +1960,34 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" s="3" t="n">
-        <v>-0.107735769549113</v>
+        <v>-0.1077351877970345</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>0.1015397582653463</v>
+        <v>0.1015393743449933</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>0.1860584573249291</v>
+        <v>0.1860580289919849</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>0.01470455401704673</v>
+        <v>0.01470481663905376</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>0.2851835064760715</v>
+        <v>0.2851836765197633</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>0.5053123127595069</v>
+        <v>0.5053119812796083</v>
       </c>
       <c r="Z16" s="2" t="n">
-        <v>0.196755304145849</v>
+        <v>0.1967555851276557</v>
       </c>
       <c r="AA16" s="3" t="n">
-        <v>-0.2645704623683697</v>
+        <v>-0.2645706438410775</v>
       </c>
       <c r="AB16" s="2" t="n">
-        <v>0.3971121437366865</v>
+        <v>0.3971121833951194</v>
       </c>
       <c r="AC16" s="2" t="n">
-        <v>0.182105971121503</v>
+        <v>0.1821060556197138</v>
       </c>
       <c r="AD16" s="2" t="n">
         <v>0.130634525722656</v>
@@ -2016,19 +2016,19 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" s="2" t="n">
-        <v>0.1003899130443875</v>
+        <v>0.1003898103206897</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0.1129317934677025</v>
+        <v>0.1129317086322299</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0.4402938155190282</v>
+        <v>-0.4402937728542912</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.791161658600974</v>
+        <v>0.7911617947921057</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>0.36723205596669</v>
+        <v>0.3672319520090901</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>-0.05823132254014851</v>
@@ -2107,10 +2107,10 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" s="3" t="n">
-        <v>-0.01079487283727121</v>
+        <v>-0.01079477136817775</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>0.03756715384690379</v>
+        <v>0.03756726262528631</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>-0.02003902719778572</v>
@@ -2166,61 +2166,61 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" s="3" t="n">
-        <v>-0.06314737579355201</v>
+        <v>-0.06314708440563754</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0.2903013367499174</v>
+        <v>0.2903017763384483</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>-0.08617872853450192</v>
+        <v>-0.08617930283149178</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.00353284952190247</v>
+        <v>0.003533294816586041</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>0.1759885082469628</v>
+        <v>0.1759881370620691</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>0.05263134601462793</v>
+        <v>0.05263135097062221</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>0.3268750200717134</v>
+        <v>0.3268750493126817</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>0.4839049467345582</v>
+        <v>0.483905181614694</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>0.4497320073849034</v>
+        <v>0.4497315121867889</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>0.1357667580681192</v>
+        <v>0.1357669174628882</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>-0.1544695661042024</v>
+        <v>-0.1544693624101963</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>0.4377252303848949</v>
+        <v>0.4377251732463376</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>-0.1527708447316244</v>
+        <v>-0.1527710124468873</v>
       </c>
       <c r="X19" s="2" t="n">
-        <v>0.3256363856927671</v>
+        <v>0.3256364205894327</v>
       </c>
       <c r="Y19" s="2" t="n">
-        <v>0.4833157061616362</v>
+        <v>0.4833159877530557</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>-0.2044971505998167</v>
+        <v>-0.2044972373089082</v>
       </c>
       <c r="AA19" s="3" t="n">
-        <v>-0.2586637538226625</v>
+        <v>-0.2586638223322273</v>
       </c>
       <c r="AB19" s="2" t="n">
-        <v>0.07599559963315494</v>
+        <v>0.07599560665618399</v>
       </c>
       <c r="AC19" s="2" t="n">
-        <v>0.01006290507347685</v>
+        <v>0.01006299182436665</v>
       </c>
       <c r="AD19" s="2" t="n">
         <v>0.3589314772096208</v>
@@ -2244,76 +2244,76 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>-0.1202897832700063</v>
+        <v>-0.1202901019456578</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-0.4579901675512388</v>
+        <v>-0.4579900963973413</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.4579541250350441</v>
+        <v>0.4579537617265388</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.04794959305509039</v>
+        <v>0.04794960500368273</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.0244160700811018</v>
+        <v>0.02441623441284424</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.006745057113050512</v>
+        <v>0.006745057634941043</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0.04515083402669684</v>
+        <v>0.04515083749678062</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-0.1227655965924382</v>
+        <v>-0.1227651644088789</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.1517239980280736</v>
+        <v>0.1517241020881421</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>0.1484332507122745</v>
+        <v>0.1484328839555493</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>0.1171503022024962</v>
+        <v>0.1171503433049872</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>0.3212942547470921</v>
+        <v>0.3212941818388522</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>0.6554046018195796</v>
+        <v>0.6554039740365305</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>0.3383145787069242</v>
+        <v>0.3383148563957101</v>
       </c>
       <c r="T20" s="2" t="n">
         <v>0.1155935129691159</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>-0.2141731993477916</v>
+        <v>-0.214173268835159</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>0.2107583078696491</v>
+        <v>0.2107587686351873</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>-0.09532247316825637</v>
+        <v>-0.09532259138813681</v>
       </c>
       <c r="X20" s="2" t="n">
-        <v>0.2541846106303181</v>
+        <v>0.2541846503190073</v>
       </c>
       <c r="Y20" s="2" t="n">
-        <v>0.2601347995980638</v>
+        <v>0.2601348137328698</v>
       </c>
       <c r="Z20" s="2" t="n">
-        <v>0.009501049332575784</v>
+        <v>0.009501047391329065</v>
       </c>
       <c r="AA20" s="3" t="n">
-        <v>-0.1369019506446574</v>
+        <v>-0.1369021253324485</v>
       </c>
       <c r="AB20" s="2" t="n">
-        <v>0.03759148128094081</v>
+        <v>0.03759159853081218</v>
       </c>
       <c r="AC20" s="3" t="n">
-        <v>-0.02410942025022245</v>
+        <v>-0.02410953052775866</v>
       </c>
       <c r="AD20" s="2" t="n">
         <v>0.2798024559839278</v>
@@ -2342,64 +2342,64 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" s="2" t="n">
-        <v>0.02759854807954243</v>
+        <v>0.02759867398890536</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0.187463145257871</v>
+        <v>0.1874631943594647</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-0.3678483527010475</v>
+        <v>-0.3678483661514395</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.3849812637720211</v>
+        <v>0.3849800252376343</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>0.1134805289798986</v>
+        <v>0.1134808538281358</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>8.874288190741098e-05</v>
+        <v>8.92649454575789e-05</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>0.1577766890630345</v>
+        <v>0.1577762714865296</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>0.3777204851854827</v>
+        <v>0.3777211624250987</v>
       </c>
       <c r="S21" s="2" t="n">
-        <v>0.227242339012502</v>
+        <v>0.2272425710560282</v>
       </c>
       <c r="T21" s="2" t="n">
-        <v>0.09685372190651709</v>
+        <v>0.09685347760196072</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>0.09303033618000911</v>
+        <v>0.09303013265556359</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>0.3081383607804609</v>
+        <v>0.3081387440449348</v>
       </c>
       <c r="W21" s="2" t="n">
-        <v>0.1545187926129168</v>
+        <v>0.1545182850370892</v>
       </c>
       <c r="X21" s="2" t="n">
-        <v>0.32750084705787</v>
+        <v>0.3275009242239995</v>
       </c>
       <c r="Y21" s="2" t="n">
-        <v>0.2417504711087888</v>
+        <v>0.241750869002181</v>
       </c>
       <c r="Z21" s="2" t="n">
-        <v>0.210352278553585</v>
+        <v>0.210352391423545</v>
       </c>
       <c r="AA21" s="3" t="n">
-        <v>-0.1979566530561633</v>
+        <v>-0.1979569605869438</v>
       </c>
       <c r="AB21" s="2" t="n">
-        <v>0.03237717243620963</v>
+        <v>0.03237725082516985</v>
       </c>
       <c r="AC21" s="2" t="n">
-        <v>0.08618299572344723</v>
+        <v>0.08618314449484976</v>
       </c>
       <c r="AD21" s="2" t="n">
-        <v>0.0688307898260585</v>
+        <v>0.06883071965258836</v>
       </c>
       <c r="AE21" s="3" t="n">
         <v>-0.211618558021382</v>
@@ -2425,64 +2425,64 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" s="2" t="n">
-        <v>0.0600972305499432</v>
+        <v>0.06009677173866756</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>-0.2194080377616012</v>
+        <v>-0.2194078613050694</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>-0.1855275179652895</v>
+        <v>-0.185527220930698</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>-0.219220665260522</v>
+        <v>-0.2192209848160505</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>0.2065467533883689</v>
+        <v>0.2065465337754442</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>-0.05967576555749166</v>
+        <v>-0.05967558074675616</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>0.1690663854130026</v>
+        <v>0.1690664036605001</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>0.475211635126584</v>
+        <v>0.4752109404204157</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>0.01838615781551733</v>
+        <v>0.01838691916108948</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>0.04852663175915217</v>
+        <v>0.04852606973992102</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>0.3497879017304391</v>
+        <v>0.3497886108188499</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>0.07485775655035432</v>
+        <v>0.07485765670788291</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>-0.1900735717687102</v>
+        <v>-0.190073879584268</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>0.2744295492415536</v>
+        <v>0.2744301301355521</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>-0.07426866103428997</v>
+        <v>-0.07426896250021819</v>
       </c>
       <c r="Z22" s="2" t="n">
-        <v>0.3929274514732848</v>
+        <v>0.3929276024722208</v>
       </c>
       <c r="AA22" s="3" t="n">
-        <v>-0.1507988190894927</v>
+        <v>-0.1507987068402721</v>
       </c>
       <c r="AB22" s="3" t="n">
-        <v>-0.07610381508010333</v>
+        <v>-0.07610402408211869</v>
       </c>
       <c r="AC22" s="2" t="n">
-        <v>0.1858358618074059</v>
+        <v>0.1858361226693541</v>
       </c>
       <c r="AD22" s="2" t="n">
-        <v>0.1020664612262538</v>
+        <v>0.1020663893229974</v>
       </c>
       <c r="AE22" s="2" t="n">
         <v>0.08030049755343716</v>
@@ -2507,64 +2507,64 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" s="2" t="n">
-        <v>0.01896072471339982</v>
+        <v>0.01896034887904374</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.1612906889342836</v>
+        <v>0.1612903611441792</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>-0.2165728768351555</v>
+        <v>-0.216572590300238</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>-0.4728197450673828</v>
+        <v>-0.472819587959062</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>-0.017550756734388</v>
+        <v>-0.0175511207704796</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>0.2305551424032819</v>
+        <v>0.230555288812518</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>-0.2205834963806587</v>
+        <v>-0.2205837889637028</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>0.2273256944701159</v>
+        <v>0.2273251143323227</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>0.4137813238478987</v>
+        <v>0.4137821933771899</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>0.02761535253715319</v>
+        <v>0.02761481687001743</v>
       </c>
       <c r="T23" s="2" t="n">
-        <v>0.02494454505433863</v>
+        <v>0.02494485285527537</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>0.3080549739654026</v>
+        <v>0.3080550185530322</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>0.1048957517849585</v>
+        <v>0.1048957633919068</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>-0.1964461866050722</v>
+        <v>-0.1964461562050057</v>
       </c>
       <c r="X23" s="2" t="n">
-        <v>0.2977723882073513</v>
+        <v>0.2977727183389964</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>-0.08749701814237087</v>
+        <v>-0.08749719340507334</v>
       </c>
       <c r="Z23" s="2" t="n">
-        <v>0.334645777019845</v>
+        <v>0.3346456717773811</v>
       </c>
       <c r="AA23" s="3" t="n">
-        <v>-0.14833797364187</v>
+        <v>-0.1483378276304768</v>
       </c>
       <c r="AB23" s="2" t="n">
-        <v>0.05300597817074659</v>
+        <v>0.05300578808573198</v>
       </c>
       <c r="AC23" s="2" t="n">
-        <v>0.2377854470475997</v>
+        <v>0.2377855558835267</v>
       </c>
       <c r="AD23" s="2" t="n">
         <v>0.1235923409024136</v>
@@ -2592,64 +2592,64 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" s="2" t="n">
-        <v>0.001951445146836761</v>
+        <v>0.001952064660555086</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.0886827891949149</v>
+        <v>0.08868251633812729</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.05715513286697405</v>
+        <v>-0.05715561740563913</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>-0.4659353359158347</v>
+        <v>-0.4659351751422328</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.2798654175306123</v>
+        <v>0.2798655584487617</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>0.2607070518893166</v>
+        <v>0.2607070231844615</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>-0.1207676573951805</v>
+        <v>-0.1207679088529847</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>0.2071740619751909</v>
+        <v>0.207174500456873</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>0.4563734438570746</v>
+        <v>0.4563727104815771</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>0.07692747516691556</v>
+        <v>0.07692795323855095</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>0.05968268091710072</v>
+        <v>0.05968256972819086</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>0.2141678698884693</v>
+        <v>0.2141679689054876</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>0.1283096184750976</v>
+        <v>0.1283097711139465</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>-0.05992920857493877</v>
+        <v>-0.05992941241265182</v>
       </c>
       <c r="X24" s="2" t="n">
-        <v>0.2718696821930771</v>
+        <v>0.2718695284228503</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>-0.03038639332578508</v>
+        <v>-0.03038615519764043</v>
       </c>
       <c r="Z24" s="2" t="n">
-        <v>0.2275082663104862</v>
+        <v>0.2275079885629538</v>
       </c>
       <c r="AA24" s="2" t="n">
-        <v>0.03484800034455793</v>
+        <v>0.03484841020285967</v>
       </c>
       <c r="AB24" s="2" t="n">
-        <v>0.1218072203178839</v>
+        <v>0.1218070862895531</v>
       </c>
       <c r="AC24" s="2" t="n">
-        <v>0.2695202115767852</v>
+        <v>0.2695199894089124</v>
       </c>
       <c r="AD24" s="2" t="n">
         <v>0.08125515208826717</v>
@@ -2678,61 +2678,61 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" s="2" t="n">
-        <v>0.03145490710355081</v>
+        <v>0.03145510614060187</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0.2761814507141991</v>
+        <v>0.2761825179158159</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-0.3864551242987692</v>
+        <v>-0.3864550755815681</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.2532831189063802</v>
+        <v>0.2532819629240373</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>0.1659099654473468</v>
+        <v>0.1659106539706725</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>0.05149254639939005</v>
+        <v>0.05149261155373708</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>0.1388686542208069</v>
+        <v>0.1388683203751697</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>0.5696247445283327</v>
+        <v>0.5696252593164912</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>0.09893174777844083</v>
+        <v>0.09893155134749687</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>0.04138835575289956</v>
+        <v>0.04138820035517754</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>0.2024956441290511</v>
+        <v>0.2024955008379306</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>0.3524364226017807</v>
+        <v>0.3524365837600802</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>-0.07217100070539839</v>
+        <v>-0.07217135314029177</v>
       </c>
       <c r="X25" s="2" t="n">
-        <v>0.3050912772336283</v>
+        <v>0.3050918679336787</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-0.135748382935205</v>
+        <v>-0.1357483002948499</v>
       </c>
       <c r="Z25" s="2" t="n">
-        <v>0.09393937633565064</v>
+        <v>0.09393936051779983</v>
       </c>
       <c r="AA25" s="2" t="n">
-        <v>0.09960035916649179</v>
+        <v>0.09960011294948612</v>
       </c>
       <c r="AB25" s="2" t="n">
-        <v>0.1433449896224452</v>
+        <v>0.1433452096280927</v>
       </c>
       <c r="AC25" s="2" t="n">
-        <v>0.1581353798880079</v>
+        <v>0.1581352380953547</v>
       </c>
       <c r="AD25" s="2" t="n">
         <v>0.4864321605915283</v>
@@ -2759,64 +2759,64 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" s="2" t="n">
-        <v>0.2676939870594479</v>
+        <v>0.2676935790507859</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.1087689938900354</v>
+        <v>0.1087685125765627</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.08978074341520781</v>
+        <v>0.08978124315168801</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0.003911186536159184</v>
+        <v>0.003911656836038002</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-0.2122832251079845</v>
+        <v>-0.2122835601035705</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.1896735214473004</v>
+        <v>0.1896737583343193</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>0.2671512358148846</v>
+        <v>0.2671510776079216</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>-0.01538881882854259</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>0.06659799861963411</v>
+        <v>0.06659809868965305</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>0.4117250082727268</v>
+        <v>0.4117250634656713</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>0.253619700277034</v>
+        <v>0.2536196665664687</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.1691379309979216</v>
+        <v>-0.1691378600511072</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>0.2215824015651242</v>
+        <v>0.2215828057892539</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>0.1889153727699993</v>
+        <v>0.1889151696323212</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.1287089356425009</v>
+        <v>-0.1287093297301771</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>0.2011385120785263</v>
+        <v>0.2011382298292455</v>
       </c>
       <c r="Y26" s="2" t="n">
-        <v>0.1420440287029752</v>
+        <v>0.1420444961919909</v>
       </c>
       <c r="Z26" s="2" t="n">
-        <v>0.2641351168835675</v>
+        <v>0.2641351709806072</v>
       </c>
       <c r="AA26" s="3" t="n">
-        <v>-0.2174355597829867</v>
+        <v>-0.2174357089562872</v>
       </c>
       <c r="AB26" s="2" t="n">
-        <v>0.2462404007762089</v>
+        <v>0.2462404933874507</v>
       </c>
       <c r="AC26" s="2" t="n">
         <v>0.04103816593975518</v>
@@ -2857,22 +2857,22 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" s="2" t="n">
-        <v>0.03200649916107023</v>
+        <v>0.03200641571867768</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>0.1246769457559946</v>
+        <v>0.1246770366912193</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>0.1865802897119984</v>
+        <v>0.1865804334946599</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>-0.1383513661427649</v>
+        <v>-0.1383514099651655</v>
       </c>
       <c r="X27" s="2" t="n">
-        <v>0.1437734101259647</v>
+        <v>0.1437734000165101</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>-0.2892825052119784</v>
+        <v>-0.2892825489044057</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>-0.05132811766108192</v>
@@ -2913,58 +2913,58 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" s="2" t="n">
-        <v>0.1052266134985729</v>
+        <v>0.1052269768009626</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0.3691171215046958</v>
+        <v>0.3691162770026983</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>-0.4267881131402129</v>
+        <v>-0.4267878999741181</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.4015179717887751</v>
+        <v>0.4015177706124218</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>0.2856562648923846</v>
+        <v>0.2856559831100738</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>0.009492410924905936</v>
+        <v>0.009493157426744947</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>0.03873733281470737</v>
+        <v>0.03873703865266842</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>0.2789680085707258</v>
+        <v>0.2789675157349261</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>-0.2942122679170698</v>
+        <v>-0.2942123291114053</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>-0.3578133848595301</v>
+        <v>-0.3578131464925306</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>0.3829331396585012</v>
+        <v>0.3829333398190737</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>-0.0947008410306508</v>
+        <v>-0.09470142843332474</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>-0.2809983261938416</v>
+        <v>-0.2809981409069383</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>-0.09437914263251945</v>
+        <v>-0.09437907370527832</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>-0.3639968232642883</v>
+        <v>-0.3639969512341</v>
       </c>
       <c r="Z28" s="2" t="n">
-        <v>0.667414737514461</v>
+        <v>0.667415376965051</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>0.4536457728795038</v>
+        <v>0.4536457327459109</v>
       </c>
       <c r="AB28" s="2" t="n">
-        <v>0.03560838915015441</v>
+        <v>0.03560832612293408</v>
       </c>
       <c r="AC28" s="3" t="n">
         <v>-0.01001785708618852</v>
@@ -2991,61 +2991,61 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>-0.31609741537398</v>
+        <v>-0.3160969922990478</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.05394522028357607</v>
+        <v>-0.0539453898851221</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.0898100530843613</v>
+        <v>0.08981000942734152</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0.3800797226945165</v>
+        <v>0.380080464053387</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.5231240950109206</v>
+        <v>0.5231234519536474</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.09118454609786553</v>
+        <v>0.09118476429768752</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0.4484907342445534</v>
+        <v>0.448490595735086</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.6014499187774291</v>
+        <v>-0.6014500508090801</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.6414608451945358</v>
+        <v>0.6414613889777823</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>0.2039396109572624</v>
+        <v>0.2039394091370663</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.1704953241245736</v>
+        <v>-0.1704951850720638</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>0.01948474365003316</v>
+        <v>0.01948484469416267</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>0.2587174785668269</v>
+        <v>0.2587173538116503</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.2355379560198837</v>
+        <v>-0.2355380347610952</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>-0.2454813484790398</v>
+        <v>-0.2454812707620108</v>
       </c>
       <c r="U29" s="2" t="n">
         <v>0.2782666256943598</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>-0.1965844629851686</v>
+        <v>-0.1965844095871995</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>-0.4502844546656753</v>
+        <v>-0.4502845576654972</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>-0.03443724599240183</v>
+        <v>-0.03443712925042253</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>-0.4118741388538679</v>
@@ -3093,52 +3093,52 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" s="2" t="n">
-        <v>0.08953619880644026</v>
+        <v>0.08953636126387043</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>0.1011593491648057</v>
+        <v>0.1011592474315932</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>0.01898109063748787</v>
+        <v>0.01898087531406745</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>0.1852997280586997</v>
+        <v>0.1853002278489306</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>0.0482455507188766</v>
+        <v>0.04824529899844032</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>-0.2732622610446588</v>
+        <v>-0.2732625663433533</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>0.1492324174889628</v>
+        <v>0.1492329256670168</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>-0.07892496998083354</v>
+        <v>-0.07892482534122713</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>-0.1266390691560122</v>
+        <v>-0.1266398327965104</v>
       </c>
       <c r="X30" s="2" t="n">
-        <v>0.05988778071694156</v>
+        <v>0.05988831560071084</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>-0.3225660046157711</v>
+        <v>-0.3225661085921732</v>
       </c>
       <c r="Z30" s="2" t="n">
-        <v>0.3908554508939497</v>
+        <v>0.3908558897669212</v>
       </c>
       <c r="AA30" s="2" t="n">
-        <v>0.2546860520748659</v>
+        <v>0.254685697068701</v>
       </c>
       <c r="AB30" s="2" t="n">
-        <v>0.2139921896306551</v>
+        <v>0.2139922988250593</v>
       </c>
       <c r="AC30" s="2" t="n">
-        <v>0.2276265774419435</v>
+        <v>0.2276268214981647</v>
       </c>
       <c r="AD30" s="2" t="n">
-        <v>0.05779086101249598</v>
+        <v>0.05779076661055282</v>
       </c>
       <c r="AE30" s="2" t="n">
         <v>0.1412241746357825</v>
@@ -3164,52 +3164,52 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" s="2" t="n">
-        <v>0.07510117509018177</v>
+        <v>0.0751004234510364</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0.1676647412697063</v>
+        <v>0.1676650223689478</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0.260746206929717</v>
+        <v>-0.2607462320081013</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.3672662840895571</v>
+        <v>0.3672663318720792</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>0.3392057410103309</v>
+        <v>0.3392061539105669</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0.1609297678990836</v>
+        <v>-0.1609300178103513</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.08867818404638661</v>
+        <v>-0.08867793751087627</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.5402366122730513</v>
+        <v>-0.5402366512562138</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-0.1244292854610013</v>
+        <v>-0.1244292728869378</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.2471336999602858</v>
+        <v>-0.2471338445597003</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>0.5291896320623406</v>
+        <v>0.5291892893732439</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>0.1198613307412797</v>
+        <v>0.1198618680376005</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.08771135926556639</v>
+        <v>-0.08771152260106829</v>
       </c>
       <c r="X31" s="2" t="n">
-        <v>0.3981793223798689</v>
+        <v>0.3981792242534072</v>
       </c>
       <c r="Y31" s="2" t="n">
-        <v>0.2366143862875261</v>
+        <v>0.2366143327118986</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.09522242870231723</v>
+        <v>-0.09522232600458813</v>
       </c>
       <c r="AA31" s="3" t="n">
         <v>-0.09006954988935456</v>
@@ -3250,40 +3250,40 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" s="2" t="n">
-        <v>0.01179233465338303</v>
+        <v>0.01179244206408026</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>0.6698716704455914</v>
+        <v>0.6698717753671468</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>-0.3396104912025626</v>
+        <v>-0.3396104070320182</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>-0.1680324113783485</v>
+        <v>-0.1680325696917858</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>-0.6077564774210578</v>
+        <v>-0.6077565060111172</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>-0.2235849545507125</v>
+        <v>-0.2235848979589456</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>-0.1914184695842673</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>0.7296681326540564</v>
+        <v>0.7296680165515703</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>0.08215336926264794</v>
+        <v>0.08215344190126728</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>-0.1102480561569544</v>
       </c>
       <c r="X32" s="2" t="n">
-        <v>0.404423739649975</v>
+        <v>0.4044236002216632</v>
       </c>
       <c r="Y32" s="2" t="n">
-        <v>0.3039701252788469</v>
+        <v>0.3039702547343426</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>-0.212460368803199</v>
@@ -3328,52 +3328,52 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" s="2" t="n">
-        <v>0.8575655224510168</v>
+        <v>0.857566301160172</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>-0.220228380566815</v>
+        <v>-0.2202284669000117</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>0.08224654917440222</v>
+        <v>0.08224647818181152</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>-0.5021387385614484</v>
+        <v>-0.502138804299177</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>-0.1725722780746296</v>
+        <v>-0.172571982785228</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>-0.3311991376910097</v>
+        <v>-0.331199244189921</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>0.7947494655643945</v>
+        <v>0.7947493465165347</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>0.01669383481478515</v>
+        <v>0.01669370325972697</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>-0.2241667106506792</v>
+        <v>-0.2241666240418552</v>
       </c>
       <c r="X33" s="2" t="n">
-        <v>0.347750494781407</v>
+        <v>0.3477505240247456</v>
       </c>
       <c r="Y33" s="2" t="n">
-        <v>0.4029637616187254</v>
+        <v>0.4029639739465996</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>-0.1835072684692803</v>
+        <v>-0.1835073410941702</v>
       </c>
       <c r="AA33" s="3" t="n">
-        <v>-0.2282915238756961</v>
+        <v>-0.2282914694065102</v>
       </c>
       <c r="AB33" s="2" t="n">
-        <v>0.01305742691578282</v>
+        <v>0.01305735541156716</v>
       </c>
       <c r="AC33" s="2" t="n">
-        <v>0.1462605817376046</v>
+        <v>0.1462606514104501</v>
       </c>
       <c r="AD33" s="2" t="n">
-        <v>1.661586446229593</v>
+        <v>1.661586284451117</v>
       </c>
       <c r="AE33" s="2" t="n">
         <v>0.1222462538821809</v>
@@ -3399,64 +3399,64 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" s="2" t="n">
-        <v>0.0936655645600728</v>
+        <v>0.09366464535506291</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0.417522226288163</v>
+        <v>0.4175229461054595</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>-0.5938448264405918</v>
+        <v>-0.593844736712022</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.8823880476085606</v>
+        <v>0.8823874087418224</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>0.3413426835024413</v>
+        <v>0.3413425606626417</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>-0.2817067767873473</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>-0.06599941315351665</v>
+        <v>-0.06599950820477729</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>-0.05381282016811439</v>
+        <v>-0.05381302918031461</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>-0.2527624352473993</v>
+        <v>-0.2527622479161065</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>-0.5052856493183429</v>
+        <v>-0.5052856137142832</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>1.06040340413151</v>
+        <v>1.060403258655804</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>0.2117473626923496</v>
+        <v>0.2117475894592271</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>-0.2678107328205952</v>
+        <v>-0.2678107598787524</v>
       </c>
       <c r="X34" s="2" t="n">
-        <v>0.1469305479346856</v>
+        <v>0.1469303770824237</v>
       </c>
       <c r="Y34" s="2" t="n">
-        <v>0.1595302218550985</v>
+        <v>0.1595303023091195</v>
       </c>
       <c r="Z34" s="2" t="n">
         <v>0.3492430200021088</v>
       </c>
       <c r="AA34" s="2" t="n">
-        <v>0.131366139839203</v>
+        <v>0.131366228539157</v>
       </c>
       <c r="AB34" s="2" t="n">
-        <v>0.2151039045141583</v>
+        <v>0.2151038092491082</v>
       </c>
       <c r="AC34" s="3" t="n">
-        <v>-0.04543454368148503</v>
+        <v>-0.04543460820333367</v>
       </c>
       <c r="AD34" s="2" t="n">
-        <v>0.8347363028562125</v>
+        <v>0.8347364268713704</v>
       </c>
       <c r="AE34" s="2" t="n">
         <v>0.2092229125343723</v>
@@ -3489,40 +3489,40 @@
         <v>0.3620255681328444</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>-0.3095771369342224</v>
+        <v>-0.3095771816576897</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>0.04818657981549856</v>
+        <v>0.04818664771380199</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>-0.2750976702875546</v>
+        <v>-0.2750976084885179</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>-0.1960451983180895</v>
+        <v>-0.1960454373595215</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>-0.4587858820186026</v>
+        <v>-0.4587857672376615</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>0.7034760472838437</v>
+        <v>0.7034756554233734</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>0.3892239040778331</v>
+        <v>0.3892242236491346</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>-0.3130901893043474</v>
+        <v>-0.3130901479078892</v>
       </c>
       <c r="X35" s="2" t="n">
-        <v>0.1248097742698864</v>
+        <v>0.1248097064834939</v>
       </c>
       <c r="Y35" s="2" t="n">
         <v>0.5165679514679979</v>
       </c>
       <c r="Z35" s="2" t="n">
-        <v>0.2338355625361099</v>
+        <v>0.2338357038492354</v>
       </c>
       <c r="AA35" s="3" t="n">
-        <v>-0.007613257120971828</v>
+        <v>-0.00761337078057156</v>
       </c>
       <c r="AB35" s="2" t="n">
         <v>0.08378747254390895</v>
@@ -3564,37 +3564,37 @@
         <v>0.212910173274613</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-0.6018562990285523</v>
+        <v>-0.6018564404026938</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-0.1858851111718172</v>
+        <v>-0.1858850588154113</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-0.2137520223220153</v>
+        <v>-0.2137518663958605</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-0.2250640533018146</v>
+        <v>-0.2250638429710232</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>-0.3712982603411885</v>
+        <v>-0.3712984921619444</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-0.01251938006562181</v>
+        <v>-0.01251909778922033</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>0.1936067366974286</v>
+        <v>0.1936065259203763</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>-0.2210719290312697</v>
+        <v>-0.2210717858250901</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>-0.0354041392692962</v>
+        <v>-0.03540413561031674</v>
       </c>
       <c r="Y36" s="2" t="n">
-        <v>0.4133174548583098</v>
+        <v>0.4133174105745703</v>
       </c>
       <c r="Z36" s="2" t="n">
-        <v>0.5757468154716803</v>
+        <v>0.5757466960158726</v>
       </c>
       <c r="AA36" s="3" t="n">
         <v>-0.1131816113967342</v>
@@ -3636,49 +3636,49 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" s="2" t="n">
-        <v>0.4303714432847212</v>
+        <v>0.4303711549099518</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>-0.3690529328666504</v>
+        <v>-0.3690527048582773</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>0.02687287186133869</v>
+        <v>0.02687254803516481</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>-0.09105417429002693</v>
+        <v>-0.09105387728589021</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>-0.1355196181511708</v>
+        <v>-0.1355196805397234</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>-0.09533455185478013</v>
+        <v>-0.09533444341404962</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>0.2396258010942223</v>
+        <v>0.2396256392118203</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>0.6418628343310553</v>
+        <v>0.6418625128239128</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>-0.2862666677850574</v>
+        <v>-0.2862666448006925</v>
       </c>
       <c r="X37" s="2" t="n">
-        <v>0.03270988715561662</v>
+        <v>0.0327100402889231</v>
       </c>
       <c r="Y37" s="2" t="n">
-        <v>1.278827100279859</v>
+        <v>1.278826934043034</v>
       </c>
       <c r="Z37" s="2" t="n">
-        <v>0.3674340842287505</v>
+        <v>0.3674338281376395</v>
       </c>
       <c r="AA37" s="3" t="n">
-        <v>-0.2991040218261947</v>
+        <v>-0.2991038905633677</v>
       </c>
       <c r="AB37" s="3" t="n">
-        <v>-0.1217903576763482</v>
+        <v>-0.1217902908766433</v>
       </c>
       <c r="AC37" s="3" t="n">
-        <v>-0.1919325675715866</v>
+        <v>-0.1919326290360245</v>
       </c>
       <c r="AD37" s="2" t="n">
         <v>0.6004628944135546</v>
@@ -3701,82 +3701,82 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" s="2" t="n">
-        <v>0.1226651726409718</v>
+        <v>0.1226641600288967</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.08328189064900871</v>
+        <v>0.0832827298717318</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.03447599696877202</v>
+        <v>0.03447598853418143</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0.3534950748769354</v>
+        <v>0.353494636529776</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0.301267761415182</v>
+        <v>0.3012675256389501</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.08951326323461672</v>
+        <v>0.08951322013506324</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.3491219006227348</v>
+        <v>0.3491218233237332</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>-0.181512948649739</v>
+        <v>-0.1815126495667155</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>-0.3987780241906231</v>
+        <v>-0.3987781358018766</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.3057867632814997</v>
+        <v>0.3057871913293908</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>0.2654410627887114</v>
+        <v>0.2654408828839165</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>0.05545269623367854</v>
+        <v>0.0554524715409852</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>0.1820659731998047</v>
+        <v>0.1820663312907127</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>0.0116366605685545</v>
+        <v>0.01163638937397726</v>
       </c>
       <c r="S38" s="2" t="n">
-        <v>0.2669108414568169</v>
+        <v>0.2669112450263924</v>
       </c>
       <c r="T38" s="2" t="n">
-        <v>0.0161652693952774</v>
+        <v>0.01616547790356426</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>0.07005402844525976</v>
+        <v>0.07005379680012536</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>0.09307265824440281</v>
+        <v>0.09307277544780912</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>-0.04330143868765501</v>
+        <v>-0.04330154667635189</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>0.2820536902517039</v>
+        <v>0.2820537789745687</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>-0.05232529334254832</v>
+        <v>-0.05232547603753546</v>
       </c>
       <c r="Z38" s="2" t="n">
-        <v>0.387441874610374</v>
+        <v>0.3874419763237666</v>
       </c>
       <c r="AA38" s="3" t="n">
-        <v>-0.2551437976056947</v>
+        <v>-0.2551438522111144</v>
       </c>
       <c r="AB38" s="2" t="n">
         <v>0.1189438169513679</v>
       </c>
       <c r="AC38" s="2" t="n">
-        <v>0.04412328681332678</v>
+        <v>0.04412319885385285</v>
       </c>
       <c r="AD38" s="2" t="n">
-        <v>0.03381499218567297</v>
+        <v>0.03381507927675864</v>
       </c>
       <c r="AE38" s="2" t="n">
         <v>0.08333897630400489</v>
@@ -3800,64 +3800,64 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" s="2" t="n">
-        <v>0.1599790215866632</v>
+        <v>0.1599794095011109</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.1193729650843929</v>
+        <v>0.119372089126933</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.3527790595073905</v>
+        <v>0.3527796657260949</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>-0.1651531542434423</v>
+        <v>-0.1651527677677507</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>-0.3698222513941635</v>
+        <v>-0.369822344723744</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.3013736539067988</v>
+        <v>0.301373663968648</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>0.2839078848817458</v>
+        <v>0.2839075513831908</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>0.08635759903973339</v>
+        <v>0.08635778204121825</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>0.1763331773851913</v>
+        <v>0.1763327897119578</v>
       </c>
       <c r="R39" s="2" t="n">
-        <v>0.02303390479276102</v>
+        <v>0.023033808758816</v>
       </c>
       <c r="S39" s="2" t="n">
-        <v>0.303990665927069</v>
+        <v>0.3039907243449145</v>
       </c>
       <c r="T39" s="2" t="n">
-        <v>0.02432461548074638</v>
+        <v>0.02432454538019035</v>
       </c>
       <c r="U39" s="2" t="n">
-        <v>0.08573679946267077</v>
+        <v>0.08573696183620805</v>
       </c>
       <c r="V39" s="2" t="n">
-        <v>0.04898979699737716</v>
+        <v>0.04898966773321733</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>-0.06026944250593569</v>
+        <v>-0.06026945392592786</v>
       </c>
       <c r="X39" s="2" t="n">
-        <v>0.2891072786484885</v>
+        <v>0.2891078074235311</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>-0.04610464547004178</v>
+        <v>-0.0461047401309187</v>
       </c>
       <c r="Z39" s="2" t="n">
-        <v>0.4053702410737114</v>
+        <v>0.4053704153924054</v>
       </c>
       <c r="AA39" s="3" t="n">
-        <v>-0.2625113740471197</v>
+        <v>-0.2625114683582211</v>
       </c>
       <c r="AB39" s="2" t="n">
-        <v>0.1185182841358188</v>
+        <v>0.1185181661632302</v>
       </c>
       <c r="AC39" s="2" t="n">
         <v>0.04811717493353518</v>
@@ -3889,58 +3889,58 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" s="2" t="n">
-        <v>0.09617665659368102</v>
+        <v>0.09617656432586141</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-0.1703214456895349</v>
+        <v>-0.1703214754166322</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>-0.3800124625382036</v>
+        <v>-0.3800123335883232</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.7739430553768185</v>
+        <v>0.7739426628255643</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>0.3734260434787648</v>
+        <v>0.3734263934232278</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>0.09747193240223173</v>
+        <v>0.09747179757307323</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>0.2069202467609792</v>
+        <v>0.2069197499332422</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>0.4217893833171016</v>
+        <v>0.4217892986239298</v>
       </c>
       <c r="S40" s="2" t="n">
-        <v>0.09854141420010509</v>
+        <v>0.09854102241857166</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>-0.08863951933585701</v>
+        <v>-0.08863928787122866</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>0.03310259114446801</v>
+        <v>0.03310280716579372</v>
       </c>
       <c r="V40" s="2" t="n">
-        <v>0.04214276564943731</v>
+        <v>0.04214276984702714</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>-0.08041063736224241</v>
+        <v>-0.08041054947138715</v>
       </c>
       <c r="X40" s="2" t="n">
-        <v>0.1411618232938372</v>
+        <v>0.1411620311609418</v>
       </c>
       <c r="Y40" s="2" t="n">
-        <v>0.4191374556284424</v>
+        <v>0.4191368328192495</v>
       </c>
       <c r="Z40" s="2" t="n">
-        <v>0.425975752770599</v>
+        <v>0.4259762471894175</v>
       </c>
       <c r="AA40" s="3" t="n">
-        <v>-0.3163955810794474</v>
+        <v>-0.3163957326245644</v>
       </c>
       <c r="AB40" s="2" t="n">
-        <v>0.2153061290998148</v>
+        <v>0.2153062891229642</v>
       </c>
       <c r="AC40" s="2" t="n">
         <v>0.1177449331626672</v>
@@ -3972,64 +3972,64 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" s="3" t="n">
-        <v>-0.164634341326807</v>
+        <v>-0.1646338096625212</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.476528907126411</v>
+        <v>-0.4765288864662831</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.3674689843077203</v>
+        <v>-0.3674692229835739</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.2764701612859006</v>
+        <v>0.2764703214602817</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>0.174260391733849</v>
+        <v>0.1742602808671734</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-0.007296844337562836</v>
+        <v>-0.007296781431672783</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>0.5732876965578302</v>
+        <v>0.573286652288695</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>0.2558704025921388</v>
+        <v>0.2558707626733436</v>
       </c>
       <c r="S41" s="2" t="n">
-        <v>0.03051184325603962</v>
+        <v>0.03051241802612026</v>
       </c>
       <c r="T41" s="2" t="n">
-        <v>0.006554717542065491</v>
+        <v>0.006554653780872055</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.002952551522459879</v>
+        <v>-0.002952977265427204</v>
       </c>
       <c r="V41" s="2" t="n">
-        <v>0.3179590679516406</v>
+        <v>0.3179589845660296</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.2572389883064691</v>
+        <v>-0.2572390360314287</v>
       </c>
       <c r="X41" s="2" t="n">
-        <v>0.412964051939235</v>
+        <v>0.4129649044334098</v>
       </c>
       <c r="Y41" s="2" t="n">
-        <v>0.2797511812755213</v>
+        <v>0.2797508172007162</v>
       </c>
       <c r="Z41" s="2" t="n">
-        <v>0.4969625549845371</v>
+        <v>0.4969621753237896</v>
       </c>
       <c r="AA41" s="3" t="n">
-        <v>-0.2893248419092674</v>
+        <v>-0.2893246646133869</v>
       </c>
       <c r="AB41" s="2" t="n">
-        <v>0.6010660167556798</v>
+        <v>0.6010657829678321</v>
       </c>
       <c r="AC41" s="2" t="n">
-        <v>0.09870958041534972</v>
+        <v>0.09870975061709708</v>
       </c>
       <c r="AD41" s="3" t="n">
-        <v>-0.006897021068539289</v>
+        <v>-0.006897094371746348</v>
       </c>
       <c r="AE41" s="3" t="n">
         <v>-0.0001872244682387114</v>
@@ -4055,64 +4055,64 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" s="3" t="n">
-        <v>-0.1506814107095437</v>
+        <v>-0.1506819737970034</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>-0.578858324691823</v>
+        <v>-0.5788580123925826</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>-0.4298389070898266</v>
+        <v>-0.4298389065439926</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.2326534109111218</v>
+        <v>0.232652878894259</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>0.1042129728836396</v>
+        <v>0.1042131479544031</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>-0.09097365598063689</v>
+        <v>-0.09097380010492706</v>
       </c>
       <c r="Q42" s="2" t="n">
         <v>0.7934360760907206</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>0.1745139930025261</v>
+        <v>0.1745144792623787</v>
       </c>
       <c r="S42" s="2" t="n">
-        <v>0.046497231933043</v>
+        <v>0.04649671587166537</v>
       </c>
       <c r="T42" s="2" t="n">
-        <v>0.05068240325960982</v>
+        <v>0.05068209077817132</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>0.01840099205361567</v>
+        <v>0.01840167673812032</v>
       </c>
       <c r="V42" s="2" t="n">
-        <v>0.5964730945533949</v>
+        <v>0.5964727702364052</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>-0.3091888153399448</v>
+        <v>-0.3091889719700797</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>0.487020093313131</v>
+        <v>0.4870204268165126</v>
       </c>
       <c r="Y42" s="2" t="n">
-        <v>0.2641360775197894</v>
+        <v>0.264136053700339</v>
       </c>
       <c r="Z42" s="2" t="n">
-        <v>0.4925369450397057</v>
+        <v>0.4925369812402105</v>
       </c>
       <c r="AA42" s="3" t="n">
-        <v>-0.2625424649237508</v>
+        <v>-0.2625425832130326</v>
       </c>
       <c r="AB42" s="2" t="n">
-        <v>0.6889404265244872</v>
+        <v>0.6889402767426034</v>
       </c>
       <c r="AC42" s="2" t="n">
-        <v>0.02058764885353948</v>
+        <v>0.02058772876106918</v>
       </c>
       <c r="AD42" s="3" t="n">
-        <v>-0.05262969500840953</v>
+        <v>-0.0526296237668733</v>
       </c>
       <c r="AE42" s="3" t="n">
         <v>-0.03179644988750718</v>
@@ -4140,52 +4140,52 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="3" t="n">
-        <v>-0.5946560663198495</v>
+        <v>-0.5946562600856271</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.05435509091761337</v>
+        <v>0.05435528597039396</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>-0.2748668329267683</v>
+        <v>-0.2748668601986508</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>-0.4397795199324298</v>
+        <v>-0.4397796502532669</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>-0.1277701013524217</v>
+        <v>-0.1277700458540476</v>
       </c>
       <c r="R43" s="2" t="n">
-        <v>0.4911205533323202</v>
+        <v>0.4911203389012035</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>-0.04798244997609247</v>
+        <v>-0.04798274757006538</v>
       </c>
       <c r="T43" s="2" t="n">
-        <v>0.03805454301669098</v>
+        <v>0.0380552259195639</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>-0.1689432163336213</v>
+        <v>-0.1689432547363894</v>
       </c>
       <c r="V43" s="2" t="n">
-        <v>0.2146537919960336</v>
+        <v>0.2146539863881047</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>-0.09033253080498793</v>
+        <v>-0.09033273987389001</v>
       </c>
       <c r="X43" s="2" t="n">
-        <v>0.4436494441637191</v>
+        <v>0.4436495704901466</v>
       </c>
       <c r="Y43" s="2" t="n">
-        <v>1.418287687996662</v>
+        <v>1.418287651394435</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>-0.2418480664002993</v>
+        <v>-0.2418481936365516</v>
       </c>
       <c r="AA43" s="3" t="n">
-        <v>-0.05430047734134413</v>
+        <v>-0.05430029161476302</v>
       </c>
       <c r="AB43" s="3" t="n">
-        <v>-0.2040249953291975</v>
+        <v>-0.2040250756715357</v>
       </c>
       <c r="AC43" s="3" t="n">
         <v>-0.2571582950754481</v>
@@ -4219,16 +4219,16 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="3" t="n">
-        <v>-0.6617776705828449</v>
+        <v>-0.66177765770956</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1687572463495337</v>
+        <v>0.1687572264976855</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>-0.2850139838229105</v>
+        <v>-0.2850142570865218</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>-0.6339614046440869</v>
+        <v>-0.6339613015879876</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>-0.3079302793743838</v>
@@ -4237,25 +4237,25 @@
         <v>1.278980994453355</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>-0.01236216057458683</v>
+        <v>-0.01236209961538404</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>-0.08741767798528788</v>
+        <v>-0.08741767258967481</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>-0.4323806626468214</v>
+        <v>-0.432380701037577</v>
       </c>
       <c r="V44" s="2" t="n">
         <v>0.5437602153083452</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>-0.2566466639363786</v>
+        <v>-0.2566467411213025</v>
       </c>
       <c r="X44" s="2" t="n">
-        <v>0.6653168321252314</v>
+        <v>0.6653169012073648</v>
       </c>
       <c r="Y44" s="2" t="n">
-        <v>2.339563982579255</v>
+        <v>2.339564190802931</v>
       </c>
       <c r="Z44" s="3" t="n">
         <v>-0.2509731316924508</v>
@@ -4303,31 +4303,31 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" s="2" t="n">
-        <v>0.2734688779389074</v>
+        <v>0.2734687590580598</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>-0.0146913312546888</v>
+        <v>-0.01469140455996965</v>
       </c>
       <c r="T45" s="2" t="n">
-        <v>0.1837351349425038</v>
+        <v>0.1837351486120848</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>-0.08537228586598877</v>
+        <v>-0.08537235408213406</v>
       </c>
       <c r="V45" s="2" t="n">
-        <v>0.697313523419159</v>
+        <v>0.6973138941216876</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>-0.3380126606979902</v>
+        <v>-0.3380127143000694</v>
       </c>
       <c r="X45" s="2" t="n">
         <v>0.2992087945986843</v>
       </c>
       <c r="Y45" s="2" t="n">
-        <v>0.5822872735639768</v>
+        <v>0.5822870852713353</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>-0.4901067325483995</v>
+        <v>-0.4901066718709466</v>
       </c>
       <c r="AA45" s="3" t="n">
         <v>-0.1723759086465272</v>
@@ -4646,40 +4646,40 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.08709175002522707</v>
+        <v>0.08709218573432431</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.003972787350134066</v>
+        <v>0.003973440818745511</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.3804894632796276</v>
+        <v>0.3804888095098511</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.2249744095556092</v>
+        <v>0.2249748049088824</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.3347517165383493</v>
+        <v>0.3347509749795154</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.2869248740962553</v>
+        <v>0.2869249108529315</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.2038936408948759</v>
+        <v>0.2038934621033734</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>-0.09741523424574006</v>
+        <v>-0.09741476230003565</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-0.1175854220591988</v>
+        <v>-0.1175852065253518</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.2158460377794128</v>
+        <v>-0.2158460295540237</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2818153341675851</v>
+        <v>0.2818149201406541</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1069794632357992</v>
+        <v>0.1069792345660829</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>0.04828269577249533</v>
@@ -4688,58 +4688,58 @@
         <v>0.1584522963115396</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0.05146241182453104</v>
+        <v>0.0514624886566919</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>-0.3679500592830817</v>
+        <v>-0.3679502516114687</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0.2635176325340436</v>
+        <v>0.2635180402970316</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>0.150561872802593</v>
+        <v>0.1505611270339779</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.0189494247003299</v>
+        <v>0.01895007145373562</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.1599032784098597</v>
+        <v>0.1599035000697346</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.3230778278304547</v>
+        <v>0.3230777408745176</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0.1346380138201633</v>
+        <v>0.1346379864312741</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>0.01234285357760156</v>
+        <v>0.01234285136468527</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.1199789886964182</v>
+        <v>0.1199789674479816</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.2170537088879978</v>
+        <v>0.2170541489529083</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>-0.04568971190383986</v>
+        <v>-0.04569020786950473</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>0.312238994952297</v>
+        <v>0.3122387226554391</v>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>0.1833158907636898</v>
+        <v>0.1833162400611312</v>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>0.2872878480335639</v>
+        <v>0.287287822844257</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>-0.1817538841351666</v>
+        <v>-0.1817538036436078</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>0.2617582431669423</v>
+        <v>0.2617579498645455</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>0.2488645960392328</v>
+        <v>0.2488646784300117</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0.1771906130702343</v>
@@ -4766,79 +4766,79 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" s="2" t="n">
-        <v>0.7894734325113975</v>
+        <v>0.7894738986207814</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0.3611489488648905</v>
+        <v>-0.3611492567716438</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.3334474422103997</v>
+        <v>-0.3334476487536184</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.3736831504741268</v>
+        <v>-0.3736828599231806</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.4966874464770659</v>
+        <v>0.4966861026925444</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1053849404070264</v>
+        <v>0.1053859159993615</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.01565448268289238</v>
+        <v>0.01565380269131222</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.07144032461901828</v>
+        <v>0.07144067169577117</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>0.190280869142633</v>
+        <v>0.1902802311144496</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>-0.4172718108882923</v>
+        <v>-0.4172713854038294</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0.5468410696497692</v>
+        <v>0.546840164138749</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0.2014378730591606</v>
+        <v>0.2014386035731266</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.03475799385563483</v>
+        <v>0.03475742302634588</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1811254145314825</v>
+        <v>0.1811256110660653</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.36634225229163</v>
+        <v>0.3663415566029096</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.1918136821240786</v>
+        <v>0.1918142711581334</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>0.09435918294341805</v>
+        <v>0.09435919052532737</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.07097862233616237</v>
+        <v>0.07097892124128147</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.3266356965925445</v>
+        <v>0.3266347381680754</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>-0.00126206942384377</v>
+        <v>-0.001261656655339616</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>0.3896154966983914</v>
+        <v>0.3896154335322985</v>
       </c>
       <c r="AD3" s="2" t="n">
-        <v>0.4840608729999387</v>
+        <v>0.4840610940382717</v>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>0.2741973394352697</v>
+        <v>0.2741974397960669</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>-0.3257698426438344</v>
+        <v>-0.3257700532767094</v>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0.5485554088029889</v>
+        <v>0.5485557706092521</v>
       </c>
       <c r="AH3" s="2" t="n">
         <v>0.2557827307615477</v>
@@ -4869,82 +4869,82 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.05612804565472307</v>
+        <v>0.05612792232943509</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.01777404312601405</v>
+        <v>0.01777349029927278</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>-0.20370376204444</v>
+        <v>-0.2037028949799548</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.4790249071936881</v>
+        <v>0.4790235543935208</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1805355395575154</v>
+        <v>0.1805361596055979</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.04462700646392381</v>
+        <v>0.04462723389127299</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.1827286030725366</v>
+        <v>0.1827278615739723</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-0.01789768875379694</v>
+        <v>-0.01789725060084368</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>-0.3414072957746407</v>
+        <v>-0.3414076805699303</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>0.2848652259375051</v>
+        <v>0.2848650440271496</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.2691839878538875</v>
+        <v>0.2691851204867823</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>-0.04426744485410727</v>
+        <v>-0.04426760879882941</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.1670375056334734</v>
+        <v>0.1670371605291825</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.3869668477513564</v>
+        <v>0.3869668893538059</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.05036311726078013</v>
+        <v>0.05036319867842076</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>-0.0447894050917077</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.2159134296177594</v>
+        <v>0.215913893162514</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.145825703404272</v>
+        <v>0.1458251395021599</v>
       </c>
       <c r="AB4" s="3" t="n">
-        <v>-0.111212379249944</v>
+        <v>-0.1112122806793789</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>0.2538969976254026</v>
+        <v>0.2538971224071904</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>0.2003078402638028</v>
+        <v>0.2003078203301336</v>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>0.1453606935424163</v>
+        <v>0.145360598582803</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.2048478913712372</v>
+        <v>-0.2048480361431856</v>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>0.1682763927037243</v>
+        <v>0.1682766054097948</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>0.1138421726449519</v>
+        <v>0.1138420168014842</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>0.1265760487117622</v>
+        <v>0.1265762063369149</v>
       </c>
       <c r="AJ4" s="2" t="n">
         <v>0.1819410897970255</v>
@@ -4965,49 +4965,49 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
-        <v>0.1946931639341132</v>
+        <v>0.1946925759407847</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1060668228947541</v>
+        <v>0.1060672172428223</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.07752034502218308</v>
+        <v>-0.07752017349194817</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.487523654580958</v>
+        <v>0.487524150198527</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.08175265146425836</v>
+        <v>0.08175188024348556</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>-0.1997797367854586</v>
+        <v>-0.1997799258758579</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>-0.1083036671515573</v>
+        <v>-0.1083039828253044</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.535256263848924</v>
+        <v>0.5352573409189854</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2276917077807243</v>
+        <v>0.2276916062331906</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.2752769829632742</v>
+        <v>0.2752770057325906</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.169211213505261</v>
+        <v>0.1692112893400595</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.2841929909717502</v>
+        <v>0.2841927690792849</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-0.4443309854683141</v>
+        <v>-0.444330975849404</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>0.5315343455247235</v>
+        <v>0.531534272689089</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.1978424766769462</v>
+        <v>0.1978427198800636</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>-0.1240306720368778</v>
@@ -5019,31 +5019,31 @@
         <v>0.05309445679169689</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.0112140561384142</v>
+        <v>0.01121422457706944</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2390936986962177</v>
+        <v>-0.2390939087262556</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.2381647162613074</v>
+        <v>0.2381647423297426</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.1573163638035227</v>
+        <v>0.1573162893091158</v>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>-0.1716730158989624</v>
+        <v>-0.1716731185102027</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>0.2757983510530533</v>
+        <v>0.2757986117835178</v>
       </c>
       <c r="AD5" s="2" t="n">
-        <v>0.05517990806890416</v>
+        <v>0.05517998433818883</v>
       </c>
       <c r="AE5" s="2" t="n">
-        <v>0.2697561372915285</v>
+        <v>0.2697564112953414</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1295434025552418</v>
+        <v>-0.1295435903931803</v>
       </c>
       <c r="AG5" s="2" t="n">
         <v>0.1472575667324385</v>
@@ -5073,91 +5073,91 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>-0.1327800314031964</v>
+        <v>-0.1327801169677192</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-0.2436507851630443</v>
+        <v>-0.2436509558209831</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.04030902502812705</v>
+        <v>0.04030948539088586</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.6086769461007495</v>
+        <v>0.6086764525990347</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0.2628796592754876</v>
+        <v>-0.262879548078337</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-0.3030506317699491</v>
+        <v>-0.3030506742626643</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-0.09857364533135837</v>
+        <v>-0.09857355785069821</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.3873535040201206</v>
+        <v>0.3873533693817355</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0.1374248488898442</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.2433665814262373</v>
+        <v>0.2433664584271329</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.05852071646876045</v>
+        <v>0.05852092010639498</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-0.05502575811779764</v>
+        <v>-0.05502603334088141</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.2696939422478691</v>
+        <v>-0.2696939461432163</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>0.03143866147318031</v>
+        <v>0.03143907411532654</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.1359268698356255</v>
+        <v>0.135926646130125</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.1475753223974873</v>
+        <v>-0.147575437978034</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.09220230837119803</v>
+        <v>0.09220238866811759</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.259967721325582</v>
+        <v>0.2599676753903055</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.06226176801705274</v>
+        <v>-0.06226177415167333</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.09170812084390012</v>
+        <v>0.0917085507655242</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.02761836134655571</v>
+        <v>0.02761796839238984</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.2426429543869166</v>
+        <v>0.2426432580873235</v>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>-0.1410105399236862</v>
+        <v>-0.1410106694081328</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0.1933779026339806</v>
+        <v>0.1933779903768846</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.1540102499491207</v>
+        <v>0.1540101651007229</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.01155419018346504</v>
+        <v>0.01155425389592102</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.1772325106710285</v>
+        <v>-0.1772326884622333</v>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>0.2029324112357298</v>
+        <v>0.2029326719624513</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>0.07034740646320725</v>
+        <v>0.07034733834839302</v>
       </c>
       <c r="AI6" s="2" t="n">
         <v>0.25840587896048</v>
@@ -5181,85 +5181,85 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
-        <v>0.1321082797390229</v>
+        <v>0.1321082587845603</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-0.1211983037293926</v>
+        <v>-0.1211984268552931</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.04203134089952143</v>
+        <v>0.04203126118495071</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.1923839531898295</v>
+        <v>0.1923841209054753</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0.1187261337740458</v>
+        <v>-0.1187259978439561</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.01895305216612031</v>
+        <v>0.01895275682783293</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.01161156004774</v>
+        <v>-0.01161156087733539</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.5526750792893982</v>
+        <v>0.5526756252344291</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.294054835978844</v>
+        <v>0.2940542882891826</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.1665376081839147</v>
+        <v>0.1665374162924547</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.3089302443950084</v>
+        <v>0.3089305247102847</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.2824693806540095</v>
+        <v>0.2824693130301357</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-0.4799992430803397</v>
+        <v>-0.4799992401407341</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>0.6815738592325091</v>
+        <v>0.6815736729103741</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.1532685122971296</v>
+        <v>0.1532691392288639</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>-0.1157189532862617</v>
+        <v>-0.1157190652999334</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.2403552003127567</v>
+        <v>0.240354995881225</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.01817237653662751</v>
+        <v>0.01817244297604481</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>-0.0464184123745891</v>
+        <v>-0.04641873561362042</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.09942169792663891</v>
+        <v>-0.09942131456014613</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1110633168431712</v>
+        <v>0.1110629960269216</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0.1988167879443294</v>
+        <v>0.1988168151381025</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>-0.1203504334666562</v>
+        <v>-0.1203501619624294</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>0.2244540558096171</v>
+        <v>0.224453817584519</v>
       </c>
       <c r="AD7" s="2" t="n">
         <v>0.08286355968129189</v>
       </c>
       <c r="AE7" s="2" t="n">
-        <v>0.08932422829989628</v>
+        <v>0.08932403265541211</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.05923138374489667</v>
+        <v>-0.05923121478122262</v>
       </c>
       <c r="AG7" s="2" t="n">
         <v>0.1380567089143108</v>
@@ -5289,79 +5289,79 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>-0.03698554566039025</v>
+        <v>-0.03698522554361161</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-0.444095585058649</v>
+        <v>-0.4440958806511268</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.05096731744488114</v>
+        <v>-0.05096712828217875</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.5266633272530803</v>
+        <v>0.5266631172270686</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0.2644578118497577</v>
+        <v>-0.2644577106597895</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>-0.2088958012763623</v>
+        <v>-0.2088961753457944</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>-0.142194687424234</v>
+        <v>-0.1421942818153415</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.4509835941321978</v>
+        <v>0.4509834563256645</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2416901293411091</v>
+        <v>0.2416902472700984</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.1427251789688528</v>
+        <v>0.1427252554569887</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.4579827537009784</v>
+        <v>0.4579826561111311</v>
       </c>
       <c r="Q8" s="2" t="n">
         <v>0.2790499987191328</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>-0.4614975267061678</v>
+        <v>-0.4614977420654637</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>0.6797392024903979</v>
+        <v>0.679740007563872</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0.2460917569588403</v>
+        <v>0.2460917374284988</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>-0.1862135109587336</v>
+        <v>-0.1862134990990271</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.3173764961100143</v>
+        <v>0.3173765495336587</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>9.457698423931404e-05</v>
+        <v>9.433934241687147e-05</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.02691209211592427</v>
+        <v>0.02691197650910593</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1831601927173927</v>
+        <v>-0.1831600037159827</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.006919356906078811</v>
+        <v>0.00691914445819064</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0.3478348658914641</v>
+        <v>0.3478350096098015</v>
       </c>
       <c r="AB8" s="3" t="n">
-        <v>-0.1133987524928749</v>
+        <v>-0.1133986599680724</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>0.1453482048775803</v>
+        <v>0.1453484402911218</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>-0.08475188533070321</v>
+        <v>-0.08475207344970048</v>
       </c>
       <c r="AE8" s="2" t="n">
         <v>0.05469051154180726</v>
@@ -5370,10 +5370,10 @@
         <v>-0.09805165728263432</v>
       </c>
       <c r="AG8" s="2" t="n">
-        <v>0.06149140288926369</v>
+        <v>0.06149128485221045</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>0.2210092978145122</v>
+        <v>0.2210094335898516</v>
       </c>
       <c r="AI8" s="2" t="n">
         <v>0.3135403505873617</v>
@@ -5397,91 +5397,91 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
-        <v>0.2028148582031959</v>
+        <v>0.2028150055976548</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-0.2594925540021038</v>
+        <v>-0.2594926279424783</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>-0.08954518869642969</v>
+        <v>-0.08954579286008835</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.5664992536409938</v>
+        <v>0.5665005379669705</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0.1761163123781812</v>
+        <v>-0.1761166849377435</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>-0.1818030371994795</v>
+        <v>-0.1818030532581844</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.1743631849652805</v>
+        <v>-0.174363311746216</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.3860348542528826</v>
+        <v>0.3860348244495668</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2365688840235458</v>
+        <v>0.2365690453144957</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.07300549969953019</v>
+        <v>0.07300589229089072</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>0.2930412053567397</v>
+        <v>0.293040645153217</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.3941289872046541</v>
+        <v>0.3941287439729344</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>-0.503236169624669</v>
+        <v>-0.5032361709010612</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>0.5510671161369607</v>
+        <v>0.5510670967113933</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0.2414033830458675</v>
+        <v>0.2414036866564202</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>-0.1618306602337773</v>
+        <v>-0.1618301921133675</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.2928370126658351</v>
+        <v>0.2928361102838033</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.09539635031991156</v>
+        <v>0.09539668378092903</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.03284125173198005</v>
+        <v>0.03284152964081888</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.01175044901418687</v>
+        <v>-0.01175071492456836</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.01348621921707105</v>
+        <v>0.01348608308132904</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>0.3646320846285547</v>
+        <v>0.36463213360748</v>
       </c>
       <c r="AB9" s="3" t="n">
-        <v>-0.0875500443389422</v>
+        <v>-0.0875497576590375</v>
       </c>
       <c r="AC9" s="2" t="n">
-        <v>0.1073421333083922</v>
+        <v>0.1073417865173159</v>
       </c>
       <c r="AD9" s="2" t="n">
-        <v>0.04168988914487604</v>
+        <v>0.04169008804620189</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>-0.03494825807210644</v>
+        <v>-0.03494816128265987</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.06806281758508625</v>
+        <v>-0.06806290130124881</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>-0.1386984194954235</v>
+        <v>-0.1386985610508342</v>
       </c>
       <c r="AH9" s="2" t="n">
-        <v>5.613967309203716e-05</v>
+        <v>5.620004172435245e-05</v>
       </c>
       <c r="AI9" s="2" t="n">
         <v>0.3449972550448173</v>
@@ -5509,40 +5509,40 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" s="3" t="n">
-        <v>-0.4286956299051793</v>
+        <v>-0.4286959417700047</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.02059135874564433</v>
+        <v>0.0205915716954741</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2439701238870562</v>
+        <v>-0.2439700979766101</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.3819021596360392</v>
+        <v>0.3819023859838591</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.08032821042151772</v>
+        <v>0.08032791204482304</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.04637673128753339</v>
+        <v>0.04637673960406885</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>0.1875484891604502</v>
+        <v>0.1875486926797401</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>0.06377462776493004</v>
+        <v>0.06377484423310742</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>-0.4535246036799383</v>
+        <v>-0.4535247148825425</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>0.7378377683960033</v>
+        <v>0.7378380166421752</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>0.2277731975241919</v>
+        <v>0.2277731649873134</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>-0.2178388103100659</v>
+        <v>-0.2178389013121613</v>
       </c>
       <c r="V10" s="2" t="n">
         <v>0.1865625640092707</v>
@@ -5554,22 +5554,22 @@
         <v>0.06872256156836287</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.1285423345756082</v>
+        <v>-0.128542280205922</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1771130371677128</v>
+        <v>0.1771130885071006</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>0.2681201161295301</v>
+        <v>0.2681200877077214</v>
       </c>
       <c r="AB10" s="3" t="n">
-        <v>-0.09898116207692376</v>
+        <v>-0.09898115380294348</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>0.3335852467200311</v>
+        <v>0.3335849374487305</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.315040149576006</v>
+        <v>0.3150403325445288</v>
       </c>
       <c r="AE10" s="2" t="n">
         <v>0.2888196513555861</v>
@@ -5609,52 +5609,52 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" s="3" t="n">
-        <v>-0.3777777117765179</v>
+        <v>-0.3777780147822382</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.4566920215944315</v>
+        <v>0.456692337650644</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0.03613809019095471</v>
+        <v>0.0361377922990167</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0.3776840392960825</v>
+        <v>0.377684579134453</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.1722821919491995</v>
+        <v>0.1722819652877381</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>0.5389799213845239</v>
+        <v>0.5389793463016304</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>0.1113840187332304</v>
+        <v>0.1113845329552878</v>
       </c>
       <c r="Q11" s="2" t="n">
         <v>0.3171365927894634</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.5597195395279786</v>
+        <v>-0.5597196185469548</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>0.7176738279258958</v>
+        <v>0.7176741362040593</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>0.295532145876064</v>
+        <v>0.2955322503628304</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-0.1349669372716702</v>
+        <v>-0.134966926386369</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>0.2193316688345428</v>
+        <v>0.219331461914501</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0.03567677452920193</v>
+        <v>0.03567677725720042</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-0.1348449583357482</v>
+        <v>-0.1348448206308883</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>-0.08000108549409524</v>
+        <v>-0.08000116400457513</v>
       </c>
       <c r="Z11" s="2" t="n">
         <v>0.0843618688953407</v>
@@ -5666,10 +5666,10 @@
         <v>-0.2036931197949428</v>
       </c>
       <c r="AC11" s="2" t="n">
-        <v>0.07965756278500957</v>
+        <v>0.07965748868557165</v>
       </c>
       <c r="AD11" s="2" t="n">
-        <v>0.3943194923841424</v>
+        <v>0.3943195880795753</v>
       </c>
       <c r="AE11" s="3" t="n">
         <v>-0.07584293112899054</v>
@@ -5720,49 +5720,49 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" s="3" t="n">
-        <v>-0.2076362652869004</v>
+        <v>-0.2076361656695803</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>0.2321335627167755</v>
+        <v>0.2321335335325518</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.02183412574317756</v>
+        <v>0.02183381740801593</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>0.06841081638976565</v>
+        <v>0.06841122947431955</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>-0.08995036901960607</v>
+        <v>-0.08995044566748434</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>-0.003229696778426772</v>
+        <v>-0.003229593747156478</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>0.5466967878323734</v>
+        <v>0.5466970873068182</v>
       </c>
       <c r="AB12" s="3" t="n">
-        <v>-0.1978640343123037</v>
+        <v>-0.1978643549152518</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>0.2372056536946359</v>
+        <v>0.2372054876019716</v>
       </c>
       <c r="AD12" s="2" t="n">
-        <v>0.2777883088052875</v>
+        <v>0.2777883460978801</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>-0.2174199751168878</v>
+        <v>-0.2174198928967028</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>-0.2276348019678395</v>
+        <v>-0.2276348690938584</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>-0.1129155010991034</v>
+        <v>-0.1129153370931627</v>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>0.1773304102324598</v>
+        <v>0.1773301969144614</v>
       </c>
       <c r="AI12" s="2" t="n">
-        <v>0.3103955030280083</v>
+        <v>0.3103956120733888</v>
       </c>
       <c r="AJ12" s="3" t="n">
         <v>-0.0827368278001066</v>
@@ -5791,67 +5791,67 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" s="2" t="n">
-        <v>0.03373076374551776</v>
+        <v>0.03373085149975319</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>0.1332175922789367</v>
+        <v>0.1332170995541415</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>0.8316830922624305</v>
+        <v>0.8316843234832376</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>0.5475516736664212</v>
+        <v>0.5475516228156763</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>-0.4778981589886192</v>
+        <v>-0.4778983168983342</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>0.473433930423719</v>
+        <v>0.4734341726490128</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>0.03539091313314735</v>
+        <v>0.03539064492371269</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>-0.1754237184774828</v>
+        <v>-0.1754236238751631</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>0.1916210607508244</v>
+        <v>0.1916204528759462</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>-0.02139458517077719</v>
+        <v>-0.02139414043737919</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>0.1145237832336203</v>
+        <v>0.1145242658350853</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>-0.1290528729143835</v>
+        <v>-0.1290534931504839</v>
       </c>
       <c r="Z13" s="2" t="n">
-        <v>0.01063766939203292</v>
+        <v>0.01063822397648795</v>
       </c>
       <c r="AA13" s="2" t="n">
-        <v>0.3625829058405234</v>
+        <v>0.3625828564926841</v>
       </c>
       <c r="AB13" s="3" t="n">
-        <v>-0.1328056836657039</v>
+        <v>-0.1328057702849343</v>
       </c>
       <c r="AC13" s="2" t="n">
-        <v>0.1490184144757862</v>
+        <v>0.1490180689322498</v>
       </c>
       <c r="AD13" s="2" t="n">
-        <v>0.08917647077692825</v>
+        <v>0.08917679832433567</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>-0.2006296161651488</v>
+        <v>-0.2006295241294574</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>-0.2065872548296062</v>
+        <v>-0.206587346179353</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>-0.1242188155280013</v>
+        <v>-0.1242187429710448</v>
       </c>
       <c r="AH13" s="2" t="n">
-        <v>0.2898039959046443</v>
+        <v>0.2898038890466228</v>
       </c>
       <c r="AI13" s="2" t="n">
         <v>0.2894812248530938</v>
@@ -5891,34 +5891,34 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" s="3" t="n">
-        <v>-0.01452869389912925</v>
+        <v>-0.01452852946182137</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>-0.05222175371196114</v>
+        <v>-0.0522216615673774</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>0.2175404463341852</v>
+        <v>0.2175403008576717</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>-0.07112355982695506</v>
+        <v>-0.07112362184218635</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>-0.01639038789450875</v>
+        <v>-0.01639038661875314</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>0.3607705111349881</v>
+        <v>0.3607702451884405</v>
       </c>
       <c r="AB14" s="3" t="n">
-        <v>-0.06669445982909128</v>
+        <v>-0.06669423497479721</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>0.06488506929912297</v>
+        <v>0.06488481197966633</v>
       </c>
       <c r="AD14" s="2" t="n">
-        <v>0.1482801076103712</v>
+        <v>0.1482803590102222</v>
       </c>
       <c r="AE14" s="2" t="n">
-        <v>0.2135485759959854</v>
+        <v>0.2135484523205815</v>
       </c>
       <c r="AF14" s="3" t="n">
         <v>-0.08944149473991125</v>
@@ -5965,37 +5965,37 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" s="2" t="n">
-        <v>0.3414845053660078</v>
+        <v>0.3414846619537675</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>0.01935021055611386</v>
+        <v>0.01934976055088988</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>0.04514930739169976</v>
+        <v>0.04514931131728095</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>-0.2330172532411492</v>
+        <v>-0.2330171062446982</v>
       </c>
       <c r="X15" s="2" t="n">
-        <v>0.2182572544798411</v>
+        <v>0.2182571223417986</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>-0.2280431157232857</v>
+        <v>-0.2280432937888334</v>
       </c>
       <c r="Z15" s="2" t="n">
-        <v>0.169993702770781</v>
+        <v>0.1699939726506428</v>
       </c>
       <c r="AA15" s="2" t="n">
-        <v>0.1939794016545275</v>
+        <v>0.193979303078041</v>
       </c>
       <c r="AB15" s="3" t="n">
-        <v>-0.1088024129034059</v>
+        <v>-0.1088022567636696</v>
       </c>
       <c r="AC15" s="2" t="n">
-        <v>0.05300028950263447</v>
+        <v>0.05300037723347795</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>-0.07131433829998379</v>
+        <v>-0.07131450170774034</v>
       </c>
       <c r="AE15" s="3" t="n">
         <v>-0.005991538181490563</v>
@@ -6004,13 +6004,13 @@
         <v>-0.001599406669874681</v>
       </c>
       <c r="AG15" s="2" t="n">
-        <v>0.02561794693876651</v>
+        <v>0.02561785148120066</v>
       </c>
       <c r="AH15" s="3" t="n">
-        <v>-0.1301471701692136</v>
+        <v>-0.1301472753556607</v>
       </c>
       <c r="AI15" s="2" t="n">
-        <v>0.04903627238388442</v>
+        <v>0.04903649687520595</v>
       </c>
       <c r="AJ15" s="3" t="n">
         <v>-0.3197861097290484</v>
@@ -6031,85 +6031,85 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="n">
-        <v>0.1209361140614464</v>
+        <v>0.1209359313890308</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.6672127293479737</v>
+        <v>-0.667212784084575</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-0.2443208994908721</v>
+        <v>-0.2443208591730504</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1.060445013767331</v>
+        <v>1.060444782194736</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0.2748162644329594</v>
+        <v>-0.2748162882987071</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.04377257241001131</v>
+        <v>0.04377271535842309</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-0.01675582434983125</v>
+        <v>-0.01675603085773947</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0.3248851100830636</v>
+        <v>0.3248849676788781</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.1332236278166901</v>
+        <v>0.1332237496203121</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-0.005740115849440675</v>
+        <v>-0.005740210697601555</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>0.3638612114038362</v>
+        <v>0.3638610553231449</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>0.4460573452509944</v>
+        <v>0.4460575087952794</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-0.4017421988396692</v>
+        <v>-0.4017420925948803</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>0.4942067086207449</v>
+        <v>0.4942067495145914</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>0.3902069865005229</v>
+        <v>0.3902066196151359</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-0.02604408955913551</v>
+        <v>-0.02604370439415071</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>0.1478202551734191</v>
+        <v>0.1478202996550975</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>0.07838467785562453</v>
+        <v>0.07838430786107531</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.1148863081272683</v>
+        <v>-0.1148863801166592</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-0.2059479885307354</v>
+        <v>-0.2059480915317718</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0.04029145556068925</v>
+        <v>-0.04029128291894424</v>
       </c>
       <c r="AA16" s="2" t="n">
-        <v>0.2424724442027355</v>
+        <v>0.2424723716842048</v>
       </c>
       <c r="AB16" s="3" t="n">
-        <v>-0.06283352817595333</v>
+        <v>-0.06283322966466443</v>
       </c>
       <c r="AC16" s="3" t="n">
-        <v>-0.01410220741927548</v>
+        <v>-0.01410236952891086</v>
       </c>
       <c r="AD16" s="2" t="n">
         <v>0.03123714227055219</v>
       </c>
       <c r="AE16" s="3" t="n">
-        <v>-0.07402588497027918</v>
+        <v>-0.07402580410602788</v>
       </c>
       <c r="AF16" s="3" t="n">
-        <v>-0.06002591920160472</v>
+        <v>-0.0600260012884497</v>
       </c>
       <c r="AG16" s="3" t="n">
         <v>-0.03612002101524436</v>
@@ -6151,55 +6151,55 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" s="3" t="n">
-        <v>-0.5247851938098084</v>
+        <v>-0.5247849363248713</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>0.814283197860054</v>
+        <v>0.8142829576436914</v>
       </c>
       <c r="T17" s="2" t="n">
-        <v>0.5674942287169271</v>
+        <v>0.5674941986903013</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>-0.04227066459281759</v>
+        <v>-0.04227066833717896</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>0.4013701317421561</v>
+        <v>0.401370723806395</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>-0.1455999743392556</v>
+        <v>-0.1456001242908895</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>0.1555965891732274</v>
+        <v>0.1555966423814943</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>-0.2202590068982408</v>
+        <v>-0.2202591632659323</v>
       </c>
       <c r="Z17" s="2" t="n">
-        <v>0.2632272400530316</v>
+        <v>0.2632270685960718</v>
       </c>
       <c r="AA17" s="2" t="n">
-        <v>0.3145108000150116</v>
+        <v>0.3145108427033509</v>
       </c>
       <c r="AB17" s="3" t="n">
-        <v>-0.08247101100828447</v>
+        <v>-0.08247081301454362</v>
       </c>
       <c r="AC17" s="2" t="n">
-        <v>0.08317737783648638</v>
+        <v>0.08317714340503013</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>-0.09894149764945215</v>
+        <v>-0.09894140403494911</v>
       </c>
       <c r="AE17" s="2" t="n">
-        <v>0.01869496271765136</v>
+        <v>0.01869519332179626</v>
       </c>
       <c r="AF17" s="2" t="n">
-        <v>0.01220813558784872</v>
+        <v>0.01220779326615506</v>
       </c>
       <c r="AG17" s="3" t="n">
-        <v>-0.1262627239647589</v>
+        <v>-0.1262627380835768</v>
       </c>
       <c r="AH17" s="3" t="n">
-        <v>-0.02210548166698623</v>
+        <v>-0.02210535651598333</v>
       </c>
       <c r="AI17" s="2" t="n">
         <v>0.02356683530096615</v>
@@ -6237,43 +6237,43 @@
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" s="2" t="n">
-        <v>0.0002344683742419029</v>
+        <v>0.000234649774784268</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>-0.04452350080567147</v>
+        <v>-0.04452368613582325</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>0.4788963038030598</v>
+        <v>0.4788966298456019</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>-0.07632283094164205</v>
+        <v>-0.07632277168781043</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>0.2210083337940223</v>
+        <v>0.2210084726952193</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>-0.1084396860649605</v>
+        <v>-0.1084400150071407</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>-0.03292528598063293</v>
+        <v>-0.03292516678698965</v>
       </c>
       <c r="AA18" s="2" t="n">
-        <v>0.2019660912783612</v>
+        <v>0.2019661179257783</v>
       </c>
       <c r="AB18" s="3" t="n">
-        <v>-0.1749686221932039</v>
+        <v>-0.1749685865144461</v>
       </c>
       <c r="AC18" s="2" t="n">
-        <v>0.08496873597988719</v>
+        <v>0.08496880815727814</v>
       </c>
       <c r="AD18" s="3" t="n">
         <v>-0.03948274914857997</v>
       </c>
       <c r="AE18" s="3" t="n">
-        <v>-0.02230753325935664</v>
+        <v>-0.02230759709474917</v>
       </c>
       <c r="AF18" s="3" t="n">
-        <v>-0.1587254421681297</v>
+        <v>-0.1587253872397171</v>
       </c>
       <c r="AG18" s="2" t="n">
         <v>0.01273894001190867</v>
@@ -6316,43 +6316,43 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" s="3" t="n">
-        <v>-0.01892691649496403</v>
+        <v>-0.01892691830830029</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>0.04031544706237367</v>
+        <v>0.04031574396617832</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>-0.4383101488861768</v>
+        <v>-0.4383102543390747</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>0.2640054047482068</v>
+        <v>0.2640054883095579</v>
       </c>
       <c r="W19" s="2" t="n">
-        <v>0.07787058292717997</v>
+        <v>0.07787018112902011</v>
       </c>
       <c r="X19" s="2" t="n">
-        <v>0.05156324614688446</v>
+        <v>0.05156369128625293</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>-0.2009723238696797</v>
+        <v>-0.2009724754011561</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>-0.09635388875368611</v>
+        <v>-0.09635374979716538</v>
       </c>
       <c r="AA19" s="2" t="n">
-        <v>0.3857565696525582</v>
+        <v>0.3857566192700477</v>
       </c>
       <c r="AB19" s="3" t="n">
-        <v>-0.1682592953828943</v>
+        <v>-0.1682594506419616</v>
       </c>
       <c r="AC19" s="2" t="n">
-        <v>0.09238469854207576</v>
+        <v>0.09238491526903814</v>
       </c>
       <c r="AD19" s="2" t="n">
-        <v>0.0983689824699443</v>
+        <v>0.0983687132200215</v>
       </c>
       <c r="AE19" s="2" t="n">
-        <v>0.2204605039197365</v>
+        <v>0.2204606464966816</v>
       </c>
       <c r="AF19" s="3" t="n">
         <v>-0.4374292092232922</v>
@@ -6389,76 +6389,76 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" s="3" t="n">
-        <v>-0.06678637830551215</v>
+        <v>-0.06678628602561176</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-0.2269142682598462</v>
+        <v>-0.2269141963796591</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-0.2149713479234807</v>
+        <v>-0.2149714985408555</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0.4295869058066248</v>
+        <v>0.4295867428721887</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.206933872015743</v>
+        <v>0.2069340095737406</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>0.08767371578955618</v>
+        <v>0.08767324362992923</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>0.3549552390365331</v>
+        <v>0.3549563481441809</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>0.1841113097181732</v>
+        <v>0.184110726327875</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>-0.4582537689801838</v>
+        <v>-0.4582537644621441</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>0.2657108992762423</v>
+        <v>0.2657111255902169</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>-0.03129355742694817</v>
+        <v>-0.03129371279196747</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>-0.1816262610841556</v>
+        <v>-0.181626112947235</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>0.2391555422826142</v>
+        <v>0.2391556180224361</v>
       </c>
       <c r="W20" s="2" t="n">
-        <v>0.27108901659769</v>
+        <v>0.2710885713691238</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>-0.09865674286816517</v>
+        <v>-0.09865669837249424</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>-0.0164132024200071</v>
+        <v>-0.01641327484089272</v>
       </c>
       <c r="Z20" s="2" t="n">
-        <v>0.01863271589756321</v>
+        <v>0.01863300503936349</v>
       </c>
       <c r="AA20" s="2" t="n">
-        <v>0.2789027274487081</v>
+        <v>0.2789027779148321</v>
       </c>
       <c r="AB20" s="3" t="n">
-        <v>-0.1675663101254872</v>
+        <v>-0.1675664559545774</v>
       </c>
       <c r="AC20" s="2" t="n">
-        <v>0.2327035268309534</v>
+        <v>0.232703344913368</v>
       </c>
       <c r="AD20" s="2" t="n">
-        <v>0.07616830469071045</v>
+        <v>0.07616864091028974</v>
       </c>
       <c r="AE20" s="2" t="n">
-        <v>0.1392234070071565</v>
+        <v>0.139223294100647</v>
       </c>
       <c r="AF20" s="3" t="n">
-        <v>-0.1724187518976087</v>
+        <v>-0.1724186649012199</v>
       </c>
       <c r="AG20" s="2" t="n">
-        <v>0.234210181352055</v>
+        <v>0.2342100516103316</v>
       </c>
       <c r="AH20" s="2" t="n">
         <v>0.02231836728992498</v>
@@ -6485,85 +6485,85 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" s="2" t="n">
-        <v>0.2779626076395374</v>
+        <v>0.277962151579016</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.1814233539239731</v>
+        <v>0.1814237262514415</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.1951109113049925</v>
+        <v>0.195110534663987</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.1193357167922837</v>
+        <v>0.1193358486426435</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0.1359594390207128</v>
+        <v>-0.1359591285221253</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-0.1393593416857748</v>
+        <v>-0.1393594115189938</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.1534124326844225</v>
+        <v>-0.1534126887387699</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0.3479964816152985</v>
+        <v>0.3479964490587846</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1835143821498759</v>
+        <v>0.1835141612064353</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>0.0588693866124419</v>
+        <v>0.0588693935167528</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>0.3036070442913748</v>
+        <v>0.3036074102035173</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>0.06447074932953867</v>
+        <v>0.06447065340868052</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.4646651895305484</v>
+        <v>-0.4646652322605992</v>
       </c>
       <c r="S21" s="2" t="n">
-        <v>0.3622145234409055</v>
+        <v>0.3622143743392467</v>
       </c>
       <c r="T21" s="2" t="n">
-        <v>0.1020978648983937</v>
+        <v>0.1020979855289075</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-0.03941641447991429</v>
+        <v>-0.03941651379536271</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>0.1526227232583468</v>
+        <v>0.1526226356473734</v>
       </c>
       <c r="W21" s="2" t="n">
-        <v>0.1953293889069287</v>
+        <v>0.1953292445483215</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.07598315897850749</v>
+        <v>-0.07598280657410883</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.07018694238462786</v>
+        <v>-0.07018701789777848</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>-0.01210329714423819</v>
       </c>
       <c r="AA21" s="2" t="n">
-        <v>0.2153960520431621</v>
+        <v>0.2153961404569116</v>
       </c>
       <c r="AB21" s="3" t="n">
-        <v>-0.1429734410169841</v>
+        <v>-0.1429736488508104</v>
       </c>
       <c r="AC21" s="2" t="n">
-        <v>0.2128603228428163</v>
+        <v>0.2128603589781852</v>
       </c>
       <c r="AD21" s="3" t="n">
-        <v>-0.1179575312297025</v>
+        <v>-0.1179574077724891</v>
       </c>
       <c r="AE21" s="2" t="n">
-        <v>0.1819451374816015</v>
+        <v>0.1819452961671644</v>
       </c>
       <c r="AF21" s="3" t="n">
-        <v>-0.04396545971878052</v>
+        <v>-0.04396558807402662</v>
       </c>
       <c r="AG21" s="2" t="n">
         <v>0.1239877475765976</v>
@@ -6593,61 +6593,61 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" s="2" t="n">
-        <v>0.07897980981820796</v>
+        <v>0.0789797442785527</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.2377688683784083</v>
+        <v>0.2377688997406211</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.2808677069198011</v>
+        <v>0.2808674171571026</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.2257175327754695</v>
+        <v>0.2257175246945504</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0.1797526293197421</v>
+        <v>-0.1797523509433401</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>-0.2161503219215745</v>
+        <v>-0.2161504874233158</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>-0.3406093110048938</v>
+        <v>-0.3406090662115058</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>0.6665262571415536</v>
+        <v>0.6665255100211078</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1628982506541361</v>
+        <v>0.1628987779495819</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>0.09640836099458228</v>
+        <v>0.09640851028956976</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>0.3495935963987353</v>
+        <v>0.3495928882518149</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>0.3369472102634328</v>
+        <v>0.3369473971705788</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>-0.4345022075233103</v>
+        <v>-0.4345022438123529</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>0.2050573364076589</v>
+        <v>0.2050575882284742</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>0.08221251174420674</v>
+        <v>0.08221244542682205</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>-0.1766597864451104</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>0.3229272162802428</v>
+        <v>0.322927078732653</v>
       </c>
       <c r="W22" s="2" t="n">
-        <v>0.3084704032871837</v>
+        <v>0.3084706433038444</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>-0.1195655145057345</v>
+        <v>-0.1195655844657892</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>-0.02786868645480467</v>
@@ -6656,28 +6656,28 @@
         <v>0.03609567557099336</v>
       </c>
       <c r="AA22" s="2" t="n">
-        <v>0.2742165941644334</v>
+        <v>0.2742165045596301</v>
       </c>
       <c r="AB22" s="3" t="n">
-        <v>-0.2139740745780447</v>
+        <v>-0.2139739489820401</v>
       </c>
       <c r="AC22" s="2" t="n">
-        <v>0.1915199738190831</v>
+        <v>0.1915198672202496</v>
       </c>
       <c r="AD22" s="2" t="n">
-        <v>0.1058628769256713</v>
+        <v>0.1058629520100924</v>
       </c>
       <c r="AE22" s="2" t="n">
-        <v>0.05836860566013913</v>
+        <v>0.05836866959378306</v>
       </c>
       <c r="AF22" s="3" t="n">
-        <v>-0.2226482570358292</v>
+        <v>-0.2226483567734779</v>
       </c>
       <c r="AG22" s="2" t="n">
-        <v>0.2334853721162209</v>
+        <v>0.233485454642836</v>
       </c>
       <c r="AH22" s="2" t="n">
-        <v>0.09791171400746501</v>
+        <v>0.09791164055144086</v>
       </c>
       <c r="AI22" s="2" t="n">
         <v>0.3578489398660751</v>
@@ -6701,85 +6701,85 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="n">
-        <v>0.169699258475831</v>
+        <v>0.1697001290918461</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.1173671352311203</v>
+        <v>0.1173668730236008</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.4209897288663118</v>
+        <v>0.4209897680290153</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.3200086363159944</v>
+        <v>0.32000898664189</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.0125588462659354</v>
+        <v>0.01255855326204913</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-0.2385035367158628</v>
+        <v>-0.2385035197286068</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>-0.2011190176887852</v>
+        <v>-0.2011189053456472</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0.4104734294222907</v>
+        <v>0.4104733333067954</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1861265957949265</v>
+        <v>0.1861262328683377</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>0.1012961601565903</v>
+        <v>0.1012963142970653</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>0.3355671364812631</v>
+        <v>0.335566628124772</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>0.1214300028680446</v>
+        <v>0.1214302394028375</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>-0.4157966339917919</v>
+        <v>-0.4157965348482087</v>
       </c>
       <c r="S23" s="2" t="n">
         <v>0.2724025141922417</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>-0.02535980006123095</v>
+        <v>-0.0253593434549253</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>-0.1765992361553002</v>
+        <v>-0.1765996219077088</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>0.2432131956871808</v>
+        <v>0.2432129112041781</v>
       </c>
       <c r="W23" s="2" t="n">
-        <v>0.2410819117915259</v>
+        <v>0.2410821957868945</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>-0.1074618714491007</v>
+        <v>-0.1074617792598531</v>
       </c>
       <c r="Y23" s="2" t="n">
-        <v>0.002442781585578979</v>
+        <v>0.002442368177861809</v>
       </c>
       <c r="Z23" s="2" t="n">
-        <v>0.0490003540356978</v>
+        <v>0.04900057525666823</v>
       </c>
       <c r="AA23" s="2" t="n">
-        <v>0.2910828387092719</v>
+        <v>0.291082867300638</v>
       </c>
       <c r="AB23" s="3" t="n">
-        <v>-0.1289960150639241</v>
+        <v>-0.1289958727200107</v>
       </c>
       <c r="AC23" s="2" t="n">
-        <v>0.266839233641913</v>
+        <v>0.2668389482959457</v>
       </c>
       <c r="AD23" s="2" t="n">
-        <v>0.02858217266046581</v>
+        <v>0.02858238344626818</v>
       </c>
       <c r="AE23" s="2" t="n">
-        <v>0.2142708618639164</v>
+        <v>0.2142709145330708</v>
       </c>
       <c r="AF23" s="3" t="n">
-        <v>-0.1204795233582733</v>
+        <v>-0.120479620463777</v>
       </c>
       <c r="AG23" s="2" t="n">
         <v>0.2170692674740964</v>
@@ -6809,85 +6809,85 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" s="2" t="n">
-        <v>0.1420098708067767</v>
+        <v>0.1420087231487299</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.3677015918376179</v>
+        <v>0.3677018899707498</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.4834774543299001</v>
+        <v>0.4834776028430459</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.008244516933447965</v>
+        <v>0.008244622173336325</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.1111590541171228</v>
+        <v>0.1111590655316153</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>-0.2760161143295659</v>
+        <v>-0.2760154467357556</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.0697718426726992</v>
+        <v>-0.06977261448033389</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0.4181736099366422</v>
+        <v>0.4181731982769297</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.3313814949778149</v>
+        <v>0.3313816879276712</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>0.01877479353933564</v>
+        <v>0.01877501429336292</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>0.3244319679868148</v>
+        <v>0.3244318735075233</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>0.03755031190038838</v>
+        <v>0.03755052734584563</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>-0.4680933482493959</v>
+        <v>-0.4680937182590321</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>0.2205238103417584</v>
+        <v>0.2205243083380644</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>-0.1419780234191049</v>
+        <v>-0.1419780347720272</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>-0.2408577354912971</v>
+        <v>-0.2408579909229006</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>0.1536978759057555</v>
+        <v>0.1536989854246131</v>
       </c>
       <c r="W24" s="2" t="n">
-        <v>0.1906178038504882</v>
+        <v>0.1906171703966428</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>-0.1091571855857959</v>
       </c>
       <c r="Y24" s="2" t="n">
-        <v>0.03142720130660326</v>
+        <v>0.03142740195207994</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>-0.08568117916668572</v>
+        <v>-0.08568125976489072</v>
       </c>
       <c r="AA24" s="2" t="n">
-        <v>0.2869958548732234</v>
+        <v>0.2869957179616254</v>
       </c>
       <c r="AB24" s="3" t="n">
-        <v>-0.1717903734927689</v>
+        <v>-0.1717902908345602</v>
       </c>
       <c r="AC24" s="2" t="n">
-        <v>0.2698414821217023</v>
+        <v>0.2698412555836303</v>
       </c>
       <c r="AD24" s="2" t="n">
-        <v>0.01687832624849706</v>
+        <v>0.01687848476553122</v>
       </c>
       <c r="AE24" s="2" t="n">
-        <v>0.1438420029790926</v>
+        <v>0.1438419918614451</v>
       </c>
       <c r="AF24" s="3" t="n">
-        <v>-0.141593746156892</v>
+        <v>-0.1415938041603676</v>
       </c>
       <c r="AG24" s="2" t="n">
         <v>0.3063141311973958</v>
@@ -6917,91 +6917,91 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="n">
-        <v>0.3543187550990596</v>
+        <v>0.3543184386739044</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.239788520115098</v>
+        <v>0.2397890434229182</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.5041471228069361</v>
+        <v>0.5041463368057213</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>-0.01476519922043651</v>
+        <v>-0.01476470299825339</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-0.1194128268696197</v>
+        <v>-0.1194129761777495</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-0.09253429158012039</v>
+        <v>-0.092534099032206</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-0.1353727173590042</v>
+        <v>-0.1353730069083271</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0.57404820338402</v>
+        <v>0.574048764626397</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.3015654166521804</v>
+        <v>0.3015652681758374</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>0.04564341893853818</v>
+        <v>0.04564353325433634</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>0.4924416963591842</v>
+        <v>0.4924410107642225</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>0.2093164933865144</v>
+        <v>0.2093164648292458</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>-0.367700267041128</v>
+        <v>-0.3677002969233043</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>0.3309980354427371</v>
+        <v>0.3309982355016112</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>-0.1881491828813201</v>
+        <v>-0.1881492112609455</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>-0.09814095161584147</v>
+        <v>-0.0981407840572226</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>0.05401646827340434</v>
+        <v>0.05401698329965576</v>
       </c>
       <c r="W25" s="2" t="n">
-        <v>0.3190613026071063</v>
+        <v>0.3190607557981298</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>-0.06252310614788381</v>
+        <v>-0.06252310151568174</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-0.1553958028495481</v>
+        <v>-0.1553958695977568</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>-0.01815299714959973</v>
       </c>
       <c r="AA25" s="2" t="n">
-        <v>0.2697783768922257</v>
+        <v>0.2697785674906714</v>
       </c>
       <c r="AB25" s="3" t="n">
-        <v>-0.1532420037314282</v>
+        <v>-0.15324220588477</v>
       </c>
       <c r="AC25" s="2" t="n">
-        <v>0.1193006996973847</v>
+        <v>0.1193007989058974</v>
       </c>
       <c r="AD25" s="3" t="n">
-        <v>-0.03936501948442284</v>
+        <v>-0.03936494029715654</v>
       </c>
       <c r="AE25" s="2" t="n">
-        <v>0.00249143117157602</v>
+        <v>0.002491348533996796</v>
       </c>
       <c r="AF25" s="3" t="n">
-        <v>-0.0517869482832739</v>
+        <v>-0.05178703051062195</v>
       </c>
       <c r="AG25" s="2" t="n">
-        <v>0.3025501573848977</v>
+        <v>0.302550183621511</v>
       </c>
       <c r="AH25" s="2" t="n">
-        <v>0.05698409306221031</v>
+        <v>0.05698416343169654</v>
       </c>
       <c r="AI25" s="2" t="n">
         <v>0.7802733727297069</v>
@@ -7025,85 +7025,85 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="n">
-        <v>0.2653457314734529</v>
+        <v>0.2653454053362996</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.1032422750025797</v>
+        <v>0.1032426452735564</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0.1205976980415799</v>
+        <v>0.1205975328997193</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0.6301739810693352</v>
+        <v>0.6301740943571457</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0.2257996363150226</v>
+        <v>-0.225799380535078</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-0.2303002951610633</v>
+        <v>-0.2303004943907633</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.2947899712014138</v>
+        <v>-0.2947900931897744</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0.6737815402759635</v>
+        <v>0.6737816086263886</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.3531674012748698</v>
+        <v>0.3531671196439408</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>0.1033396052920941</v>
+        <v>0.1033405288440608</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>0.4373029107325921</v>
+        <v>0.437301931513302</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-0.01306124791437924</v>
+        <v>-0.01306124938994635</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.46901700731004</v>
+        <v>-0.4690170609974788</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>0.5541611523738423</v>
+        <v>0.5541617029936392</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>0.3590833884936273</v>
+        <v>0.3590831999753652</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-0.1679475535334709</v>
+        <v>-0.1679476045641425</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>0.2444558547503495</v>
+        <v>0.2444556857498525</v>
       </c>
       <c r="W26" s="2" t="n">
-        <v>0.2354558137416842</v>
+        <v>0.2354562544256544</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.0842471940339804</v>
+        <v>-0.08424726037298946</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.04543510942815498</v>
+        <v>-0.04543519259132323</v>
       </c>
       <c r="Z26" s="2" t="n">
         <v>0.02374464505833962</v>
       </c>
       <c r="AA26" s="2" t="n">
-        <v>0.2185663284705663</v>
+        <v>0.2185664176220361</v>
       </c>
       <c r="AB26" s="3" t="n">
-        <v>-0.1278348587635185</v>
+        <v>-0.1278348494109995</v>
       </c>
       <c r="AC26" s="2" t="n">
-        <v>0.2174594402703625</v>
+        <v>0.2174592542603777</v>
       </c>
       <c r="AD26" s="2" t="n">
-        <v>0.2226676601285502</v>
+        <v>0.222667606569499</v>
       </c>
       <c r="AE26" s="2" t="n">
-        <v>0.228347088557405</v>
+        <v>0.2283471142935329</v>
       </c>
       <c r="AF26" s="3" t="n">
-        <v>-0.2784350344464113</v>
+        <v>-0.2784349682396939</v>
       </c>
       <c r="AG26" s="2" t="n">
         <v>0.2506899393534947</v>
@@ -7133,91 +7133,91 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>-0.03268500386430495</v>
+        <v>-0.03268465275184651</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.3399519378944031</v>
+        <v>0.3399520835477212</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0.225772685746997</v>
+        <v>0.2257727211743705</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.03524728921436027</v>
+        <v>-0.03524745572280541</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.07204681103274524</v>
+        <v>0.07204624061078779</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.2484152383070403</v>
+        <v>-0.2484150645552784</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.1116934263322115</v>
+        <v>-0.1116930935270035</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.3344102116392749</v>
+        <v>0.3344099951714303</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1728331445586424</v>
+        <v>0.17283283613921</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>0.129628701048345</v>
+        <v>0.1296285567727278</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>0.2995350279369902</v>
+        <v>0.2995352625868004</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>0.05511963418964982</v>
+        <v>0.05511986625043441</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.2720454807165854</v>
+        <v>-0.2720454516024188</v>
       </c>
       <c r="S27" s="2" t="n">
-        <v>0.2211651916753625</v>
+        <v>0.2211656737098606</v>
       </c>
       <c r="T27" s="2" t="n">
-        <v>0.1445039858153705</v>
+        <v>0.1445031250073361</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>-0.07917009054177382</v>
+        <v>-0.07916968644450217</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>0.2178495382745496</v>
+        <v>0.2178492600400133</v>
       </c>
       <c r="W27" s="2" t="n">
-        <v>0.2572092018525867</v>
+        <v>0.2572090142564614</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>-0.01737743371811251</v>
+        <v>-0.01737721248660229</v>
       </c>
       <c r="Y27" s="2" t="n">
-        <v>0.002694897757433257</v>
+        <v>0.002694897552816267</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>-0.02505941077865204</v>
+        <v>-0.02505963605160044</v>
       </c>
       <c r="AA27" s="2" t="n">
-        <v>0.2334163158318243</v>
+        <v>0.2334166627702272</v>
       </c>
       <c r="AB27" s="3" t="n">
-        <v>-0.09207304171725361</v>
+        <v>-0.09207328200665965</v>
       </c>
       <c r="AC27" s="2" t="n">
-        <v>0.3158040679151994</v>
+        <v>0.3158045278655379</v>
       </c>
       <c r="AD27" s="2" t="n">
-        <v>0.1180604986708409</v>
+        <v>0.1180603683566566</v>
       </c>
       <c r="AE27" s="2" t="n">
-        <v>0.2020096586872837</v>
+        <v>0.2020095453498407</v>
       </c>
       <c r="AF27" s="3" t="n">
         <v>-0.1889292228466681</v>
       </c>
       <c r="AG27" s="2" t="n">
-        <v>0.1766681109604489</v>
+        <v>0.1766680142443475</v>
       </c>
       <c r="AH27" s="3" t="n">
-        <v>-0.02805081320743597</v>
+        <v>-0.02805073331817665</v>
       </c>
       <c r="AI27" s="2" t="n">
         <v>0.3292380888351607</v>
@@ -7241,91 +7241,91 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" s="2" t="n">
-        <v>0.2134448254085528</v>
+        <v>0.2134453852978337</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.2020961749390262</v>
+        <v>0.2020957800227097</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0.2387052777133265</v>
+        <v>0.238705095518714</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.05650994741280191</v>
+        <v>0.05650988218218456</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>-0.08561231284464177</v>
+        <v>-0.08561205228761259</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-0.2389669109527874</v>
+        <v>-0.2389669688872649</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>-0.2071032567150605</v>
+        <v>-0.2071031566851115</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0.2882034382108785</v>
+        <v>0.2882032756942468</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.1415246108021053</v>
+        <v>0.1415244149361501</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>0.1297947303842717</v>
+        <v>0.1297953531946143</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>0.3174029525040183</v>
+        <v>0.3174027560581598</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>0.1789948493867255</v>
+        <v>0.1789946928371573</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>-0.4747382272670739</v>
+        <v>-0.4747381808478631</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>0.4082939668310575</v>
+        <v>0.4082941700543228</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>0.04863845915205611</v>
+        <v>0.04863798044001344</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>-0.1601459703856665</v>
+        <v>-0.1601456754430591</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>0.2205883599992766</v>
+        <v>0.2205878600751399</v>
       </c>
       <c r="W28" s="2" t="n">
-        <v>0.2874091070340565</v>
+        <v>0.2874094674536567</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>-0.05769579939982006</v>
+        <v>-0.0576957938891649</v>
       </c>
       <c r="Y28" s="2" t="n">
-        <v>0.01505960898838965</v>
+        <v>0.01505950610163698</v>
       </c>
       <c r="Z28" s="2" t="n">
-        <v>0.0409576479556526</v>
+        <v>0.04095784766868493</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>0.3373095622307913</v>
+        <v>0.3373092097336514</v>
       </c>
       <c r="AB28" s="3" t="n">
-        <v>-0.1537527646311421</v>
+        <v>-0.1537526321965955</v>
       </c>
       <c r="AC28" s="2" t="n">
-        <v>0.3245353971574048</v>
+        <v>0.324535369648318</v>
       </c>
       <c r="AD28" s="2" t="n">
-        <v>0.2322992785512508</v>
+        <v>0.2322994556720923</v>
       </c>
       <c r="AE28" s="2" t="n">
-        <v>0.2273981381368282</v>
+        <v>0.2273979870361338</v>
       </c>
       <c r="AF28" s="3" t="n">
-        <v>-0.2442791661804476</v>
+        <v>-0.2442791455092661</v>
       </c>
       <c r="AG28" s="2" t="n">
-        <v>0.2208053892678217</v>
+        <v>0.2208051405952027</v>
       </c>
       <c r="AH28" s="2" t="n">
-        <v>0.01674219778068853</v>
+        <v>0.01674229103780123</v>
       </c>
       <c r="AI28" s="2" t="n">
         <v>0.348663215067716</v>
@@ -7363,40 +7363,40 @@
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
       <c r="T29" s="2" t="n">
-        <v>0.3731917148420318</v>
+        <v>0.3731918820929758</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>-0.3203135241666748</v>
+        <v>-0.3203133911220188</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>0.4160932232850985</v>
+        <v>0.4160928155971002</v>
       </c>
       <c r="W29" s="2" t="n">
-        <v>0.03733140870394114</v>
+        <v>0.03733178075294252</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>-0.1632165642582</v>
+        <v>-0.1632168761030076</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>-0.231618007702372</v>
+        <v>-0.2316178199647856</v>
       </c>
       <c r="Z29" s="2" t="n">
-        <v>0.0241230497152074</v>
+        <v>0.02412311546471924</v>
       </c>
       <c r="AA29" s="2" t="n">
-        <v>0.5242384942584111</v>
+        <v>0.524237781073341</v>
       </c>
       <c r="AB29" s="3" t="n">
-        <v>-0.1375526690443432</v>
+        <v>-0.1375523515282424</v>
       </c>
       <c r="AC29" s="3" t="n">
-        <v>-0.06124842275623443</v>
+        <v>-0.06124862172384893</v>
       </c>
       <c r="AD29" s="3" t="n">
-        <v>-0.08377345664766678</v>
+        <v>-0.08377330182220966</v>
       </c>
       <c r="AE29" s="2" t="n">
-        <v>0.122049342732665</v>
+        <v>0.1220492757922103</v>
       </c>
       <c r="AF29" s="3" t="n">
         <v>-0.2461740629359921</v>
@@ -7441,58 +7441,58 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" s="3" t="n">
-        <v>-0.4212640816448128</v>
+        <v>-0.4212641277214552</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>1.030803786749836</v>
+        <v>1.03080378341861</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>0.2558097156570478</v>
+        <v>0.2558094754064211</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>-0.3656557490984244</v>
+        <v>-0.3656556953007726</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>0.656034751991512</v>
+        <v>0.6560348856859273</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>-0.2724400882364624</v>
+        <v>-0.2724403084368522</v>
       </c>
       <c r="X30" s="2" t="n">
-        <v>0.1578733561782311</v>
+        <v>0.1578737241008621</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>-0.3143877077234976</v>
+        <v>-0.3143877734276097</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>-0.08556988020281064</v>
+        <v>-0.08556967053746178</v>
       </c>
       <c r="AA30" s="2" t="n">
-        <v>0.3758289617550656</v>
+        <v>0.3758289520114466</v>
       </c>
       <c r="AB30" s="3" t="n">
-        <v>-0.4146457835598029</v>
+        <v>-0.4146459691781925</v>
       </c>
       <c r="AC30" s="2" t="n">
-        <v>0.144882239478423</v>
+        <v>0.144882348129127</v>
       </c>
       <c r="AD30" s="3" t="n">
-        <v>-0.01189453958611697</v>
+        <v>-0.01189445669445111</v>
       </c>
       <c r="AE30" s="3" t="n">
-        <v>-0.2741205780590051</v>
+        <v>-0.2741206389526566</v>
       </c>
       <c r="AF30" s="2" t="n">
         <v>1.057454201267682</v>
       </c>
       <c r="AG30" s="3" t="n">
-        <v>-0.08825816236255635</v>
+        <v>-0.08825810619145924</v>
       </c>
       <c r="AH30" s="2" t="n">
-        <v>0.129142374413425</v>
+        <v>0.1291424280657016</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>-0.01536996919633293</v>
+        <v>-0.01537007664359225</v>
       </c>
       <c r="AJ30" s="2" t="n">
         <v>0.1098199533724717</v>
@@ -7517,79 +7517,79 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" s="3" t="n">
-        <v>-0.1091421307443152</v>
+        <v>-0.1091421754301295</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0.1881945761503924</v>
+        <v>-0.1881949955583976</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0.3634153265258313</v>
+        <v>-0.363414908857528</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1.169701480216635</v>
+        <v>1.169701142604302</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.3363004365250744</v>
+        <v>0.3363005248157578</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>0.5267367687948801</v>
+        <v>0.5267360666249157</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>0.4330928322334808</v>
+        <v>0.4330929451912819</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>0.7482233365810442</v>
+        <v>0.7482238367455838</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.5432140515937307</v>
+        <v>-0.5432140470950122</v>
       </c>
       <c r="S31" s="2" t="n">
-        <v>1.219892313279451</v>
+        <v>1.21989160451167</v>
       </c>
       <c r="T31" s="2" t="n">
-        <v>0.07803848451551043</v>
+        <v>0.07803860320331002</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-0.2414155085289234</v>
+        <v>-0.2414151029734337</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>0.003594389330432879</v>
+        <v>0.003594073902038364</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.1748124790591427</v>
+        <v>-0.1748125197368631</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.1547493670176098</v>
+        <v>-0.1547493552883936</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.4177177068117194</v>
+        <v>-0.4177176245185648</v>
       </c>
       <c r="Z31" s="2" t="n">
-        <v>0.6447317367987055</v>
+        <v>0.6447315108655529</v>
       </c>
       <c r="AA31" s="2" t="n">
-        <v>0.236163383978454</v>
+        <v>0.2361635491306282</v>
       </c>
       <c r="AB31" s="3" t="n">
-        <v>-0.02518544294032199</v>
+        <v>-0.02518566445028714</v>
       </c>
       <c r="AC31" s="2" t="n">
-        <v>0.2766672496851739</v>
+        <v>0.276667405087708</v>
       </c>
       <c r="AD31" s="3" t="n">
-        <v>-0.2035513195738451</v>
+        <v>-0.2035514165216818</v>
       </c>
       <c r="AE31" s="3" t="n">
-        <v>-0.1731401805668112</v>
+        <v>-0.173140333401727</v>
       </c>
       <c r="AF31" s="2" t="n">
-        <v>0.1209164256074231</v>
+        <v>0.1209167252140375</v>
       </c>
       <c r="AG31" s="2" t="n">
-        <v>0.3262063253195822</v>
+        <v>0.3262062984240706</v>
       </c>
       <c r="AH31" s="3" t="n">
-        <v>-0.3041066900755016</v>
+        <v>-0.3041067333387379</v>
       </c>
       <c r="AI31" s="2" t="n">
         <v>0.4880613855707459</v>
@@ -7613,94 +7613,94 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" s="2" t="n">
-        <v>0.1218843447364519</v>
+        <v>0.1218842564458127</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.4719288275753954</v>
+        <v>0.471928943414027</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>-0.3534703823147317</v>
+        <v>-0.3534705427134959</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0.7735981091427409</v>
+        <v>0.7735977221849626</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-0.2394523060430083</v>
+        <v>-0.2394519980502505</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.1539253058266241</v>
+        <v>0.1539258670258437</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>-0.1472053752987579</v>
+        <v>-0.1472059502799528</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>0.4353765382474184</v>
+        <v>0.4353768959429034</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.4896128348447772</v>
+        <v>0.4896124876192394</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>0.4381429421236704</v>
+        <v>0.4381431608028172</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>0.448304953088049</v>
+        <v>0.4483049083779818</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>0.1135113224604229</v>
+        <v>0.1135113351636896</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>-0.4106884957769399</v>
+        <v>-0.4106885873044062</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>0.5387045506445116</v>
+        <v>0.5387052853582506</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>0.2792472186779289</v>
+        <v>0.2792469351043467</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>-0.1196507854762191</v>
+        <v>-0.1196510454012845</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>0.3281193102435596</v>
+        <v>0.3281200960436093</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>-0.01579946586675129</v>
+        <v>-0.0158000540061316</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>-0.1156634579548321</v>
+        <v>-0.1156633422042885</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>-0.1424871608873631</v>
+        <v>-0.1424869297300261</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>-0.1031245963356886</v>
+        <v>-0.1031245860967426</v>
       </c>
       <c r="AA32" s="2" t="n">
-        <v>0.1446564525076366</v>
+        <v>0.1446563257903004</v>
       </c>
       <c r="AB32" s="3" t="n">
-        <v>-0.1457704899007239</v>
+        <v>-0.1457707800403294</v>
       </c>
       <c r="AC32" s="2" t="n">
-        <v>0.1263697402974546</v>
+        <v>0.1263701228697953</v>
       </c>
       <c r="AD32" s="3" t="n">
         <v>-0.03057892832879294</v>
       </c>
       <c r="AE32" s="2" t="n">
-        <v>0.2027451548832315</v>
+        <v>0.2027452585686682</v>
       </c>
       <c r="AF32" s="2" t="n">
-        <v>0.01239704367512839</v>
+        <v>0.01239695639909977</v>
       </c>
       <c r="AG32" s="2" t="n">
-        <v>0.4031794619571196</v>
+        <v>0.4031793768054288</v>
       </c>
       <c r="AH32" s="3" t="n">
-        <v>-0.2821652901529293</v>
+        <v>-0.2821653072760798</v>
       </c>
       <c r="AI32" s="2" t="n">
-        <v>0.5364440027015189</v>
+        <v>0.5364441325905198</v>
       </c>
       <c r="AJ32" s="2" t="n">
         <v>0.1312562849240395</v>
@@ -7732,61 +7732,61 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" s="2" t="n">
-        <v>0.02592664155547264</v>
+        <v>0.02592646127724718</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>-0.3768452609243595</v>
+        <v>-0.3768450962239013</v>
       </c>
       <c r="S33" s="2" t="n">
-        <v>0.8606201054433043</v>
+        <v>0.8606204779852462</v>
       </c>
       <c r="T33" s="2" t="n">
-        <v>0.4660697682041308</v>
+        <v>0.4660694086803638</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>-0.2644525170344872</v>
+        <v>-0.264452271449243</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>0.1129716611122382</v>
+        <v>0.11297144700122</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>-0.2389747677881847</v>
+        <v>-0.238974854213484</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>-0.1474311073518804</v>
+        <v>-0.1474307266196911</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>-0.1852610242712258</v>
+        <v>-0.1852611623818436</v>
       </c>
       <c r="Z33" s="2" t="n">
-        <v>0.194656966854406</v>
+        <v>0.1946566897932829</v>
       </c>
       <c r="AA33" s="2" t="n">
-        <v>0.4178767505488614</v>
+        <v>0.4178763001609924</v>
       </c>
       <c r="AB33" s="3" t="n">
-        <v>-0.1897939998088927</v>
+        <v>-0.1897934939703683</v>
       </c>
       <c r="AC33" s="3" t="n">
-        <v>-0.1779102595732783</v>
+        <v>-0.1779103958779545</v>
       </c>
       <c r="AD33" s="3" t="n">
-        <v>-0.07132354294377397</v>
+        <v>-0.07132368268573308</v>
       </c>
       <c r="AE33" s="3" t="n">
-        <v>-0.1980278704302431</v>
+        <v>-0.1980278078607908</v>
       </c>
       <c r="AF33" s="2" t="n">
-        <v>0.2512175401665919</v>
+        <v>0.2512176374511181</v>
       </c>
       <c r="AG33" s="2" t="n">
-        <v>0.09014102948475999</v>
+        <v>0.09014094472424317</v>
       </c>
       <c r="AH33" s="3" t="n">
-        <v>-0.08668870160161002</v>
+        <v>-0.08668877292438948</v>
       </c>
       <c r="AI33" s="2" t="n">
-        <v>0.6540960619192455</v>
+        <v>0.6540961910917826</v>
       </c>
       <c r="AJ33" s="2" t="n">
         <v>0.03910886031391181</v>
@@ -7820,49 +7820,49 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" s="2" t="n">
-        <v>0.888790279451442</v>
+        <v>0.8887901638935074</v>
       </c>
       <c r="T34" s="2" t="n">
-        <v>0.517317260533581</v>
+        <v>0.5173172310026031</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>-0.1522148589286278</v>
+        <v>-0.1522146292731105</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>0.2737838429654822</v>
+        <v>0.2737833152663796</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>-0.1500764769322841</v>
+        <v>-0.1500763611997136</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>-0.2689279174420982</v>
+        <v>-0.2689277653441225</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>-0.4106962419604909</v>
+        <v>-0.4106963127855918</v>
       </c>
       <c r="Z34" s="2" t="n">
-        <v>0.2407977598083588</v>
+        <v>0.240797453893838</v>
       </c>
       <c r="AA34" s="2" t="n">
-        <v>0.1188301394722571</v>
+        <v>0.1188305796806071</v>
       </c>
       <c r="AB34" s="3" t="n">
-        <v>-0.1988307199241253</v>
+        <v>-0.1988308376218045</v>
       </c>
       <c r="AC34" s="2" t="n">
         <v>0.3042705172844229</v>
       </c>
       <c r="AD34" s="3" t="n">
-        <v>-0.1459712922642524</v>
+        <v>-0.1459711516751334</v>
       </c>
       <c r="AE34" s="3" t="n">
-        <v>-0.1149525988605421</v>
+        <v>-0.1149526622465448</v>
       </c>
       <c r="AF34" s="3" t="n">
-        <v>-0.2131687184625546</v>
+        <v>-0.2131688846377583</v>
       </c>
       <c r="AG34" s="2" t="n">
-        <v>0.2492300742409836</v>
+        <v>0.2492302218944265</v>
       </c>
       <c r="AH34" s="2" t="n">
         <v>0.04683238937813639</v>
@@ -7894,73 +7894,73 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" s="2" t="n">
-        <v>0.1463940871761515</v>
+        <v>0.1463942800828377</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>-0.2327530992288027</v>
+        <v>-0.2327532347762635</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0.6212270676926526</v>
+        <v>0.621227041290215</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.3852579530167755</v>
+        <v>0.385257986145358</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>0.5459578483448455</v>
+        <v>0.5459573235555237</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>0.4106035152421306</v>
+        <v>0.4106044028761449</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>0.4850163032976988</v>
+        <v>0.4850155096776221</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>-0.4722582098994554</v>
+        <v>-0.4722578946960839</v>
       </c>
       <c r="S35" s="2" t="n">
-        <v>0.9114101107046721</v>
+        <v>0.9114098458735997</v>
       </c>
       <c r="T35" s="2" t="n">
-        <v>0.1553517386742089</v>
+        <v>0.1553515630374152</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>-0.1848906330438044</v>
+        <v>-0.1848906988333863</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>0.05768972178534293</v>
+        <v>0.05768964572904101</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>-0.1254791044563134</v>
+        <v>-0.1254792762275557</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>-0.1228683701642634</v>
+        <v>-0.1228680640118534</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>-0.3153882778821187</v>
+        <v>-0.315388427106317</v>
       </c>
       <c r="Z35" s="2" t="n">
-        <v>0.3235177974310017</v>
+        <v>0.3235183765425675</v>
       </c>
       <c r="AA35" s="2" t="n">
-        <v>0.2632964301418579</v>
+        <v>0.2632961527402027</v>
       </c>
       <c r="AB35" s="3" t="n">
-        <v>-0.06845987019504118</v>
+        <v>-0.06846004401458483</v>
       </c>
       <c r="AC35" s="2" t="n">
-        <v>0.1376921752107623</v>
+        <v>0.1376924807939042</v>
       </c>
       <c r="AD35" s="3" t="n">
-        <v>-0.1171271978668108</v>
+        <v>-0.117127352272471</v>
       </c>
       <c r="AE35" s="3" t="n">
-        <v>-0.1358476661375025</v>
+        <v>-0.1358475858709742</v>
       </c>
       <c r="AF35" s="2" t="n">
-        <v>0.09812526387929865</v>
+        <v>0.09812537136577482</v>
       </c>
       <c r="AG35" s="2" t="n">
-        <v>0.3314327624475304</v>
+        <v>0.3314326321245096</v>
       </c>
       <c r="AH35" s="3" t="n">
         <v>-0.2311395994326024</v>
@@ -8006,31 +8006,31 @@
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" s="3" t="n">
-        <v>-0.05833973586913499</v>
+        <v>-0.05833991963185758</v>
       </c>
       <c r="Z36" s="2" t="n">
-        <v>0.07671577266492724</v>
+        <v>0.07671588088083059</v>
       </c>
       <c r="AA36" s="2" t="n">
-        <v>0.0614485204891253</v>
+        <v>0.06144833380005599</v>
       </c>
       <c r="AB36" s="2" t="n">
-        <v>0.1307334483715052</v>
+        <v>0.1307334713650934</v>
       </c>
       <c r="AC36" s="2" t="n">
-        <v>0.09295501981776666</v>
+        <v>0.09295511204974694</v>
       </c>
       <c r="AD36" s="2" t="n">
-        <v>0.02654856425415741</v>
+        <v>0.02654870846053825</v>
       </c>
       <c r="AE36" s="2" t="n">
-        <v>0.3362396649874075</v>
+        <v>0.3362395723615463</v>
       </c>
       <c r="AF36" s="3" t="n">
-        <v>-0.06060041087591728</v>
+        <v>-0.06060030712461251</v>
       </c>
       <c r="AG36" s="2" t="n">
-        <v>0.1504966678962796</v>
+        <v>0.1504965408305254</v>
       </c>
       <c r="AH36" s="3" t="n">
         <v>-0.001856006745903915</v>
@@ -8069,55 +8069,55 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" s="3" t="n">
-        <v>-0.3724789881890436</v>
+        <v>-0.3724790018871232</v>
       </c>
       <c r="S37" s="2" t="n">
-        <v>0.812782717662055</v>
+        <v>0.8127825625071787</v>
       </c>
       <c r="T37" s="2" t="n">
         <v>0.153073436624469</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>-0.3268981373428166</v>
+        <v>-0.3268980963962967</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>0.08722107731935913</v>
+        <v>0.08722113284604815</v>
       </c>
       <c r="W37" s="2" t="n">
-        <v>0.1829518781805415</v>
+        <v>0.1829516338979895</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>-0.01677976627709699</v>
+        <v>-0.01677938947299917</v>
       </c>
       <c r="Y37" s="2" t="n">
-        <v>0.07789297058742872</v>
+        <v>0.07789275568017828</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>-0.0398818917317072</v>
+        <v>-0.03988206669099881</v>
       </c>
       <c r="AA37" s="2" t="n">
-        <v>0.127731285871427</v>
+        <v>0.1277313907135529</v>
       </c>
       <c r="AB37" s="3" t="n">
-        <v>-0.04835607370237283</v>
+        <v>-0.04835615613981725</v>
       </c>
       <c r="AC37" s="2" t="n">
-        <v>0.2093215848360912</v>
+        <v>0.2093217762215833</v>
       </c>
       <c r="AD37" s="2" t="n">
-        <v>0.1201478144588719</v>
+        <v>0.1201476625880493</v>
       </c>
       <c r="AE37" s="2" t="n">
-        <v>0.2282720272534751</v>
+        <v>0.2282719779023374</v>
       </c>
       <c r="AF37" s="3" t="n">
-        <v>-0.2705142172990875</v>
+        <v>-0.2705141413390429</v>
       </c>
       <c r="AG37" s="2" t="n">
-        <v>0.05477049884443286</v>
+        <v>0.05477057021538756</v>
       </c>
       <c r="AH37" s="2" t="n">
-        <v>0.3450058015896924</v>
+        <v>0.3450057105799973</v>
       </c>
       <c r="AI37" s="2" t="n">
         <v>0.4510768183118878</v>
@@ -8148,70 +8148,70 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="2" t="n">
-        <v>0.458089379392518</v>
+        <v>0.4580898141122591</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.4362082700590006</v>
+        <v>0.4362083379297994</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>0.2587052064401671</v>
+        <v>0.2587049094600582</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>0.1973676781399147</v>
+        <v>0.197367832158202</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>0.1551041271540423</v>
+        <v>0.1551043762476019</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>-0.3760827841443772</v>
+        <v>-0.3760828463742452</v>
       </c>
       <c r="S38" s="2" t="n">
-        <v>0.5162846951364197</v>
+        <v>0.5162847466309621</v>
       </c>
       <c r="T38" s="2" t="n">
-        <v>0.3699169151161759</v>
+        <v>0.3699175314655043</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>-0.1568355428773046</v>
+        <v>-0.1568359628028096</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>0.2100685492803664</v>
+        <v>0.210068573206676</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>-0.07464784569686234</v>
+        <v>-0.07464766447321047</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>0.02803885951387364</v>
+        <v>0.02803895837976333</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>-0.2599968496330031</v>
+        <v>-0.2599969960702544</v>
       </c>
       <c r="Z38" s="2" t="n">
-        <v>0.1678114558518824</v>
+        <v>0.1678111884376503</v>
       </c>
       <c r="AA38" s="2" t="n">
-        <v>0.3602611190321705</v>
+        <v>0.3602615450088211</v>
       </c>
       <c r="AB38" s="3" t="n">
-        <v>-0.2524080736942348</v>
+        <v>-0.2524081366193576</v>
       </c>
       <c r="AC38" s="2" t="n">
-        <v>0.09829592460338366</v>
+        <v>0.0982958120146582</v>
       </c>
       <c r="AD38" s="3" t="n">
-        <v>-0.05189649097682536</v>
+        <v>-0.05189649629684912</v>
       </c>
       <c r="AE38" s="2" t="n">
-        <v>0.07911098761013724</v>
+        <v>0.0791108880404563</v>
       </c>
       <c r="AF38" s="3" t="n">
-        <v>-0.05177747542849898</v>
+        <v>-0.05177748580437125</v>
       </c>
       <c r="AG38" s="2" t="n">
-        <v>0.01508251876531186</v>
+        <v>0.01508262762079093</v>
       </c>
       <c r="AH38" s="2" t="n">
-        <v>0.07160427384414869</v>
+        <v>0.07160438539593494</v>
       </c>
       <c r="AI38" s="2" t="n">
         <v>0.7520076120570864</v>
@@ -8242,16 +8242,16 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="2" t="n">
-        <v>0.631529549563179</v>
+        <v>0.631529729904253</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.2463709655272015</v>
+        <v>0.2463706635092107</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>0.3262586057864481</v>
+        <v>0.3262584761739105</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>0.3121227517806766</v>
+        <v>0.3121228800117586</v>
       </c>
       <c r="Q39" s="2" t="n">
         <v>0.3333457467999883</v>
@@ -8263,28 +8263,28 @@
         <v>0.6895437849008179</v>
       </c>
       <c r="T39" s="2" t="n">
-        <v>0.1652308772864763</v>
+        <v>0.1652307479380239</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>-0.1879367004186285</v>
+        <v>-0.1879367212808667</v>
       </c>
       <c r="V39" s="2" t="n">
-        <v>0.1904961873122379</v>
+        <v>0.1904962133525219</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>-0.03648429723388669</v>
+        <v>-0.03648441624681398</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>-0.03898589783542772</v>
+        <v>-0.03898572837009162</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>-0.1617484428562854</v>
+        <v>-0.1617484528851771</v>
       </c>
       <c r="Z39" s="2" t="n">
-        <v>0.108683667899969</v>
+        <v>0.1086838978402205</v>
       </c>
       <c r="AA39" s="2" t="n">
-        <v>0.372628417024593</v>
+        <v>0.3726282338717302</v>
       </c>
       <c r="AB39" s="3" t="n">
         <v>-0.1531032804054638</v>
@@ -8293,19 +8293,19 @@
         <v>0.1822293969212461</v>
       </c>
       <c r="AD39" s="2" t="n">
-        <v>0.1702050235269079</v>
+        <v>0.1702047322561753</v>
       </c>
       <c r="AE39" s="3" t="n">
-        <v>-0.03632430624165961</v>
+        <v>-0.03632398340860388</v>
       </c>
       <c r="AF39" s="3" t="n">
-        <v>-0.2056367363848723</v>
+        <v>-0.2056367186803834</v>
       </c>
       <c r="AG39" s="2" t="n">
-        <v>0.08948334404163316</v>
+        <v>0.08948311757592742</v>
       </c>
       <c r="AH39" s="2" t="n">
-        <v>0.06490033679512908</v>
+        <v>0.06490044273318296</v>
       </c>
       <c r="AI39" s="2" t="n">
         <v>0.3398020830511308</v>
@@ -8334,79 +8334,79 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" s="3" t="n">
-        <v>-0.06957220737051883</v>
+        <v>-0.06957186971258811</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-0.1541967828230595</v>
+        <v>-0.1541972017731521</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>0.4030115464264155</v>
+        <v>0.4030119619126136</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.1895924739816128</v>
+        <v>0.1895923814218963</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>0.1332151294205954</v>
+        <v>0.1332152602350185</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>0.2580577872964176</v>
+        <v>0.2580577575071252</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>0.09951034403277448</v>
+        <v>0.09950987611330797</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>-0.4103108517457673</v>
+        <v>-0.4103105714464543</v>
       </c>
       <c r="S40" s="2" t="n">
-        <v>0.2699138138435628</v>
+        <v>0.269913634124392</v>
       </c>
       <c r="T40" s="2" t="n">
-        <v>0.08169412541910259</v>
+        <v>0.08169434830160194</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>-0.1223014860184618</v>
+        <v>-0.1223019759418751</v>
       </c>
       <c r="V40" s="2" t="n">
-        <v>0.1875999422018173</v>
+        <v>0.1876003604053669</v>
       </c>
       <c r="W40" s="2" t="n">
-        <v>0.2144433828095604</v>
+        <v>0.2144437781634014</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>-0.06194021821489337</v>
+        <v>-0.06194044220803541</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>-0.009929217075876129</v>
+        <v>-0.009929389733861038</v>
       </c>
       <c r="Z40" s="2" t="n">
-        <v>0.01372572215737611</v>
+        <v>0.0137256357303277</v>
       </c>
       <c r="AA40" s="2" t="n">
-        <v>0.2507541099695694</v>
+        <v>0.2507543262082985</v>
       </c>
       <c r="AB40" s="3" t="n">
-        <v>-0.1382103819424406</v>
+        <v>-0.1382104510554069</v>
       </c>
       <c r="AC40" s="2" t="n">
-        <v>0.2204346037344549</v>
+        <v>0.2204348620037597</v>
       </c>
       <c r="AD40" s="2" t="n">
-        <v>0.07595114796319846</v>
+        <v>0.07595113798141728</v>
       </c>
       <c r="AE40" s="2" t="n">
-        <v>0.1144585237343572</v>
+        <v>0.1144583876071104</v>
       </c>
       <c r="AF40" s="3" t="n">
-        <v>-0.1438591920644862</v>
+        <v>-0.1438590824627853</v>
       </c>
       <c r="AG40" s="2" t="n">
-        <v>0.1836341390272465</v>
+        <v>0.1836339875004216</v>
       </c>
       <c r="AH40" s="2" t="n">
-        <v>0.03487468227530743</v>
+        <v>0.03487479043230235</v>
       </c>
       <c r="AI40" s="2" t="n">
-        <v>0.3154783354639881</v>
+        <v>0.3154781979805117</v>
       </c>
       <c r="AJ40" s="2" t="n">
         <v>0.0913256730599028</v>
@@ -8436,64 +8436,64 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" s="2" t="n">
-        <v>0.2351969454382041</v>
+        <v>0.2351973055866188</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>0.2936559698547461</v>
+        <v>0.293656540332569</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>0.373117867798886</v>
+        <v>0.3731176601668988</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.5245926189807258</v>
+        <v>-0.5245925235035109</v>
       </c>
       <c r="S41" s="2" t="n">
-        <v>0.7631091823312679</v>
+        <v>0.7631088901864158</v>
       </c>
       <c r="T41" s="2" t="n">
-        <v>0.1948132062902372</v>
+        <v>0.1948128744741593</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.1875103398197081</v>
+        <v>-0.1875099877136734</v>
       </c>
       <c r="V41" s="2" t="n">
-        <v>0.1921046511948679</v>
+        <v>0.1921038340020673</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.04941475970836928</v>
+        <v>-0.04941465007499224</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.0004169381776150116</v>
+        <v>-0.0004164119057881166</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.1581946793821897</v>
+        <v>-0.1581950222490424</v>
       </c>
       <c r="Z41" s="2" t="n">
-        <v>0.1217107246228588</v>
+        <v>0.1217108123306772</v>
       </c>
       <c r="AA41" s="2" t="n">
-        <v>0.314855117091416</v>
+        <v>0.3148548382633276</v>
       </c>
       <c r="AB41" s="3" t="n">
-        <v>-0.1476050587321192</v>
+        <v>-0.147604930988261</v>
       </c>
       <c r="AC41" s="2" t="n">
-        <v>0.207502522953497</v>
+        <v>0.2075024736638531</v>
       </c>
       <c r="AD41" s="2" t="n">
-        <v>0.1517555631351573</v>
+        <v>0.1517556817830632</v>
       </c>
       <c r="AE41" s="2" t="n">
-        <v>0.01258961597726893</v>
+        <v>0.01258943709413662</v>
       </c>
       <c r="AF41" s="3" t="n">
-        <v>-0.1797882246488504</v>
+        <v>-0.1797883447396221</v>
       </c>
       <c r="AG41" s="2" t="n">
-        <v>0.09255578615815785</v>
+        <v>0.09255635451629285</v>
       </c>
       <c r="AH41" s="2" t="n">
-        <v>0.1059234291599083</v>
+        <v>0.1059232111424493</v>
       </c>
       <c r="AI41" s="2" t="n">
         <v>0.2560600839900984</v>
@@ -8529,55 +8529,55 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" s="3" t="n">
-        <v>-0.3528940725027419</v>
+        <v>-0.3528942643887052</v>
       </c>
       <c r="S42" s="2" t="n">
-        <v>0.3236167205378218</v>
+        <v>0.323616829914942</v>
       </c>
       <c r="T42" s="2" t="n">
-        <v>0.127797122444268</v>
+        <v>0.1277973721692272</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>-0.07821345670666457</v>
+        <v>-0.07821343938808167</v>
       </c>
       <c r="V42" s="2" t="n">
-        <v>0.1674765824646098</v>
+        <v>0.1674763020189789</v>
       </c>
       <c r="W42" s="2" t="n">
         <v>0.2237600194151326</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>0.03833511121281363</v>
+        <v>0.03833494307857332</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>-0.02209053438502606</v>
+        <v>-0.02209021410850276</v>
       </c>
       <c r="Z42" s="2" t="n">
-        <v>0.08396654959006633</v>
+        <v>0.08396645289420746</v>
       </c>
       <c r="AA42" s="2" t="n">
-        <v>0.2433339443655194</v>
+        <v>0.2433334675058072</v>
       </c>
       <c r="AB42" s="3" t="n">
-        <v>-0.09124921660347274</v>
+        <v>-0.0912489374768598</v>
       </c>
       <c r="AC42" s="2" t="n">
-        <v>0.2658966938316276</v>
+        <v>0.2658969642283999</v>
       </c>
       <c r="AD42" s="2" t="n">
-        <v>0.1633677953591557</v>
+        <v>0.1633672264613106</v>
       </c>
       <c r="AE42" s="2" t="n">
-        <v>0.1866169425663875</v>
+        <v>0.1866171775680756</v>
       </c>
       <c r="AF42" s="3" t="n">
-        <v>-0.1838555381260354</v>
+        <v>-0.18385547498485</v>
       </c>
       <c r="AG42" s="2" t="n">
-        <v>0.2227439973192393</v>
+        <v>0.222744092112753</v>
       </c>
       <c r="AH42" s="2" t="n">
-        <v>0.1744933299615026</v>
+        <v>0.1744932389086402</v>
       </c>
       <c r="AI42" s="2" t="n">
         <v>0.2241319038774059</v>
@@ -8785,76 +8785,76 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>0.02407807942076801</v>
+        <v>0.02407693938447042</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.02220308776997371</v>
+        <v>0.02220352030642392</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.006636849919984034</v>
+        <v>0.006635997205672428</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.01530306286277483</v>
+        <v>0.0153027869678648</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.03894008048443576</v>
+        <v>0.03894121290081642</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.07352691091885921</v>
+        <v>0.07352600998852465</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.0662258589137823</v>
+        <v>0.06622613197759231</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.003527029532931936</v>
+        <v>0.00352633106068212</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.02279578634000856</v>
+        <v>0.02279603700396526</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.01440408960572537</v>
+        <v>0.01440500565264879</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.002502481057429895</v>
+        <v>0.002502032726789505</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.002145830789932246</v>
+        <v>0.0021461658098334</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.00446999313053964</v>
+        <v>0.004469992135031964</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0.004298889558846719</v>
+        <v>0.00429811259301216</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>0.008225959618939571</v>
+        <v>0.008226736850610594</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0.002626845788069154</v>
+        <v>0.002627173664324856</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>0.01463261598550125</v>
+        <v>0.01463206201163025</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.0338070396328447</v>
+        <v>0.03380693201064222</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.03034034326855717</v>
+        <v>0.0303408669411025</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>-0.007155460822993231</v>
+        <v>-0.00715555896836928</v>
       </c>
       <c r="X2" s="3" t="n">
-        <v>-0.03880052706371206</v>
+        <v>-0.03880112581067618</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>0.04163715445300387</v>
+        <v>0.0416372735512569</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.03913802032115621</v>
+        <v>0.03913843484274504</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.04950313368855808</v>
+        <v>0.0495029283781987</v>
       </c>
       <c r="AB2" s="2" t="n">
         <v>0.005363816272516697</v>
@@ -8873,79 +8873,79 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>0.07574025073065327</v>
+        <v>0.07574003483134484</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.05308707400860646</v>
+        <v>0.0530858446839948</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.04119574709905161</v>
+        <v>0.04119686382214449</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.02638332282335809</v>
+        <v>0.02638332072639793</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.02516075050847388</v>
+        <v>0.02516098087248175</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.1037885383623991</v>
+        <v>0.1037873739497164</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.1791730313340436</v>
+        <v>0.1791740558568717</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.06593148111005254</v>
+        <v>-0.06593176363611253</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.09359818568879463</v>
+        <v>0.09359751968039176</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1564971537635804</v>
+        <v>0.1564971646128963</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.03663913526582729</v>
+        <v>0.03663975358192939</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.06090198412623193</v>
+        <v>-0.06090114264992652</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.09068154703301179</v>
+        <v>0.09068128111442397</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>0.0150789308971091</v>
+        <v>0.01507846124334478</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.01001593400537715</v>
+        <v>0.0100154782011157</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0.02552851701142966</v>
+        <v>0.02552925058714361</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0.009877459166623748</v>
+        <v>0.00987692849834243</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.08029497586226797</v>
+        <v>0.08029551975094829</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1000677965226611</v>
+        <v>0.1000673689461831</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>-0.03327870482624817</v>
+        <v>-0.03327826970656211</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>-0.1515515058242155</v>
+        <v>-0.1515518391279624</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>0.03644402855933815</v>
+        <v>0.03644421063322856</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.006342211301973877</v>
+        <v>-0.00634246954667439</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.08031959556926371</v>
+        <v>0.08031995677329751</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>-0.003056012402448904</v>
+        <v>-0.003056172631363707</v>
       </c>
     </row>
     <row r="4">
@@ -8961,76 +8961,76 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>0.1108229654052604</v>
+        <v>0.1108227661020644</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.01601608684339073</v>
+        <v>0.0160147447416461</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.08705267717873899</v>
+        <v>0.08705432548225378</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.08598846034851793</v>
+        <v>0.08598700858209929</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.007083671273060421</v>
+        <v>0.007084863990576507</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.1030425069807803</v>
+        <v>0.1030416466457675</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.3395182153187464</v>
+        <v>0.3395180254209917</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>-0.2180630404238304</v>
+        <v>-0.2180622876163734</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.09012705581421043</v>
+        <v>0.09012698825467003</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.3400113858998002</v>
+        <v>0.3400108395391883</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.02409436328397652</v>
+        <v>0.02409389003803852</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.133813433874693</v>
+        <v>-0.133813184941023</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.2730189552832523</v>
+        <v>0.27301945246586</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-0.0178954102572767</v>
+        <v>-0.01789622760844023</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.01171588899775022</v>
+        <v>0.01171606119592417</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>0.09182607830854983</v>
+        <v>0.09182634304065562</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.01611935992620395</v>
+        <v>-0.01611913021828926</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1411842705683324</v>
+        <v>0.1411847687080996</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.1815232519128727</v>
+        <v>0.1815226416529032</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>-0.04599161011310327</v>
+        <v>-0.04599200142101023</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>-0.3123454150481653</v>
+        <v>-0.3123450501935372</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.02767958273180215</v>
+        <v>0.027679310508685</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.08053079078398528</v>
+        <v>-0.08053103938940942</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.04247208659637991</v>
+        <v>0.04247227968828104</v>
       </c>
       <c r="AB4" s="3" t="n">
         <v>-0.001381006869054402</v>
@@ -9049,73 +9049,73 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>0.1074494639850645</v>
+        <v>0.1074488557867623</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.09110332908215102</v>
+        <v>0.09110497292665487</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.05713209196875435</v>
+        <v>0.05713127440138122</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.01159655951011929</v>
+        <v>0.01159591215613753</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.04218307063500504</v>
+        <v>0.04218317409676153</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.0373004470268643</v>
+        <v>0.03730054082258616</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.02423258028151909</v>
+        <v>0.02423266312068995</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.08447325695961672</v>
+        <v>0.08447292064120937</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.093164715093357</v>
+        <v>0.09316516998653834</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.09740703434904718</v>
+        <v>0.09740772148595855</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1024438060134991</v>
+        <v>0.1024426515844632</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.02001708680016023</v>
+        <v>-0.02001669650772597</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.0820998362043508</v>
+        <v>0.08210016100365269</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-0.0125549299528972</v>
+        <v>-0.01255511848220747</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.06204736584900528</v>
+        <v>0.06204737180966347</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>0.07054937313687737</v>
+        <v>0.07054937951833873</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.03787183321640919</v>
+        <v>-0.03787175192339665</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1736820686728688</v>
+        <v>0.1736819808541041</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.1097003843149116</v>
+        <v>0.1097006169929711</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-0.01841628858898892</v>
+        <v>-0.01841621867892607</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-0.1792165802892411</v>
+        <v>-0.1792168868152572</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.0940453169661859</v>
+        <v>0.09404516532689611</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.008583103640729783</v>
+        <v>0.008583412251941924</v>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.07895441603847231</v>
@@ -9142,61 +9142,61 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" s="2" t="n">
-        <v>0.01633933450773783</v>
+        <v>0.01633879269040839</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0.1755443198874899</v>
+        <v>-0.1755442641123141</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.2851900559137621</v>
+        <v>0.2851908520005568</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.1191320284358366</v>
+        <v>0.1191313214882228</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.06754699395671326</v>
+        <v>0.06754701409183195</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1105564789255851</v>
+        <v>0.1105564167197357</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.05753482750933236</v>
+        <v>0.05753400869083047</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.01894271947717208</v>
+        <v>0.01894218573715989</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-0.05021619068833816</v>
+        <v>-0.05021448381977744</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1341427323193736</v>
+        <v>0.1341430379087571</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>0.06073914818444814</v>
+        <v>0.06073890525836667</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.02024153567340503</v>
+        <v>-0.02024221223640454</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.1408870427118081</v>
+        <v>0.1408871807056815</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.04467509311066342</v>
+        <v>0.0446755966057284</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.03756141669713409</v>
+        <v>0.03756106256469716</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.1098285955836036</v>
+        <v>-0.1098280584454313</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.1154153493008745</v>
+        <v>0.1154146744590105</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.07966015746167376</v>
+        <v>0.07966074132233114</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.08592215175643592</v>
+        <v>0.08592181028894963</v>
       </c>
       <c r="AB6" s="2" t="n">
         <v>0.01603903544942664</v>
@@ -9216,73 +9216,73 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="3" t="n">
-        <v>-0.0002232737019952635</v>
+        <v>-0.0002246263023196748</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.08278674433706379</v>
+        <v>0.08278748929985347</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.02490391134255043</v>
+        <v>0.0249042619037767</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.002772550040928135</v>
+        <v>0.002771736671401737</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.1192700402942384</v>
+        <v>0.1192701803474585</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.0005348712455741644</v>
+        <v>0.0005355956895258807</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.089320079622631</v>
+        <v>0.08931969617370195</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.06131263558231415</v>
+        <v>0.06131264237217371</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1329575071637363</v>
+        <v>0.1329576253810512</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.06397170947002784</v>
+        <v>0.06397143317373533</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.08490580573499706</v>
+        <v>-0.08490504873185512</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.03590807588572176</v>
+        <v>0.03590748794959797</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>-0.01754166651447686</v>
+        <v>-0.0175411186313148</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.04681360596114725</v>
+        <v>0.04681311513379827</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>0.02920194612162108</v>
+        <v>0.02920212110439202</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.01425268944427249</v>
+        <v>-0.01425285829269363</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.08349621502448601</v>
+        <v>0.08349629523314017</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.1083794008398486</v>
+        <v>0.1083794641036173</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.05677149872387122</v>
+        <v>0.05677148631241669</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>-0.1226251948087771</v>
+        <v>-0.1226253763170364</v>
       </c>
       <c r="Y7" s="2" t="n">
         <v>0.0380484789827813</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.01652273067994425</v>
+        <v>0.01652265496401228</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0.06764748820898769</v>
+        <v>0.0676475677329651</v>
       </c>
       <c r="AB7" s="2" t="n">
         <v>0.01694170652616767</v>
@@ -9306,64 +9306,64 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" s="2" t="n">
-        <v>0.06098698217975751</v>
+        <v>0.06098668299016219</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.06863978376335322</v>
+        <v>0.0686386477248091</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.03636589479931507</v>
+        <v>0.03636690643970719</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.06198615565131949</v>
+        <v>0.06198701904914627</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.07929638589907073</v>
+        <v>0.0792956562472793</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.02941085836350865</v>
+        <v>0.02941037498109966</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.02107552589529593</v>
+        <v>-0.02107513376890202</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.05817849753490223</v>
+        <v>0.05817842562649655</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.005590562978136759</v>
+        <v>0.005590241884404046</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.02521522678064358</v>
+        <v>0.02521510710859753</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>0.03999358900607985</v>
+        <v>0.03999398019119127</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0.001160237682514609</v>
+        <v>0.001159698691568511</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.0883375546691707</v>
+        <v>0.08833868439022541</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.07715151637085516</v>
+        <v>0.07715038303803512</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>-0.01861162535342886</v>
+        <v>-0.01861082022295302</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>-0.1311216249791867</v>
+        <v>-0.1311218057086256</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.05654331336219176</v>
+        <v>0.05654415123685563</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.01382699920164154</v>
+        <v>0.01382608191263301</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0.07082348576530539</v>
+        <v>0.07082371717043934</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.004784245113304664</v>
+        <v>0.004784140259367353</v>
       </c>
     </row>
     <row r="9">
@@ -9391,40 +9391,40 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" s="3" t="n">
-        <v>-0.01674932541747975</v>
+        <v>-0.01675067105674644</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.005772655121781378</v>
+        <v>0.005774039820085175</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>-0.06821487320132924</v>
+        <v>-0.06821535087798047</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>0.06960286896771861</v>
+        <v>0.06960228641358834</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0.01891175964073288</v>
+        <v>0.0189117656534552</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.02677182503938913</v>
+        <v>0.0267717293816172</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.1201479945180763</v>
+        <v>0.1201489548976962</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.05932101766502229</v>
+        <v>0.05932035780389722</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>-0.0799098119192132</v>
+        <v>-0.07990965482333956</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.0292434378392421</v>
+        <v>0.02924325227089275</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.01844039197405678</v>
+        <v>0.01844066574265013</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>0.05454751937475355</v>
+        <v>0.05454742603077611</v>
       </c>
       <c r="AB9" s="2" t="n">
         <v>0.05353290893049767</v>
@@ -9464,16 +9464,16 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" s="2" t="n">
-        <v>0.05763602100063836</v>
+        <v>0.05763620975121597</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.0723133127477249</v>
+        <v>0.07231322837817178</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>0.130728224597255</v>
+        <v>0.130728392242849</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.07256361630083652</v>
+        <v>0.0725635416681889</v>
       </c>
     </row>
     <row r="11">
@@ -9507,31 +9507,31 @@
         <v>0</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>0.002114986867047142</v>
+        <v>0.002114986596470692</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>0.01978321817501016</v>
+        <v>0.0197831518179834</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-0.008908007899506964</v>
+        <v>-0.008908195121389406</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.0019942059651743</v>
+        <v>-0.00199407990554934</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>-0.05485291851594976</v>
       </c>
       <c r="Y11" s="2" t="n">
-        <v>0.00537370945840232</v>
+        <v>0.005373776413004849</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-0.02804042048643318</v>
+        <v>-0.02804055181248655</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>-0.06433319922075842</v>
+        <v>-0.06433313511073158</v>
       </c>
       <c r="AB11" s="3" t="n">
-        <v>-0.02781422957897683</v>
+        <v>-0.02721433707924414</v>
       </c>
     </row>
     <row r="12">
@@ -9561,28 +9561,28 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" s="3" t="n">
-        <v>-0.07010000678328188</v>
+        <v>-0.070099937292742</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>0.01062886773815896</v>
+        <v>0.01062873456771918</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>-0.02562574740790513</v>
+        <v>-0.02562574574604959</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>0.0586587040157307</v>
+        <v>0.05865843388533354</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>0.07699111060704333</v>
+        <v>0.07699143947197773</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>-0.03904807603623417</v>
+        <v>-0.03904824660076811</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>-0.1760430294129653</v>
+        <v>-0.1760431008534579</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>-0.02930264472630617</v>
+        <v>-0.02930250159633774</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>-0.07088518626650075</v>
@@ -9621,10 +9621,10 @@
         <v>-0.03453021553229296</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>0.07395264223481979</v>
+        <v>0.07395256071870482</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>0.07222631085818243</v>
+        <v>0.07222639224326999</v>
       </c>
       <c r="R13" s="2" t="n">
         <v>0.007956653870195174</v>
@@ -9636,10 +9636,10 @@
         <v>0.06588596031594207</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>0.02794326513582424</v>
+        <v>0.0279433318287412</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>0.01219016575531962</v>
+        <v>0.0121901000844673</v>
       </c>
       <c r="W13" s="2" t="n">
         <v>0.04259267758257046</v>
@@ -9695,19 +9695,19 @@
         <v>0.02442489390220404</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>0.02313273275378513</v>
+        <v>0.02313281465174089</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>0.04735272987786932</v>
+        <v>0.04735264604120015</v>
       </c>
       <c r="X14" s="2" t="n">
         <v>0.02326475416188289</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>0.0368264511105072</v>
+        <v>0.03682637642091358</v>
       </c>
       <c r="Z14" s="2" t="n">
-        <v>0.08715292520295992</v>
+        <v>0.08715300351791422</v>
       </c>
       <c r="AA14" s="2" t="n">
         <v>0.0013103938430572</v>
@@ -9738,52 +9738,52 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="2" t="n">
-        <v>0.0126422005693172</v>
+        <v>0.01264230328461657</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.07427093089637227</v>
+        <v>0.07427081290470516</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>0.00606375545074811</v>
+        <v>0.006063659241629438</v>
       </c>
       <c r="P15" s="2" t="n">
         <v>0.1116451181792431</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>0.06599237384670986</v>
+        <v>0.06599245935320486</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>0.01668343119324933</v>
+        <v>0.01668342985502047</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>-0.01414974245330636</v>
+        <v>-0.01414974133693736</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>0.06784160690888608</v>
+        <v>0.06784160147957907</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>0.03752066134283827</v>
+        <v>0.03752065853086028</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>0.01424616176527849</v>
+        <v>0.01424601626720978</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>-0.02436938342086259</v>
+        <v>-0.02436931393654551</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>-0.09188290198687499</v>
+        <v>-0.09188297498570863</v>
       </c>
       <c r="Y15" s="2" t="n">
-        <v>0.0808086938438648</v>
+        <v>0.08080886110932028</v>
       </c>
       <c r="Z15" s="2" t="n">
-        <v>0.0429316811836169</v>
+        <v>0.04293160361588955</v>
       </c>
       <c r="AA15" s="3" t="n">
         <v>-0.003396429509450627</v>
       </c>
       <c r="AB15" s="3" t="n">
-        <v>-0.0348507052573731</v>
+        <v>-0.03562923612383218</v>
       </c>
     </row>
     <row r="16">
@@ -9806,58 +9806,58 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" s="2" t="n">
-        <v>0.01436424799224589</v>
+        <v>0.01436481980241511</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0.06902204965535885</v>
+        <v>0.0690219143451456</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0.04519876146862112</v>
+        <v>0.0451989617109414</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.04353753180840281</v>
+        <v>0.04353731368439973</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>0.01772310250530418</v>
+        <v>0.01772261839546663</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>0.05074563108043439</v>
+        <v>0.05074611779275906</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>0.03151780983892727</v>
+        <v>0.03151780417177652</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>0.01359587566292664</v>
+        <v>0.01359604760686639</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>0.002895383878270152</v>
+        <v>0.002894780967449329</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>0.03204947382446255</v>
+        <v>0.03204973928715193</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>0.02503934113914252</v>
+        <v>0.02503925806208818</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>0.01620807596306717</v>
+        <v>0.01620823937205551</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.003968528996405318</v>
+        <v>-0.003968369169910058</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.0220314621928408</v>
+        <v>-0.02203169711873421</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>0.04948009566793199</v>
+        <v>0.04948017754456391</v>
       </c>
       <c r="Z16" s="2" t="n">
-        <v>0.03383835412911806</v>
+        <v>0.03383827347280421</v>
       </c>
       <c r="AA16" s="2" t="n">
         <v>0.01422051870738805</v>
       </c>
       <c r="AB16" s="3" t="n">
-        <v>-0.005619047619047635</v>
+        <v>-0.006285714285714339</v>
       </c>
     </row>
     <row r="17">
@@ -9921,31 +9921,31 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>0.07304636418694255</v>
+        <v>0.07304624091304968</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>-0.04993660760734941</v>
+        <v>-0.04993631844604485</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0.03421354964926548</v>
+        <v>0.0342134198509938</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0.11980125382556</v>
+        <v>0.1198010111206771</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.001688182010685768</v>
+        <v>0.00168850748552507</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>-0.04126543720091713</v>
+        <v>-0.04126564911048125</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>0.1366926624289411</v>
+        <v>0.1366929035408948</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>0.002968180045697544</v>
+        <v>0.002967981203943815</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>0.1033639758192431</v>
+        <v>0.1033640850299622</v>
       </c>
       <c r="S18" s="2" t="n">
         <v>0.01385017397378707</v>
@@ -9954,19 +9954,19 @@
         <v>0.005344122447455524</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>0.06696464404655456</v>
+        <v>0.06696455603512019</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>0.08075964221135279</v>
+        <v>0.08075981384839515</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>-0.05032493328918763</v>
+        <v>-0.05032492944819811</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>-0.2371004619330206</v>
+        <v>-0.2371002821410184</v>
       </c>
       <c r="Y18" s="2" t="n">
-        <v>0.03560406382274928</v>
+        <v>0.03560373653298177</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>-0.01317601634828214</v>
@@ -9997,52 +9997,52 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" s="2" t="n">
-        <v>0.07667566527936676</v>
+        <v>0.07667560806784501</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-0.1139713456930488</v>
+        <v>-0.113971358811121</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0.1537613107642108</v>
+        <v>0.1537617204542447</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>-0.1085549797310473</v>
+        <v>-0.1085551241751737</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.04030697602983602</v>
+        <v>0.04030697348437662</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>0.01435005551776003</v>
+        <v>0.01435011535163855</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>0.08081470076567832</v>
+        <v>0.0808145714003754</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>-0.03988666585086165</v>
+        <v>-0.03988655510809325</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>0.2115572736088112</v>
+        <v>0.2115573645504918</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>0.04562024129676634</v>
+        <v>0.04561994700261263</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>0.02049930698091429</v>
+        <v>0.02049939989631344</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>0.01386496677580951</v>
+        <v>0.01386505599581156</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>0.0999945352070386</v>
+        <v>0.09999435040777382</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>-0.09545107125994223</v>
+        <v>-0.09545099889575581</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>-0.153913920978666</v>
+        <v>-0.1539138325364692</v>
       </c>
       <c r="Y19" s="2" t="n">
-        <v>0.06627765118496831</v>
+        <v>0.06627753972594497</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>-0.03527030933795894</v>
@@ -10131,49 +10131,49 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" s="2" t="n">
-        <v>0.03090599460068466</v>
+        <v>0.03090578397901278</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>0.003820437269439036</v>
+        <v>0.003820645972737458</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>0.0931630807414332</v>
+        <v>0.09316319373311188</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>0.02932531521692883</v>
+        <v>0.02932559887670738</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>0.01815556141006458</v>
+        <v>0.01815528082850593</v>
       </c>
       <c r="S21" s="2" t="n">
         <v>0.02975547917008203</v>
       </c>
       <c r="T21" s="2" t="n">
-        <v>0.05245922293367089</v>
+        <v>0.05245896009040396</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>0.07376046595862595</v>
+        <v>0.07376081736912732</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>0.03881772651988769</v>
+        <v>0.03881780103916466</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.03269258253803886</v>
+        <v>-0.03269272692168679</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.1024399754557358</v>
+        <v>-0.1024398211475238</v>
       </c>
       <c r="Y21" s="2" t="n">
-        <v>0.03880871367907113</v>
+        <v>0.03880836316783576</v>
       </c>
       <c r="Z21" s="2" t="n">
-        <v>0.0189987998162322</v>
+        <v>0.01899896845743765</v>
       </c>
       <c r="AA21" s="2" t="n">
         <v>0.02618370847234042</v>
       </c>
       <c r="AB21" s="2" t="n">
-        <v>0.01046020171166084</v>
+        <v>0.009630406311699424</v>
       </c>
     </row>
     <row r="22">
@@ -10204,31 +10204,31 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" s="3" t="n">
-        <v>-0.001187659913960304</v>
+        <v>-0.001187109279565224</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>-0.01220486960268563</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>0.06404403954335569</v>
+        <v>0.06404394641602251</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>0.07646242808968218</v>
+        <v>0.07646208469353577</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>-0.03519103404528023</v>
+        <v>-0.03519072313016303</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>-0.1227811064762145</v>
+        <v>-0.1227812010939368</v>
       </c>
       <c r="Y22" s="2" t="n">
-        <v>0.05610893799309435</v>
+        <v>0.05610933303719401</v>
       </c>
       <c r="Z22" s="2" t="n">
-        <v>0.0324612035109566</v>
+        <v>0.03246119760547672</v>
       </c>
       <c r="AA22" s="2" t="n">
-        <v>0.01883290970842566</v>
+        <v>0.01883273018554688</v>
       </c>
       <c r="AB22" s="2" t="n">
         <v>0.01736486671119475</v>
@@ -10252,61 +10252,61 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" s="2" t="n">
-        <v>0.03976892687083455</v>
+        <v>0.03976912955065814</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.0418862811642573</v>
+        <v>0.04188646897106119</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.05430216452280123</v>
+        <v>0.05430198317023871</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0.03831609824406979</v>
+        <v>0.03831635265004341</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0.03955924604939787</v>
+        <v>0.0395595622395748</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.05660899152567489</v>
+        <v>0.0566084221605494</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>-0.03584828100738868</v>
+        <v>-0.03584821022151607</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>-0.02524054432383771</v>
+        <v>-0.02524069661888995</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>-0.06687144859898508</v>
+        <v>-0.06687177152413593</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>0.006391588991367714</v>
+        <v>0.006391927072541659</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>0.09935045100082651</v>
+        <v>0.09935046752994814</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>-0.01754466810466615</v>
+        <v>-0.01754459509155104</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>0.05583977903403481</v>
+        <v>0.05584001439341191</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>0.095015386913752</v>
+        <v>0.09501508126683378</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>-0.08601232660774072</v>
+        <v>-0.08601240468408222</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>-0.1972168159256414</v>
+        <v>-0.1972164946199411</v>
       </c>
       <c r="Y23" s="2" t="n">
-        <v>0.05097557025082722</v>
+        <v>0.05097556099455636</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>-0.05929981983865384</v>
+        <v>-0.0592997232055289</v>
       </c>
       <c r="AA23" s="2" t="n">
-        <v>0.07667382721527627</v>
+        <v>0.07667353059182225</v>
       </c>
       <c r="AB23" s="3" t="n">
         <v>-0.008593748667288792</v>
@@ -10332,31 +10332,31 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" s="2" t="n">
-        <v>0.1060399944677339</v>
+        <v>0.1060405219600065</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0.01789038803111653</v>
+        <v>0.01789056050932114</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0.01572940169458592</v>
+        <v>0.0157293990292906</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.05283884300105735</v>
+        <v>0.0528388341863395</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>-0.01371285051600946</v>
+        <v>-0.01371300679355902</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>-0.02220872555186648</v>
+        <v>-0.02220880587856477</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>-0.07150166836705896</v>
+        <v>-0.07150150993864945</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>0.008557805065405155</v>
+        <v>0.008557538875885173</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>0.1137556619914473</v>
+        <v>0.1137558574037187</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>-0.0259823332893816</v>
@@ -10406,55 +10406,55 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" s="2" t="n">
-        <v>0.1297391524057825</v>
+        <v>0.1297397548836288</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0.01592498336150006</v>
+        <v>0.01592413209307697</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-0.005031603755049741</v>
+        <v>-0.005031604946103663</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0298675403414792</v>
+        <v>0.02986730953566541</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-0.02179850801004668</v>
+        <v>-0.02179840257550592</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-0.09763216769988536</v>
+        <v>-0.09763208420515679</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>-0.0772496874677564</v>
+        <v>-0.07724983854050427</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>-0.01485378956767469</v>
+        <v>-0.0148536540764731</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>0.1018644293600715</v>
+        <v>0.1018649625067791</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>-0.03365793684791396</v>
+        <v>-0.03365786493180778</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>0.00998096237737478</v>
+        <v>0.009980824487551221</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>0.06464361961543275</v>
+        <v>0.06464327632464251</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>-0.06845501730484471</v>
+        <v>-0.0684547158956037</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>-0.1055745086498228</v>
+        <v>-0.1055744269173523</v>
       </c>
       <c r="Y25" s="2" t="n">
-        <v>0.02962455946328069</v>
+        <v>0.02962432641119972</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>-0.05285906494100712</v>
+        <v>-0.05285899166293373</v>
       </c>
       <c r="AA25" s="2" t="n">
-        <v>0.1044491972254722</v>
+        <v>0.104449111776834</v>
       </c>
       <c r="AB25" s="2" t="n">
         <v>0.001908326494614698</v>
@@ -10484,46 +10484,46 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>-0.004959120517212257</v>
+        <v>-0.004958906272579333</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>0.08740337452654146</v>
+        <v>0.08740314039516917</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>0.0118975865444626</v>
+        <v>0.01189778455046309</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>0.04612500022013766</v>
+        <v>0.04612459983876138</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>0.02396842742021477</v>
+        <v>0.02396843190351494</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>0.02812297177153522</v>
+        <v>0.02812261156503038</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>0.07866085562467418</v>
+        <v>0.07866178592892381</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>0.0465198044432249</v>
+        <v>0.04651962439973611</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.02285912065267792</v>
+        <v>-0.02285943184706762</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.1275696619337031</v>
+        <v>-0.1275693603257648</v>
       </c>
       <c r="Y26" s="2" t="n">
-        <v>0.08783917766517702</v>
+        <v>0.08783888449978394</v>
       </c>
       <c r="Z26" s="2" t="n">
-        <v>0.03558521414375893</v>
+        <v>0.03558555661029184</v>
       </c>
       <c r="AA26" s="2" t="n">
-        <v>0.02865646471032424</v>
+        <v>0.02865629377431422</v>
       </c>
       <c r="AB26" s="2" t="n">
-        <v>0.009281030797943624</v>
+        <v>0.00928095039583221</v>
       </c>
     </row>
     <row r="27">
@@ -10544,58 +10544,58 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" s="2" t="n">
-        <v>0.002877017614374866</v>
+        <v>0.002876650503059741</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.02127095055325512</v>
+        <v>-0.02126958852192795</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.1537348387827677</v>
+        <v>0.1537335990697664</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0.1083821312839628</v>
+        <v>0.1083822477142831</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.07648791058339</v>
+        <v>0.07648822050759563</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1652157599725104</v>
+        <v>0.1652156806553313</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-0.07792997891071818</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>0.06044665775199487</v>
+        <v>0.06044691117770862</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>0.01034670584666753</v>
+        <v>0.01034706184416767</v>
       </c>
       <c r="R27" s="2" t="n">
-        <v>0.09266682009762661</v>
+        <v>0.09266641050176738</v>
       </c>
       <c r="S27" s="2" t="n">
-        <v>0.1028439243994148</v>
+        <v>0.1028435774271133</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>-0.05470837917023375</v>
+        <v>-0.05470838453948224</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>0.1547703787008248</v>
+        <v>0.1547700833003609</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>0.05421423359977551</v>
+        <v>0.05421470263693862</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>-0.02228172794943528</v>
+        <v>-0.02228206718648607</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>-0.1862516047758338</v>
+        <v>-0.1862515662869197</v>
       </c>
       <c r="Y27" s="2" t="n">
-        <v>0.1061576983315127</v>
+        <v>0.1061580426685127</v>
       </c>
       <c r="Z27" s="2" t="n">
-        <v>0.05536491554250644</v>
+        <v>0.05536481327186427</v>
       </c>
       <c r="AA27" s="2" t="n">
         <v>0.1385588865029508</v>
@@ -10625,52 +10625,52 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" s="2" t="n">
-        <v>0.06702317309589501</v>
+        <v>0.06702290013833778</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>-0.03062333722261745</v>
+        <v>-0.03062259166488657</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.1687345054064209</v>
+        <v>0.1687338875253115</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>-0.09941681915209633</v>
+        <v>-0.09941695907302417</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>-0.05054688764524407</v>
+        <v>-0.05054689177730243</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>-0.1507042000074562</v>
+        <v>-0.1507036102893911</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>0.09003606892785387</v>
+        <v>0.09003550727759801</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>0.138335797922305</v>
+        <v>0.1383354130432175</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>-0.07568019485400335</v>
+        <v>-0.07568013170230536</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>0.09788973681970514</v>
+        <v>0.0978893121718003</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>0.03079923976468346</v>
+        <v>0.03079949865082066</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>-0.09713971513135722</v>
+        <v>-0.09713927685533907</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>-0.1046313224487578</v>
+        <v>-0.1046316503750435</v>
       </c>
       <c r="Y28" s="2" t="n">
-        <v>0.1117538354041603</v>
+        <v>0.1117542434642154</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>-0.0295901003303326</v>
+        <v>-0.02959018209175701</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>0.1881363902543693</v>
+        <v>0.1881362838515546</v>
       </c>
       <c r="AB28" s="2" t="n">
         <v>0.01244075146196955</v>
@@ -10698,43 +10698,43 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="3" t="n">
-        <v>-0.02139336974558415</v>
+        <v>-0.02139327637319743</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.1120099771238627</v>
+        <v>0.1120102038787585</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.06728693130374308</v>
+        <v>-0.06728702299105083</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.02926000129168471</v>
+        <v>-0.02925980756451541</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.1211041177684574</v>
+        <v>-0.1211041055048822</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>0.06274802141674507</v>
+        <v>0.06274766853270086</v>
       </c>
       <c r="S29" s="2" t="n">
-        <v>0.1248541814472832</v>
+        <v>0.1248544253501001</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>-0.04262988460901973</v>
+        <v>-0.04262978822738861</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>0.06397246061105899</v>
+        <v>0.06397235349742614</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>0.03098651813056152</v>
+        <v>0.03098642351032743</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>-0.09920065506325371</v>
+        <v>-0.09920057239112245</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>-0.1073718471196371</v>
+        <v>-0.1073717452363447</v>
       </c>
       <c r="Y29" s="2" t="n">
-        <v>0.07230746280138711</v>
+        <v>0.07230734040977116</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>-0.01715685517936705</v>
@@ -10770,46 +10770,46 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>-0.01826262429650127</v>
+        <v>-0.01826227593933627</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>0.04168450905479437</v>
+        <v>0.04168396814869024</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>0.01593283186667471</v>
+        <v>0.01593327733138605</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>0.08980066019691635</v>
+        <v>0.08980101873234658</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>0.08413867897706262</v>
+        <v>0.08413905929955257</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>-0.02924586063787515</v>
+        <v>-0.02924599098365199</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>0.1446498037304527</v>
+        <v>0.1446494504686586</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>0.05648946199305138</v>
+        <v>0.05648978500514845</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>-0.0179918300198838</v>
+        <v>-0.01799194703727314</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>-0.1739022465050947</v>
+        <v>-0.1739024546157918</v>
       </c>
       <c r="Y30" s="2" t="n">
         <v>0.106809778655091</v>
       </c>
       <c r="Z30" s="2" t="n">
-        <v>0.05206133593905093</v>
+        <v>0.05206140481992549</v>
       </c>
       <c r="AA30" s="2" t="n">
-        <v>0.1349476401655532</v>
+        <v>0.134947434913337</v>
       </c>
       <c r="AB30" s="2" t="n">
-        <v>0.01698366335971113</v>
+        <v>0.01698378069422768</v>
       </c>
     </row>
     <row r="31">
@@ -10835,46 +10835,46 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" s="2" t="n">
-        <v>0.09223240313932668</v>
+        <v>0.09223132984903493</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0.04946369412785345</v>
+        <v>-0.04946321711273316</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>0.04094796373464615</v>
+        <v>0.04094917276019405</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.01769777693845842</v>
+        <v>-0.01769942882234321</v>
       </c>
       <c r="R31" s="2" t="n">
-        <v>0.1229753015959041</v>
+        <v>0.1229756435743787</v>
       </c>
       <c r="S31" s="2" t="n">
-        <v>0.07107384233144698</v>
+        <v>0.07107363424300339</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.02553464106127723</v>
+        <v>-0.02553389381850191</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>0.1388966933784777</v>
+        <v>0.1388963276382269</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>0.06765220442954112</v>
+        <v>0.06765270092329878</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.005900215271552378</v>
+        <v>-0.005900396635785565</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.1258746571388324</v>
+        <v>-0.125875003138528</v>
       </c>
       <c r="Y31" s="2" t="n">
-        <v>0.08369131639521421</v>
+        <v>0.08369154527589506</v>
       </c>
       <c r="Z31" s="2" t="n">
-        <v>0.0581171141735195</v>
+        <v>0.05811721162038253</v>
       </c>
       <c r="AA31" s="2" t="n">
-        <v>0.08865716047878514</v>
+        <v>0.08865706021935815</v>
       </c>
       <c r="AB31" s="2" t="n">
         <v>0.01610361019589091</v>
@@ -10903,46 +10903,46 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" s="2" t="n">
-        <v>0.1807587177518248</v>
+        <v>0.18075887698767</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>-0.06275647516885974</v>
+        <v>-0.06275562895376896</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>0.01644466509363651</v>
+        <v>0.0164440695452015</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>0.02038772607180306</v>
+        <v>0.02038739576527071</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>0.1413275969197347</v>
+        <v>0.1413270674427585</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>0.08537742753933752</v>
+        <v>0.08537833432509623</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>-0.05211773364239813</v>
+        <v>-0.05211753187660906</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>0.1298231767567297</v>
+        <v>0.1298224465397355</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>0.03822552545963975</v>
+        <v>0.03822608328336385</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>-0.01903335777224668</v>
+        <v>-0.0190334702356435</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>-0.1301556367134692</v>
+        <v>-0.1301559787483514</v>
       </c>
       <c r="Y32" s="2" t="n">
-        <v>0.1145815606918201</v>
+        <v>0.1145815235828866</v>
       </c>
       <c r="Z32" s="2" t="n">
-        <v>0.119705464082829</v>
+        <v>0.119705685266795</v>
       </c>
       <c r="AA32" s="2" t="n">
-        <v>0.1369728350436292</v>
+        <v>0.1369729598696245</v>
       </c>
       <c r="AB32" s="2" t="n">
         <v>0.02872294764184313</v>
@@ -11360,46 +11360,46 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" s="2" t="n">
-        <v>0.3372272378631023</v>
+        <v>0.337227298612917</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>-0.1912623351683717</v>
+        <v>-0.1912623774931489</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.009931215894420475</v>
+        <v>0.00993121505269623</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0.2235249895705973</v>
+        <v>0.2235248029680177</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>-0.1072642840539101</v>
+        <v>-0.1072642228208786</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>-0.03220220050329314</v>
+        <v>-0.03220212367168718</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>-0.1323792209648033</v>
+        <v>-0.1323792898435427</v>
       </c>
       <c r="P38" s="2" t="n">
         <v>0.02639169428087396</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>-0.1719565677473143</v>
+        <v>-0.1719564785991906</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>-0.03105281856939834</v>
+        <v>-0.03105313820968758</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>-0.06059098648006456</v>
+        <v>-0.06059066661022205</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>-0.08735167337461081</v>
+        <v>-0.08735172218185649</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>-0.007078229950685078</v>
+        <v>-0.007078229492020194</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>-0.02536230630851699</v>
+        <v>-0.02536236991464347</v>
       </c>
       <c r="W38" s="2" t="n">
         <v>0.2236679534507875</v>
@@ -11649,43 +11649,43 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" s="2" t="n">
-        <v>0.04057496342900624</v>
+        <v>0.04057537320369864</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0.3157874321105087</v>
+        <v>0.3157873063980494</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>-0.3179922619111587</v>
+        <v>-0.3179921892994099</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.1618689157740953</v>
+        <v>0.1618687920726765</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0.1190089622504922</v>
+        <v>0.1190088706156869</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>-0.02577128414218754</v>
+        <v>-0.02577128625257885</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.03502221501960268</v>
+        <v>0.03502230201888645</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>-0.07631382373353868</v>
+        <v>-0.07631390494480805</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>-0.2809819650607837</v>
+        <v>-0.2809820776858106</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>-0.2758808662077004</v>
+        <v>-0.2758806891184515</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>0.1856287490875963</v>
+        <v>0.185628580221662</v>
       </c>
       <c r="S42" s="2" t="n">
-        <v>0.04861101665409873</v>
+        <v>0.0486112372186589</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>-0.1163029291218244</v>
+        <v>-0.1163029891357866</v>
       </c>
       <c r="U42" s="2" t="n">
         <v>0.1183924026420207</v>
@@ -11694,13 +11694,13 @@
         <v>-0.07836996023877618</v>
       </c>
       <c r="W42" s="2" t="n">
-        <v>0.4136056850231622</v>
+        <v>0.4136055359070183</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>0.1933989367184052</v>
+        <v>0.1933991680921394</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>-0.06194497290312928</v>
+        <v>-0.06194505581925702</v>
       </c>
       <c r="Z42" s="2" t="n">
         <v>0.02184255034418392</v>
@@ -11773,7 +11773,7 @@
         <v>-0.06336749968935373</v>
       </c>
       <c r="AB43" s="3" t="n">
-        <v>-0.156336458910842</v>
+        <v>-0.1560762173102178</v>
       </c>
     </row>
     <row r="44">
@@ -11831,7 +11831,7 @@
         <v>-0.109674616576496</v>
       </c>
       <c r="AB44" s="3" t="n">
-        <v>-0.3211713977124634</v>
+        <v>-0.3214073068133214</v>
       </c>
     </row>
     <row r="45">
@@ -11855,46 +11855,46 @@
         <v>-0.04294150302825317</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.04877488879906089</v>
+        <v>0.04877498578226258</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>-0.06520852396225818</v>
+        <v>-0.06520861040508097</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>-0.01603134529733985</v>
+        <v>-0.01603124637383524</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>-0.01056786011690436</v>
+        <v>-0.0105679595896716</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>-0.02937262431786059</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>-0.01329641901678413</v>
+        <v>-0.01329652370063261</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>0.1138474893313997</v>
+        <v>0.1138475014099964</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>0.07008750567812028</v>
+        <v>0.07008770285500043</v>
       </c>
       <c r="R45" s="2" t="n">
-        <v>0.03157901014521758</v>
+        <v>0.03157882931057543</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>-0.09098103074846475</v>
+        <v>-0.0909808660248983</v>
       </c>
       <c r="T45" s="2" t="n">
-        <v>0.07048277670192848</v>
+        <v>0.07048277001147629</v>
       </c>
       <c r="U45" s="2" t="n">
-        <v>0.04086109568442176</v>
+        <v>0.04086091471456865</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>-0.06661530710355068</v>
+        <v>-0.06661531277865851</v>
       </c>
       <c r="W45" s="2" t="n">
-        <v>0.057343150468816</v>
+        <v>0.05734324697505055</v>
       </c>
       <c r="X45" s="2" t="n">
         <v>0.09460674155363535</v>
@@ -11928,70 +11928,70 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" s="3" t="n">
-        <v>-0.008782288555969298</v>
+        <v>-0.008782363429013396</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0.1397101174292168</v>
+        <v>0.1397102227749085</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0.1425701117529663</v>
+        <v>0.1425703908563387</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-0.01180334088998891</v>
+        <v>-0.01180311152210844</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.02528742846304399</v>
+        <v>0.02528776582912529</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.06865389601212057</v>
+        <v>-0.06865474987773912</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.02926406125109415</v>
+        <v>-0.02926382667798777</v>
       </c>
       <c r="N46" s="2" t="n">
         <v>0.0158235599568457</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>0.03840890419644816</v>
+        <v>0.03840878167062733</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-0.123905887666827</v>
+        <v>-0.1239060202807781</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-0.1069333309629361</v>
+        <v>-0.106933023062624</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.03890961243080737</v>
+        <v>-0.03890983570894979</v>
       </c>
       <c r="S46" s="2" t="n">
-        <v>0.1305492953602636</v>
+        <v>0.130549551215519</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-0.05302286493118591</v>
+        <v>-0.0530231388396305</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-0.02904654322296796</v>
+        <v>-0.02904603662991634</v>
       </c>
       <c r="V46" s="2" t="n">
-        <v>0.07939777919435898</v>
+        <v>0.07939767974924195</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.07826387079140007</v>
+        <v>-0.07826378445081339</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.06566296857606646</v>
+        <v>-0.06566370725441628</v>
       </c>
       <c r="Y46" s="2" t="n">
-        <v>0.04866894041111047</v>
+        <v>0.04866985722851425</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.04182743012644652</v>
+        <v>-0.04182787847518177</v>
       </c>
       <c r="AA46" s="2" t="n">
-        <v>0.1452336718345226</v>
+        <v>0.1452336835698838</v>
       </c>
       <c r="AB46" s="3" t="n">
-        <v>-0.003997077563455576</v>
+        <v>-0.003997007289299526</v>
       </c>
     </row>
     <row r="47">
@@ -12089,67 +12089,67 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" s="2" t="n">
-        <v>0.09680830611466473</v>
+        <v>0.09680906235137043</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0.06548008499468261</v>
+        <v>0.06547950664942448</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>-0.2383407116604315</v>
+        <v>-0.2383407742957512</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.1061122651175774</v>
+        <v>0.1061125317516418</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>-0.03326534238728596</v>
+        <v>-0.03326503391333424</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>-0.01072069794028074</v>
+        <v>-0.01072080318957791</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.04289403190070562</v>
+        <v>0.04289424467924796</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>0.0161160111780323</v>
+        <v>0.01611590188846601</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>-0.06270682694747309</v>
+        <v>-0.06270681408054746</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>-0.05710123114897203</v>
+        <v>-0.05710209432651436</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>-0.1667131988431539</v>
+        <v>-0.1667126184322109</v>
       </c>
       <c r="S48" s="2" t="n">
-        <v>0.09096959121764003</v>
+        <v>0.09096931258946572</v>
       </c>
       <c r="T48" s="3" t="n">
-        <v>-0.05754566430600816</v>
+        <v>-0.0575455513053561</v>
       </c>
       <c r="U48" s="2" t="n">
-        <v>0.03865749756465342</v>
+        <v>0.03865770604450414</v>
       </c>
       <c r="V48" s="2" t="n">
-        <v>0.02873133252618532</v>
+        <v>0.02873106974879636</v>
       </c>
       <c r="W48" s="3" t="n">
-        <v>-0.01536453967692786</v>
+        <v>-0.01536460600362688</v>
       </c>
       <c r="X48" s="3" t="n">
-        <v>-0.1045398795287089</v>
+        <v>-0.1045395200941691</v>
       </c>
       <c r="Y48" s="2" t="n">
-        <v>0.08391753923614287</v>
+        <v>0.08391731143362113</v>
       </c>
       <c r="Z48" s="2" t="n">
-        <v>0.01351938941491349</v>
+        <v>0.0135195229992775</v>
       </c>
       <c r="AA48" s="2" t="n">
-        <v>0.1037129775117767</v>
+        <v>0.1037130361816028</v>
       </c>
       <c r="AB48" s="2" t="n">
-        <v>0.007068299654627186</v>
+        <v>0.007068180200697549</v>
       </c>
     </row>
     <row r="49">
@@ -12169,67 +12169,67 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" s="2" t="n">
-        <v>0.1078894813866165</v>
+        <v>0.1078898812750295</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0.1704244202542509</v>
+        <v>0.1704223779944267</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>-0.1409523003155445</v>
+        <v>-0.1409507432112111</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.293300736592732</v>
+        <v>0.2933012064645044</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0.1791287103167971</v>
+        <v>0.1791277444251487</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0.03970220368407218</v>
+        <v>0.03970302325997044</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.04483198651433007</v>
+        <v>0.04483057013923664</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>-0.1259520744693182</v>
+        <v>-0.1259511715195727</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>-0.06935688546334573</v>
+        <v>-0.06935705582106866</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>-0.09404658351623263</v>
+        <v>-0.09404647175435987</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>-0.001016186021127741</v>
+        <v>-0.001015509236837908</v>
       </c>
       <c r="S49" s="2" t="n">
-        <v>0.0904888715915888</v>
+        <v>0.09048822551194191</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>-0.08845751281113878</v>
+        <v>-0.08845779586584468</v>
       </c>
       <c r="U49" s="2" t="n">
-        <v>0.001257022491845561</v>
+        <v>0.001257590252681906</v>
       </c>
       <c r="V49" s="2" t="n">
-        <v>0.09524104928838306</v>
+        <v>0.0952403148248957</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>-0.06169471012463823</v>
+        <v>-0.0616946129653444</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>-0.06458441804091164</v>
+        <v>-0.06458485946493675</v>
       </c>
       <c r="Y49" s="2" t="n">
-        <v>0.01201107316891892</v>
+        <v>0.01201178668956326</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>-0.07749049766529048</v>
+        <v>-0.07749077103624935</v>
       </c>
       <c r="AA49" s="2" t="n">
-        <v>0.09095759303851758</v>
+        <v>0.09095753560182307</v>
       </c>
       <c r="AB49" s="2" t="n">
-        <v>0.08113094818894839</v>
+        <v>0.08113107341818782</v>
       </c>
     </row>
     <row r="50">
@@ -12252,46 +12252,46 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" s="2" t="n">
-        <v>0.06122941155870998</v>
+        <v>0.06122976889931575</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0.06433021083826462</v>
+        <v>0.06433019668612716</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>-0.08002221975336077</v>
+        <v>-0.08002240990847842</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.07055852013317798</v>
+        <v>0.07055840779601907</v>
       </c>
       <c r="O50" s="3" t="n">
-        <v>-0.04883844165765117</v>
+        <v>-0.04883844678242688</v>
       </c>
       <c r="P50" s="3" t="n">
-        <v>-0.07328004381073039</v>
+        <v>-0.07328005189506914</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>-0.09628838731635414</v>
+        <v>-0.09628822021184724</v>
       </c>
       <c r="R50" s="2" t="n">
-        <v>0.04107135729680089</v>
+        <v>0.04107135459166322</v>
       </c>
       <c r="S50" s="2" t="n">
-        <v>0.1109206666178675</v>
+        <v>0.1109205963344484</v>
       </c>
       <c r="T50" s="3" t="n">
         <v>-0.05091169234368409</v>
       </c>
       <c r="U50" s="2" t="n">
-        <v>0.04784142815277215</v>
+        <v>0.04784118813677751</v>
       </c>
       <c r="V50" s="3" t="n">
-        <v>-0.0006423919106034459</v>
+        <v>-0.0006420484713381969</v>
       </c>
       <c r="W50" s="3" t="n">
-        <v>-0.06601711174226466</v>
+        <v>-0.06601727608012176</v>
       </c>
       <c r="X50" s="3" t="n">
-        <v>-0.01654979727949291</v>
+        <v>-0.01654973694339978</v>
       </c>
       <c r="Y50" s="2" t="n">
         <v>0.0909864582678952</v>
@@ -12337,19 +12337,19 @@
         <v>-0.007095083970101057</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.01349748756292812</v>
+        <v>0.01349740936694088</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v>0.006036421134772763</v>
+        <v>0.006036575909710518</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-0.01358140117026863</v>
+        <v>-0.01358147682033373</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-0.03263026722306972</v>
+        <v>-0.03263034497064177</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-0.04319208052630819</v>
+        <v>-0.04319200362758369</v>
       </c>
       <c r="S51" s="2" t="n">
         <v>0.1208081996951205</v>
@@ -12983,7 +12983,7 @@
         <v>-0.01440265628059278</v>
       </c>
       <c r="AB58" s="3" t="n">
-        <v>-0.04415729795722534</v>
+        <v>-0.04370709092918801</v>
       </c>
     </row>
     <row r="59">
@@ -13848,76 +13848,76 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>-0.04404106664514063</v>
+        <v>-0.04404158836028937</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>-0.2047960978172273</v>
+        <v>-0.2047955549891542</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.3074315811196773</v>
+        <v>0.3074308449836964</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0.1278148370590912</v>
+        <v>0.1278151849802369</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.06304001594937447</v>
+        <v>0.06304067326972462</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>0.1569672469429999</v>
+        <v>0.156965887092303</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0.05369847229234281</v>
+        <v>0.0536990364214347</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>-0.3698601190497952</v>
+        <v>-0.3698603113588427</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.2890457276992036</v>
+        <v>0.289046026844622</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0.174283103589165</v>
+        <v>0.1742830135740145</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.009685487460171727</v>
+        <v>0.009685258236375116</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.1645132061089856</v>
+        <v>0.1645137115890754</v>
       </c>
       <c r="O69" s="2" t="n">
-        <v>0.3344973629071255</v>
+        <v>0.334497188902847</v>
       </c>
       <c r="P69" s="2" t="n">
-        <v>0.1254932724998115</v>
+        <v>0.125493761033534</v>
       </c>
       <c r="Q69" s="2" t="n">
-        <v>0.003550973405462843</v>
+        <v>0.00355053780243253</v>
       </c>
       <c r="R69" s="2" t="n">
-        <v>0.1281771737177486</v>
+        <v>0.1281770007073531</v>
       </c>
       <c r="S69" s="2" t="n">
-        <v>0.2121346352365756</v>
+        <v>0.212134591091286</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>-0.05234803754400608</v>
+        <v>-0.0523478577048575</v>
       </c>
       <c r="U69" s="2" t="n">
-        <v>0.306686414618611</v>
+        <v>0.3066862811143387</v>
       </c>
       <c r="V69" s="2" t="n">
-        <v>0.210761065021047</v>
+        <v>0.2107612908947332</v>
       </c>
       <c r="W69" s="2" t="n">
-        <v>0.2568186257984404</v>
+        <v>0.256818688511808</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>-0.1952343448911162</v>
+        <v>-0.1952345200996223</v>
       </c>
       <c r="Y69" s="2" t="n">
-        <v>0.2604697604310071</v>
+        <v>0.2604697821620539</v>
       </c>
       <c r="Z69" s="2" t="n">
-        <v>0.2381024055016936</v>
+        <v>0.2381024874514117</v>
       </c>
       <c r="AA69" s="2" t="n">
         <v>0.1709825812345391</v>

--- a/annual_returns.xlsx
+++ b/annual_returns.xlsx
@@ -647,79 +647,79 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.01804040779399996</v>
+        <v>0.01804032203817263</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.6513726898542658</v>
+        <v>0.6513724577590174</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.4187935468621899</v>
+        <v>-0.4187933642828604</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-0.2335323719070335</v>
+        <v>-0.233533013049034</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-0.3816689470136782</v>
+        <v>-0.3816688430631088</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.3867550935122182</v>
+        <v>0.3867551937140166</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.05637591282105126</v>
+        <v>0.05637598562926605</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>-0.003164670762113686</v>
+        <v>-0.003163845804667886</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.1215720181060984</v>
+        <v>0.1215719318299022</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.1545706417347239</v>
+        <v>0.1545698057255185</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>-0.4150723733287494</v>
+        <v>-0.415072274231967</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.5132495393810286</v>
+        <v>0.5132498896958384</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.1139461624595113</v>
+        <v>0.1139458176085961</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.02613839069011181</v>
+        <v>0.02613820541723078</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0.1529628513875854</v>
+        <v>0.1529631498358723</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>0.2624124353850541</v>
+        <v>0.2624115535405716</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0.1784237074846831</v>
+        <v>0.1784240662460739</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>0.05469197133524273</v>
+        <v>0.05469272546866</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.1501184363113264</v>
+        <v>0.1501180769579711</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.3425644983699243</v>
+        <v>0.3425645554221748</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>-0.01677213674165112</v>
+        <v>-0.01677213457343363</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0.4985586155451527</v>
+        <v>0.4985586814747527</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>0.4361878816592968</v>
+        <v>0.4361877173812527</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.3474411383158325</v>
+        <v>0.3474411781811286</v>
       </c>
       <c r="AA2" s="3" t="n">
-        <v>-0.2772628451652474</v>
+        <v>-0.277262910700634</v>
       </c>
       <c r="AB2" s="2" t="n">
         <v>0.5601837127392593</v>
@@ -746,85 +746,85 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.005361818070140245</v>
+        <v>0.005361560869362014</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.02667724292698437</v>
+        <v>0.02667792497493737</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.2585642013214875</v>
+        <v>0.2585637204630549</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0.09430590823655149</v>
+        <v>-0.09430602115392872</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.1473600809963762</v>
+        <v>-0.1473604333398754</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.3049175182126205</v>
+        <v>0.3049181330214072</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.1085968176254271</v>
+        <v>0.1085966729339096</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.06204472158120211</v>
+        <v>0.06204483931356841</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.1888865326163121</v>
+        <v>0.1888867333862478</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.1917571256179862</v>
+        <v>-0.1917572584628258</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>-0.5490219948626047</v>
+        <v>-0.549022277617505</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1756540918114273</v>
+        <v>0.175654565392523</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.1190398169471818</v>
+        <v>0.1190397211037872</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>-0.1714258964607454</v>
+        <v>-0.1714255409088771</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>0.2841543621948239</v>
+        <v>0.2841540608414281</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.3552737510013197</v>
+        <v>0.3552732941427903</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0.1505354581402556</v>
+        <v>0.1505354414659079</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-0.01770048250976808</v>
+        <v>-0.01770019574168658</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2241521338682404</v>
+        <v>0.2241519682773452</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.2199984639987025</v>
+        <v>0.2199990916538781</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>-0.1305208104823241</v>
+        <v>-0.1305209285486152</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.3187401092112139</v>
+        <v>0.3187396831236253</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.01736370155120315</v>
+        <v>-0.01736349495498701</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.3479787350429144</v>
+        <v>0.3479787812732029</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>-0.1058645421227001</v>
+        <v>-0.1058647413839354</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>0.120309247772477</v>
+        <v>0.120309261927402</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>0.3055624605979379</v>
+        <v>0.3055625977076728</v>
       </c>
       <c r="AD3" s="2" t="n">
         <v>0.1490234443656935</v>
@@ -845,79 +845,79 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.003357609239917236</v>
+        <v>0.003357941725854685</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.1794932440436889</v>
+        <v>0.1794933502510401</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.2440085387764839</v>
+        <v>0.2440073121653634</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.1813307804506186</v>
+        <v>-0.1813300359332447</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-0.1468158265297973</v>
+        <v>-0.1468163965908286</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.2581169035875202</v>
+        <v>0.2581167445463728</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.3393517955447292</v>
+        <v>0.3393516269207091</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.4017879080671634</v>
+        <v>0.4017882352941176</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.1806893140033559</v>
+        <v>0.1806895811611706</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.3688826562334613</v>
+        <v>0.3688829308694554</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>-0.389552759857675</v>
+        <v>-0.3895530656373416</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2176375666070041</v>
+        <v>0.2176372409736174</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.2177688614852282</v>
+        <v>0.2177700358357268</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.02839100987220888</v>
+        <v>0.0283909083372802</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.05212638610848597</v>
+        <v>0.05212555778007966</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.2624633778506473</v>
+        <v>0.262464487951565</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.08678222066901442</v>
+        <v>-0.08678240238270896</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.2149819220013339</v>
+        <v>-0.2149819808825666</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.2802539451406645</v>
+        <v>0.2802537540464207</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>-0.008874343066584078</v>
+        <v>-0.008874642916767983</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>-0.1821761288165611</v>
+        <v>-0.1821759099247501</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.1174147149461418</v>
+        <v>0.117415012787121</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.3267132288846153</v>
+        <v>-0.3267132019639813</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.5327984493676385</v>
+        <v>0.5327981393980432</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.6432489237047789</v>
+        <v>0.6432490549056917</v>
       </c>
       <c r="AB4" s="3" t="n">
         <v>-0.006302365240602015</v>
@@ -944,85 +944,85 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.03870166523491259</v>
+        <v>0.03870187924761925</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.1950547509559353</v>
+        <v>0.195053769344403</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-0.1176962360479208</v>
+        <v>-0.1176961768441683</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0.008257911805174101</v>
+        <v>-0.008258328421057448</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.007389447477419653</v>
+        <v>-0.007389033756864727</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1493006200905111</v>
+        <v>0.1493007569215181</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.01272996228739953</v>
+        <v>0.01272987177439666</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.06416021513718517</v>
+        <v>0.06416104150286817</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.07051494234451594</v>
+        <v>0.07051421979755146</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.07159572256562141</v>
+        <v>0.07159541039086892</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-0.2331009409599678</v>
+        <v>-0.2331008049197375</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1951871649997579</v>
+        <v>0.1951879763228013</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.03299273859592566</v>
+        <v>0.03299207533889148</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.123968089133258</v>
+        <v>0.1239683435154795</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.1737187922364509</v>
+        <v>0.1737185710830447</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.4140925371021849</v>
+        <v>0.4140924675324675</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>0.2513642265816867</v>
+        <v>0.251364016890987</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.06831146206771876</v>
+        <v>0.06831175339105555</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>-0.02761730238663895</v>
+        <v>-0.02761717850044387</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.2177285373670519</v>
+        <v>0.2177287170860358</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.06279948512455324</v>
+        <v>0.0627996839795073</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.2045182056346055</v>
+        <v>0.2045175250468685</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.132951999297906</v>
+        <v>0.1329521870785686</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.2603860080794023</v>
+        <v>0.2603857154905533</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>-0.02079263347628268</v>
+        <v>-0.02079252223197869</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>0.02066588670111313</v>
+        <v>0.02066588915076073</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>0.02474434746980259</v>
+        <v>0.02474446647926998</v>
       </c>
       <c r="AD5" s="2" t="n">
         <v>0.1450371540118705</v>
@@ -1043,88 +1043,88 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.05503312659525528</v>
+        <v>0.05503380557904891</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.2185889212082963</v>
+        <v>0.2185882890554596</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.0670869661086031</v>
+        <v>0.06708697990117796</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.1054063703024659</v>
+        <v>-0.1054060052767642</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-0.245729949440172</v>
+        <v>-0.245730165727913</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.3185764265012714</v>
+        <v>0.318576235093271</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.1775141022599671</v>
+        <v>0.1775142489726804</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.02748661456332946</v>
+        <v>0.02748689294169115</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.1351579794042939</v>
+        <v>0.1351582236850937</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.1349327649203098</v>
+        <v>0.1349316868745112</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.3872761734982253</v>
+        <v>-0.3872759024698319</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2203114502944477</v>
+        <v>0.2203119287376325</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.2782061442677479</v>
+        <v>0.278206252531521</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-0.01099632130759831</v>
+        <v>-0.01099653535112</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.1492437314934294</v>
+        <v>0.1492435625822468</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.4054854018850627</v>
+        <v>0.405485913442226</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>0.1036581903682121</v>
+        <v>0.1036575156890021</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.04323381000439519</v>
+        <v>-0.04323357335770683</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2000549089572952</v>
+        <v>0.2000547366127963</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.2397917484367993</v>
+        <v>0.2397920701019487</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.1324738222700244</v>
+        <v>-0.1324738648431751</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.2908456224856271</v>
+        <v>0.2908458033565295</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.1090499899042059</v>
+        <v>0.1090498639033435</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.2108200802845017</v>
+        <v>0.2108199673519549</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>-0.05568730254320731</v>
+        <v>-0.05568707145318796</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.1812933068733693</v>
+        <v>0.1812930993626167</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0.1730970190041738</v>
+        <v>0.1730967998903981</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.1934700823065034</v>
+        <v>0.1934702228122263</v>
       </c>
       <c r="AE6" s="2" t="n">
         <v>0.1389572081129995</v>
@@ -1142,88 +1142,88 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.02576701401263137</v>
+        <v>0.02576721998679421</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.1950855803280476</v>
+        <v>0.1950846688835857</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-0.1687412304191127</v>
+        <v>-0.1687402641361985</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1273006672123249</v>
+        <v>0.1273008032606171</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-0.186600021083428</v>
+        <v>-0.1866003480268155</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.3720009998072857</v>
+        <v>0.3719999394979614</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.1288062101579308</v>
+        <v>0.1288063609818495</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0.065734746858087</v>
+        <v>-0.06573463404571234</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.1841201012450469</v>
+        <v>0.1841202318384723</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.1366818746064243</v>
+        <v>-0.1366820276731842</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>-0.3297118369749136</v>
+        <v>-0.3297112225819254</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4056913519990228</v>
+        <v>0.4056904708386309</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.2746230687109885</v>
+        <v>0.2746236367049117</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.05994354121219536</v>
+        <v>0.05994266159153594</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.2359898600251651</v>
+        <v>0.235991009390762</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.427326977332116</v>
+        <v>0.4273261229152592</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>0.09461649529574601</v>
+        <v>0.09461676976571831</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.09902858810238158</v>
+        <v>0.09902869595712049</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.05968987029894124</v>
+        <v>0.05968974837285534</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.2282249464348396</v>
+        <v>0.2282245118260144</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.01581993915723445</v>
+        <v>0.01582036156857236</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.2838960583599079</v>
+        <v>0.2838956820444023</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.2963030077549145</v>
+        <v>0.2963033024515886</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.2792809480253811</v>
+        <v>0.2792808213753373</v>
       </c>
       <c r="AA7" s="3" t="n">
         <v>-0.3627218065326756</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>0.3963929141610039</v>
+        <v>0.3963926712906749</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>0.2651149022156725</v>
+        <v>0.2651152092167373</v>
       </c>
       <c r="AD7" s="2" t="n">
-        <v>0.0737073866175042</v>
+        <v>0.07370731281131726</v>
       </c>
       <c r="AE7" s="3" t="n">
         <v>-0.02157083930593795</v>
@@ -1241,64 +1241,64 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.02476459408268972</v>
+        <v>0.02476446446191849</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>-0.1425789208785704</v>
+        <v>-0.1425785120227513</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.2554234940925442</v>
+        <v>0.2554233190613322</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-0.099271566490575</v>
+        <v>-0.09927113991877079</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-0.2009407431595074</v>
+        <v>-0.200941140816177</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.1117331193960744</v>
+        <v>0.1117328713332522</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.07645499191531679</v>
+        <v>0.07645493828676964</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.02841763899088856</v>
+        <v>0.02841829509606653</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.1448983167931497</v>
+        <v>0.1448981367778162</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.1268623729292915</v>
+        <v>0.1268624793691076</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>-0.1502355206357229</v>
+        <v>-0.1502354881305025</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1427768121901469</v>
+        <v>0.1427765212234269</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.1377995040187494</v>
+        <v>0.1377989470118193</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.1408673000171439</v>
+        <v>0.1408680543452847</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.1072601948651519</v>
+        <v>0.1072594898931667</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.2630876694599873</v>
+        <v>0.2630884118616215</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>0.1571980601685015</v>
+        <v>0.1571980408762168</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0.06873048598384579</v>
+        <v>0.06873047869467364</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.04980675164539949</v>
+        <v>0.0498067467028751</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.1298197389191897</v>
+        <v>0.1298196321218599</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>-0.08071122669478692</v>
@@ -1307,22 +1307,22 @@
         <v>0.274339477402936</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.1011073435966086</v>
+        <v>0.1011075578492973</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1720549888866036</v>
+        <v>0.1720548905485202</v>
       </c>
       <c r="AA8" s="3" t="n">
-        <v>-0.008093919615959622</v>
+        <v>-0.008094140074122569</v>
       </c>
       <c r="AB8" s="3" t="n">
-        <v>-0.008182170166377123</v>
+        <v>-0.008181947919080779</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>0.1220216586191225</v>
+        <v>0.1220214198903997</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.01516152200171828</v>
+        <v>0.01516162378790931</v>
       </c>
       <c r="AE8" s="2" t="n">
         <v>0.111007415145006</v>
@@ -1340,85 +1340,85 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.01361931822223261</v>
+        <v>0.01361972923893906</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>-0.04408552800857568</v>
+        <v>-0.04408519470329164</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.2247936630460627</v>
+        <v>0.224792770857225</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-0.130051391869741</v>
+        <v>-0.1300512720035488</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-0.2877555752514018</v>
+        <v>-0.2877551792930909</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.2646595504613556</v>
+        <v>0.2646581802830061</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.2358586429607477</v>
+        <v>0.2358593828027082</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1638563902061467</v>
+        <v>0.1638563785495619</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.2089277547742689</v>
+        <v>0.208927680880316</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0.1842052361289785</v>
+        <v>0.1842053372492496</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>-0.2891021486980588</v>
+        <v>-0.2891023801838635</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1170581646176629</v>
+        <v>0.1170581927389929</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.05308577855772612</v>
+        <v>0.0530863276227187</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>0.1964013684663568</v>
+        <v>0.1964006956487643</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.01036990102579249</v>
+        <v>0.01037067180295659</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1306574185653899</v>
+        <v>0.1306569299905393</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>0.2874723724050381</v>
+        <v>0.2874721267994449</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>-0.04929044995791221</v>
+        <v>-0.04929057173456186</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1607639586147376</v>
+        <v>0.1607639978646946</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.1204806897897852</v>
+        <v>0.1204807151308005</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.03935182295570083</v>
+        <v>0.03935192420087485</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.2593130606895184</v>
+        <v>0.2593133550202684</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.005105275786289498</v>
+        <v>0.005105203344753395</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1770401279189429</v>
+        <v>0.1770401866331077</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>0.0144296491715854</v>
+        <v>0.01442940496631095</v>
       </c>
       <c r="AB9" s="3" t="n">
-        <v>-0.07174776132378935</v>
+        <v>-0.07174759064245928</v>
       </c>
       <c r="AC9" s="2" t="n">
-        <v>0.2331223191408995</v>
+        <v>0.2331222397645389</v>
       </c>
       <c r="AD9" s="2" t="n">
         <v>0.1602436283709976</v>
@@ -1456,37 +1456,37 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" s="2" t="n">
-        <v>0.04365458272558342</v>
+        <v>0.04365421622624988</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.02755220397483882</v>
+        <v>0.02755247168672681</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.1069550597607811</v>
+        <v>0.1069548907289506</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>-0.02387652448812538</v>
+        <v>-0.02387622273439449</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>0.2868376896812701</v>
+        <v>0.286838035897119</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.02186256423971478</v>
+        <v>-0.02186291963369691</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.4610097732055063</v>
+        <v>0.4610099309815641</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>-0.2624924801489543</v>
+        <v>-0.2624927757551877</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.1236000843386613</v>
+        <v>0.1236002281942641</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>0.05094228271366008</v>
+        <v>0.0509424932525071</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.02629930747751974</v>
+        <v>0.02629920722994261</v>
       </c>
       <c r="AE10" s="2" t="n">
         <v>0.1317195794111845</v>
@@ -1503,93 +1503,35 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>0.05251384302344975</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>0.2292260915553637</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>-0.1622407531759722</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>0.02140553822215296</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>-0.05328452198017419</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>0.374128356800997</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0.1349252956310882</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>0.04080120617035798</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>0.1836470431720671</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0.2208554667705649</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>-0.4404881874485662</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>0.4815784537345147</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>0.2055496888836075</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>-0.1092181644402689</v>
-      </c>
-      <c r="Q11" s="2" t="n">
-        <v>0.1469341761040541</v>
-      </c>
-      <c r="R11" s="2" t="n">
-        <v>0.2598792981150506</v>
-      </c>
-      <c r="S11" s="2" t="n">
-        <v>0.07183019539229996</v>
-      </c>
-      <c r="T11" s="3" t="n">
-        <v>-0.08693307798366934</v>
-      </c>
-      <c r="U11" s="2" t="n">
-        <v>0.1679631010651892</v>
-      </c>
-      <c r="V11" s="2" t="n">
-        <v>0.2401265200750262</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>-0.1487742860140687</v>
-      </c>
-      <c r="X11" s="2" t="n">
-        <v>0.2412910793566372</v>
-      </c>
-      <c r="Y11" s="2" t="n">
-        <v>0.2046066697931446</v>
-      </c>
-      <c r="Z11" s="2" t="n">
-        <v>0.2743794693199266</v>
-      </c>
-      <c r="AA11" s="3" t="n">
-        <v>-0.1229692268181752</v>
-      </c>
-      <c r="AB11" s="2" t="n">
-        <v>0.1245591766016814</v>
-      </c>
-      <c r="AC11" s="2" t="n">
-        <v>0.001492305986267262</v>
-      </c>
-      <c r="AD11" s="2" t="n">
-        <v>0.09943347889217247</v>
-      </c>
-      <c r="AE11" s="2" t="n">
-        <v>0.1557232943740223</v>
-      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1623,19 +1565,19 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="3" t="n">
-        <v>-0.168804754489161</v>
+        <v>-0.1688049876313856</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>0.3104778360042144</v>
+        <v>0.3104783928800177</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>0.26904394563616</v>
+        <v>0.2690435066205037</v>
       </c>
       <c r="Z12" s="2" t="n">
-        <v>0.1596195640453781</v>
+        <v>0.1596199404947714</v>
       </c>
       <c r="AA12" s="3" t="n">
-        <v>-0.3762952158105665</v>
+        <v>-0.3762953439743156</v>
       </c>
       <c r="AB12" s="2" t="n">
         <v>0.5282087776455806</v>
@@ -1664,76 +1606,76 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" s="3" t="n">
-        <v>-0.5034831628843297</v>
+        <v>-0.5034832539248002</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0.1459184402224979</v>
+        <v>-0.1459184669778563</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.4707288095967512</v>
+        <v>-0.4707286959702808</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.8731380622116651</v>
+        <v>0.8731378594000061</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0.1957098696925568</v>
+        <v>-0.1957098908827981</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.09799196397885224</v>
+        <v>0.09799224641109094</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0.0816044374493714</v>
+        <v>-0.08160473395880297</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0.0353643653771073</v>
+        <v>-0.03536403870861626</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0.4574861065979198</v>
+        <v>-0.4574861470801648</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.5854627225093494</v>
+        <v>0.5854626213972094</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>0.1651145619489538</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-0.06455575604096164</v>
+        <v>-0.06455568699271985</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>0.08549929283152391</v>
+        <v>0.08549928652053795</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>0.3332982456355087</v>
+        <v>0.3332982909708344</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>0.3022336967453672</v>
+        <v>0.3022333599116012</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>-0.003373053374263524</v>
+        <v>-0.003372975574321146</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>0.3554262641047721</v>
+        <v>0.3554262134454997</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>0.3847760368056496</v>
+        <v>0.3847760814275922</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>-0.090522560293953</v>
+        <v>-0.09052240038402282</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>0.6445056188145319</v>
+        <v>0.6445056515487246</v>
       </c>
       <c r="Y13" s="2" t="n">
-        <v>0.5553445242394166</v>
+        <v>0.5553443500626898</v>
       </c>
       <c r="Z13" s="2" t="n">
         <v>0.4213155024938897</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>-0.3353174649409912</v>
+        <v>-0.3353174142831742</v>
       </c>
       <c r="AB13" s="2" t="n">
-        <v>0.7337543573193133</v>
+        <v>0.7337542251837452</v>
       </c>
       <c r="AC13" s="2" t="n">
         <v>0.3909952227465419</v>
@@ -1760,76 +1702,76 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" s="3" t="n">
-        <v>-0.08465273671220253</v>
+        <v>-0.08465193066656185</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-0.4784963169431508</v>
+        <v>-0.4784962690780189</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.8095302555694013</v>
+        <v>0.8095301121095146</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>-0.1426294294063647</v>
+        <v>-0.142629342249887</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.1338385222831617</v>
+        <v>0.1338380258762053</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.00227217638327204</v>
+        <v>0.002272062468702041</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>-0.02148667466199095</v>
+        <v>-0.02148656564213636</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>-0.5170983314714446</v>
+        <v>-0.5170985371909591</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.7494304552741651</v>
+        <v>0.7494312836683232</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>0.1364555636323548</v>
+        <v>0.1364561242472413</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>-0.1059526220950533</v>
+        <v>-0.1059530015282015</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>0.06621163788660489</v>
+        <v>0.0662117057001339</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>0.4157921242270251</v>
+        <v>0.4157920341793735</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>0.2985079293544064</v>
+        <v>0.2985078395074374</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>-0.02018544965417601</v>
+        <v>-0.02018538185838392</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>0.3834408455903098</v>
+        <v>0.3834409868261559</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>0.3978630261004998</v>
+        <v>0.397862781302047</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>-0.06488537966475183</v>
+        <v>-0.06488538440353242</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>0.624171976472323</v>
+        <v>0.6241721033212868</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>0.5271725080823733</v>
+        <v>0.5271724119094405</v>
       </c>
       <c r="Z14" s="2" t="n">
-        <v>0.4408976083668432</v>
+        <v>0.4408976991066624</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>-0.3508612299038707</v>
+        <v>-0.3508612736089228</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>0.671178142019403</v>
+        <v>0.671178119880566</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>0.1292434118500967</v>
+        <v>0.1292435028391075</v>
       </c>
       <c r="AD14" s="2" t="n">
         <v>0.4073725605928256</v>
@@ -1853,61 +1795,61 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>-0.1013034387528807</v>
+        <v>-0.1013034189267831</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.4469347043034491</v>
+        <v>-0.4469345525313098</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.5001990420388205</v>
+        <v>0.5001981067784216</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.1380474906543689</v>
+        <v>0.138048164938507</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0.05530996743860972</v>
+        <v>-0.0553104031847117</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.1076018736169149</v>
+        <v>0.107602117749106</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0.157469956318133</v>
+        <v>0.1574701420244462</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>-0.3843022947475001</v>
+        <v>-0.3843024816329531</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.475291502701753</v>
+        <v>0.4752912339846438</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>0.2464262196514051</v>
+        <v>0.2464262454825246</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>-0.07322438672857345</v>
+        <v>-0.0732243928866555</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>0.167748086130741</v>
+        <v>0.167748282839612</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>0.3068085760453167</v>
+        <v>0.3068084744957973</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>0.1342320798168319</v>
+        <v>0.1342318419609221</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>0.1211962375287507</v>
+        <v>0.1211964726510082</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>0.05785943534467086</v>
+        <v>0.05785934182555486</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>0.4215573585277959</v>
+        <v>0.4215575726034242</v>
       </c>
       <c r="W15" s="2" t="n">
-        <v>0.1244064524245596</v>
+        <v>0.1244061337469264</v>
       </c>
       <c r="X15" s="2" t="n">
-        <v>0.3432288193234976</v>
+        <v>0.3432291164865426</v>
       </c>
       <c r="Y15" s="2" t="n">
         <v>0.5286013805189052</v>
@@ -1960,37 +1902,37 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" s="3" t="n">
-        <v>-0.1077354895080983</v>
+        <v>-0.1077356689787786</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>0.1015396341068229</v>
+        <v>0.1015395213932124</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>0.1860582526775298</v>
+        <v>0.1860583740394106</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>0.01470464282630068</v>
+        <v>0.01470472909836973</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>0.2851836157447549</v>
+        <v>0.2851835914979175</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>0.5053124450703335</v>
+        <v>0.5053122131749554</v>
       </c>
       <c r="Z16" s="2" t="n">
-        <v>0.1967551989559371</v>
+        <v>0.1967552162499184</v>
       </c>
       <c r="AA16" s="3" t="n">
-        <v>-0.2645705358135679</v>
+        <v>-0.2645704817998011</v>
       </c>
       <c r="AB16" s="2" t="n">
-        <v>0.3971121833951194</v>
+        <v>0.3971120835280326</v>
       </c>
       <c r="AC16" s="2" t="n">
-        <v>0.1821059841386343</v>
+        <v>0.1821061401179367</v>
       </c>
       <c r="AD16" s="2" t="n">
-        <v>0.1306345940912943</v>
+        <v>0.130634525722656</v>
       </c>
       <c r="AE16" s="2" t="n">
         <v>0.1963385392215096</v>
@@ -2016,13 +1958,13 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" s="2" t="n">
-        <v>0.100389819692289</v>
+        <v>0.1003900157681044</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0.1129317182128455</v>
+        <v>0.1129317934677025</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0.4402937301895476</v>
+        <v>-0.4402938155190282</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0.7911617947921057</v>
@@ -2107,10 +2049,10 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" s="3" t="n">
-        <v>-0.01079477024867237</v>
+        <v>-0.01079487395678713</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>0.03756715384690379</v>
+        <v>0.03756726262528631</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>-0.02003902719778572</v>
@@ -2119,10 +2061,10 @@
         <v>0.8732698119931106</v>
       </c>
       <c r="W18" s="2" t="n">
-        <v>0.03519209408366297</v>
+        <v>0.0351919839979391</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>0.3507754392535807</v>
+        <v>0.3507755828994881</v>
       </c>
       <c r="Y18" s="2" t="n">
         <v>1.527107913231815</v>
@@ -2166,58 +2108,58 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" s="3" t="n">
-        <v>-0.06314726466462173</v>
+        <v>-0.06314719553460779</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0.2903012902537261</v>
+        <v>0.2903009056191892</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>-0.08617843263436431</v>
+        <v>-0.08617864448694224</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.003532959864033458</v>
+        <v>0.003533183296579701</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>0.1759878961016355</v>
+        <v>0.1759883585342881</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>0.0526314500909344</v>
+        <v>0.0526314352229249</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>0.3268747809443453</v>
+        <v>0.3268746037654393</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>0.4839056165806741</v>
+        <v>0.4839051468202804</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>0.4497316530542592</v>
+        <v>0.4497318256518719</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>0.1357667038995776</v>
+        <v>0.1357667750873388</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>-0.1544692520386725</v>
+        <v>-0.1544693072244343</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>0.4377248550373989</v>
+        <v>0.4377248183390479</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>-0.1527710263174095</v>
+        <v>-0.1527710401879341</v>
       </c>
       <c r="X19" s="2" t="n">
-        <v>0.3256367769796877</v>
+        <v>0.325636704711864</v>
       </c>
       <c r="Y19" s="2" t="n">
-        <v>0.4833154245702624</v>
+        <v>0.4833156643928516</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>-0.2044971728898261</v>
+        <v>-0.2044971183902661</v>
       </c>
       <c r="AA19" s="3" t="n">
-        <v>-0.2586637207549755</v>
+        <v>-0.2586638400531743</v>
       </c>
       <c r="AB19" s="2" t="n">
-        <v>0.07599569906981074</v>
+        <v>0.07599579850648475</v>
       </c>
       <c r="AC19" s="2" t="n">
         <v>0.01006290507347685</v>
@@ -2244,79 +2186,79 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" s="3" t="n">
-        <v>-0.1202901019456578</v>
+        <v>-0.1202897255267713</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-0.4579900963973413</v>
+        <v>-0.4579901703087189</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.4579537617265388</v>
+        <v>0.4579529468284107</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.04794943887655534</v>
+        <v>0.04795062566414554</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.02441663459819821</v>
+        <v>0.02441550943494031</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.006744669200553499</v>
+        <v>0.006745446069508665</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0.04515084443695017</v>
+        <v>0.04515036942448014</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-0.1227647412527855</v>
+        <v>-0.1227651269839157</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.1517235482578423</v>
+        <v>0.1517243917219004</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>0.1484327599960407</v>
+        <v>0.1484329567387088</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>0.1171506265074398</v>
+        <v>0.1171498922480174</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>0.3212946356797703</v>
+        <v>0.321294858502565</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>0.6554037489170657</v>
+        <v>0.6554045484408877</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>0.3383145787069242</v>
+        <v>0.3383141621739612</v>
       </c>
       <c r="T20" s="2" t="n">
         <v>0.1155934354494597</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>-0.2141732142301244</v>
+        <v>-0.2141731447427522</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>0.2107587686351873</v>
+        <v>0.210758396295454</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>-0.09532273745490916</v>
+        <v>-0.09532246620653184</v>
       </c>
       <c r="X20" s="2" t="n">
-        <v>0.2541847720876449</v>
+        <v>0.2541847515676496</v>
       </c>
       <c r="Y20" s="2" t="n">
-        <v>0.2601347661096416</v>
+        <v>0.2601345562631254</v>
       </c>
       <c r="Z20" s="2" t="n">
-        <v>0.009501150521565638</v>
+        <v>0.009500947172952134</v>
       </c>
       <c r="AA20" s="3" t="n">
-        <v>-0.1369018217381039</v>
+        <v>-0.1369018633007354</v>
       </c>
       <c r="AB20" s="2" t="n">
-        <v>0.03759123355849603</v>
+        <v>0.03759159853081218</v>
       </c>
       <c r="AC20" s="3" t="n">
-        <v>-0.02410941752581108</v>
+        <v>-0.02410953052775866</v>
       </c>
       <c r="AD20" s="2" t="n">
-        <v>0.2798023077909104</v>
+        <v>0.2798024559839278</v>
       </c>
       <c r="AE20" s="2" t="n">
         <v>0.01193727573952463</v>
@@ -2342,58 +2284,58 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" s="2" t="n">
-        <v>0.02759873094522303</v>
+        <v>0.02759861189112822</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0.1874630281859302</v>
+        <v>0.1874633869778441</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-0.367848430491813</v>
+        <v>-0.3678484813817974</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.3849805082545579</v>
+        <v>0.3849809417607128</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>0.1134810467536738</v>
+        <v>0.1134806716155565</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>8.811646156448028e-05</v>
+        <v>8.842968096822723e-05</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>0.1577773098598121</v>
+        <v>0.1577772769177497</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>0.3777206094114587</v>
+        <v>0.3777202707917811</v>
       </c>
       <c r="S21" s="2" t="n">
-        <v>0.2272427316948662</v>
+        <v>0.2272422884377812</v>
       </c>
       <c r="T21" s="2" t="n">
-        <v>0.09685347760196072</v>
+        <v>0.09685405220802101</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>0.09302993817730698</v>
+        <v>0.09302973465292008</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>0.3081386209449481</v>
+        <v>0.3081388262837039</v>
       </c>
       <c r="W21" s="2" t="n">
-        <v>0.1545187351140624</v>
+        <v>0.1545189286274131</v>
       </c>
       <c r="X21" s="2" t="n">
-        <v>0.3275007678303641</v>
+        <v>0.3275003372326657</v>
       </c>
       <c r="Y21" s="2" t="n">
-        <v>0.2417505140176299</v>
+        <v>0.2417510679489301</v>
       </c>
       <c r="Z21" s="2" t="n">
-        <v>0.2103527374321799</v>
+        <v>0.2103520190472257</v>
       </c>
       <c r="AA21" s="3" t="n">
-        <v>-0.1979569605869438</v>
+        <v>-0.1979566530561633</v>
       </c>
       <c r="AB21" s="2" t="n">
-        <v>0.03237725082516985</v>
+        <v>0.03237709881458128</v>
       </c>
       <c r="AC21" s="2" t="n">
         <v>0.08618314449484976</v>
@@ -2425,58 +2367,58 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" s="2" t="n">
-        <v>0.06009705659852127</v>
+        <v>0.06009684392173753</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>-0.2194079013152244</v>
+        <v>-0.2194075099315165</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>-0.1855270306606303</v>
+        <v>-0.1855276159176742</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>-0.2192205545783317</v>
+        <v>-0.2192211013838071</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>0.2065457464721745</v>
+        <v>0.206547563980402</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>-0.05967518084272327</v>
+        <v>-0.05967625483828476</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>0.1690662409870931</v>
+        <v>0.1690664219080016</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>0.4752114989315999</v>
+        <v>0.4752112612600969</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>0.0183862203979579</v>
+        <v>0.01838710460709603</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>0.04852656732450611</v>
+        <v>0.04852648499740853</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>0.3497880189474221</v>
+        <v>0.3497875442933518</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>0.07485757636756829</v>
+        <v>0.07485748952653748</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>-0.1900737487114517</v>
+        <v>-0.1900737640680924</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>0.2744300303819536</v>
+        <v>0.2744300577573393</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>-0.07426889004037329</v>
+        <v>-0.07426873930740352</v>
       </c>
       <c r="Z22" s="2" t="n">
-        <v>0.3929277715777129</v>
+        <v>0.3929275692491159</v>
       </c>
       <c r="AA22" s="3" t="n">
-        <v>-0.1507989920401571</v>
+        <v>-0.1507988797909539</v>
       </c>
       <c r="AB22" s="3" t="n">
-        <v>-0.07610368299866554</v>
+        <v>-0.07610374903938921</v>
       </c>
       <c r="AC22" s="2" t="n">
         <v>0.1858358618074059</v>
@@ -2507,64 +2449,64 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" s="2" t="n">
-        <v>0.01896041440512031</v>
+        <v>0.01895998459301396</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.16129044984033</v>
+        <v>0.1612908470449266</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>-0.2165726640665269</v>
+        <v>-0.2165728476582582</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>-0.4728196483023108</v>
+        <v>-0.4728196118805011</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>-0.01755143780463742</v>
+        <v>-0.01755131427198398</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>0.2305558156037546</v>
+        <v>0.2305559912595903</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>-0.2205834736416415</v>
+        <v>-0.2205835312493589</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>0.2273252676234851</v>
+        <v>0.2273249730371156</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>0.4137816285543312</v>
+        <v>0.4137818886705373</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>0.02761459030537217</v>
+        <v>0.02761489309318965</v>
       </c>
       <c r="T23" s="2" t="n">
-        <v>0.02494537948048658</v>
+        <v>0.02494499935467887</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>0.3080547345628444</v>
+        <v>0.3080545898236788</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>0.1048959846963549</v>
+        <v>0.1048958856510938</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>-0.1964463171523188</v>
+        <v>-0.1964461061314026</v>
       </c>
       <c r="X23" s="2" t="n">
-        <v>0.2977723444479106</v>
+        <v>0.297772263576997</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>-0.08749683447692302</v>
+        <v>-0.08749673844285166</v>
       </c>
       <c r="Z23" s="2" t="n">
-        <v>0.3346456365584498</v>
+        <v>0.3346453908546423</v>
       </c>
       <c r="AA23" s="3" t="n">
-        <v>-0.1483378947876408</v>
+        <v>-0.1483379064847121</v>
       </c>
       <c r="AB23" s="2" t="n">
-        <v>0.0530056954971001</v>
+        <v>0.05300588558210606</v>
       </c>
       <c r="AC23" s="2" t="n">
-        <v>0.2377857526474227</v>
+        <v>0.2377856438114687</v>
       </c>
       <c r="AD23" s="2" t="n">
         <v>0.1235922610863625</v>
@@ -2592,64 +2534,64 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" s="2" t="n">
-        <v>0.001951445297881493</v>
+        <v>0.001952220218985889</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.08868310504851062</v>
+        <v>0.08868245963980637</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.0571554754897835</v>
+        <v>-0.05715520788053297</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>-0.4659351802696304</v>
+        <v>-0.4659350673805073</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.2798650962562421</v>
+        <v>0.2798646848039066</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>0.2607071906980707</v>
+        <v>0.2607071092990456</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>-0.1207681814053253</v>
+        <v>-0.1207678531597556</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>0.2071750794275948</v>
+        <v>0.207174839607694</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>0.4563735780521891</v>
+        <v>0.4563729197811117</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>0.07692699709560413</v>
+        <v>0.07692748385959502</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>0.05968279210603389</v>
+        <v>0.05968258225277268</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>0.2141679689054876</v>
+        <v>0.2141681103350817</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>0.1283099342166159</v>
+        <v>0.1283099446804632</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>-0.05992947602698806</v>
+        <v>-0.05992933580367943</v>
       </c>
       <c r="X24" s="2" t="n">
-        <v>0.2718688155541649</v>
+        <v>0.2718693328472144</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>-0.03038598854100294</v>
+        <v>-0.03038639699952872</v>
       </c>
       <c r="Z24" s="2" t="n">
-        <v>0.2275083712073485</v>
+        <v>0.227508419368269</v>
       </c>
       <c r="AA24" s="2" t="n">
-        <v>0.03484830862324584</v>
+        <v>0.03484810192416155</v>
       </c>
       <c r="AB24" s="2" t="n">
-        <v>0.1218072945638891</v>
+        <v>0.1218070120435142</v>
       </c>
       <c r="AC24" s="2" t="n">
-        <v>0.2695198783250052</v>
+        <v>0.2695203226607508</v>
       </c>
       <c r="AD24" s="2" t="n">
         <v>0.08125515208826717</v>
@@ -2678,49 +2620,49 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" s="2" t="n">
-        <v>0.03145501806377826</v>
+        <v>0.03145519135696095</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0.27618283110675</v>
+        <v>0.2761815632274909</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-0.3864552561362136</v>
+        <v>-0.3864551242987692</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.2532823577577412</v>
+        <v>0.2532831189063802</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>0.1659101898505249</v>
+        <v>0.1659098756045188</v>
       </c>
       <c r="P25" s="2" t="n">
         <v>0.05149255036730915</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>0.138868664397729</v>
+        <v>0.138869177389352</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>0.569625102925464</v>
+        <v>0.5696243959043727</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>0.0989319775318358</v>
+        <v>0.09893115760962834</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>0.04138804186950562</v>
+        <v>0.0413887442474079</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>0.2024957012666935</v>
+        <v>0.2024953575468103</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>0.3524360231206545</v>
+        <v>0.3524366257569436</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>-0.07217110153192907</v>
+        <v>-0.0721709189555626</v>
       </c>
       <c r="X25" s="2" t="n">
-        <v>0.3050917439991916</v>
+        <v>0.3050912772336283</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-0.1357483730577579</v>
+        <v>-0.1357483101722917</v>
       </c>
       <c r="Z25" s="2" t="n">
         <v>0.09393936842672446</v>
@@ -2759,67 +2701,67 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" s="2" t="n">
-        <v>0.2676933750465098</v>
+        <v>0.26769401114151</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.1087687331885281</v>
+        <v>0.1087689306443498</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.08978199969406608</v>
+        <v>0.08978126693076383</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0.003910479019584745</v>
+        <v>0.003910950237809629</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-0.2122830496042566</v>
+        <v>-0.2122830832678509</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.189673330654281</v>
+        <v>0.1896733908346715</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>0.2671509070064402</v>
+        <v>0.2671509985044547</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.01538872333098662</v>
+        <v>-0.01538872029848304</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>0.06659800528409776</v>
+        <v>0.06659749160512685</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>0.411725140723155</v>
+        <v>0.4117258195397426</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>0.25361996611261</v>
+        <v>0.2536193174167858</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-0.1691380541722542</v>
+        <v>-0.1691376308495081</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>0.221582451232474</v>
+        <v>0.2215826002344854</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>0.1889155619626646</v>
+        <v>0.1889152938308021</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.1287090774450204</v>
+        <v>-0.1287090661360341</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>0.2011381892619579</v>
+        <v>0.2011381689783203</v>
       </c>
       <c r="Y26" s="2" t="n">
-        <v>0.1420445562979338</v>
+        <v>0.142044460414984</v>
       </c>
       <c r="Z26" s="2" t="n">
-        <v>0.2641351862418937</v>
+        <v>0.2641354803014639</v>
       </c>
       <c r="AA26" s="3" t="n">
-        <v>-0.2174358328398941</v>
+        <v>-0.2174360730320096</v>
       </c>
       <c r="AB26" s="2" t="n">
-        <v>0.2462406980261933</v>
+        <v>0.2462406420124539</v>
       </c>
       <c r="AC26" s="2" t="n">
-        <v>0.04103791763412779</v>
+        <v>0.04103804178692672</v>
       </c>
       <c r="AD26" s="2" t="n">
         <v>0.1147569022013819</v>
@@ -2857,16 +2799,16 @@
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" s="2" t="n">
-        <v>0.0320060739371173</v>
+        <v>0.0320062461632149</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>0.1246771276264584</v>
+        <v>0.1246769659173876</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>0.1865802178206675</v>
+        <v>0.186580460321695</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>-0.1383512533510668</v>
+        <v>-0.1383513055557727</v>
       </c>
       <c r="X27" s="2" t="n">
         <v>0.1437733297013193</v>
@@ -2913,61 +2855,61 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" s="2" t="n">
-        <v>0.1052261966756831</v>
+        <v>0.1052267932508613</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0.3691165470304791</v>
+        <v>0.3691164014304531</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>-0.4267880920471674</v>
+        <v>-0.4267883532314553</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.4015177376127896</v>
+        <v>0.4015176373424265</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>0.285656444181982</v>
+        <v>0.2856571101912706</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>0.009492878481504041</v>
+        <v>0.009492689870069126</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>0.03873723357133585</v>
+        <v>0.03873723000335083</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>0.278967451799204</v>
+        <v>0.278967781752274</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>-0.2942123005763579</v>
+        <v>-0.2942124759108533</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>-0.357813181641408</v>
+        <v>-0.357813097376289</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>0.382933245429101</v>
+        <v>0.3829329281173504</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>-0.09470078572588392</v>
+        <v>-0.09470100694495143</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>-0.2809984312077257</v>
+        <v>-0.2809984387825094</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>-0.09437906568635068</v>
+        <v>-0.09437866491751801</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>-0.3639968701741482</v>
+        <v>-0.3639970833330988</v>
       </c>
       <c r="Z28" s="2" t="n">
-        <v>0.6674150080129908</v>
+        <v>0.6674151064664342</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>0.4536456442768999</v>
+        <v>0.4536458613485226</v>
       </c>
       <c r="AB28" s="2" t="n">
-        <v>0.03560838915015441</v>
+        <v>0.03560856956329661</v>
       </c>
       <c r="AC28" s="3" t="n">
-        <v>-0.01001797462114662</v>
+        <v>-0.01001820733608372</v>
       </c>
       <c r="AD28" s="3" t="n">
         <v>-0.02153896894800622</v>
@@ -2991,58 +2933,58 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" s="3" t="n">
-        <v>-0.316097240274917</v>
+        <v>-0.3160967967556562</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.05394575512445132</v>
+        <v>-0.05394539762311568</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.08981077017410999</v>
+        <v>0.08980986916766676</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0.3800788146093255</v>
+        <v>0.3800790756225756</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.5231236182303718</v>
+        <v>0.5231238150514363</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.0911848876693313</v>
+        <v>0.09118539035383133</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0.4484914992310451</v>
+        <v>0.4484896690555904</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.6014501952780094</v>
+        <v>-0.6014500905143043</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.6414604545261047</v>
+        <v>0.641460998309312</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>0.203939895095838</v>
+        <v>0.2039396932755602</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.1704950174388801</v>
+        <v>-0.1704948783862956</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>0.0194846386682872</v>
+        <v>0.01948473971239606</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>0.2587171555857917</v>
+        <v>0.2587172290564985</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.2355377568893059</v>
+        <v>-0.2355380347610952</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>-0.2454813746949979</v>
+        <v>-0.2454813222630763</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>0.2782664019302488</v>
+        <v>0.2782667129448086</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>-0.1965843237856686</v>
+        <v>-0.1965843561892304</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>-0.4502845576654972</v>
+        <v>-0.4502845942016146</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>-0.03443700834478614</v>
@@ -3054,13 +2996,13 @@
         <v>0.2122489580192914</v>
       </c>
       <c r="AA29" s="2" t="n">
-        <v>0.6617259015195689</v>
+        <v>0.6617262527837688</v>
       </c>
       <c r="AB29" s="2" t="n">
-        <v>0.03204387679542631</v>
+        <v>0.03204376432926859</v>
       </c>
       <c r="AC29" s="3" t="n">
-        <v>-0.1053345652686413</v>
+        <v>-0.1053346568921582</v>
       </c>
       <c r="AD29" s="2" t="n">
         <v>0.06814408002532968</v>
@@ -3093,52 +3035,52 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" s="2" t="n">
-        <v>0.08953595131337067</v>
+        <v>0.08953587389149686</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>0.1011595368408631</v>
+        <v>0.1011597087264979</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>0.01898095157294777</v>
+        <v>0.01898073894013463</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>0.1853003360732433</v>
+        <v>0.1853004442976012</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>0.04824495256100403</v>
+        <v>0.04824542768983764</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>-0.2732621848846756</v>
+        <v>-0.2732624289919044</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>0.1492332223012489</v>
+        <v>0.1492327601062216</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>-0.0789255362140503</v>
+        <v>-0.07892469657250656</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>-0.1266392331341338</v>
+        <v>-0.1266396780343345</v>
       </c>
       <c r="X30" s="2" t="n">
-        <v>0.05988788400303902</v>
+        <v>0.05988805065384617</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>-0.3225657662247201</v>
+        <v>-0.3225660299749989</v>
       </c>
       <c r="Z30" s="2" t="n">
-        <v>0.3908552894832371</v>
+        <v>0.3908556123047</v>
       </c>
       <c r="AA30" s="2" t="n">
-        <v>0.2546861355137355</v>
+        <v>0.2546857183193876</v>
       </c>
       <c r="AB30" s="2" t="n">
-        <v>0.2139918428908594</v>
+        <v>0.2139925125613604</v>
       </c>
       <c r="AC30" s="2" t="n">
-        <v>0.2276268464367019</v>
+        <v>0.2276266870007884</v>
       </c>
       <c r="AD30" s="2" t="n">
-        <v>0.05779086101249598</v>
+        <v>0.05779076661055282</v>
       </c>
       <c r="AE30" s="2" t="n">
         <v>0.1529461085654731</v>
@@ -3164,25 +3106,25 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" s="2" t="n">
-        <v>0.07510049742209346</v>
+        <v>0.07510093361138015</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0.1676653781142092</v>
+        <v>0.1676650035392977</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0.2607461818513375</v>
+        <v>-0.2607462550193561</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.3672659761006973</v>
+        <v>0.3672665031356173</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>0.3392061539105669</v>
+        <v>0.3392057087329714</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0.1609298046488812</v>
+        <v>-0.1609298985720737</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.08867833839080197</v>
+        <v>-0.08867810687415922</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>-0.5402365658121674</v>
@@ -3197,25 +3139,25 @@
         <v>0.5291892082481875</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>0.1198615552726288</v>
+        <v>0.119861755771872</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.08771126974591015</v>
+        <v>-0.08771143308142804</v>
       </c>
       <c r="X31" s="2" t="n">
-        <v>0.3981789889285887</v>
+        <v>0.3981791851814926</v>
       </c>
       <c r="Y31" s="2" t="n">
-        <v>0.2366145598627023</v>
+        <v>0.2366142459243263</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.09522242870231723</v>
+        <v>-0.09522232600458813</v>
       </c>
       <c r="AA31" s="3" t="n">
-        <v>-0.09006961261528945</v>
+        <v>-0.09006954988935456</v>
       </c>
       <c r="AB31" s="2" t="n">
-        <v>0.09976268480922212</v>
+        <v>0.09976260899722722</v>
       </c>
       <c r="AC31" s="2" t="n">
         <v>0.1063561136612767</v>
@@ -3250,46 +3192,46 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" s="2" t="n">
-        <v>0.01179254947480035</v>
+        <v>0.01179233465338303</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>0.6698717753671468</v>
+        <v>0.6698718802887023</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>-0.3396103441999152</v>
+        <v>-0.3396105741898806</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>-0.1680328391364504</v>
+        <v>-0.1680324113783485</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>-0.6077563877069121</v>
+        <v>-0.6077565060111172</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>-0.2235848816621678</v>
+        <v>-0.2235848250703958</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>-0.1914187332491746</v>
+        <v>-0.1914186393708576</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>0.729668418189177</v>
+        <v>0.7296682173703504</v>
       </c>
       <c r="V32" s="2" t="n">
         <v>0.08215344190126728</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>-0.1102481181852601</v>
+        <v>-0.1102479941286487</v>
       </c>
       <c r="X32" s="2" t="n">
-        <v>0.4044238375581974</v>
+        <v>0.4044236417417661</v>
       </c>
       <c r="Y32" s="2" t="n">
         <v>0.3039701252788469</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>-0.212460368803199</v>
+        <v>-0.2124602926680563</v>
       </c>
       <c r="AA32" s="3" t="n">
-        <v>-0.1453338515096235</v>
+        <v>-0.1453339341341927</v>
       </c>
       <c r="AB32" s="2" t="n">
         <v>0.07121056041072138</v>
@@ -3328,52 +3270,52 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" s="2" t="n">
-        <v>0.8575649201110205</v>
+        <v>0.8575643031243281</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>-0.2202282079003645</v>
+        <v>-0.2202278381844689</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>0.08224647818181152</v>
+        <v>0.08224632451887093</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>-0.502138804299177</v>
+        <v>-0.5021387715004606</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>-0.172571982785228</v>
+        <v>-0.1725721690540203</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>-0.3311990849513236</v>
+        <v>-0.3311991376910097</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>0.7947490382423301</v>
+        <v>0.7947494655643945</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>0.0166939011459708</v>
+        <v>0.01669350315885687</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>-0.2241667612676268</v>
+        <v>-0.2241665228079089</v>
       </c>
       <c r="X33" s="2" t="n">
-        <v>0.3477502425028056</v>
+        <v>0.3477508603962423</v>
       </c>
       <c r="Y33" s="2" t="n">
-        <v>0.4029640242324684</v>
+        <v>0.4029633742151415</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>-0.183507357416669</v>
+        <v>-0.1835072847917741</v>
       </c>
       <c r="AA33" s="3" t="n">
-        <v>-0.2282913853378304</v>
+        <v>-0.2282914398070222</v>
       </c>
       <c r="AB33" s="2" t="n">
-        <v>0.01305728482897828</v>
+        <v>0.01305742691578282</v>
       </c>
       <c r="AC33" s="2" t="n">
-        <v>0.1462606616008466</v>
+        <v>0.1462606514104501</v>
       </c>
       <c r="AD33" s="2" t="n">
-        <v>1.661586446229593</v>
+        <v>1.661586284451117</v>
       </c>
       <c r="AE33" s="3" t="n">
         <v>-0.0220306083793812</v>
@@ -3399,61 +3341,61 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" s="2" t="n">
-        <v>0.09366597841101743</v>
+        <v>0.09366540517863187</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0.4175210844046122</v>
+        <v>0.4175208695326806</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>-0.5938446361030476</v>
+        <v>-0.593844563931598</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.8823875608553162</v>
+        <v>0.8823882301346286</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>0.3413423171834908</v>
+        <v>0.3413421630837017</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>-0.2817067171717345</v>
+        <v>-0.2817063565648437</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>-0.06599895044378012</v>
+        <v>-0.06599976826511456</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>-0.05381351611381957</v>
+        <v>-0.05381302370387664</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>-0.2527620599905416</v>
+        <v>-0.2527620593963905</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>-0.5052858288602254</v>
+        <v>-0.5052857917345304</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>1.060404003608962</v>
+        <v>1.06040340413151</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>0.2117476451141418</v>
+        <v>0.2117473626923496</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>-0.2678109034718079</v>
+        <v>-0.2678107328205952</v>
       </c>
       <c r="X34" s="2" t="n">
-        <v>0.1469305479346856</v>
+        <v>0.1469306275144726</v>
       </c>
       <c r="Y34" s="2" t="n">
-        <v>0.1595301524700889</v>
+        <v>0.1595303495561025</v>
       </c>
       <c r="Z34" s="2" t="n">
-        <v>0.3492432204171285</v>
+        <v>0.3492428974682826</v>
       </c>
       <c r="AA34" s="2" t="n">
-        <v>0.1313660394870872</v>
+        <v>0.1313662168869796</v>
       </c>
       <c r="AB34" s="2" t="n">
-        <v>0.2151039045141583</v>
+        <v>0.2151036355833351</v>
       </c>
       <c r="AC34" s="3" t="n">
-        <v>-0.04543454368148503</v>
+        <v>-0.04543448209115319</v>
       </c>
       <c r="AD34" s="2" t="n">
         <v>0.8347363028562125</v>
@@ -3486,49 +3428,49 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" s="2" t="n">
-        <v>0.3620255681328444</v>
+        <v>0.362025485165735</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>-0.309577047487288</v>
+        <v>-0.3095771369342224</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>0.0481864440189177</v>
+        <v>0.04818657981549856</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>-0.2750976702875546</v>
+        <v>-0.2750977320865913</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>-0.1960451983180895</v>
+        <v>-0.1960452150312452</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>-0.4587858820186026</v>
+        <v>-0.4587857716080278</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>0.7034756554233734</v>
+        <v>0.7034758804026287</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>0.3892242236491346</v>
+        <v>0.3892237890599346</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>-0.313090313493722</v>
+        <v>-0.3130899668472298</v>
       </c>
       <c r="X35" s="2" t="n">
-        <v>0.1248102186882154</v>
+        <v>0.1248093825948651</v>
       </c>
       <c r="Y35" s="2" t="n">
-        <v>0.5165677336063941</v>
+        <v>0.5165682211320699</v>
       </c>
       <c r="Z35" s="2" t="n">
-        <v>0.2338354753575362</v>
+        <v>0.2338356166706517</v>
       </c>
       <c r="AA35" s="3" t="n">
-        <v>-0.007613142589400712</v>
+        <v>-0.00761337078057156</v>
       </c>
       <c r="AB35" s="2" t="n">
-        <v>0.08378734746377425</v>
+        <v>0.08378735713369023</v>
       </c>
       <c r="AC35" s="2" t="n">
-        <v>0.03567215835257298</v>
+        <v>0.03567226863910622</v>
       </c>
       <c r="AD35" s="2" t="n">
         <v>0.9350033298275122</v>
@@ -3561,46 +3503,46 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" s="2" t="n">
-        <v>0.2129099203034039</v>
+        <v>0.2129100346194805</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-0.6018563086284511</v>
+        <v>-0.6018562519038384</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-0.1858850739928389</v>
+        <v>-0.1858852667118411</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-0.2137519651672091</v>
+        <v>-0.2137521105534177</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-0.2250640070739697</v>
+        <v>-0.2250637713237531</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>-0.3712982978456104</v>
+        <v>-0.371298372854441</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-0.01251928518157963</v>
+        <v>-0.01251919029753734</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>0.1936065259203763</v>
+        <v>0.1936063151433647</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>-0.2210718663264786</v>
+        <v>-0.2210716426188875</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>-0.03540393257143815</v>
+        <v>-0.03540433864915327</v>
       </c>
       <c r="Y36" s="2" t="n">
-        <v>0.4133173662908405</v>
+        <v>0.4133174548583098</v>
       </c>
       <c r="Z36" s="2" t="n">
-        <v>0.5757467281780935</v>
+        <v>0.5757469670897137</v>
       </c>
       <c r="AA36" s="3" t="n">
-        <v>-0.1131817929459928</v>
+        <v>-0.1131816967262085</v>
       </c>
       <c r="AB36" s="2" t="n">
-        <v>0.4624837887422342</v>
+        <v>0.4624836300627455</v>
       </c>
       <c r="AC36" s="3" t="n">
         <v>-0.00581544244160892</v>
@@ -3642,43 +3584,43 @@
         <v>-0.3690530096687293</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>0.02687294959785191</v>
+        <v>0.02687278983144314</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>-0.09105423791601486</v>
+        <v>-0.09105394091193419</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>-0.1355197777238779</v>
+        <v>-0.1355197545267938</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>-0.09533436328832523</v>
+        <v>-0.09533454241643236</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>0.2396257748706885</v>
+        <v>0.2396259937413923</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>0.6418626893858304</v>
+        <v>0.6418625760573431</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>-0.2862666677850574</v>
+        <v>-0.2862667445381945</v>
       </c>
       <c r="X37" s="2" t="n">
-        <v>0.0327100378247267</v>
+        <v>0.03270996249017166</v>
       </c>
       <c r="Y37" s="2" t="n">
-        <v>1.278826767806233</v>
+        <v>1.278826934043034</v>
       </c>
       <c r="Z37" s="2" t="n">
-        <v>0.367433956183195</v>
+        <v>0.3674338281376395</v>
       </c>
       <c r="AA37" s="3" t="n">
-        <v>-0.2991040030144363</v>
+        <v>-0.2991038905633677</v>
       </c>
       <c r="AB37" s="3" t="n">
-        <v>-0.1217902322124899</v>
+        <v>-0.1217903576763482</v>
       </c>
       <c r="AC37" s="3" t="n">
-        <v>-0.1919326290360245</v>
+        <v>-0.1919325675715866</v>
       </c>
       <c r="AD37" s="2" t="n">
         <v>0.6004628944135546</v>
@@ -3701,76 +3643,76 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" s="2" t="n">
-        <v>0.12266436354218</v>
+        <v>0.122663983888454</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.08328328199661872</v>
+        <v>0.08328272435370354</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.03447512382095019</v>
+        <v>0.03447568061167661</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0.3534954367758734</v>
+        <v>0.3534948383792673</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0.3012677877356063</v>
+        <v>0.3012682508838336</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.08951360493840754</v>
+        <v>0.08951304378885072</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.3491216913219184</v>
+        <v>0.3491217773772575</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>-0.1815127493633882</v>
+        <v>-0.1815128738790036</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>-0.3987783929167951</v>
+        <v>-0.3987778567737428</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.3057871268923056</v>
+        <v>0.3057863068505846</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>0.2654410627887114</v>
+        <v>0.265441437076509</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>0.05545303327271878</v>
+        <v>0.05545290846650874</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>0.1820657021730272</v>
+        <v>0.1820652570184458</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>0.01163638937397726</v>
+        <v>0.01163666266429209</v>
       </c>
       <c r="S38" s="2" t="n">
-        <v>0.2669108889739458</v>
+        <v>0.266910354895276</v>
       </c>
       <c r="T38" s="2" t="n">
-        <v>0.01616576348655796</v>
+        <v>0.01616562978141212</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>0.07005379680012536</v>
+        <v>0.07005445782992581</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>0.09307290467911677</v>
+        <v>0.09307244635560297</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>-0.04330154155691701</v>
+        <v>-0.04330126134629986</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>0.282053620540061</v>
+        <v>0.2820535761786271</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>-0.05232537964634454</v>
+        <v>-0.05232509551645004</v>
       </c>
       <c r="Z38" s="2" t="n">
-        <v>0.3874417334889684</v>
+        <v>0.3874417563863277</v>
       </c>
       <c r="AA38" s="3" t="n">
-        <v>-0.255143724295674</v>
+        <v>-0.2551438148019204</v>
       </c>
       <c r="AB38" s="2" t="n">
-        <v>0.1189438052447152</v>
+        <v>0.1189436951163747</v>
       </c>
       <c r="AC38" s="2" t="n">
         <v>0.04412310701333366</v>
@@ -3800,70 +3742,70 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" s="2" t="n">
-        <v>0.159979149594387</v>
+        <v>0.1599788121149162</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.1193731422719642</v>
+        <v>0.1193728078568816</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.3527789584709926</v>
+        <v>0.3527789144883835</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>-0.1651528781893769</v>
+        <v>-0.1651525464229233</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>-0.3698223275057073</v>
+        <v>-0.3698223691811452</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.3013733807662466</v>
+        <v>0.3013736955957556</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>0.2839081268027144</v>
+        <v>0.2839078161984918</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>0.08635764557624781</v>
+        <v>0.08635726872534444</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>0.176332442818</v>
+        <v>0.1763331977748364</v>
       </c>
       <c r="R39" s="2" t="n">
-        <v>0.02303430704217879</v>
+        <v>0.02303400535508571</v>
       </c>
       <c r="S39" s="2" t="n">
-        <v>0.3039903776723256</v>
+        <v>0.3039901855024967</v>
       </c>
       <c r="T39" s="2" t="n">
-        <v>0.02432484191372786</v>
+        <v>0.02432506655440947</v>
       </c>
       <c r="U39" s="2" t="n">
-        <v>0.08573701526909594</v>
+        <v>0.08573672135968402</v>
       </c>
       <c r="V39" s="2" t="n">
-        <v>0.04898952224003827</v>
+        <v>0.04898966448740771</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>-0.06026982527713676</v>
+        <v>-0.06026963960154408</v>
       </c>
       <c r="X39" s="2" t="n">
-        <v>0.2891081539954565</v>
+        <v>0.2891077118631593</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>-0.04610442730261188</v>
+        <v>-0.04610464547004178</v>
       </c>
       <c r="Z39" s="2" t="n">
-        <v>0.4053699545037506</v>
+        <v>0.40537045970592</v>
       </c>
       <c r="AA39" s="3" t="n">
-        <v>-0.2625117017118432</v>
+        <v>-0.2625116443466503</v>
       </c>
       <c r="AB39" s="2" t="n">
-        <v>0.1185184146088329</v>
+        <v>0.1185185200810701</v>
       </c>
       <c r="AC39" s="2" t="n">
-        <v>0.04811727376719044</v>
+        <v>0.04811726922990611</v>
       </c>
       <c r="AD39" s="2" t="n">
-        <v>0.03245537752207839</v>
+        <v>0.03245528463476699</v>
       </c>
       <c r="AE39" s="2" t="n">
         <v>0.1251336280499176</v>
@@ -3889,64 +3831,64 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" s="2" t="n">
-        <v>0.09617695130952431</v>
+        <v>0.09617650410095768</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-0.170321514164074</v>
+        <v>-0.1703214961233581</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>-0.3800126793979858</v>
+        <v>-0.3800126090701049</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.7739427542848729</v>
+        <v>0.7739432382956151</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>0.373426218451008</v>
+        <v>0.3734266261604868</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>0.09747210750576119</v>
+        <v>0.0974721950575006</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>0.2069198200348263</v>
+        <v>0.2069196066718628</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>0.4217896762662692</v>
+        <v>0.4217902621646044</v>
       </c>
       <c r="S40" s="2" t="n">
-        <v>0.09854118785383292</v>
+        <v>0.09854032307664262</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>-0.08863951933585701</v>
+        <v>-0.08863936502613368</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>0.03310259114446801</v>
+        <v>0.03310290666068183</v>
       </c>
       <c r="V40" s="2" t="n">
-        <v>0.0421430644615397</v>
+        <v>0.04214296065989664</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>-0.08041090103470749</v>
+        <v>-0.08041080545854573</v>
       </c>
       <c r="X40" s="2" t="n">
-        <v>0.1411619272273896</v>
+        <v>0.1411622243565553</v>
       </c>
       <c r="Y40" s="2" t="n">
-        <v>0.4191372353007716</v>
+        <v>0.4191367182981731</v>
       </c>
       <c r="Z40" s="2" t="n">
         <v>0.4259759726418195</v>
       </c>
       <c r="AA40" s="3" t="n">
-        <v>-0.3163956426122579</v>
+        <v>-0.3163956876184112</v>
       </c>
       <c r="AB40" s="2" t="n">
-        <v>0.2153062607729173</v>
+        <v>0.2153060774382733</v>
       </c>
       <c r="AC40" s="2" t="n">
-        <v>0.1177447037142936</v>
+        <v>0.1177450542654539</v>
       </c>
       <c r="AD40" s="2" t="n">
-        <v>0.08069850222081687</v>
+        <v>0.08069839746618879</v>
       </c>
       <c r="AE40" s="2" t="n">
         <v>0.03138838126977861</v>
@@ -3972,55 +3914,55 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" s="3" t="n">
-        <v>-0.1646345808265789</v>
+        <v>-0.1646342385049538</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.476528403226136</v>
+        <v>-0.4765288484723609</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.3674689290657563</v>
+        <v>-0.3674689566867319</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.2764693565881149</v>
+        <v>0.2764698054038461</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>0.1742602588101281</v>
+        <v>0.1742602461230394</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-0.007296721692629626</v>
+        <v>-0.007296907243468542</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>0.573287794820369</v>
+        <v>0.5732879913454829</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>0.255870085005921</v>
+        <v>0.2558703231955843</v>
       </c>
       <c r="S41" s="2" t="n">
-        <v>0.0305124199551261</v>
+        <v>0.03051203484604237</v>
       </c>
       <c r="T41" s="2" t="n">
-        <v>0.006554776879922564</v>
+        <v>0.006554532692389037</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.00295303803440583</v>
+        <v>-0.00295242980444399</v>
       </c>
       <c r="V41" s="2" t="n">
-        <v>0.3179591068249839</v>
+        <v>0.3179587428676431</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.2572390585508691</v>
+        <v>-0.2572388505037216</v>
       </c>
       <c r="X41" s="2" t="n">
-        <v>0.4129641917475053</v>
+        <v>0.4129644266109056</v>
       </c>
       <c r="Y41" s="2" t="n">
-        <v>0.2797513827805909</v>
+        <v>0.2797511070947136</v>
       </c>
       <c r="Z41" s="2" t="n">
-        <v>0.4969624515932702</v>
+        <v>0.4969623829455005</v>
       </c>
       <c r="AA41" s="3" t="n">
-        <v>-0.2893247034942322</v>
+        <v>-0.2893247690729903</v>
       </c>
       <c r="AB41" s="2" t="n">
         <v>0.6010658347669158</v>
@@ -4055,61 +3997,61 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" s="3" t="n">
-        <v>-0.1506821365737798</v>
+        <v>-0.1506822993505277</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>-0.5788579687471176</v>
+        <v>-0.5788578473746463</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>-0.429838660460776</v>
+        <v>-0.4298389502534872</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.2326527784806309</v>
+        <v>0.2326532853937588</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>0.1042121485762024</v>
+        <v>0.1042121394539564</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>-0.09097361276584648</v>
+        <v>-0.09097352627997435</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>0.7934370505264419</v>
+        <v>0.7934372609693876</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>0.1745139590588733</v>
+        <v>0.1745133246318795</v>
       </c>
       <c r="S42" s="2" t="n">
-        <v>0.04649697582731904</v>
+        <v>0.04649715298121171</v>
       </c>
       <c r="T42" s="2" t="n">
-        <v>0.05068224902395979</v>
+        <v>0.0506823321569867</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>0.01840122212936124</v>
+        <v>0.01840152335418654</v>
       </c>
       <c r="V42" s="2" t="n">
-        <v>0.5964732424444319</v>
+        <v>0.5964726223454122</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>-0.3091889256520354</v>
+        <v>-0.3091889542940907</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>0.4870201930160241</v>
+        <v>0.4870199901290764</v>
       </c>
       <c r="Y42" s="2" t="n">
-        <v>0.2641362578772237</v>
+        <v>0.2641365096931325</v>
       </c>
       <c r="Z42" s="2" t="n">
-        <v>0.4925364467508557</v>
+        <v>0.4925364105503156</v>
       </c>
       <c r="AA42" s="3" t="n">
-        <v>-0.2625423239357253</v>
+        <v>-0.2625422056463846</v>
       </c>
       <c r="AB42" s="2" t="n">
-        <v>0.6889402969026672</v>
+        <v>0.6889403170627282</v>
       </c>
       <c r="AC42" s="2" t="n">
-        <v>0.0205877271810142</v>
+        <v>0.02058764885353948</v>
       </c>
       <c r="AD42" s="3" t="n">
         <v>-0.05262969500840953</v>
@@ -4140,28 +4082,28 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="3" t="n">
-        <v>-0.5946560306334985</v>
+        <v>-0.5946560467181097</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.05435456961995011</v>
+        <v>0.05435507703303499</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>-0.274866492189407</v>
+        <v>-0.2748670691755118</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>-0.4397797388104894</v>
+        <v>-0.4397793896115709</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>-0.1277698317335468</v>
+        <v>-0.12777045504476</v>
       </c>
       <c r="R43" s="2" t="n">
-        <v>0.4911195711992828</v>
+        <v>0.491120593790018</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>-0.04798207624885165</v>
+        <v>-0.04798257561436614</v>
       </c>
       <c r="T43" s="2" t="n">
-        <v>0.03805497134245073</v>
+        <v>0.03805515883846056</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>-0.1689434091396821</v>
@@ -4170,19 +4112,19 @@
         <v>0.2146540711600158</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>-0.09033279733139754</v>
+        <v>-0.09033262495887484</v>
       </c>
       <c r="X43" s="2" t="n">
-        <v>0.4436495353492633</v>
+        <v>0.4436490091398422</v>
       </c>
       <c r="Y43" s="2" t="n">
-        <v>1.418288213026175</v>
+        <v>1.41828828623074</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>-0.2418482310010853</v>
+        <v>-0.2418480488979202</v>
       </c>
       <c r="AA43" s="3" t="n">
-        <v>-0.05430038188643904</v>
+        <v>-0.05430047215809775</v>
       </c>
       <c r="AB43" s="3" t="n">
         <v>-0.2040250756715357</v>
@@ -4219,52 +4161,52 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="3" t="n">
-        <v>-0.6617776179225953</v>
+        <v>-0.6617775910089092</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.168757206645842</v>
+        <v>0.1687569713748087</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>-0.2850141277497227</v>
+        <v>-0.2850141851231288</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>-0.6339614398371209</v>
+        <v>-0.6339612663949435</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>-0.3079301647620043</v>
+        <v>-0.3079303459138998</v>
       </c>
       <c r="R44" s="2" t="n">
-        <v>1.278980419375238</v>
+        <v>1.278980855528491</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>-0.01236204091692172</v>
+        <v>-0.01236210036896779</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>-0.08741755993644829</v>
+        <v>-0.08741767798528788</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>-0.432380701037577</v>
+        <v>-0.4323806626468214</v>
       </c>
       <c r="V44" s="2" t="n">
-        <v>0.5437600961533307</v>
+        <v>0.5437599769983159</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>-0.2566466837456334</v>
+        <v>-0.2566466263699554</v>
       </c>
       <c r="X44" s="2" t="n">
-        <v>0.6653170050408019</v>
+        <v>0.6653169012073648</v>
       </c>
       <c r="Y44" s="2" t="n">
-        <v>2.339563982579255</v>
+        <v>2.339564190802931</v>
       </c>
       <c r="Z44" s="3" t="n">
         <v>-0.2509731316924508</v>
       </c>
       <c r="AA44" s="3" t="n">
-        <v>-0.05235802755323582</v>
+        <v>-0.05235812725736377</v>
       </c>
       <c r="AB44" s="3" t="n">
-        <v>-0.2678983130274255</v>
+        <v>-0.2678982360009006</v>
       </c>
       <c r="AC44" s="3" t="n">
         <v>-0.3761248542296416</v>
@@ -4303,37 +4245,37 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" s="2" t="n">
-        <v>0.2734687845869137</v>
+        <v>0.2734688779389074</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>-0.01469133233164099</v>
+        <v>-0.0146913312546888</v>
       </c>
       <c r="T45" s="2" t="n">
-        <v>0.1837348510188996</v>
+        <v>0.1837349117476315</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>-0.08537199844206245</v>
+        <v>-0.08537217626212068</v>
       </c>
       <c r="V45" s="2" t="n">
-        <v>0.6973136608531185</v>
+        <v>0.697313777487395</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>-0.3380127547857977</v>
+        <v>-0.3380127952715261</v>
       </c>
       <c r="X45" s="2" t="n">
-        <v>0.2992088740555237</v>
+        <v>0.2992090758281158</v>
       </c>
       <c r="Y45" s="2" t="n">
-        <v>0.5822870852713353</v>
+        <v>0.5822871245974657</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>-0.4901065528706443</v>
+        <v>-0.4901066730482555</v>
       </c>
       <c r="AA45" s="3" t="n">
-        <v>-0.1723761601453321</v>
+        <v>-0.1723760052231051</v>
       </c>
       <c r="AB45" s="3" t="n">
-        <v>-0.09057855229496115</v>
+        <v>-0.09057861640718068</v>
       </c>
       <c r="AC45" s="2" t="n">
         <v>0.1201438450169943</v>
@@ -4646,97 +4588,97 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.08709126977614901</v>
+        <v>0.08709101247374029</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.003973151669812269</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.3804897524332094</v>
+        <v>0.3804898970100001</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.2249747813475809</v>
+        <v>0.2249742341432241</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.3347518867997925</v>
+        <v>0.3347522577612587</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.2869241778911085</v>
+        <v>0.286923876005676</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.2038937201424234</v>
+        <v>0.2038935819436831</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>-0.09741538350613388</v>
+        <v>-0.09741484498504271</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>-0.1175853304500893</v>
+        <v>-0.1175852172972258</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.2158466901776195</v>
+        <v>-0.2158461557787353</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2818163999290109</v>
+        <v>0.2818147299755154</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.106979245615481</v>
+        <v>0.1069800017620504</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.04828270027745774</v>
+        <v>0.04828221573843505</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.1584523994212093</v>
+        <v>0.1584527695501243</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0.05146233499237018</v>
+        <v>0.05146216946619941</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>-0.3679502323132643</v>
+        <v>-0.3679499862113675</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0.2635179551518327</v>
+        <v>0.2635174864579464</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>0.150561429083562</v>
+        <v>0.1505616898044895</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.01895022899787202</v>
+        <v>0.01894974581645892</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.1599032284902469</v>
+        <v>0.1599031754034619</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.3230776063002299</v>
+        <v>0.3230778733786235</v>
       </c>
       <c r="X2" s="2" t="n">
         <v>0.1346382035518612</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>0.01234302954546029</v>
+        <v>0.01234293990184376</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.1199787584740741</v>
+        <v>0.1199786805476291</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.2170536574042266</v>
+        <v>0.2170541661142029</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>-0.04568976796320345</v>
+        <v>-0.04568995098214368</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>0.3122385439962228</v>
+        <v>0.3122384546666328</v>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>0.1833162400611312</v>
+        <v>0.1833163438139214</v>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>0.2872875598052143</v>
+        <v>0.2872876222956082</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>-0.1817536364465472</v>
+        <v>-0.1817536116873572</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>0.2617579498645455</v>
+        <v>0.2617577398036186</v>
       </c>
       <c r="AH2" s="2" t="n">
         <v>0.2488646784300117</v>
@@ -4766,85 +4708,85 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" s="2" t="n">
-        <v>0.7894733113230272</v>
+        <v>0.7894743367637653</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0.3611490753314831</v>
+        <v>-0.3611491303051623</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.3334474422103997</v>
+        <v>-0.3334477262205851</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>-0.373682685592613</v>
+        <v>-0.3736827290221612</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.4966855933208252</v>
+        <v>0.4966865205134561</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.105385364615052</v>
+        <v>0.1053852568938243</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.01565470876160302</v>
+        <v>0.01565414268702603</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.07144086889292267</v>
+        <v>0.07144099510440904</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>0.1902796177077575</v>
+        <v>0.1902803588048496</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>-0.4172715152925822</v>
+        <v>-0.417271774755701</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0.5468414005158444</v>
+        <v>0.5468406911933703</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0.2014374307426501</v>
+        <v>0.2014382766732943</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.03475815655275216</v>
+        <v>0.03475766568229233</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1811251687161162</v>
+        <v>0.181125505800698</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.366341776840015</v>
+        <v>0.3663415980589178</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.1918139654967512</v>
+        <v>0.1918138697326006</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>0.09435920568914979</v>
+        <v>0.09435913291946374</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.07097900508772881</v>
+        <v>0.07097908893420102</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.3266353775768713</v>
+        <v>0.326635331412815</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>-0.001262172909420212</v>
+        <v>-0.001262173039872194</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>0.3896156808234486</v>
+        <v>0.3896157211431244</v>
       </c>
       <c r="AD3" s="2" t="n">
-        <v>0.4840611324606401</v>
+        <v>0.4840613919213803</v>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>0.274197412277396</v>
+        <v>0.2741971840371769</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>-0.3257699488538589</v>
+        <v>-0.3257699745127801</v>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0.5485556424440821</v>
+        <v>0.5485555897060994</v>
       </c>
       <c r="AH3" s="2" t="n">
-        <v>0.2557824658546981</v>
+        <v>0.2557827307615477</v>
       </c>
       <c r="AI3" s="2" t="n">
-        <v>0.2077255566107012</v>
+        <v>0.2077254840592282</v>
       </c>
       <c r="AJ3" s="2" t="n">
         <v>0.1757086522525462</v>
@@ -4869,82 +4811,82 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.05612840907657812</v>
+        <v>0.0561277924500696</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.01777370946481294</v>
+        <v>0.01777359889947694</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>-0.2037033717649597</v>
+        <v>-0.2037032852596659</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.4790243672180816</v>
+        <v>0.4790239579440967</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1805351872515237</v>
+        <v>0.1805360673659417</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.04462772710196949</v>
+        <v>0.04462770618039169</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.1827280996285716</v>
+        <v>0.1827271948717046</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-0.01789762777745529</v>
+        <v>-0.01789782315687949</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>-0.3414073177587155</v>
+        <v>-0.3414069784910211</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>0.2848652537896044</v>
+        <v>0.284865058243805</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.2691840844335081</v>
+        <v>0.2691845819761955</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>-0.0442675647671128</v>
+        <v>-0.04426785393304367</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.1670379029925793</v>
+        <v>0.1670375998036189</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.3869662270012622</v>
+        <v>0.3869671043719642</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.05036343902755513</v>
+        <v>0.05036295832936077</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.04478918039496371</v>
+        <v>-0.04478933459988921</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.2159129766069121</v>
+        <v>0.2159135841326776</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.1458255220539699</v>
+        <v>0.1458254307187068</v>
       </c>
       <c r="AB4" s="3" t="n">
-        <v>-0.1112123484655915</v>
+        <v>-0.1112125579406805</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>0.2538973571025214</v>
+        <v>0.253897638347951</v>
       </c>
       <c r="AD4" s="2" t="n">
-        <v>0.2003078203301336</v>
+        <v>0.2003077008813063</v>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>0.1453603498586749</v>
+        <v>0.1453606814908457</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.2048478634695995</v>
+        <v>-0.2048480937010309</v>
       </c>
       <c r="AG4" s="2" t="n">
         <v>0.1682765143756559</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>0.1138421815157322</v>
+        <v>0.1138422594374719</v>
       </c>
       <c r="AI4" s="2" t="n">
-        <v>0.1265761275243331</v>
+        <v>0.1265760487117622</v>
       </c>
       <c r="AJ4" s="2" t="n">
         <v>0.1921966236819175</v>
@@ -4965,55 +4907,55 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
-        <v>0.194692991107744</v>
+        <v>0.1946924668386916</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1060664382331296</v>
+        <v>0.1060671356068026</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.07751994499856052</v>
+        <v>-0.07752026885774099</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.4875231656634254</v>
+        <v>0.487523654580958</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.08175271655253158</v>
+        <v>0.08175253112571479</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>-0.1997797924074824</v>
+        <v>-0.1997793696555572</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>-0.1083038832047625</v>
+        <v>-0.1083041855784455</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.5352572102511495</v>
+        <v>0.5352567787736333</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2276910291311351</v>
+        <v>0.2276915831116719</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.2752768858428001</v>
+        <v>0.275277065677471</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.1692115926793509</v>
+        <v>0.1692112673900434</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.2841932128642157</v>
+        <v>0.2841927375491713</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-0.4443312110715284</v>
+        <v>-0.4443309374619867</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>0.5315342362712632</v>
+        <v>0.531534034570772</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.1978431460331509</v>
+        <v>0.1978430244315244</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>-0.1240305557521284</v>
+        <v>-0.1240307252520569</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.09086606358578186</v>
+        <v>0.09086627466820829</v>
       </c>
       <c r="W5" s="2" t="n">
         <v>0.05309446150069275</v>
@@ -5022,31 +4964,31 @@
         <v>0.01121397286351966</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2390935719514846</v>
+        <v>-0.2390936552368594</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.2381644973503565</v>
+        <v>0.2381647423297426</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.1573163916174964</v>
+        <v>0.1573162893091158</v>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>-0.1716729657405696</v>
+        <v>-0.1716728893557529</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>0.2757984687017827</v>
+        <v>0.2757984432688165</v>
       </c>
       <c r="AD5" s="2" t="n">
-        <v>0.05517983578807462</v>
+        <v>0.05517975951880638</v>
       </c>
       <c r="AE5" s="2" t="n">
-        <v>0.2697563612729561</v>
+        <v>0.2697564982748719</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1295436043704444</v>
+        <v>-0.1295436443412861</v>
       </c>
       <c r="AG5" s="2" t="n">
-        <v>0.1472577089391696</v>
+        <v>0.1472576378357997</v>
       </c>
       <c r="AH5" s="2" t="n">
         <v>0.1237909403449178</v>
@@ -5073,91 +5015,91 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" s="3" t="n">
-        <v>-0.1327799458386567</v>
+        <v>-0.1327803142983294</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-0.2436508989350035</v>
+        <v>-0.2436503286303787</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.04030925672533581</v>
+        <v>0.04030870902473138</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.6086766852041083</v>
+        <v>0.6086768297981771</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0.2628794581944778</v>
+        <v>-0.2628795693916365</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-0.3030508202176589</v>
+        <v>-0.3030508996641247</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-0.09857365395464668</v>
+        <v>-0.09857323379781202</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.387353347517714</v>
+        <v>0.3873530406495544</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1374252974357173</v>
+        <v>0.1374249380670194</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.2433663520268157</v>
+        <v>0.2433669038909538</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.05852071646876045</v>
+        <v>0.05852100166321317</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-0.05502575811779764</v>
+        <v>-0.05502619968129929</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.2696942883876148</v>
+        <v>-0.2696941894905446</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>0.03143962430511582</v>
+        <v>0.03143901066341082</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.1359262165652728</v>
+        <v>0.135926738544577</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.1475753972446057</v>
+        <v>-0.1475755706154457</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.09220192035273023</v>
+        <v>0.09220248146682763</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.2599683010602274</v>
+        <v>0.2599679100164534</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.0622613800336872</v>
+        <v>-0.06226187268116989</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.09170788179342981</v>
+        <v>0.0917086654729149</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.02761806995353489</v>
+        <v>0.02761787214744427</v>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.2426432808128791</v>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>-0.1410103785552418</v>
+        <v>-0.1410106800361385</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0.1933775007598533</v>
+        <v>0.1933780950873445</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.1540103347975315</v>
+        <v>0.1540103121503664</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.01155419018346504</v>
+        <v>0.01155406128627789</v>
       </c>
       <c r="AF6" s="3" t="n">
         <v>-0.1772326366404656</v>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>0.2029326719624513</v>
+        <v>0.2029325954101702</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>0.07034733834839302</v>
+        <v>0.07034740646320725</v>
       </c>
       <c r="AI6" s="2" t="n">
         <v>0.25840587896048</v>
@@ -5181,76 +5123,76 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
-        <v>0.1321080687370997</v>
+        <v>0.1321085176627861</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>-0.1211985584715157</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.04203110510630048</v>
+        <v>0.04203102539172332</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.1923843180556466</v>
+        <v>0.1923847152690792</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0.1187256846783962</v>
+        <v>-0.1187259749928209</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.01895253290965848</v>
+        <v>0.01895246148967455</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.01161170293902369</v>
+        <v>-0.01161163315258296</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.5526761711795394</v>
+        <v>0.5526757051347433</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2940543923712207</v>
+        <v>0.2940544087788797</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.1665371405217766</v>
+        <v>0.1665374882447876</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.3089307333214744</v>
+        <v>0.3089308140566593</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.28246923316596</v>
+        <v>0.2824688561849484</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-0.4799993180374824</v>
+        <v>-0.4799990916962074</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>0.681573554089014</v>
+        <v>0.6815730338031381</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.1532688030636751</v>
+        <v>0.1532684926602521</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>-0.1157186617972454</v>
+        <v>-0.1157184209042023</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.2403546266328616</v>
+        <v>0.2403546662473723</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.01817257826963026</v>
+        <v>0.01817264712381683</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>-0.04641873561362042</v>
+        <v>-0.04641854288179759</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.09942151985025316</v>
+        <v>-0.09942143781339241</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1110632492977319</v>
+        <v>0.1110629200424054</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0.1988169519161544</v>
+        <v>0.1988170339020838</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>-0.1203503764195599</v>
+        <v>-0.1203504334666562</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>0.2244539764012408</v>
+        <v>0.2244540558096171</v>
       </c>
       <c r="AD7" s="2" t="n">
         <v>0.08286355968129189</v>
@@ -5289,79 +5231,79 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>-0.03698554566039025</v>
+        <v>-0.03698543895479733</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-0.444095585058649</v>
+        <v>-0.4440959236642169</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.05096721778410651</v>
+        <v>-0.05096674487715958</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.5266628518946077</v>
+        <v>0.5266629569076025</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0.2644575912788186</v>
+        <v>-0.2644576418738179</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>-0.2088961558103779</v>
+        <v>-0.2088957817409807</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>-0.1421946196400374</v>
+        <v>-0.1421947888263972</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.4509837184292036</v>
+        <v>0.450983318519131</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2416906501228544</v>
+        <v>0.241690175249947</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.1427250697303932</v>
+        <v>0.1427253537787172</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.457982023042586</v>
+        <v>0.4579820843525</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.2790502848438465</v>
+        <v>0.2790502186473411</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>-0.4614975929646989</v>
+        <v>-0.4614973002909863</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>0.6797393837191477</v>
+        <v>0.6797385786460304</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0.2460922721918315</v>
+        <v>0.246091974273996</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>-0.186213718274886</v>
+        <v>-0.1862135228184417</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.3173769656834919</v>
+        <v>0.3173770687843807</v>
       </c>
       <c r="W8" s="2" t="n">
         <v>9.433931999880407e-05</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.0269118513105453</v>
+        <v>0.02691173250648871</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1831602139073069</v>
+        <v>-0.1831600037159827</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.006919216254135385</v>
+        <v>0.006919286090116161</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0.3478349637434623</v>
+        <v>0.3478345387077886</v>
       </c>
       <c r="AB8" s="3" t="n">
-        <v>-0.1133985674432506</v>
+        <v>-0.113398579277412</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>0.1453482048775803</v>
+        <v>0.1453485751064041</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>-0.08475178256128324</v>
+        <v>-0.0847519706803016</v>
       </c>
       <c r="AE8" s="2" t="n">
         <v>0.05469039311499135</v>
@@ -5370,10 +5312,10 @@
         <v>-0.09805176374595892</v>
       </c>
       <c r="AG8" s="2" t="n">
-        <v>0.06149141014752857</v>
+        <v>0.0614915281845958</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>0.2210094335898516</v>
+        <v>0.2210092978145122</v>
       </c>
       <c r="AI8" s="2" t="n">
         <v>0.3135403505873617</v>
@@ -5397,82 +5339,82 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
-        <v>0.2028153391870058</v>
+        <v>0.2028145433635666</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-0.2594924742250451</v>
+        <v>-0.25949249708763</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>-0.08954567047987894</v>
+        <v>-0.08954550007239492</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.5664996602225032</v>
+        <v>0.566499789384644</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0.1761163595186885</v>
+        <v>-0.1761162396043491</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>-0.1818030211407777</v>
+        <v>-0.1818031978012136</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.1743634360344142</v>
+        <v>-0.1743631498104488</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.3860340800518631</v>
+        <v>0.3860340295754947</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2365698172711952</v>
+        <v>0.2365695119383373</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.07300527082829333</v>
+        <v>0.073005663419619</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>0.2930411967624584</v>
+        <v>0.2930412053567397</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.3941290738916821</v>
+        <v>0.3941289872046541</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>-0.5032362884595452</v>
+        <v>-0.503236169624669</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>0.5510675730920815</v>
+        <v>0.551066957343461</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0.2414038172677968</v>
+        <v>0.2414034077600087</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>-0.1618306201958896</v>
+        <v>-0.1618305911110268</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.2928361390963692</v>
+        <v>0.2928368158829016</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.0953969954615479</v>
+        <v>0.09539697368095612</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.03284096697804495</v>
+        <v>0.03284096013295157</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.0117506516087591</v>
+        <v>-0.01175071650546333</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.01348622288898493</v>
+        <v>0.01348608491726733</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>0.3646321825864189</v>
+        <v>0.3646323169106711</v>
       </c>
       <c r="AB9" s="3" t="n">
-        <v>-0.08754966784421547</v>
+        <v>-0.0875497576590375</v>
       </c>
       <c r="AC9" s="2" t="n">
         <v>0.1073417865173159</v>
       </c>
       <c r="AD9" s="2" t="n">
-        <v>0.04169008804620189</v>
+        <v>0.04169018546615155</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>-0.03494825480370867</v>
+        <v>-0.03494834505635158</v>
       </c>
       <c r="AF9" s="3" t="n">
         <v>-0.06806281098926781</v>
@@ -5509,73 +5451,73 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" s="3" t="n">
-        <v>-0.4286956973271007</v>
+        <v>-0.428696076613726</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.02059166859981243</v>
+        <v>0.02059188154973812</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2439704546204352</v>
+        <v>-0.2439705299108694</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.3819024784734104</v>
+        <v>0.3819028898004642</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.0803280089100511</v>
+        <v>0.08032790426384229</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.04637664578300638</v>
+        <v>0.04637673544580068</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>0.1875484356132391</v>
+        <v>0.18754850523126</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>0.06377507450655884</v>
+        <v>0.06377492099091353</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>-0.4535247487976419</v>
+        <v>-0.4535247827127413</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>0.7378378762489033</v>
+        <v>0.7378378599787154</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>0.2277730546764667</v>
+        <v>0.2277731423687668</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>-0.2178387193079494</v>
+        <v>-0.2178387774814549</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.1865625640092707</v>
+        <v>0.1865628753862776</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>0.07873936039082063</v>
+        <v>0.07873915754036953</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>0.06872255358196244</v>
+        <v>0.06872243736975525</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.1285423749676772</v>
+        <v>-0.1285422258362356</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1771128389496752</v>
+        <v>0.1771130150677773</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>0.2681203565594186</v>
+        <v>0.2681199817037072</v>
       </c>
       <c r="AB10" s="3" t="n">
-        <v>-0.09898123739440723</v>
+        <v>-0.0989812456683945</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>0.3335852467200311</v>
+        <v>0.3335852776682009</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.3150402887112997</v>
+        <v>0.3150402410602611</v>
       </c>
       <c r="AE10" s="2" t="n">
-        <v>0.2888195149945163</v>
+        <v>0.2888197571586626</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.2889831353058531</v>
+        <v>-0.2889831936753585</v>
       </c>
       <c r="AG10" s="2" t="n">
         <v>0.2899659327887845</v>
@@ -5609,76 +5551,76 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" s="3" t="n">
-        <v>-0.377777846779095</v>
+        <v>-0.377777795778119</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.4566920121979663</v>
+        <v>0.4566921300786337</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0.03613832168389419</v>
+        <v>0.03613771513474884</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0.3776840392960825</v>
+        <v>0.3776844353833322</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.1722820876066393</v>
+        <v>0.1722821919491995</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>0.538979880350019</v>
+        <v>0.5389799213845239</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>0.1113842629602122</v>
+        <v>0.1113840187332304</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>0.3171366638610498</v>
+        <v>0.3171369050258188</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.5597196881279538</v>
+        <v>-0.5597197624279239</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>0.7176741362040593</v>
+        <v>0.7176744698174147</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>0.295532145876064</v>
+        <v>0.2955320105101138</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>-0.1349667759684304</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>0.2193312549944977</v>
+        <v>0.2193314414650696</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0.03567685644947916</v>
+        <v>0.03567677452920193</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-0.1348448944611367</v>
+        <v>-0.1348448845055054</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>-0.08000108549409524</v>
+        <v>-0.08000107866699635</v>
       </c>
       <c r="Z11" s="2" t="n">
-        <v>0.08436177613698548</v>
+        <v>0.08436176831172659</v>
       </c>
       <c r="AA11" s="2" t="n">
-        <v>0.4497177502585716</v>
+        <v>0.4497176262469869</v>
       </c>
       <c r="AB11" s="3" t="n">
-        <v>-0.2036930607890504</v>
+        <v>-0.203693178800835</v>
       </c>
       <c r="AC11" s="2" t="n">
-        <v>0.07965726048469923</v>
+        <v>0.07965756868759066</v>
       </c>
       <c r="AD11" s="2" t="n">
-        <v>0.3943196422057482</v>
+        <v>0.3943197253442892</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>-0.07584284014972797</v>
+        <v>-0.07584302210823524</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>-0.2658970710362862</v>
+        <v>-0.2658971242986938</v>
       </c>
       <c r="AG11" s="2" t="n">
-        <v>0.1905146132207638</v>
+        <v>0.1905146995978599</v>
       </c>
       <c r="AH11" s="3" t="n">
         <v>-0.2048391645929544</v>
@@ -5720,49 +5662,49 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" s="3" t="n">
-        <v>-0.2076361365450757</v>
+        <v>-0.2076361158609202</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>0.2321333595421164</v>
+        <v>0.2321332046362385</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.0218341279710399</v>
+        <v>0.02183423000682727</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>0.06841092307649288</v>
+        <v>0.0684110161008038</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>-0.08995008863442788</v>
+        <v>-0.08995044566748434</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>-0.00323000388204342</v>
+        <v>-0.003229799146320045</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>0.5466973029941511</v>
+        <v>0.5466971999617956</v>
       </c>
       <c r="AB12" s="3" t="n">
-        <v>-0.1978642348670173</v>
+        <v>-0.1978641814331988</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>0.2372055509492528</v>
+        <v>0.2372054679029274</v>
       </c>
       <c r="AD12" s="2" t="n">
-        <v>0.2777884430535136</v>
+        <v>0.2777881260792299</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>-0.2174200048055794</v>
+        <v>-0.2174198106765005</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>-0.227634853813637</v>
+        <v>-0.2276348019678395</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>-0.1129153272797259</v>
+        <v>-0.1129154141894146</v>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>0.1773301795410216</v>
+        <v>0.1773301969144614</v>
       </c>
       <c r="AI12" s="2" t="n">
-        <v>0.3103955030280083</v>
+        <v>0.3103956120733888</v>
       </c>
       <c r="AJ12" s="3" t="n">
         <v>-0.0872315280571081</v>
@@ -5791,64 +5733,64 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" s="2" t="n">
-        <v>0.03373093925400328</v>
+        <v>0.03373102414481433</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>0.1332175922789367</v>
+        <v>0.1332173349766252</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>0.8316829473285718</v>
+        <v>0.8316835026692473</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>0.5475516378659668</v>
+        <v>0.5475520259710684</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>-0.4778982078583286</v>
+        <v>-0.4778982680286286</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>0.4734340231512284</v>
+        <v>0.4734339819907305</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>0.03539098430192666</v>
+        <v>0.03539064257149827</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>-0.1754238581233238</v>
+        <v>-0.175423740999251</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>0.1916206384090142</v>
+        <v>0.191620857038695</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>-0.02139414043737919</v>
+        <v>-0.0213940695162389</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>0.1145243325937364</v>
+        <v>0.114523827055897</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>-0.1290533656227706</v>
+        <v>-0.1290532612854711</v>
       </c>
       <c r="Z13" s="2" t="n">
-        <v>0.01063815300723392</v>
+        <v>0.01063794668420326</v>
       </c>
       <c r="AA13" s="2" t="n">
-        <v>0.3625826710440321</v>
+        <v>0.3625830853178822</v>
       </c>
       <c r="AB13" s="3" t="n">
-        <v>-0.132805570516027</v>
+        <v>-0.1328057570197039</v>
       </c>
       <c r="AC13" s="2" t="n">
-        <v>0.1490181497852563</v>
+        <v>0.149018051768175</v>
       </c>
       <c r="AD13" s="2" t="n">
-        <v>0.08917627029070907</v>
+        <v>0.08917658889871505</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>-0.2006293769882014</v>
+        <v>-0.2006293585231362</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>-0.206587346179353</v>
+        <v>-0.2065874950966796</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>-0.1242188155280013</v>
+        <v>-0.1242187519839795</v>
       </c>
       <c r="AH13" s="2" t="n">
         <v>0.2898039959046443</v>
@@ -5891,28 +5833,28 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" s="3" t="n">
-        <v>-0.01452861287499829</v>
+        <v>-0.01452901799551976</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>-0.05222167028116675</v>
+        <v>-0.05222175371196114</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>0.217540251129088</v>
+        <v>0.2175402702786686</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>-0.07112342036983732</v>
+        <v>-0.0711234255120371</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>-0.01639038661875314</v>
+        <v>-0.01639038789450875</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>0.3607702451884405</v>
+        <v>0.3607703528697523</v>
       </c>
       <c r="AB14" s="3" t="n">
-        <v>-0.06669446758603159</v>
+        <v>-0.06669440943322291</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>0.06488507738489746</v>
+        <v>0.06488501103357724</v>
       </c>
       <c r="AD14" s="2" t="n">
         <v>0.1482803590102222</v>
@@ -5965,46 +5907,46 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" s="2" t="n">
-        <v>0.3414849809441771</v>
+        <v>0.3414848620496349</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>0.01934993780899408</v>
+        <v>0.01934993952396091</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>0.04514921651947912</v>
+        <v>0.04514930739169976</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>-0.2330170868598542</v>
+        <v>-0.2330171700505017</v>
       </c>
       <c r="X15" s="2" t="n">
-        <v>0.2182568817389858</v>
+        <v>0.2182572308066093</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>-0.2280432250593805</v>
+        <v>-0.228043362518274</v>
       </c>
       <c r="Z15" s="2" t="n">
-        <v>0.1699939726506428</v>
+        <v>0.1699938573167477</v>
       </c>
       <c r="AA15" s="2" t="n">
-        <v>0.1939792045015545</v>
+        <v>0.1939795193528335</v>
       </c>
       <c r="AB15" s="3" t="n">
-        <v>-0.1088021831852169</v>
+        <v>-0.1088024129034059</v>
       </c>
       <c r="AC15" s="2" t="n">
-        <v>0.05300037723347795</v>
+        <v>0.05300019686179147</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>-0.07131441372977143</v>
+        <v>-0.07131443255206826</v>
       </c>
       <c r="AE15" s="3" t="n">
-        <v>-0.005991727081606002</v>
+        <v>-0.005991349848923133</v>
       </c>
       <c r="AF15" s="3" t="n">
-        <v>-0.001599216212507026</v>
+        <v>-0.001599406669874681</v>
       </c>
       <c r="AG15" s="2" t="n">
-        <v>0.02561784903578324</v>
+        <v>0.02561794693876651</v>
       </c>
       <c r="AH15" s="3" t="n">
         <v>-0.1301471701692136</v>
@@ -6031,70 +5973,70 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="n">
-        <v>0.1209357690489603</v>
+        <v>0.1209355228172746</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.6672127568062469</v>
+        <v>-0.6672125189544502</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-0.2443208371397944</v>
+        <v>-0.2443212112461065</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1.060445232140412</v>
+        <v>1.060446324005818</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0.2748165002655945</v>
+        <v>-0.2748166725858389</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.04377287430000121</v>
+        <v>0.0437722769173412</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-0.01675575316773392</v>
+        <v>-0.01675554783277855</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0.3248849214139053</v>
+        <v>0.3248850157484777</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0.133223735300867</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-0.005740115305001292</v>
+        <v>-0.005740399849457067</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>0.3638608905058254</v>
+        <v>0.3638610900339476</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>0.4460572677595629</v>
+        <v>0.4460578897217595</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-0.4017419379803716</v>
+        <v>-0.4017421116056965</v>
       </c>
       <c r="S16" s="2" t="n">
         <v>0.4942061844951109</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>0.3902071369476019</v>
+        <v>0.3902070287284083</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-0.02604408955913551</v>
+        <v>-0.02604393589862852</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>0.1478204150244635</v>
+        <v>0.1478201634332932</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>0.07838452767453807</v>
+        <v>0.07838467785562453</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.1148865018404365</v>
+        <v>-0.1148864372693804</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-0.2059477417947095</v>
+        <v>-0.2059478726749195</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0.04029145185897576</v>
+        <v>-0.04029145556068925</v>
       </c>
       <c r="AA16" s="2" t="n">
-        <v>0.2424720380685867</v>
+        <v>0.2424721570111086</v>
       </c>
       <c r="AB16" s="3" t="n">
         <v>-0.06283315745742613</v>
@@ -6103,19 +6045,19 @@
         <v>-0.01410236952891086</v>
       </c>
       <c r="AD16" s="2" t="n">
-        <v>0.03123722566077158</v>
+        <v>0.03123714227055219</v>
       </c>
       <c r="AE16" s="3" t="n">
-        <v>-0.07402587898423185</v>
+        <v>-0.07402580410602788</v>
       </c>
       <c r="AF16" s="3" t="n">
-        <v>-0.06002608861728842</v>
+        <v>-0.06002591395961099</v>
       </c>
       <c r="AG16" s="3" t="n">
-        <v>-0.03611993146539816</v>
+        <v>-0.03612001765949291</v>
       </c>
       <c r="AH16" s="2" t="n">
-        <v>0.1946160482775963</v>
+        <v>0.1946159331320385</v>
       </c>
       <c r="AI16" s="2" t="n">
         <v>0.1573815659295486</v>
@@ -6151,55 +6093,55 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" s="3" t="n">
-        <v>-0.5247849603188759</v>
+        <v>-0.5247851967769072</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>0.8142833706006254</v>
+        <v>0.8142835523366176</v>
       </c>
       <c r="T17" s="2" t="n">
-        <v>0.5674936846023013</v>
+        <v>0.5674939810443946</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>-0.04227057601221273</v>
+        <v>-0.04227057975656634</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>0.4013699096389052</v>
+        <v>0.4013702242323842</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>-0.1455999179489724</v>
+        <v>-0.1456000307295313</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>0.1555964346791849</v>
+        <v>0.1555965891732274</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>-0.2202589694990974</v>
+        <v>-0.2202588732062207</v>
       </c>
       <c r="Z17" s="2" t="n">
-        <v>0.2632270911621302</v>
+        <v>0.2632271091924319</v>
       </c>
       <c r="AA17" s="2" t="n">
-        <v>0.3145109319121928</v>
+        <v>0.3145105750768975</v>
       </c>
       <c r="AB17" s="3" t="n">
-        <v>-0.08247070975991644</v>
+        <v>-0.08247081301454362</v>
       </c>
       <c r="AC17" s="2" t="n">
-        <v>0.08317702150913719</v>
+        <v>0.08317703086950679</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>-0.09894140403494911</v>
+        <v>-0.0989412065264923</v>
       </c>
       <c r="AE17" s="2" t="n">
-        <v>0.0186950780197237</v>
+        <v>0.01869484526002463</v>
       </c>
       <c r="AF17" s="2" t="n">
-        <v>0.01220790783395742</v>
+        <v>0.01220802240178553</v>
       </c>
       <c r="AG17" s="3" t="n">
-        <v>-0.1262627380835768</v>
+        <v>-0.1262626262626263</v>
       </c>
       <c r="AH17" s="3" t="n">
-        <v>-0.02210535651598333</v>
+        <v>-0.02210548166698623</v>
       </c>
       <c r="AI17" s="2" t="n">
         <v>0.02356683530096615</v>
@@ -6237,49 +6179,49 @@
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" s="2" t="n">
-        <v>0.0002345590851342561</v>
+        <v>0.0002343777271345271</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>-0.04452377678293584</v>
+        <v>-0.04452378081888797</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>0.4788967701502018</v>
+        <v>0.478896720712543</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>-0.07632270753787407</v>
+        <v>-0.07632278148001359</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>0.2210085267966435</v>
+        <v>0.2210087811959978</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>-0.1084398320319828</v>
+        <v>-0.1084397182725909</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>-0.03292528388006777</v>
+        <v>-0.03292553487063787</v>
       </c>
       <c r="AA18" s="2" t="n">
-        <v>0.2019661439246696</v>
+        <v>0.2019660386320457</v>
       </c>
       <c r="AB18" s="3" t="n">
-        <v>-0.1749688225272101</v>
+        <v>-0.1749686413995436</v>
       </c>
       <c r="AC18" s="2" t="n">
-        <v>0.08496901338440321</v>
+        <v>0.08496888033467864</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>-0.03948274430681142</v>
+        <v>-0.03948268783358422</v>
       </c>
       <c r="AE18" s="3" t="n">
-        <v>-0.02230759424672113</v>
+        <v>-0.02230765950612346</v>
       </c>
       <c r="AF18" s="3" t="n">
-        <v>-0.1587254970965349</v>
+        <v>-0.1587253872397171</v>
       </c>
       <c r="AG18" s="2" t="n">
-        <v>0.01273886240122479</v>
+        <v>0.01273894001190867</v>
       </c>
       <c r="AH18" s="3" t="n">
-        <v>-0.01411100745024774</v>
+        <v>-0.01411108300330077</v>
       </c>
       <c r="AI18" s="2" t="n">
         <v>0.01557960977014239</v>
@@ -6316,43 +6258,43 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" s="3" t="n">
-        <v>-0.01892691649496403</v>
+        <v>-0.0189264428985193</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>0.04031554471795595</v>
+        <v>0.04031534153275484</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>-0.4383102016126307</v>
+        <v>-0.4383102954837479</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>0.2640054883095579</v>
+        <v>0.2640055324308761</v>
       </c>
       <c r="W19" s="2" t="n">
-        <v>0.0778703133457741</v>
+        <v>0.07787038974992133</v>
       </c>
       <c r="X19" s="2" t="n">
-        <v>0.05156319430197431</v>
+        <v>0.05156338146169115</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>-0.2009722541065453</v>
+        <v>-0.2009721140131934</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>-0.09635361084062433</v>
+        <v>-0.09635409367174941</v>
       </c>
       <c r="AA19" s="2" t="n">
-        <v>0.3857565073311073</v>
+        <v>0.3857568431479825</v>
       </c>
       <c r="AB19" s="3" t="n">
-        <v>-0.1682593340584053</v>
+        <v>-0.1682593923501834</v>
       </c>
       <c r="AC19" s="2" t="n">
-        <v>0.09238469206737943</v>
+        <v>0.09238476862615919</v>
       </c>
       <c r="AD19" s="2" t="n">
-        <v>0.09836891200193199</v>
+        <v>0.09836878368801649</v>
       </c>
       <c r="AE19" s="2" t="n">
-        <v>0.2204605039197365</v>
+        <v>0.2204606464966816</v>
       </c>
       <c r="AF19" s="3" t="n">
         <v>-0.4374292092232922</v>
@@ -6389,76 +6331,76 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" s="3" t="n">
-        <v>-0.06678637830551215</v>
+        <v>-0.06678621223478631</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-0.2269143177018487</v>
+        <v>-0.2269141918140253</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-0.2149712337635717</v>
+        <v>-0.2149711560611796</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0.4295866264077433</v>
+        <v>0.4295859046757202</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.2069337816275358</v>
+        <v>0.2069343082747805</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>0.0876741100757279</v>
+        <v>0.08767353520488608</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>0.3549551774020552</v>
+        <v>0.3549558524089411</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>0.1841110298200606</v>
+        <v>0.1841114665547474</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>-0.4582537103489984</v>
+        <v>-0.4582538366474194</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>0.2657109991627513</v>
+        <v>0.2657108461943847</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>-0.03129363387465611</v>
+        <v>-0.03129378923965698</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>-0.1816261796174552</v>
+        <v>-0.1816260314805279</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>0.2391554189283343</v>
+        <v>0.2391552955740788</v>
       </c>
       <c r="W20" s="2" t="n">
-        <v>0.271088614924706</v>
+        <v>0.2710887755938995</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>-0.09865645803732692</v>
+        <v>-0.09865669837249424</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>-0.01641334265824101</v>
+        <v>-0.01641299436438559</v>
       </c>
       <c r="Z20" s="2" t="n">
-        <v>0.01863300371103116</v>
+        <v>0.01863314230442747</v>
       </c>
       <c r="AA20" s="2" t="n">
-        <v>0.2789025484402403</v>
+        <v>0.2789019609489847</v>
       </c>
       <c r="AB20" s="3" t="n">
-        <v>-0.1675664195711634</v>
+        <v>-0.1675661095735208</v>
       </c>
       <c r="AC20" s="2" t="n">
-        <v>0.232703294472526</v>
+        <v>0.2327032332823884</v>
       </c>
       <c r="AD20" s="2" t="n">
-        <v>0.07616864903422904</v>
+        <v>0.07616841947185882</v>
       </c>
       <c r="AE20" s="2" t="n">
         <v>0.1392234070071565</v>
       </c>
       <c r="AF20" s="3" t="n">
-        <v>-0.1724186649012199</v>
+        <v>-0.1724187518976087</v>
       </c>
       <c r="AG20" s="2" t="n">
-        <v>0.2342100516103316</v>
+        <v>0.234210181352055</v>
       </c>
       <c r="AH20" s="2" t="n">
         <v>0.02231836728992498</v>
@@ -6485,76 +6427,76 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" s="2" t="n">
-        <v>0.2779627596597836</v>
+        <v>0.2779635064559351</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.1814236331695744</v>
+        <v>0.1814230833242423</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.1951108651878655</v>
+        <v>0.1951107863999824</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.1193357591157695</v>
+        <v>0.1193358329081708</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0.1359593480937852</v>
+        <v>-0.1359594658871572</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-0.1393595668461614</v>
+        <v>-0.1393593813520573</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.1534122621303267</v>
+        <v>-0.1534124875851222</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0.3479964774999043</v>
+        <v>0.3479962619504899</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1835137759857164</v>
+        <v>0.1835141866790739</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>0.0588696349848068</v>
+        <v>0.05886951770293614</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>0.3036071550527628</v>
+        <v>0.3036077424877188</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>0.06447074385176133</v>
+        <v>0.0644707219406615</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-0.4646651923509483</v>
+        <v>-0.4646654430903725</v>
       </c>
       <c r="S21" s="2" t="n">
-        <v>0.3622144218866905</v>
+        <v>0.3622143267917957</v>
       </c>
       <c r="T21" s="2" t="n">
-        <v>0.1020978648983937</v>
+        <v>0.1020986534362855</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-0.03941651379536271</v>
+        <v>-0.03941689148362504</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>0.1526230492103791</v>
+        <v>0.1526228266490874</v>
       </c>
       <c r="W21" s="2" t="n">
-        <v>0.1953288156622643</v>
+        <v>0.1953290125841602</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.07598295665900812</v>
+        <v>-0.07598295095706131</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.07018694808473924</v>
+        <v>-0.0701871048111633</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.01210321085772526</v>
+        <v>-0.01210303722753037</v>
       </c>
       <c r="AA21" s="2" t="n">
-        <v>0.2153963172844107</v>
+        <v>0.2153959445854496</v>
       </c>
       <c r="AB21" s="3" t="n">
-        <v>-0.1429738462840033</v>
+        <v>-0.1429735137617896</v>
       </c>
       <c r="AC21" s="2" t="n">
-        <v>0.2128605468068303</v>
+        <v>0.2128603409104992</v>
       </c>
       <c r="AD21" s="3" t="n">
         <v>-0.1179574695011002</v>
@@ -6593,79 +6535,79 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" s="2" t="n">
-        <v>0.0789797442785527</v>
+        <v>0.0789800457785621</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.2377688997406211</v>
+        <v>0.2377689500105589</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.2808677368502994</v>
+        <v>0.2808672806622508</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.2257175515544991</v>
+        <v>0.2257174414974938</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0.1797526415206655</v>
+        <v>-0.1797523631442488</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>-0.2161503398082033</v>
+        <v>-0.2161505053099583</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>-0.3406091358232963</v>
+        <v>-0.3406091021695555</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>0.6665261504293296</v>
+        <v>0.6665262571415536</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1628980428659441</v>
+        <v>0.162898058515452</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>0.09640853418306938</v>
+        <v>0.09640862475957834</v>
       </c>
       <c r="P22" s="2" t="n">
         <v>0.3495933440141388</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>0.3369470245668846</v>
+        <v>0.3369474712070619</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>-0.4345021911124437</v>
+        <v>-0.4345022547529209</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>0.2050575295257384</v>
+        <v>0.2050570410266499</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>0.08221245550268974</v>
+        <v>0.08221289957275957</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>-0.1766597498273244</v>
+        <v>-0.176659709814439</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>0.3229273072629739</v>
+        <v>0.322926943332124</v>
       </c>
       <c r="W22" s="2" t="n">
         <v>0.3084702993150314</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>-0.1195654445456688</v>
+        <v>-0.119565524006511</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>-0.02786868645480467</v>
+        <v>-0.02786850846630062</v>
       </c>
       <c r="Z22" s="2" t="n">
-        <v>0.03609567557099336</v>
+        <v>0.03609567221990173</v>
       </c>
       <c r="AA22" s="2" t="n">
-        <v>0.2742164149548267</v>
+        <v>0.2742163903837209</v>
       </c>
       <c r="AB22" s="3" t="n">
-        <v>-0.2139741046719984</v>
+        <v>-0.2139739489820401</v>
       </c>
       <c r="AC22" s="2" t="n">
-        <v>0.1915201870168073</v>
+        <v>0.1915199566848291</v>
       </c>
       <c r="AD22" s="2" t="n">
-        <v>0.1058628769256713</v>
+        <v>0.1058627938926036</v>
       </c>
       <c r="AE22" s="2" t="n">
         <v>0.05836867355682207</v>
@@ -6701,91 +6643,91 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="n">
-        <v>0.16969995229003</v>
+        <v>0.169700055692577</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.1173670419151973</v>
+        <v>0.1173671174909106</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.4209894974797319</v>
+        <v>0.4209894013678159</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.3200089523725025</v>
+        <v>0.3200092379649897</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.01255848386034764</v>
+        <v>0.0125582647868081</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-0.2385033027802214</v>
+        <v>-0.2385033740045773</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>-0.2011189988777088</v>
+        <v>-0.2011190176887852</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0.4104731472068559</v>
+        <v>0.4104736635799997</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1861269432718353</v>
+        <v>0.1861266479021575</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>0.101295928945959</v>
+        <v>0.1012961388900591</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>0.335566628124772</v>
+        <v>0.3355667547881294</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>0.1214305248752057</v>
+        <v>0.1214302047378693</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>-0.4157966835635709</v>
+        <v>-0.4157966411367536</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>0.2724022236987362</v>
+        <v>0.2724024217860816</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>-0.02535946339614714</v>
+        <v>-0.02535968590965454</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>-0.1765995082760569</v>
+        <v>-0.1765994497151834</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>0.2432136031835361</v>
+        <v>0.2432133725237173</v>
       </c>
       <c r="W23" s="2" t="n">
-        <v>0.2410817697938905</v>
+        <v>0.2410822550347489</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>-0.1074619636383483</v>
+        <v>-0.1074621182962878</v>
       </c>
       <c r="Y23" s="2" t="n">
-        <v>0.00244278183789115</v>
+        <v>0.002442884874441109</v>
       </c>
       <c r="Z23" s="2" t="n">
-        <v>0.04900046212173126</v>
+        <v>0.04899993683822457</v>
       </c>
       <c r="AA23" s="2" t="n">
-        <v>0.2910827404851251</v>
+        <v>0.2910831209317388</v>
       </c>
       <c r="AB23" s="3" t="n">
         <v>-0.1289958727200107</v>
       </c>
       <c r="AC23" s="2" t="n">
-        <v>0.2668390356421377</v>
+        <v>0.2668389482959457</v>
       </c>
       <c r="AD23" s="2" t="n">
-        <v>0.02858224357929084</v>
+        <v>0.02858238344626818</v>
       </c>
       <c r="AE23" s="2" t="n">
-        <v>0.2142708618639164</v>
+        <v>0.2142707804686663</v>
       </c>
       <c r="AF23" s="3" t="n">
-        <v>-0.1204795233582733</v>
+        <v>-0.1204794681546043</v>
       </c>
       <c r="AG23" s="2" t="n">
-        <v>0.2170692674740964</v>
+        <v>0.2170693166152449</v>
       </c>
       <c r="AH23" s="3" t="n">
-        <v>-0.05626740912598682</v>
+        <v>-0.05626750646469902</v>
       </c>
       <c r="AI23" s="2" t="n">
         <v>0.2889725408625792</v>
@@ -6809,73 +6751,73 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" s="2" t="n">
-        <v>0.1420091170570075</v>
+        <v>0.1420086032016865</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.3677021664452951</v>
+        <v>0.3677021386543766</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.4834776079183445</v>
+        <v>0.4834777960974703</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.008244723145273802</v>
+        <v>0.008244516933447965</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.1111590198736592</v>
+        <v>0.1111589514310081</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>-0.2760162688404537</v>
+        <v>-0.2760157701830906</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.06977190204256278</v>
+        <v>-0.06977219889176667</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>0.4181734727167379</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.3313816237998839</v>
+        <v>0.3313814302834956</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>0.01877493888938742</v>
+        <v>0.01877479626825318</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>0.32443163635684</v>
+        <v>0.3244321569454385</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>0.03755010049993057</v>
+        <v>0.03755020417765986</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>-0.4680933383113545</v>
+        <v>-0.468093448760828</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>0.2205239725048094</v>
+        <v>0.2205242652933972</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>-0.1419781260874905</v>
+        <v>-0.1419783319162642</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>-0.240857756233797</v>
+        <v>-0.2408572902635137</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>0.1536983527446123</v>
+        <v>0.153697399067191</v>
       </c>
       <c r="W24" s="2" t="n">
-        <v>0.1906174643443981</v>
+        <v>0.1906180369489945</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>-0.1091567582379133</v>
+        <v>-0.1091572652020062</v>
       </c>
       <c r="Y24" s="2" t="n">
-        <v>0.03142699120260151</v>
+        <v>0.03142710098386514</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>-0.08568117083282589</v>
+        <v>-0.0856810902345958</v>
       </c>
       <c r="AA24" s="2" t="n">
-        <v>0.286995611580865</v>
+        <v>0.2869958548732234</v>
       </c>
       <c r="AB24" s="3" t="n">
-        <v>-0.1717901397180082</v>
+        <v>-0.1717902081763516</v>
       </c>
       <c r="AC24" s="2" t="n">
         <v>0.2698412286525373</v>
@@ -6887,13 +6829,13 @@
         <v>0.1438420802697877</v>
       </c>
       <c r="AF24" s="3" t="n">
-        <v>-0.1415937365892435</v>
+        <v>-0.1415938041603676</v>
       </c>
       <c r="AG24" s="2" t="n">
-        <v>0.3063143432361357</v>
+        <v>0.3063143673482689</v>
       </c>
       <c r="AH24" s="2" t="n">
-        <v>0.1022808382458829</v>
+        <v>0.1022809046680215</v>
       </c>
       <c r="AI24" s="2" t="n">
         <v>0.5571768930577996</v>
@@ -6917,73 +6859,73 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="n">
-        <v>0.3543180848770309</v>
+        <v>0.3543190034209782</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.239789158653277</v>
+        <v>0.2397885793207604</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.5041464312925514</v>
+        <v>0.5041468081980207</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>-0.01476487005001614</v>
+        <v>-0.01476503340199165</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-0.1194129116472316</v>
+        <v>-0.1194129863012955</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-0.09253401166686437</v>
+        <v>-0.09253430048876365</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-0.1353731129993185</v>
+        <v>-0.1353729439028851</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0.5740484669586103</v>
+        <v>0.5740493963056177</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.3015655181128378</v>
+        <v>0.3015646754908665</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>0.04564365850478436</v>
+        <v>0.0456439661636574</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>0.4924415835364193</v>
+        <v>0.4924411834617775</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>0.2093157704461772</v>
+        <v>0.2093162631172865</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>-0.367700049583491</v>
+        <v>-0.3677003370559447</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>0.3309979682876198</v>
+        <v>0.3309981351205447</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>-0.1881491358430645</v>
+        <v>-0.1881491500328747</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>-0.09814086783653975</v>
+        <v>-0.09814096984969112</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>0.05401688029440543</v>
+        <v>0.05401709743299543</v>
       </c>
       <c r="W25" s="2" t="n">
         <v>0.319060689252405</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>-0.06252303669223214</v>
+        <v>-0.06252311078008654</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-0.1553958818785348</v>
+        <v>-0.1553956570723362</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>-0.01815281170963212</v>
+        <v>-0.01815299545103743</v>
       </c>
       <c r="AA25" s="2" t="n">
-        <v>0.2697781605841307</v>
+        <v>0.2697784464817723</v>
       </c>
       <c r="AB25" s="3" t="n">
-        <v>-0.1532420152325257</v>
+        <v>-0.15324220588477</v>
       </c>
       <c r="AC25" s="2" t="n">
         <v>0.1193008875402677</v>
@@ -6992,10 +6934,10 @@
         <v>-0.03936501636721479</v>
       </c>
       <c r="AE25" s="2" t="n">
-        <v>0.002491183669586672</v>
+        <v>0.002491430966201857</v>
       </c>
       <c r="AF25" s="3" t="n">
-        <v>-0.05178687457252051</v>
+        <v>-0.05178710847965351</v>
       </c>
       <c r="AG25" s="2" t="n">
         <v>0.3025502703397387</v>
@@ -7025,85 +6967,85 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="n">
-        <v>0.2653459267250025</v>
+        <v>0.2653450503528532</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.1032425504882688</v>
+        <v>0.1032429207593804</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0.120597766525165</v>
+        <v>0.1205975235081693</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0.6301736155051774</v>
+        <v>0.6301741200579387</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0.225799740826686</v>
+        <v>-0.2257995318033772</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-0.2303002357588775</v>
+        <v>-0.2303006298794291</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.2947897987632688</v>
+        <v>-0.2947898198521283</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0.6737811675965946</v>
+        <v>0.673781235946975</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.3531669592271336</v>
+        <v>0.3531674048811246</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>0.1033401890456704</v>
+        <v>0.10333998211842</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>0.4373027940406615</v>
+        <v>0.4373023525962703</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-0.01306113494148742</v>
+        <v>-0.01306102491967909</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.4690170680905872</v>
+        <v>-0.46901700731004</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>0.554161044585092</v>
+        <v>0.5541608290075912</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>0.3590836214626638</v>
+        <v>0.3590839486909287</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-0.1679475874231861</v>
+        <v>-0.1679476723435556</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>0.2444559010886818</v>
+        <v>0.2444555331022502</v>
       </c>
       <c r="W26" s="2" t="n">
-        <v>0.2354559876673112</v>
+        <v>0.2354562544256544</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.08424733343337965</v>
+        <v>-0.08424734015478308</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.04543510546977814</v>
+        <v>-0.04543510942815498</v>
       </c>
       <c r="Z26" s="2" t="n">
-        <v>0.02374455162287425</v>
+        <v>0.02374464505833962</v>
       </c>
       <c r="AA26" s="2" t="n">
-        <v>0.2185665067735059</v>
+        <v>0.2185665959249754</v>
       </c>
       <c r="AB26" s="3" t="n">
-        <v>-0.1278349132194208</v>
+        <v>-0.1278349038668992</v>
       </c>
       <c r="AC26" s="2" t="n">
-        <v>0.2174593381446559</v>
+        <v>0.2174591521346954</v>
       </c>
       <c r="AD26" s="2" t="n">
-        <v>0.2226676601285502</v>
+        <v>0.2226680199760818</v>
       </c>
       <c r="AE26" s="2" t="n">
-        <v>0.228347088557405</v>
+        <v>0.2283465862606029</v>
       </c>
       <c r="AF26" s="3" t="n">
-        <v>-0.2784350344464113</v>
+        <v>-0.2784349020329644</v>
       </c>
       <c r="AG26" s="2" t="n">
         <v>0.2506899393534947</v>
@@ -7133,70 +7075,70 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" s="3" t="n">
-        <v>-0.03268500386430495</v>
+        <v>-0.03268471925337446</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.3399520850082862</v>
+        <v>0.3399513965296139</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0.2257728805401336</v>
+        <v>0.2257731496963966</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.0352475484481708</v>
+        <v>-0.03524763801648112</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.07204690387346324</v>
+        <v>0.07204691056235024</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.2484153033953015</v>
+        <v>-0.2484152383070403</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.1116931382696729</v>
+        <v>-0.1116930806571651</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.3344096492000659</v>
+        <v>0.3344098220810166</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1728330641527811</v>
+        <v>0.1728330305518491</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>0.1296288882993242</v>
+        <v>0.1296285352850743</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>0.2995350279369902</v>
+        <v>0.2995353653739752</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>0.05511997294475868</v>
+        <v>0.05511974088398808</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.2720457144324838</v>
+        <v>-0.2720456900369367</v>
       </c>
       <c r="S27" s="2" t="n">
-        <v>0.2211654121963389</v>
+        <v>0.2211652814395493</v>
       </c>
       <c r="T27" s="2" t="n">
-        <v>0.1445037791380983</v>
+        <v>0.1445039858153705</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>-0.07916998535359843</v>
+        <v>-0.07917009054177382</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>0.217849284925351</v>
+        <v>0.217849652506477</v>
       </c>
       <c r="W27" s="2" t="n">
-        <v>0.2572091321802423</v>
+        <v>0.2572091777268641</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>-0.01737706327026411</v>
+        <v>-0.01737720859715708</v>
       </c>
       <c r="Y27" s="2" t="n">
-        <v>0.002694745288447598</v>
+        <v>0.002694593228719233</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>-0.02505963605160044</v>
+        <v>-0.02505948650216949</v>
       </c>
       <c r="AA27" s="2" t="n">
-        <v>0.2334165074304455</v>
+        <v>0.2334164116311275</v>
       </c>
       <c r="AB27" s="3" t="n">
         <v>-0.09207316765993456</v>
@@ -7241,88 +7183,88 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" s="2" t="n">
-        <v>0.213445252416236</v>
+        <v>0.2134445835419021</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.2020958021537536</v>
+        <v>0.202095846415856</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0.2387056638479943</v>
+        <v>0.2387056162415611</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.05650964077581588</v>
+        <v>0.05650980032808706</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>-0.08561238841278418</v>
+        <v>-0.08561225515459969</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-0.2389667950838061</v>
+        <v>-0.238966929144408</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>-0.2071033567450095</v>
+        <v>-0.2071033774615497</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0.288203600727551</v>
+        <v>0.2882036370866343</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.1415244149361501</v>
+        <v>0.1415244287960589</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>0.1297950958204146</v>
+        <v>0.1297950211643113</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>0.3174026005583528</v>
+        <v>0.3174035599870089</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>0.1789948700213269</v>
+        <v>0.1789944210073082</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>-0.474738127018455</v>
+        <v>-0.4747381319585932</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>0.408293928828684</v>
+        <v>0.4082939458999513</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>0.04863812548085567</v>
+        <v>0.04863818192849423</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>-0.1601456326038342</v>
+        <v>-0.1601457182822733</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>0.2205878766288913</v>
+        <v>0.2205879185651807</v>
       </c>
       <c r="W28" s="2" t="n">
-        <v>0.287409546605762</v>
+        <v>0.2874090632227748</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>-0.0576957938891649</v>
+        <v>-0.05769590042273731</v>
       </c>
       <c r="Y28" s="2" t="n">
-        <v>0.01505970882224905</v>
+        <v>0.01506001748263097</v>
       </c>
       <c r="Z28" s="2" t="n">
         <v>0.0409574400628856</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>0.3373095622307913</v>
+        <v>0.3373096581583408</v>
       </c>
       <c r="AB28" s="3" t="n">
-        <v>-0.1537526211676508</v>
+        <v>-0.1537526818704482</v>
       </c>
       <c r="AC28" s="2" t="n">
-        <v>0.3245353421392358</v>
+        <v>0.3245350878457014</v>
       </c>
       <c r="AD28" s="2" t="n">
-        <v>0.2322992488189601</v>
+        <v>0.2322994854044114</v>
       </c>
       <c r="AE28" s="2" t="n">
         <v>0.227398114518387</v>
       </c>
       <c r="AF28" s="3" t="n">
-        <v>-0.2442791455092661</v>
+        <v>-0.2442792301304062</v>
       </c>
       <c r="AG28" s="2" t="n">
-        <v>0.2208051405952027</v>
+        <v>0.2208052772937388</v>
       </c>
       <c r="AH28" s="2" t="n">
         <v>0.01674229103780123</v>
@@ -7363,46 +7305,46 @@
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
       <c r="T29" s="2" t="n">
-        <v>0.3731918893749682</v>
+        <v>0.3731919275467179</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>-0.3203135366397952</v>
+        <v>-0.3203134195326779</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>0.4160933699809966</v>
+        <v>0.41609313088778</v>
       </c>
       <c r="W29" s="2" t="n">
-        <v>0.03733159644852768</v>
+        <v>0.0373315008561399</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>-0.1632167274303705</v>
+        <v>-0.1632164609228977</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>-0.2316177668830456</v>
+        <v>-0.2316181177688096</v>
       </c>
       <c r="Z29" s="2" t="n">
-        <v>0.02412276838590133</v>
+        <v>0.02412304804872756</v>
       </c>
       <c r="AA29" s="2" t="n">
-        <v>0.5242383272552773</v>
+        <v>0.5242378517985222</v>
       </c>
       <c r="AB29" s="3" t="n">
-        <v>-0.1375523393534672</v>
+        <v>-0.1375521866827472</v>
       </c>
       <c r="AC29" s="3" t="n">
-        <v>-0.06124871806476506</v>
+        <v>-0.06124861543810756</v>
       </c>
       <c r="AD29" s="3" t="n">
-        <v>-0.08377335648347051</v>
+        <v>-0.08377334732515695</v>
       </c>
       <c r="AE29" s="2" t="n">
-        <v>0.122049342732665</v>
+        <v>0.1220490895335691</v>
       </c>
       <c r="AF29" s="3" t="n">
-        <v>-0.2461740629359921</v>
+        <v>-0.2461740359442564</v>
       </c>
       <c r="AG29" s="2" t="n">
-        <v>0.5070333256052437</v>
+        <v>0.5070334319011609</v>
       </c>
       <c r="AH29" s="3" t="n">
         <v>-0.02615474879777924</v>
@@ -7441,46 +7383,46 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" s="3" t="n">
-        <v>-0.4212641013560233</v>
+        <v>-0.4212637655108921</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>1.030802914940248</v>
+        <v>1.030803350844995</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>0.2558096636430085</v>
+        <v>0.2558095298954139</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>-0.3656555453012892</v>
+        <v>-0.3656554180888313</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>0.6560346412902205</v>
+        <v>0.6560343091864349</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>-0.2724401689681106</v>
+        <v>-0.2724400882364624</v>
       </c>
       <c r="X30" s="2" t="n">
-        <v>0.15787348465842</v>
+        <v>0.1578734671404309</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>-0.3143877077234976</v>
+        <v>-0.3143879171767365</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>-0.08556960064901209</v>
+        <v>-0.08556947881306742</v>
       </c>
       <c r="AA30" s="2" t="n">
-        <v>0.3758289997158393</v>
+        <v>0.3758286462978349</v>
       </c>
       <c r="AB30" s="3" t="n">
-        <v>-0.4146459231103646</v>
+        <v>-0.4146457835598029</v>
       </c>
       <c r="AC30" s="2" t="n">
-        <v>0.1448821308277395</v>
+        <v>0.144882239478423</v>
       </c>
       <c r="AD30" s="3" t="n">
-        <v>-0.01189453958611697</v>
+        <v>-0.01189462247778272</v>
       </c>
       <c r="AE30" s="3" t="n">
-        <v>-0.2741205780590051</v>
+        <v>-0.2741205171653436</v>
       </c>
       <c r="AF30" s="2" t="n">
         <v>1.057453970128762</v>
@@ -7517,79 +7459,79 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" s="3" t="n">
-        <v>-0.1091423155616194</v>
+        <v>-0.1091424931274436</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0.1881946647657753</v>
+        <v>-0.188194441026201</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0.3634154392337084</v>
+        <v>-0.3634155687465314</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1.16970255165293</v>
+        <v>1.169702106460522</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.3363003917876706</v>
+        <v>0.3363001704688648</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>0.5267369154575545</v>
+        <v>0.5267375705146922</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>0.4330925519028062</v>
+        <v>0.4330927562404248</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>0.7482233365810442</v>
+        <v>0.7482237693054015</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.5432140515937307</v>
+        <v>-0.5432142893578942</v>
       </c>
       <c r="S31" s="2" t="n">
-        <v>1.219891857472292</v>
+        <v>1.219892085375872</v>
       </c>
       <c r="T31" s="2" t="n">
-        <v>0.07803880853185263</v>
+        <v>0.07803849252727368</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-0.2414153426896671</v>
+        <v>-0.2414150553572022</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>0.003594137123057006</v>
+        <v>0.003593948136822567</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>-0.1748125306705164</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.154749594402393</v>
+        <v>-0.1547493670176098</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.4177174604976575</v>
+        <v>-0.4177177068117194</v>
       </c>
       <c r="Z31" s="2" t="n">
-        <v>0.6447314835098623</v>
+        <v>0.6447320447989424</v>
       </c>
       <c r="AA31" s="2" t="n">
-        <v>0.236163383978454</v>
+        <v>0.2361633397533911</v>
       </c>
       <c r="AB31" s="3" t="n">
-        <v>-0.02518529145166959</v>
+        <v>-0.02518551486932852</v>
       </c>
       <c r="AC31" s="2" t="n">
-        <v>0.2766671289891338</v>
+        <v>0.2766669950839966</v>
       </c>
       <c r="AD31" s="3" t="n">
-        <v>-0.2035513680477664</v>
+        <v>-0.2035511617633937</v>
       </c>
       <c r="AE31" s="3" t="n">
-        <v>-0.173140256984269</v>
+        <v>-0.1731403201707838</v>
       </c>
       <c r="AF31" s="2" t="n">
         <v>0.1209166216201605</v>
       </c>
       <c r="AG31" s="2" t="n">
-        <v>0.3262062159746841</v>
+        <v>0.3262061335252975</v>
       </c>
       <c r="AH31" s="3" t="n">
-        <v>-0.3041066900755016</v>
+        <v>-0.3041066468122599</v>
       </c>
       <c r="AI31" s="2" t="n">
         <v>0.4880613855707459</v>
@@ -7613,88 +7555,88 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" s="2" t="n">
-        <v>0.1218838709996404</v>
+        <v>0.1218845428402591</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.4719287444585412</v>
+        <v>0.471928670178352</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>-0.3534702975108993</v>
+        <v>-0.3534700993146481</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0.7735982558145305</v>
+        <v>0.7735968608776314</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-0.2394521661624439</v>
+        <v>-0.2394519290935829</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.1539253388234918</v>
+        <v>0.1539252869532464</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>-0.1472057159184452</v>
+        <v>-0.1472055721731369</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>0.4353765573192736</v>
+        <v>0.4353765924952755</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.4896125726222338</v>
+        <v>0.489612443314341</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>0.4381436780637955</v>
+        <v>0.4381433284169096</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>0.4483042320956578</v>
+        <v>0.4483052325430621</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>0.1135116963059779</v>
+        <v>0.1135116454927552</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>-0.4106886465323148</v>
+        <v>-0.4106889336956017</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>0.5387051148141355</v>
+        <v>0.5387054165668272</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>0.2792469660549954</v>
+        <v>0.2792472676126898</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>-0.119650969126358</v>
+        <v>-0.1196513608676505</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>0.3281198992087337</v>
+        <v>0.3281201283363515</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>-0.015799611730833</v>
+        <v>-0.01579975876567818</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>-0.115663608539666</v>
+        <v>-0.1156633160785688</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>-0.1424868445900074</v>
+        <v>-0.1424871487560068</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>-0.1031245758577986</v>
+        <v>-0.1031249832452954</v>
       </c>
       <c r="AA32" s="2" t="n">
-        <v>0.1446561990729922</v>
+        <v>0.1446571647700956</v>
       </c>
       <c r="AB32" s="3" t="n">
-        <v>-0.1457705866139257</v>
+        <v>-0.1457709311728126</v>
       </c>
       <c r="AC32" s="2" t="n">
-        <v>0.1263700942553294</v>
+        <v>0.1263701085625608</v>
       </c>
       <c r="AD32" s="3" t="n">
-        <v>-0.03057912321117529</v>
+        <v>-0.03057902576999394</v>
       </c>
       <c r="AE32" s="2" t="n">
-        <v>0.2027452585686682</v>
+        <v>0.2027450511977948</v>
       </c>
       <c r="AF32" s="2" t="n">
-        <v>0.01239687019178715</v>
+        <v>0.0123969585365169</v>
       </c>
       <c r="AG32" s="2" t="n">
-        <v>0.4031794962885356</v>
+        <v>0.4031796157716627</v>
       </c>
       <c r="AH32" s="3" t="n">
         <v>-0.2821653072760798</v>
@@ -7732,61 +7674,61 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" s="2" t="n">
-        <v>0.0259260847262146</v>
+        <v>0.02592615121673703</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>-0.3768448408797869</v>
+        <v>-0.3768447659351745</v>
       </c>
       <c r="S33" s="2" t="n">
         <v>0.8606195533554886</v>
       </c>
       <c r="T33" s="2" t="n">
-        <v>0.4660696090946705</v>
+        <v>0.4660695053680102</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>-0.2644522194081196</v>
+        <v>-0.2644520966154591</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>0.1129715431901104</v>
+        <v>0.1129713399457417</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>-0.238974660709429</v>
+        <v>-0.2389747677881847</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>-0.1474311306482045</v>
+        <v>-0.1474310505697294</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>-0.1852610538566209</v>
+        <v>-0.1852610785338535</v>
       </c>
       <c r="Z33" s="2" t="n">
-        <v>0.1946569350297485</v>
+        <v>0.1946568851089041</v>
       </c>
       <c r="AA33" s="2" t="n">
-        <v>0.4178762828062041</v>
+        <v>0.4178767107165398</v>
       </c>
       <c r="AB33" s="3" t="n">
-        <v>-0.18979345733306</v>
+        <v>-0.1897938250898663</v>
       </c>
       <c r="AC33" s="3" t="n">
-        <v>-0.1779107108756545</v>
+        <v>-0.1779102383790482</v>
       </c>
       <c r="AD33" s="3" t="n">
-        <v>-0.07132340320179464</v>
+        <v>-0.07132367751798696</v>
       </c>
       <c r="AE33" s="3" t="n">
-        <v>-0.1980277769607405</v>
+        <v>-0.1980277924107644</v>
       </c>
       <c r="AF33" s="2" t="n">
-        <v>0.2512172967184283</v>
+        <v>0.2512173211579816</v>
       </c>
       <c r="AG33" s="2" t="n">
-        <v>0.09014095173287195</v>
+        <v>0.09014111424528992</v>
       </c>
       <c r="AH33" s="3" t="n">
-        <v>-0.08668870778448967</v>
+        <v>-0.08668870160161002</v>
       </c>
       <c r="AI33" s="2" t="n">
-        <v>0.6540961910917826</v>
+        <v>0.6540960619192455</v>
       </c>
       <c r="AJ33" s="2" t="n">
         <v>0.02722768397462727</v>
@@ -7820,52 +7762,52 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" s="2" t="n">
-        <v>0.8887898300709214</v>
+        <v>0.8887901638935074</v>
       </c>
       <c r="T34" s="2" t="n">
-        <v>0.5173169567478957</v>
+        <v>0.5173174757263139</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>-0.1522145854549314</v>
+        <v>-0.1522147660099407</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>0.2737835575976058</v>
+        <v>0.2737832201437722</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>-0.1500761371680289</v>
+        <v>-0.1500760736980659</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>-0.2689281337745366</v>
+        <v>-0.2689278701842382</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>-0.4106962913197719</v>
+        <v>-0.4106964437028535</v>
       </c>
       <c r="Z34" s="2" t="n">
-        <v>0.2407978089173897</v>
+        <v>0.2407976823913545</v>
       </c>
       <c r="AA34" s="2" t="n">
-        <v>0.1188304055503904</v>
+        <v>0.1188304877326178</v>
       </c>
       <c r="AB34" s="3" t="n">
-        <v>-0.1988308522266643</v>
+        <v>-0.1988306907144253</v>
       </c>
       <c r="AC34" s="2" t="n">
-        <v>0.3042705451808962</v>
+        <v>0.3042702781252822</v>
       </c>
       <c r="AD34" s="3" t="n">
-        <v>-0.1459713025252408</v>
+        <v>-0.1459712922642524</v>
       </c>
       <c r="AE34" s="3" t="n">
-        <v>-0.1149525260128477</v>
+        <v>-0.1149525165511784</v>
       </c>
       <c r="AF34" s="3" t="n">
-        <v>-0.2131687184625546</v>
+        <v>-0.2131688846377583</v>
       </c>
       <c r="AG34" s="2" t="n">
-        <v>0.2492300742409836</v>
+        <v>0.2492301036988709</v>
       </c>
       <c r="AH34" s="2" t="n">
-        <v>0.04683238937813639</v>
+        <v>0.0468324884238891</v>
       </c>
       <c r="AI34" s="2" t="n">
         <v>0.6888423803666632</v>
@@ -7894,76 +7836,76 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" s="2" t="n">
-        <v>0.1463944027036417</v>
+        <v>0.1463945432754621</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>-0.2327534238047676</v>
+        <v>-0.232753316842623</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0.6212268490749389</v>
+        <v>0.6212277383420692</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.3852580855311403</v>
+        <v>0.3852569605963483</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>0.5459572390006604</v>
+        <v>0.545958051688713</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>0.4106045821062765</v>
+        <v>0.4106038550858295</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>0.4850160203493734</v>
+        <v>0.4850163032976988</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>-0.4722580544248732</v>
+        <v>-0.4722579415413249</v>
       </c>
       <c r="S35" s="2" t="n">
-        <v>0.9114102752974957</v>
+        <v>0.9114100104664333</v>
       </c>
       <c r="T35" s="2" t="n">
-        <v>0.1553512353805053</v>
+        <v>0.1553509837337683</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>-0.1848905915819719</v>
+        <v>-0.1848906695354439</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>0.05768964572904101</v>
+        <v>0.05768957432900179</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>-0.1254791236070036</v>
+        <v>-0.1254789997124628</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>-0.1228683043476099</v>
+        <v>-0.1228680532904435</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>-0.3153881600336172</v>
+        <v>-0.3153884454719911</v>
       </c>
       <c r="Z35" s="2" t="n">
-        <v>0.323517701269016</v>
+        <v>0.3235181350677669</v>
       </c>
       <c r="AA35" s="2" t="n">
-        <v>0.2632963203490533</v>
+        <v>0.26329607185543</v>
       </c>
       <c r="AB35" s="3" t="n">
-        <v>-0.06845978923509399</v>
+        <v>-0.06845979518491974</v>
       </c>
       <c r="AC35" s="2" t="n">
-        <v>0.1376922685076252</v>
+        <v>0.1376925612444981</v>
       </c>
       <c r="AD35" s="3" t="n">
-        <v>-0.117127352272471</v>
+        <v>-0.1171275790783698</v>
       </c>
       <c r="AE35" s="3" t="n">
-        <v>-0.1358475858709742</v>
+        <v>-0.1358474127197246</v>
       </c>
       <c r="AF35" s="2" t="n">
-        <v>0.09812526387929865</v>
+        <v>0.09812525333216104</v>
       </c>
       <c r="AG35" s="2" t="n">
-        <v>0.3314328603293293</v>
+        <v>0.3314326321245096</v>
       </c>
       <c r="AH35" s="3" t="n">
-        <v>-0.2311396559562479</v>
+        <v>-0.2311395994326024</v>
       </c>
       <c r="AI35" s="2" t="n">
         <v>0.5264846239702883</v>
@@ -8006,34 +7948,34 @@
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" s="3" t="n">
-        <v>-0.05833973586913499</v>
+        <v>-0.05833965226983895</v>
       </c>
       <c r="Z36" s="2" t="n">
-        <v>0.07671567215939445</v>
+        <v>0.07671578037528759</v>
       </c>
       <c r="AA36" s="2" t="n">
-        <v>0.06144852622500951</v>
+        <v>0.06144843288046609</v>
       </c>
       <c r="AB36" s="2" t="n">
-        <v>0.1307337236904462</v>
+        <v>0.130733559305817</v>
       </c>
       <c r="AC36" s="2" t="n">
-        <v>0.09295484981267177</v>
+        <v>0.09295518259349533</v>
       </c>
       <c r="AD36" s="2" t="n">
-        <v>0.02654849309555174</v>
+        <v>0.02654849120639802</v>
       </c>
       <c r="AE36" s="2" t="n">
-        <v>0.3362398962499002</v>
+        <v>0.3362398036240164</v>
       </c>
       <c r="AF36" s="3" t="n">
-        <v>-0.06060040458854621</v>
+        <v>-0.06060050833984032</v>
       </c>
       <c r="AG36" s="2" t="n">
-        <v>0.1504964303862644</v>
+        <v>0.1504966678962796</v>
       </c>
       <c r="AH36" s="3" t="n">
-        <v>-0.001855910927027193</v>
+        <v>-0.001856006745903915</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>-0.08203687100955659</v>
@@ -8069,52 +8011,52 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" s="3" t="n">
-        <v>-0.3724786248400005</v>
+        <v>-0.372478880770816</v>
       </c>
       <c r="S37" s="2" t="n">
-        <v>0.8127824233761565</v>
+        <v>0.8127824073523291</v>
       </c>
       <c r="T37" s="2" t="n">
-        <v>0.1530731388839077</v>
+        <v>0.1530735310531575</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>-0.3268979452050307</v>
+        <v>-0.3268983562512351</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>0.08722094504245903</v>
+        <v>0.0872213418732557</v>
       </c>
       <c r="W37" s="2" t="n">
-        <v>0.1829518781805415</v>
+        <v>0.1829517662758395</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>-0.01677995547279298</v>
+        <v>-0.01677967326656993</v>
       </c>
       <c r="Y37" s="2" t="n">
-        <v>0.07789317800052209</v>
+        <v>0.07789316301196347</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>-0.03988215951042906</v>
+        <v>-0.03988224165025922</v>
       </c>
       <c r="AA37" s="2" t="n">
-        <v>0.1277316003978628</v>
+        <v>0.1277315885230006</v>
       </c>
       <c r="AB37" s="3" t="n">
-        <v>-0.04835623857726157</v>
+        <v>-0.04835615215345956</v>
       </c>
       <c r="AC37" s="2" t="n">
-        <v>0.2093220542334784</v>
+        <v>0.209321671462446</v>
       </c>
       <c r="AD37" s="2" t="n">
-        <v>0.1201476453751724</v>
+        <v>0.1201478058524212</v>
       </c>
       <c r="AE37" s="2" t="n">
-        <v>0.2282719487068676</v>
+        <v>0.2282718208091283</v>
       </c>
       <c r="AF37" s="3" t="n">
-        <v>-0.2705142172990875</v>
+        <v>-0.2705141934031451</v>
       </c>
       <c r="AG37" s="2" t="n">
-        <v>0.05477049884443286</v>
+        <v>0.05477057412441577</v>
       </c>
       <c r="AH37" s="2" t="n">
         <v>0.3450058015896924</v>
@@ -8148,64 +8090,64 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="2" t="n">
-        <v>0.4580894738101819</v>
+        <v>0.4580894833183393</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.4362091399031047</v>
+        <v>0.4362084935224448</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>0.2587049337148193</v>
+        <v>0.2587046647616917</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>0.1973681084856957</v>
+        <v>0.1973687959066179</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>0.1551035682344455</v>
+        <v>0.1551036178180956</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>-0.3760827064917958</v>
+        <v>-0.3760828852005248</v>
       </c>
       <c r="S38" s="2" t="n">
-        <v>0.5162843959146655</v>
+        <v>0.5162840484467996</v>
       </c>
       <c r="T38" s="2" t="n">
-        <v>0.3699173170131509</v>
+        <v>0.3699182938133738</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>-0.1568357198845205</v>
+        <v>-0.1568357556724145</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>0.2100691426948225</v>
+        <v>0.210068387530173</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>-0.07464819409155454</v>
+        <v>-0.07464802692048012</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>0.02803906294978398</v>
+        <v>0.02803896408389495</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>-0.2599970455420881</v>
+        <v>-0.2599968496330031</v>
       </c>
       <c r="Z38" s="2" t="n">
-        <v>0.1678115339242385</v>
+        <v>0.1678113221447664</v>
       </c>
       <c r="AA38" s="2" t="n">
-        <v>0.3602612335259232</v>
+        <v>0.3602610457860569</v>
       </c>
       <c r="AB38" s="3" t="n">
-        <v>-0.2524081366193576</v>
+        <v>-0.2524080320143938</v>
       </c>
       <c r="AC38" s="2" t="n">
-        <v>0.09829592460338366</v>
+        <v>0.09829593567039785</v>
       </c>
       <c r="AD38" s="3" t="n">
-        <v>-0.05189649097682536</v>
+        <v>-0.05189629127243889</v>
       </c>
       <c r="AE38" s="2" t="n">
-        <v>0.07911087948671658</v>
+        <v>0.07911065468616041</v>
       </c>
       <c r="AF38" s="3" t="n">
-        <v>-0.05177758081320094</v>
+        <v>-0.05177748580437125</v>
       </c>
       <c r="AG38" s="2" t="n">
         <v>0.01508273328879084</v>
@@ -8242,67 +8184,67 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="2" t="n">
-        <v>0.6315299449120837</v>
+        <v>0.6315303159819738</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.2463706635092107</v>
+        <v>0.2463704621639646</v>
       </c>
       <c r="O39" s="2" t="n">
         <v>0.3262584761739105</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>0.3121233686515672</v>
+        <v>0.3121228800117586</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>0.3333452502568841</v>
+        <v>0.3333458957615882</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>-0.4887882116462458</v>
+        <v>-0.4887883246189756</v>
       </c>
       <c r="S39" s="2" t="n">
-        <v>0.6895435663609439</v>
+        <v>0.6895438602472319</v>
       </c>
       <c r="T39" s="2" t="n">
-        <v>0.1652312867042449</v>
+        <v>0.165230693949965</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>-0.1879369917142386</v>
+        <v>-0.1879366866397394</v>
       </c>
       <c r="V39" s="2" t="n">
-        <v>0.1904966234439422</v>
+        <v>0.1904965681155402</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>-0.03648486297350251</v>
+        <v>-0.03648475233918724</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>-0.03898555425870387</v>
+        <v>-0.03898579260187562</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>-0.1617483808532706</v>
+        <v>-0.1617482969627692</v>
       </c>
       <c r="Z39" s="2" t="n">
-        <v>0.1086837338280251</v>
+        <v>0.1086838238731411</v>
       </c>
       <c r="AA39" s="2" t="n">
-        <v>0.3726282338717302</v>
+        <v>0.3726281920159222</v>
       </c>
       <c r="AB39" s="3" t="n">
-        <v>-0.1531030859868717</v>
+        <v>-0.1531031008699164</v>
       </c>
       <c r="AC39" s="2" t="n">
-        <v>0.1822288959559455</v>
+        <v>0.1822292612214946</v>
       </c>
       <c r="AD39" s="2" t="n">
-        <v>0.1702051536676721</v>
+        <v>0.1702049264366639</v>
       </c>
       <c r="AE39" s="3" t="n">
-        <v>-0.03632430925543584</v>
+        <v>-0.03632422628685306</v>
       </c>
       <c r="AF39" s="3" t="n">
-        <v>-0.2056366679934054</v>
+        <v>-0.2056368224808238</v>
       </c>
       <c r="AG39" s="2" t="n">
-        <v>0.08948323565803151</v>
+        <v>0.08948335374016136</v>
       </c>
       <c r="AH39" s="2" t="n">
         <v>0.06490044273318296</v>
@@ -8334,79 +8276,79 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" s="3" t="n">
-        <v>-0.06957180173435962</v>
+        <v>-0.06957139609792151</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-0.1541970455830555</v>
+        <v>-0.1541968466807733</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>0.4030120710780567</v>
+        <v>0.4030117207623107</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.1895924444780228</v>
+        <v>0.1895925075341398</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>0.1332149811797314</v>
+        <v>0.1332149637532951</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>0.2580579027329484</v>
+        <v>0.2580575266340905</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>0.09951033490193173</v>
+        <v>0.09951072019458507</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>-0.4103109426838819</v>
+        <v>-0.410310915926944</v>
       </c>
       <c r="S40" s="2" t="n">
-        <v>0.2699139037031675</v>
+        <v>0.2699137756451542</v>
       </c>
       <c r="T40" s="2" t="n">
-        <v>0.0816944597428515</v>
+        <v>0.08169456207995718</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>-0.1223020663664527</v>
+        <v>-0.1223022472155519</v>
       </c>
       <c r="V40" s="2" t="n">
         <v>0.1876003604053669</v>
       </c>
       <c r="W40" s="2" t="n">
-        <v>0.2144436793249411</v>
+        <v>0.2144434816480205</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>-0.0619404472491073</v>
+        <v>-0.06194021317383891</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>-0.009929477355060334</v>
+        <v>-0.009929476493581557</v>
       </c>
       <c r="Z40" s="2" t="n">
-        <v>0.01372607628511147</v>
+        <v>0.01372589982261974</v>
       </c>
       <c r="AA40" s="2" t="n">
-        <v>0.2507540882935517</v>
+        <v>0.2507541099695694</v>
       </c>
       <c r="AB40" s="3" t="n">
-        <v>-0.1382105106162347</v>
+        <v>-0.1382104510554069</v>
       </c>
       <c r="AC40" s="2" t="n">
-        <v>0.2204347016096908</v>
+        <v>0.2204346214126562</v>
       </c>
       <c r="AD40" s="2" t="n">
-        <v>0.07595127938691881</v>
+        <v>0.07595148151341258</v>
       </c>
       <c r="AE40" s="2" t="n">
-        <v>0.114458509753645</v>
+        <v>0.1144581293333768</v>
       </c>
       <c r="AF40" s="3" t="n">
-        <v>-0.1438592858989646</v>
+        <v>-0.1438590982299871</v>
       </c>
       <c r="AG40" s="2" t="n">
         <v>0.1836341390272465</v>
       </c>
       <c r="AH40" s="2" t="n">
-        <v>0.03487468227530743</v>
+        <v>0.03487479043230235</v>
       </c>
       <c r="AI40" s="2" t="n">
-        <v>0.3154783354639881</v>
+        <v>0.3154781979805117</v>
       </c>
       <c r="AJ40" s="2" t="n">
         <v>0.09361655709723582</v>
@@ -8436,67 +8378,67 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" s="2" t="n">
-        <v>0.2351968240384423</v>
+        <v>0.2351971528791976</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>0.2936560964396799</v>
+        <v>0.2936563119723894</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>0.3731179921272993</v>
+        <v>0.3731177633556861</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.5245924126121781</v>
+        <v>-0.5245924429459559</v>
       </c>
       <c r="S41" s="2" t="n">
-        <v>0.7631087172296425</v>
+        <v>0.7631090849496256</v>
       </c>
       <c r="T41" s="2" t="n">
-        <v>0.1948133651481525</v>
+        <v>0.1948131198111203</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.1875101467283555</v>
+        <v>-0.1875102186647353</v>
       </c>
       <c r="V41" s="2" t="n">
-        <v>0.1921043702297434</v>
+        <v>0.1921039515284544</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.04941513187606794</v>
+        <v>-0.04941421845457195</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.000416346166309145</v>
+        <v>-0.000417135505482058</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.1581947693749896</v>
+        <v>-0.1581948214382332</v>
       </c>
       <c r="Z41" s="2" t="n">
-        <v>0.1217103928250594</v>
+        <v>0.1217107531729571</v>
       </c>
       <c r="AA41" s="2" t="n">
-        <v>0.3148550215725836</v>
+        <v>0.3148553920553776</v>
       </c>
       <c r="AB41" s="3" t="n">
-        <v>-0.1476048779732665</v>
+        <v>-0.1476048996871692</v>
       </c>
       <c r="AC41" s="2" t="n">
-        <v>0.2075022741721833</v>
+        <v>0.2075020488692239</v>
       </c>
       <c r="AD41" s="2" t="n">
         <v>0.1517561094755215</v>
       </c>
       <c r="AE41" s="2" t="n">
-        <v>0.01258934427453839</v>
+        <v>0.01258916539145383</v>
       </c>
       <c r="AF41" s="3" t="n">
-        <v>-0.1797884013079131</v>
+        <v>-0.1797880797509813</v>
       </c>
       <c r="AG41" s="2" t="n">
-        <v>0.09255612916648981</v>
+        <v>0.09255578615815785</v>
       </c>
       <c r="AH41" s="2" t="n">
-        <v>0.1059232215830959</v>
+        <v>0.1059234291599083</v>
       </c>
       <c r="AI41" s="2" t="n">
-        <v>0.2560601959394799</v>
+        <v>0.2560600839900984</v>
       </c>
       <c r="AJ41" s="2" t="n">
         <v>0.1077009132496234</v>
@@ -8529,13 +8471,13 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" s="3" t="n">
-        <v>-0.3528940945112206</v>
+        <v>-0.3528943178623134</v>
       </c>
       <c r="S42" s="2" t="n">
-        <v>0.3236173792094503</v>
+        <v>0.3236168566570339</v>
       </c>
       <c r="T42" s="2" t="n">
-        <v>0.1277968408052479</v>
+        <v>0.1277971928540449</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>-0.07821334599306451</v>
@@ -8544,13 +8486,13 @@
         <v>0.1674760819189209</v>
       </c>
       <c r="W42" s="2" t="n">
-        <v>0.223760705743165</v>
+        <v>0.2237606028651526</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>0.0383347652762529</v>
+        <v>0.03833502070026396</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>-0.02209045521016395</v>
+        <v>-0.02209061355987529</v>
       </c>
       <c r="Z42" s="2" t="n">
         <v>0.08396663238237267</v>
@@ -8559,25 +8501,25 @@
         <v>0.2433334675058072</v>
       </c>
       <c r="AB42" s="3" t="n">
-        <v>-0.0912489374768598</v>
+        <v>-0.09124887604602128</v>
       </c>
       <c r="AC42" s="2" t="n">
-        <v>0.2658969642283999</v>
+        <v>0.2658967434564155</v>
       </c>
       <c r="AD42" s="2" t="n">
-        <v>0.1633672264613106</v>
+        <v>0.163367457509964</v>
       </c>
       <c r="AE42" s="2" t="n">
-        <v>0.1866172693709593</v>
+        <v>0.1866169768303314</v>
       </c>
       <c r="AF42" s="3" t="n">
-        <v>-0.1838555381260354</v>
+        <v>-0.1838553344784416</v>
       </c>
       <c r="AG42" s="2" t="n">
-        <v>0.222744092112753</v>
+        <v>0.2227438814110505</v>
       </c>
       <c r="AH42" s="2" t="n">
-        <v>0.1744932389086402</v>
+        <v>0.1744933299615026</v>
       </c>
       <c r="AI42" s="2" t="n">
         <v>0.2241319038774059</v>
@@ -8785,79 +8727,79 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="n">
-        <v>0.0240775775167239</v>
+        <v>0.02407878272286235</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.02220301498055988</v>
+        <v>0.0222024957015956</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.006635560384486983</v>
+        <v>0.006636412326118668</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.01530453234963947</v>
+        <v>0.01530409623449525</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.03894056511353661</v>
+        <v>0.03893929853163502</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.07352583571384397</v>
+        <v>0.07352709819461256</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.06622631384630107</v>
+        <v>0.0662257908491799</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.003526142027014734</v>
+        <v>0.003526609740742037</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.02279590726991487</v>
+        <v>0.02279578289366913</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.01440600770859368</v>
+        <v>0.01440543532783245</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.002500239274794813</v>
+        <v>0.002501923175317389</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.002147598725408928</v>
+        <v>0.002145916982460028</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.004469825051168108</v>
+        <v>0.004470496654219502</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0.004297941702320784</v>
+        <v>0.004297606707166279</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0.008226187780895566</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0.002628146577974055</v>
+        <v>0.002626828881018284</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>0.01463091896684743</v>
+        <v>0.01463280004205592</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.03380754319554713</v>
+        <v>0.03380741700855161</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.0303414440909433</v>
+        <v>0.03034049171962994</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>-0.00715647747803716</v>
+        <v>-0.007155771748979856</v>
       </c>
       <c r="X2" s="3" t="n">
-        <v>-0.03880080861427737</v>
+        <v>-0.03880090276053982</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>0.04163718650818038</v>
+        <v>0.04163686352596785</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.03913843194066779</v>
+        <v>0.03913874574760023</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.04950296221374839</v>
+        <v>0.04950276115180907</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>0.005523092041656685</v>
+        <v>0.005523186033416394</v>
       </c>
     </row>
     <row r="3">
@@ -8873,64 +8815,64 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>0.07573966233600826</v>
+        <v>0.07574069703598907</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.05308623936576673</v>
+        <v>0.05308618830482703</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.04119714628925197</v>
+        <v>0.04119578013484215</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.02638250254534436</v>
+        <v>0.02638394852257919</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.02516140541550183</v>
+        <v>0.0251602145356955</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.1037885292676954</v>
+        <v>0.1037890755354181</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.1791734369558362</v>
+        <v>0.1791730321210285</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-0.0659315108185804</v>
+        <v>-0.06593116143389344</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.09359774569889057</v>
+        <v>0.09359733664305825</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1564972575253734</v>
+        <v>0.1564963454383621</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.03663952514579183</v>
+        <v>0.03664044128904376</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.06090225513857905</v>
+        <v>-0.0609019640512285</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.09068126110443608</v>
+        <v>0.0906807180436171</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>0.01507881920123832</v>
+        <v>0.0150789134477034</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.0100154780836299</v>
+        <v>0.01001639275586896</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0.02552955994253403</v>
+        <v>0.02552854066141141</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0.009877269933999289</v>
+        <v>0.009877182500400483</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.08029530253924921</v>
+        <v>0.08029549146590975</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1000674739145653</v>
+        <v>0.1000671501433821</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>-0.03327839861999526</v>
+        <v>-0.0332781140950037</v>
       </c>
       <c r="X3" s="3" t="n">
         <v>-0.1515519923960311</v>
@@ -8939,13 +8881,13 @@
         <v>0.03644432156412369</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.006342317764176375</v>
+        <v>-0.006342577425638374</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.08031965216024872</v>
+        <v>0.08032002157448814</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>-0.004672997795492573</v>
+        <v>-0.004673078048797019</v>
       </c>
     </row>
     <row r="4">
@@ -8961,76 +8903,76 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>0.1108237527575089</v>
+        <v>0.1108237292500149</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.01601549017614068</v>
+        <v>0.01601558259482738</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.08705398696064459</v>
+        <v>0.08705283475606773</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.08598738228159752</v>
+        <v>0.08598883232503596</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.007084230510525424</v>
+        <v>0.007083828554967031</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.1030416361763218</v>
+        <v>0.1030410665951709</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.3395180370990505</v>
+        <v>0.3395186603509222</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>-0.2180624010269393</v>
+        <v>-0.2180625916776243</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.09012651767505209</v>
+        <v>0.09012673524833681</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.3400120482207474</v>
+        <v>0.3400109600017673</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.02409414542548816</v>
+        <v>0.02409510015435457</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1338138221636449</v>
+        <v>-0.1338137976854589</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.2730194306779883</v>
+        <v>0.2730194786133129</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-0.01789587182259111</v>
+        <v>-0.01789619915831775</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.01171619875266283</v>
+        <v>0.01171653757712554</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>0.09182545799153563</v>
+        <v>0.09182560195585099</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.01611854617993946</v>
+        <v>-0.0161186929371907</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1411839190846982</v>
+        <v>0.1411838861695198</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.1815231133031092</v>
+        <v>0.181523416708842</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>-0.04599142771940745</v>
+        <v>-0.04599198287066253</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>-0.3123454489159411</v>
+        <v>-0.3123453658276067</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.02767977975659797</v>
+        <v>0.02767960404543324</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.08053113792358213</v>
+        <v>-0.0805308952248599</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.04247226014383698</v>
+        <v>0.04247216321812708</v>
       </c>
       <c r="AB4" s="2" t="n">
         <v>0.002663800021726281</v>
@@ -9049,76 +8991,76 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="n">
-        <v>0.1074497419950071</v>
+        <v>0.1074495381971361</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.09110356361148852</v>
+        <v>0.09110321476591188</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.05713155630688682</v>
+        <v>0.057131017360323</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.0115968867655416</v>
+        <v>0.01159599551307999</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.04218318075206118</v>
+        <v>0.04218410330417255</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.03730005217619037</v>
+        <v>0.03730082437925364</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.02423188669788301</v>
+        <v>0.02423142552189916</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.08447392844933632</v>
+        <v>0.08447456180838198</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.09316488956987179</v>
+        <v>0.09316428074694838</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.09740749063610932</v>
+        <v>0.09740673386363552</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1024432843771064</v>
+        <v>0.1024434413116675</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.0200163316609554</v>
+        <v>-0.02001633772439126</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.08209870717155443</v>
+        <v>0.0820994538098998</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-0.0125546335423693</v>
+        <v>-0.01255567617781828</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.06204768099269353</v>
+        <v>0.06204820502821407</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>0.07054922475499636</v>
+        <v>0.07054914676954782</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.03787206386230679</v>
+        <v>-0.03787156461911145</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.173682365836213</v>
+        <v>0.1736819672983763</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.1097000687003171</v>
+        <v>0.1097006026881677</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-0.01841598750965656</v>
+        <v>-0.01841631844190228</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-0.1792167726608562</v>
+        <v>-0.1792168982075235</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.09404548355480102</v>
+        <v>0.09404549145533569</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.008583160404432855</v>
+        <v>0.008583084277304476</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.0789543626148701</v>
+        <v>0.07895452690238014</v>
       </c>
       <c r="AB5" s="2" t="n">
         <v>0.008195163751214762</v>
@@ -9142,64 +9084,64 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" s="2" t="n">
-        <v>0.01633816765630414</v>
+        <v>0.01633973436256286</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0.1755441931511893</v>
+        <v>-0.1755448911117841</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.2851902348688669</v>
+        <v>0.285190071003385</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.1191317340372167</v>
+        <v>0.1191319043158889</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.06754813838286999</v>
+        <v>0.06754649995216133</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.110555230511399</v>
+        <v>0.1105561759154341</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.05753504350601601</v>
+        <v>0.05753496411304093</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.01894187445967899</v>
+        <v>0.01894211644737309</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-0.05021469826503544</v>
+        <v>-0.05021508521871332</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1341425622768244</v>
+        <v>0.1341433472224292</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>0.06073958310880823</v>
+        <v>0.06073876275737189</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.0202426474014169</v>
+        <v>-0.02024176627599705</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.1408870825150228</v>
+        <v>0.1408868739832081</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.04467506741011773</v>
+        <v>0.04467499252954177</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.03756223499446443</v>
+        <v>0.03756187464743088</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.1098285562366534</v>
+        <v>-0.1098285121710494</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.1154151357542086</v>
+        <v>0.1154149527656687</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.07966048350230404</v>
+        <v>0.07966061536981095</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.08592167153871499</v>
+        <v>0.08592189129678984</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.01653510985877116</v>
+        <v>0.01653501123748979</v>
       </c>
     </row>
     <row r="7">
@@ -9216,73 +9158,73 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="3" t="n">
-        <v>-0.0002239686778359173</v>
+        <v>-0.0002235126827482281</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.08278812067422536</v>
+        <v>0.08278722705965835</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.02490322800842937</v>
+        <v>0.02490402674722447</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.002772371067957691</v>
+        <v>0.002772782955627884</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.1192699480801007</v>
+        <v>0.1192703417712213</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.0005349233128029152</v>
+        <v>0.0005341293971656835</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.08931970115958099</v>
+        <v>0.08932125385365208</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.06131305219119865</v>
+        <v>0.06131219930035692</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.132957416605725</v>
+        <v>0.132957374501969</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.06397182704655324</v>
+        <v>0.06397143648816828</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.08490528119313301</v>
+        <v>-0.08490563889851155</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.03590742029398242</v>
+        <v>0.03590810732136118</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>-0.01754079991575364</v>
+        <v>-0.01754144330293073</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.04681292019635364</v>
+        <v>0.04681350635264026</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>0.02920199547612801</v>
+        <v>0.02920199285320613</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.01425282541344852</v>
+        <v>-0.01425282416958373</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.08349647070822397</v>
+        <v>0.08349619771610639</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.1083788489439539</v>
+        <v>0.1083794386307237</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.05677154996246125</v>
+        <v>0.05677116043155928</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>-0.1226251505868501</v>
+        <v>-0.1226252203473922</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.03804865249523925</v>
+        <v>0.03804833747835024</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.01652255611166065</v>
+        <v>0.01652309861275891</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0.06764763326530621</v>
+        <v>0.06764747236835733</v>
       </c>
       <c r="AB7" s="2" t="n">
         <v>0.01396298571221988</v>
@@ -9306,64 +9248,64 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" s="2" t="n">
-        <v>0.06098632083647626</v>
+        <v>0.0609862226515312</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.06863854953526016</v>
+        <v>0.06863846231339421</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.03636627193516917</v>
+        <v>0.03636717271919676</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.06198693208868034</v>
+        <v>0.06198648949303109</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.07929663441875712</v>
+        <v>0.07929608590540327</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.02940982465292064</v>
+        <v>0.02940982869443154</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.02107495675616688</v>
+        <v>-0.02107422535041115</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.05817766093133292</v>
+        <v>0.05817823888730067</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.005591258170013713</v>
+        <v>0.005589834106590086</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.02521482197627112</v>
+        <v>0.02521502067066539</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>0.03999459989368548</v>
+        <v>0.03999447739092843</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0.001159524041042914</v>
+        <v>0.001159464152437062</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.0883385917900843</v>
+        <v>0.08833885311349943</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.07715053890951284</v>
+        <v>0.07715042859817123</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>-0.0186112340035065</v>
+        <v>-0.01861062144744929</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>-0.1311217325680263</v>
+        <v>-0.1311219772108961</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.05654419708539615</v>
+        <v>0.05654394330310919</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.01382600737576523</v>
+        <v>0.01382634839378816</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0.07082372677369064</v>
+        <v>0.07082347870604444</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.005154713117650589</v>
+        <v>0.00515460787118216</v>
       </c>
     </row>
     <row r="9">
@@ -9391,43 +9333,43 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" s="3" t="n">
-        <v>-0.01674972897868543</v>
+        <v>-0.01674992585937252</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.005773858110281749</v>
+        <v>0.005772791519058851</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>-0.06821549928809456</v>
+        <v>-0.06821479516253026</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>0.06960246938798664</v>
+        <v>0.06960222662485349</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0.01891211142858062</v>
+        <v>0.0189118992321673</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.02677195904276797</v>
+        <v>0.02677186048930813</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.1201480439547957</v>
+        <v>0.1201481819227304</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.05932062598486332</v>
+        <v>0.05932090833460313</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>-0.07990962802539714</v>
+        <v>-0.07990962119582434</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.02924329423173644</v>
+        <v>0.02924329151535843</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.01844045751200429</v>
+        <v>0.01844036559803164</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>0.05454752331742863</v>
+        <v>0.05454761193305058</v>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>0.05296017459810076</v>
+        <v>0.05296008611587411</v>
       </c>
     </row>
     <row r="10">
@@ -9464,13 +9406,13 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" s="2" t="n">
-        <v>0.05763648259113463</v>
+        <v>0.05763620460820507</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.07231304743702638</v>
+        <v>0.07231339101622947</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>0.130728392242849</v>
+        <v>0.1307281253459458</v>
       </c>
       <c r="AB10" s="2" t="n">
         <v>0.07073948182199175</v>
@@ -9507,16 +9449,16 @@
         <v>0</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>0.002114986867047142</v>
+        <v>0.002114922630023885</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>0.01978334583791486</v>
+        <v>0.01978308924932248</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-0.008908194563797434</v>
+        <v>-0.008908071050249378</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.001994142935365817</v>
+        <v>-0.00199407990554934</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>-0.05485285523400241</v>
@@ -9525,10 +9467,10 @@
         <v>0.005373709098607682</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-0.02804041861903295</v>
+        <v>-0.02804048521575975</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>-0.06433326333077649</v>
+        <v>-0.06433319922075842</v>
       </c>
       <c r="AB11" s="3" t="n">
         <v>-0.0226551687270885</v>
@@ -9561,16 +9503,16 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" s="3" t="n">
-        <v>-0.07010011585818865</v>
+        <v>-0.07010005491227145</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>0.01062860488034034</v>
+        <v>0.01062853864344304</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>-0.02562575239347298</v>
+        <v>-0.02562568754244909</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>0.05865878228468668</v>
+        <v>0.05865871182397653</v>
       </c>
       <c r="V12" s="2" t="n">
         <v>0.07699137176283943</v>
@@ -9579,13 +9521,13 @@
         <v>-0.03904824660076811</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>-0.176042979360467</v>
+        <v>-0.1760430401069625</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>-0.02930264472630617</v>
+        <v>-0.02930264688665318</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>-0.07088518626650075</v>
+        <v>-0.07088511569940548</v>
       </c>
       <c r="AA12" s="2" t="n">
         <v>0.04377884233932172</v>
@@ -9618,13 +9560,13 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" s="3" t="n">
-        <v>-0.03453021553229296</v>
+        <v>-0.03453029423363896</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>0.07395264223481979</v>
+        <v>0.07395264826315229</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>0.07222623495528713</v>
+        <v>0.07222631634036891</v>
       </c>
       <c r="R13" s="2" t="n">
         <v>0.007956654433446841</v>
@@ -9689,25 +9631,25 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" s="2" t="n">
-        <v>0.0006000649426747273</v>
+        <v>0.0005999809436583181</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>0.02442497780050856</v>
+        <v>0.02442489390220404</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>0.02313273085926171</v>
+        <v>0.02313273275378513</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>0.04735264604120015</v>
+        <v>0.04735272987786932</v>
       </c>
       <c r="X14" s="2" t="n">
         <v>0.02326475416188289</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>0.03682637642091358</v>
+        <v>0.0368264511105072</v>
       </c>
       <c r="Z14" s="2" t="n">
-        <v>0.08715300351791422</v>
+        <v>0.08715292520295992</v>
       </c>
       <c r="AA14" s="2" t="n">
         <v>0.0013103938430572</v>
@@ -9738,46 +9680,46 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="2" t="n">
-        <v>0.01264219925414323</v>
+        <v>0.01264230328461657</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.07427092326639206</v>
+        <v>0.07427081290470516</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>0.006063754870875737</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>0.1116448224084476</v>
+        <v>0.1116449174613166</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>0.06599264165179419</v>
+        <v>0.06599255050249186</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>0.01668342985502047</v>
+        <v>0.01668334964198115</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>-0.01414982023370803</v>
+        <v>-0.01414966355652947</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>0.06784160690888608</v>
+        <v>0.06784152145041644</v>
       </c>
       <c r="U15" s="2" t="n">
         <v>0.03752066134283827</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>0.01424608953077122</v>
+        <v>0.01424616176527849</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>-0.02436938515644771</v>
+        <v>-0.0243693122009655</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>-0.09188283569538114</v>
+        <v>-0.09188304127718749</v>
       </c>
       <c r="Y15" s="2" t="n">
-        <v>0.0808086938438648</v>
+        <v>0.08080886110932028</v>
       </c>
       <c r="Z15" s="2" t="n">
-        <v>0.0429316811836169</v>
+        <v>0.04293160361588955</v>
       </c>
       <c r="AA15" s="3" t="n">
         <v>-0.003396429509450627</v>
@@ -9806,46 +9748,46 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" s="2" t="n">
-        <v>0.01436493514453119</v>
+        <v>0.01436435680086223</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0.06902169014829718</v>
+        <v>0.0690214582142521</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0.04519907605089357</v>
+        <v>0.04519939537280893</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.04353741837843916</v>
+        <v>0.04353730931647126</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>0.0177227145358716</v>
+        <v>0.01772300125319015</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>0.05074582960034379</v>
+        <v>0.05074543256060005</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>0.03151798964684027</v>
+        <v>0.03151807955079677</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>0.01359587329297685</v>
+        <v>0.01359578495106484</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>0.002894953441010761</v>
+        <v>0.00289503942887559</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>0.03204973928715193</v>
+        <v>0.03204965079957356</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>0.02503942421619709</v>
+        <v>0.02503934113914252</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>0.01620791255410547</v>
+        <v>0.0162081570107413</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.003968369802904603</v>
+        <v>-0.003968608434887999</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.02203154050148448</v>
+        <v>-0.0220314621928408</v>
       </c>
       <c r="Y16" s="2" t="n">
         <v>0.04948017754456391</v>
@@ -9921,55 +9863,55 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>0.07304625493211492</v>
+        <v>0.07304637820603044</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>-0.04993602928463692</v>
+        <v>-0.04993619920894532</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0.03421322730060061</v>
+        <v>0.03421297629198516</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0.119801321770872</v>
+        <v>0.119801593552203</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.001688073641061161</v>
+        <v>0.001688182010685768</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>-0.04126544166530077</v>
+        <v>-0.04126522082694672</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>0.13669301638443</v>
+        <v>0.136692631579185</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>0.002967980909301948</v>
+        <v>0.00296788163576589</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>0.103363777859711</v>
+        <v>0.1033638870704106</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>0.01385053528783975</v>
+        <v>0.01385044558055726</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>0.005343856056452712</v>
+        <v>0.005344033492827638</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>0.06696456192876732</v>
+        <v>0.06696446802368561</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>0.08075990299777591</v>
+        <v>0.08076006797315616</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>-0.05032508209577491</v>
+        <v>-0.05032507441377421</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>-0.2371003202517264</v>
+        <v>-0.2371004428776552</v>
       </c>
       <c r="Y18" s="2" t="n">
-        <v>0.03560395472613709</v>
+        <v>0.03560406007200823</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>-0.01317601634828214</v>
+        <v>-0.01317611673204477</v>
       </c>
       <c r="AA18" s="2" t="n">
         <v>0.04726736024564926</v>
@@ -9997,52 +9939,52 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" s="2" t="n">
-        <v>0.07667604655667315</v>
+        <v>0.0766758559180083</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-0.1139715496563123</v>
+        <v>-0.1139716203242612</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0.1537615705746025</v>
+        <v>0.1537617953940804</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>-0.1085552367679303</v>
+        <v>-0.1085550678787952</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.04030697857529564</v>
+        <v>0.0403069077870879</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>0.0143502992089044</v>
+        <v>0.01434981182664496</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>0.08081462641012593</v>
+        <v>0.08081489481369086</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>-0.03988666143370234</v>
+        <v>-0.03988666585086165</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>0.2115572492070716</v>
+        <v>0.2115575042956779</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>0.04562033215621653</v>
+        <v>0.04561994700261263</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>0.02049903010123266</v>
+        <v>0.02049930884735485</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>0.01386505723285203</v>
+        <v>0.01386496801284198</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>0.09999462320692531</v>
+        <v>0.09999463200644154</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>-0.095451143624117</v>
+        <v>-0.09545107125994223</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>-0.153913920978666</v>
+        <v>-0.1539138325364692</v>
       </c>
       <c r="Y19" s="2" t="n">
-        <v>0.06627765118496831</v>
+        <v>0.06627753972594497</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>-0.03527030933795894</v>
@@ -10131,46 +10073,46 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" s="2" t="n">
-        <v>0.03090567040369385</v>
+        <v>0.03090545978200998</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>0.003820438062233533</v>
+        <v>0.003820646765575475</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>0.09316320336266037</v>
+        <v>0.09316352307870401</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>0.02932569620280701</v>
+        <v>0.02932531244412484</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>0.01815518896907919</v>
+        <v>0.01815528416397383</v>
       </c>
       <c r="S21" s="2" t="n">
-        <v>0.02975539163322449</v>
+        <v>0.02975557476069435</v>
       </c>
       <c r="T21" s="2" t="n">
-        <v>0.05245940735491672</v>
+        <v>0.05245913991542572</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>0.07376063245328979</v>
+        <v>0.07376097772342649</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>0.0388174103858614</v>
+        <v>0.03881748189568035</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.03269251278609797</v>
+        <v>-0.03269265472986815</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.1024398290511772</v>
+        <v>-0.1024398983016298</v>
       </c>
       <c r="Y21" s="2" t="n">
-        <v>0.03880836650379571</v>
+        <v>0.03880845246361697</v>
       </c>
       <c r="Z21" s="2" t="n">
-        <v>0.01899905277806124</v>
+        <v>0.01899888570895669</v>
       </c>
       <c r="AA21" s="2" t="n">
-        <v>0.02618370847234042</v>
+        <v>0.02618379180426977</v>
       </c>
       <c r="AB21" s="2" t="n">
         <v>0.0139867925946735</v>
@@ -10204,31 +10146,31 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" s="3" t="n">
-        <v>-0.001187552730353425</v>
+        <v>-0.001187644955230938</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>-0.01220468748314008</v>
+        <v>-0.01220459750927894</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>0.06404420770946029</v>
+        <v>0.06404393359543858</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>0.07646198407078564</v>
+        <v>0.07646201090740057</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>-0.03519091248330419</v>
+        <v>-0.03519043488311702</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>-0.1227811901922188</v>
+        <v>-0.1227810849603328</v>
       </c>
       <c r="Y22" s="2" t="n">
-        <v>0.05610948587003373</v>
+        <v>0.05610898810545395</v>
       </c>
       <c r="Z22" s="2" t="n">
-        <v>0.03246087058658742</v>
+        <v>0.03246096770081008</v>
       </c>
       <c r="AA22" s="2" t="n">
-        <v>0.01883290720169972</v>
+        <v>0.01883299719174425</v>
       </c>
       <c r="AB22" s="2" t="n">
         <v>0.01722841707876599</v>
@@ -10252,61 +10194,61 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" s="2" t="n">
-        <v>0.03976922350830669</v>
+        <v>0.03976834198832613</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.04188593671732477</v>
+        <v>0.04188668947238861</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.05430239663657765</v>
+        <v>0.0543015812919958</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0.03831574436044938</v>
+        <v>0.03831634775461623</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0.03955971674027481</v>
+        <v>0.03955971034689743</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.05660860761264774</v>
+        <v>0.05660836561721982</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>-0.03584829344917306</v>
+        <v>-0.03584822251931896</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>-0.02524068643179</v>
+        <v>-0.02524038122212813</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>-0.06687151030841854</v>
+        <v>-0.06687156764828295</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>0.006391756434434459</v>
+        <v>0.006391503162154422</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>0.09935015501138178</v>
+        <v>0.09935057178706996</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>-0.01754426935499809</v>
+        <v>-0.01754486928107546</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>0.05583967541546264</v>
+        <v>0.05584038292982663</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>0.09501561264358438</v>
+        <v>0.09501454764871187</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>-0.08601264098214256</v>
+        <v>-0.08601195264068184</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>-0.1972163835626843</v>
+        <v>-0.1972167055219433</v>
       </c>
       <c r="Y23" s="2" t="n">
-        <v>0.05097525255364799</v>
+        <v>0.05097535280460552</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>-0.05929985168241858</v>
+        <v>-0.05929959712564759</v>
       </c>
       <c r="AA23" s="2" t="n">
-        <v>0.07667390067277724</v>
+        <v>0.07667370252155248</v>
       </c>
       <c r="AB23" s="3" t="n">
         <v>-0.01688340813690314</v>
@@ -10332,40 +10274,40 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" s="2" t="n">
-        <v>0.1060405768856754</v>
+        <v>0.1060400898516303</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0.01789020783873441</v>
+        <v>0.01789047272736055</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0.01572888935656169</v>
+        <v>0.01572931430593649</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0528394401027894</v>
+        <v>0.05283858835964583</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>-0.01371300462072855</v>
+        <v>-0.01371269423841048</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>-0.02220888263733067</v>
+        <v>-0.02220872555186648</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>-0.07150142191354558</v>
+        <v>-0.07150125761120329</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>0.008557360406720171</v>
+        <v>0.008557358892453903</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>0.1137559451304431</v>
+        <v>0.1137556619914473</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>-0.0259824887759621</v>
+        <v>-0.0259823332893816</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>0.03760550405001628</v>
+        <v>0.03760550100894577</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>0.1088301593161696</v>
+        <v>0.1088300728974472</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>-0.09247692287146747</v>
@@ -10406,58 +10348,58 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" s="2" t="n">
-        <v>0.1297402772024123</v>
+        <v>0.1297392829994992</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0.01592421829882928</v>
+        <v>0.01592592204434262</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-0.005031831348987548</v>
+        <v>-0.005032658387398414</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.02986804788040254</v>
+        <v>0.02986781665084037</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-0.02179906983568858</v>
+        <v>-0.02179850133567551</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-0.09763213687217254</v>
+        <v>-0.09763206617424469</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>-0.07724984358618125</v>
+        <v>-0.07724956620368839</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>-0.01485379380018348</v>
+        <v>-0.01485449676817341</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>0.1018649118061905</v>
+        <v>0.1018651501610788</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>-0.03365783487264451</v>
+        <v>-0.03365770399182566</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>0.009981275500702491</v>
+        <v>0.009981003270048916</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>0.06464281114145298</v>
+        <v>0.06464335621385864</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>-0.06845472037096323</v>
+        <v>-0.06845482046214324</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>-0.1055744078627879</v>
+        <v>-0.1055744469196988</v>
       </c>
       <c r="Y25" s="2" t="n">
-        <v>0.02962460782401077</v>
+        <v>0.02962444993141955</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>-0.05285906920431582</v>
+        <v>-0.05285921214902434</v>
       </c>
       <c r="AA25" s="2" t="n">
-        <v>0.1044490652289958</v>
+        <v>0.1044490733248136</v>
       </c>
       <c r="AB25" s="3" t="n">
-        <v>-0.005082541649794381</v>
+        <v>-0.005082471826953538</v>
       </c>
     </row>
     <row r="26">
@@ -10484,46 +10426,46 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>-0.004959354595625243</v>
+        <v>-0.004960105159297457</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>0.0874028263975517</v>
+        <v>0.08740373684230396</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>0.01189763691620671</v>
+        <v>0.01189793108540171</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>0.04612540878156857</v>
+        <v>0.04612430286761349</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>0.02396847276897107</v>
+        <v>0.02396876524255775</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>0.02812262823441314</v>
+        <v>0.02812254183188734</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>0.07866145761863352</v>
+        <v>0.07866174577540197</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>0.04651923821653714</v>
+        <v>0.04651940332416138</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.02285897883008925</v>
+        <v>-0.0228588174553308</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.1275693600259755</v>
+        <v>-0.1275697224792561</v>
       </c>
       <c r="Y26" s="2" t="n">
-        <v>0.08783872566492223</v>
+        <v>0.08783919646349481</v>
       </c>
       <c r="Z26" s="2" t="n">
-        <v>0.03558539806530847</v>
+        <v>0.03558513077051972</v>
       </c>
       <c r="AA26" s="2" t="n">
-        <v>0.0286564521988748</v>
+        <v>0.02865628556634103</v>
       </c>
       <c r="AB26" s="2" t="n">
-        <v>0.01020193787471624</v>
+        <v>0.01020201854047165</v>
       </c>
     </row>
     <row r="27">
@@ -10544,61 +10486,61 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" s="2" t="n">
-        <v>0.002875910059829234</v>
+        <v>0.002877112413268268</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.02126957449798861</v>
+        <v>-0.02126983708874197</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.1537341136958514</v>
+        <v>0.1537341499313662</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0.1083820560376283</v>
+        <v>0.1083813593288427</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.07648750957839745</v>
+        <v>0.07648767364011189</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1652162975546148</v>
+        <v>0.1652162404893327</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.07792951716041119</v>
+        <v>-0.0779294089707917</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>0.06044629069848084</v>
+        <v>0.06044609982369531</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>0.01034687931968703</v>
+        <v>0.01034706117687323</v>
       </c>
       <c r="R27" s="2" t="n">
         <v>0.09266643087331516</v>
       </c>
       <c r="S27" s="2" t="n">
-        <v>0.102843739181427</v>
+        <v>0.102843413095711</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>-0.05470865400754432</v>
+        <v>-0.05470827594730554</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>0.1547706231475043</v>
+        <v>0.1547705027474902</v>
       </c>
       <c r="V27" s="2" t="n">
         <v>0.05421451723478188</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>-0.022281871676193</v>
+        <v>-0.02228195732200611</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>-0.1862517936714375</v>
+        <v>-0.1862518099866589</v>
       </c>
       <c r="Y27" s="2" t="n">
-        <v>0.1061582550487576</v>
+        <v>0.1061582664763896</v>
       </c>
       <c r="Z27" s="2" t="n">
-        <v>0.05536455087939296</v>
+        <v>0.05536484821590193</v>
       </c>
       <c r="AA27" s="2" t="n">
-        <v>0.1385589912856009</v>
+        <v>0.1385587813103493</v>
       </c>
       <c r="AB27" s="2" t="n">
         <v>0.02290155964955964</v>
@@ -10625,55 +10567,55 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" s="2" t="n">
-        <v>0.06702278524145733</v>
+        <v>0.06702288072189178</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>-0.0306228355130832</v>
+        <v>-0.03062317096243106</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.1687336298488435</v>
+        <v>0.1687340342848918</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>-0.09941696864406813</v>
+        <v>-0.09941652451429783</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>-0.05054598760447249</v>
+        <v>-0.05054694899293477</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>-0.1507046086929874</v>
+        <v>-0.1507037347145551</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>0.09003643081381663</v>
+        <v>0.0900354675569095</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>0.1383356615931206</v>
+        <v>0.1383364614222062</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>-0.07568023327071549</v>
+        <v>-0.07568037269676786</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>0.09788932570828912</v>
+        <v>0.09788886394527707</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>0.03079929014443605</v>
+        <v>0.03079970236765361</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>-0.0971395584317799</v>
+        <v>-0.09713954317503248</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>-0.1046311626375739</v>
+        <v>-0.1046317532902259</v>
       </c>
       <c r="Y28" s="2" t="n">
-        <v>0.1117537686782475</v>
+        <v>0.1117541143893248</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>-0.02959021220747859</v>
+        <v>-0.02959013000004018</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>0.1881362882295186</v>
+        <v>0.188136485255697</v>
       </c>
       <c r="AB28" s="2" t="n">
-        <v>0.01399044184399156</v>
+        <v>0.01399036499872985</v>
       </c>
     </row>
     <row r="29">
@@ -10698,28 +10640,28 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="3" t="n">
-        <v>-0.02139357356670013</v>
+        <v>-0.02139337828376642</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.1120106345482321</v>
+        <v>0.1120104306337468</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.0672871023396121</v>
+        <v>-0.06728702299105083</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.02926000129168471</v>
+        <v>-0.0292599058662546</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.1211041177684574</v>
+        <v>-0.1211042190331931</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>0.06274790619861981</v>
+        <v>0.06274814386459382</v>
       </c>
       <c r="S29" s="2" t="n">
-        <v>0.1248541949833859</v>
+        <v>0.1248539646167217</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>-0.04262979233611752</v>
+        <v>-0.04262970006319744</v>
       </c>
       <c r="U29" s="2" t="n">
         <v>0.06397246061105899</v>
@@ -10728,13 +10670,13 @@
         <v>0.03098651813056152</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>-0.09920065506325371</v>
+        <v>-0.09920056328685067</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>-0.1073717452363447</v>
+        <v>-0.1073719380635229</v>
       </c>
       <c r="Y29" s="2" t="n">
-        <v>0.07230734040977116</v>
+        <v>0.07230746280138711</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>-0.01715685517936705</v>
@@ -10770,40 +10712,40 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>-0.01826289546555548</v>
+        <v>-0.01826298337871057</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>0.04168444207651811</v>
+        <v>0.04168471571977439</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>0.01593294602454787</v>
+        <v>0.01593285427475033</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>0.08980109686755799</v>
+        <v>0.08980065043217911</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>0.08413973600472135</v>
+        <v>0.08413999323474175</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>-0.0292468316394412</v>
+        <v>-0.02924690459019263</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>0.144650328256644</v>
+        <v>0.1446498130866054</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>0.05648890484087166</v>
+        <v>0.05648939407417952</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>-0.01799176398679314</v>
+        <v>-0.01799151653799091</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>-0.1739021702840599</v>
+        <v>-0.1739026435120976</v>
       </c>
       <c r="Y30" s="2" t="n">
-        <v>0.1068097396503116</v>
+        <v>0.106810010363404</v>
       </c>
       <c r="Z30" s="2" t="n">
-        <v>0.05206127723847698</v>
+        <v>0.05206142286305604</v>
       </c>
       <c r="AA30" s="2" t="n">
         <v>0.1349475715215622</v>
@@ -10835,46 +10777,46 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" s="2" t="n">
-        <v>0.09223205651694677</v>
+        <v>0.09223115035875851</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0.04946396393291719</v>
+        <v>-0.0494631753306034</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>0.04094916516912339</v>
+        <v>0.04094923230847791</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.01769888844435297</v>
+        <v>-0.01769869380819833</v>
       </c>
       <c r="R31" s="2" t="n">
-        <v>0.1229754788902724</v>
+        <v>0.1229755779124515</v>
       </c>
       <c r="S31" s="2" t="n">
-        <v>0.07107338318013623</v>
+        <v>0.07107277354689367</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.02553416911430262</v>
+        <v>-0.02553362878931464</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>0.138896638389765</v>
+        <v>0.1388959194578026</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>0.06765213303963269</v>
+        <v>0.06765244813624172</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>-0.005899830318487953</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.1258749931409436</v>
+        <v>-0.1258749004509923</v>
       </c>
       <c r="Y31" s="2" t="n">
-        <v>0.08369151002997244</v>
+        <v>0.08369150115554258</v>
       </c>
       <c r="Z31" s="2" t="n">
-        <v>0.05811731193403302</v>
+        <v>0.05811701270237601</v>
       </c>
       <c r="AA31" s="2" t="n">
-        <v>0.0886569456153965</v>
+        <v>0.08865714696034677</v>
       </c>
       <c r="AB31" s="2" t="n">
         <v>0.01539102663529657</v>
@@ -10903,46 +10845,46 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" s="2" t="n">
-        <v>0.1807595549298293</v>
+        <v>0.1807599938112918</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>-0.06275644753710419</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>0.01644421273121632</v>
+        <v>0.0164437928932688</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>0.02038793751146728</v>
+        <v>0.02038877202443379</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>0.1413266211123594</v>
+        <v>0.141326806779986</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>0.08537805166714518</v>
+        <v>0.08537736481437253</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>-0.05211722616400938</v>
+        <v>-0.05211690280030579</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>0.1298223028353953</v>
+        <v>0.1298216465063693</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>0.0382261184856989</v>
+        <v>0.03822631322417891</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>-0.01903356437806136</v>
+        <v>-0.01903339028142581</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>-0.1301560547499346</v>
+        <v>-0.1301564064621864</v>
       </c>
       <c r="Y32" s="2" t="n">
-        <v>0.1145817037914623</v>
+        <v>0.1145824320980646</v>
       </c>
       <c r="Z32" s="2" t="n">
-        <v>0.1197056607537721</v>
+        <v>0.1197055619603773</v>
       </c>
       <c r="AA32" s="2" t="n">
-        <v>0.1369729848832715</v>
+        <v>0.1369727338600604</v>
       </c>
       <c r="AB32" s="2" t="n">
         <v>0.03335519846392598</v>
@@ -11360,25 +11302,25 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" s="2" t="n">
-        <v>0.3372271152927262</v>
+        <v>0.337227360433501</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>-0.191262403713269</v>
+        <v>-0.1912623351683717</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.00993130149156829</v>
+        <v>0.009931215894420475</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0.2235249895705973</v>
+        <v>0.2235249056486284</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>-0.1072642840539101</v>
+        <v>-0.1072641542305551</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>-0.03220204684008121</v>
+        <v>-0.03220227486074656</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>-0.1323794381103355</v>
+        <v>-0.13237930035288</v>
       </c>
       <c r="P38" s="2" t="n">
         <v>0.02639178819663979</v>
@@ -11387,16 +11329,16 @@
         <v>-0.1719565677473143</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>-0.03105303389173597</v>
+        <v>-0.03105292623056721</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>-0.06059077772174049</v>
+        <v>-0.06059088210091412</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>-0.08735161423557114</v>
+        <v>-0.08735155509653147</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>-0.007078294291389398</v>
+        <v>-0.007078358632085391</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>-0.02536230630851699</v>
@@ -11649,58 +11591,58 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" s="2" t="n">
-        <v>0.04057516629936608</v>
+        <v>0.04057506688113177</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0.3157874019396667</v>
+        <v>0.3157875276521351</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>-0.3179922388211861</v>
+        <v>-0.3179923114329296</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.1618687920726765</v>
+        <v>0.161869128709359</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0.1190089622504922</v>
+        <v>0.1190085739006161</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>-0.02577136603143815</v>
+        <v>-0.0257712883629706</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.03502238607436126</v>
+        <v>0.03502255712914892</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>-0.07631389874725947</v>
+        <v>-0.07631397376096793</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>-0.2809820090212063</v>
+        <v>-0.2809821409024741</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>-0.2758808830749271</v>
+        <v>-0.2758807502579936</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>0.1856287647607837</v>
+        <v>0.1856288491937579</v>
       </c>
       <c r="S42" s="2" t="n">
-        <v>0.04861130497054322</v>
+        <v>0.04861108786776258</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>-0.1163031091636865</v>
+        <v>-0.1163029891357866</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>0.1183923257917328</v>
+        <v>0.1183924026420207</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>-0.07836982819403815</v>
+        <v>-0.07836989152381746</v>
       </c>
       <c r="W42" s="2" t="n">
         <v>0.413605430511323</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>0.19339906260575</v>
+        <v>0.1933991680921394</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>-0.06194497290312928</v>
+        <v>-0.06194505581925702</v>
       </c>
       <c r="Z42" s="2" t="n">
         <v>0.02184255034418392</v>
@@ -11773,7 +11715,7 @@
         <v>-0.06336749968935373</v>
       </c>
       <c r="AB43" s="3" t="n">
-        <v>-0.2513997694875427</v>
+        <v>-0.2499821892969727</v>
       </c>
     </row>
     <row r="44">
@@ -11831,7 +11773,7 @@
         <v>-0.109674616576496</v>
       </c>
       <c r="AB44" s="3" t="n">
-        <v>-0.419319786923148</v>
+        <v>-0.4192625170472508</v>
       </c>
     </row>
     <row r="45">
@@ -11852,22 +11794,22 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" s="3" t="n">
-        <v>-0.04294159584685042</v>
+        <v>-0.04294158787529456</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.0487750874958286</v>
+        <v>0.04877488406871655</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>-0.06520861040508097</v>
+        <v>-0.06520851793224069</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>-0.01603124637383524</v>
+        <v>-0.01603114586447363</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>-0.0105679595896716</v>
+        <v>-0.01056805799995697</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>-0.02937252270885149</v>
+        <v>-0.02937262133333762</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>-0.01329662699253908</v>
@@ -11876,13 +11818,13 @@
         <v>0.1138475014099964</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>0.07008751235399058</v>
+        <v>0.07008760760449562</v>
       </c>
       <c r="R45" s="2" t="n">
-        <v>0.03157901295612464</v>
+        <v>0.03157901014521758</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>-0.0909808660248983</v>
+        <v>-0.09098094446144778</v>
       </c>
       <c r="T45" s="2" t="n">
         <v>0.07048277001147629</v>
@@ -11894,16 +11836,16 @@
         <v>-0.06661522758640903</v>
       </c>
       <c r="W45" s="2" t="n">
-        <v>0.057343150468816</v>
+        <v>0.05734324174119587</v>
       </c>
       <c r="X45" s="2" t="n">
-        <v>0.09460674155363535</v>
+        <v>0.09460664706458166</v>
       </c>
       <c r="Y45" s="2" t="n">
-        <v>0.03631006499689948</v>
+        <v>0.03631014385844789</v>
       </c>
       <c r="Z45" s="2" t="n">
-        <v>0.1350201915716598</v>
+        <v>0.1350201051984341</v>
       </c>
       <c r="AA45" s="3" t="n">
         <v>-0.04985919362731739</v>
@@ -11928,67 +11870,67 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" s="3" t="n">
-        <v>-0.00878258608315563</v>
+        <v>-0.008782292229514987</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0.1397105290601441</v>
+        <v>0.1397100522638004</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0.1425704411758284</v>
+        <v>0.1425701431898003</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-0.01180350647432038</v>
+        <v>-0.01180316962059624</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.02528757314150787</v>
+        <v>0.02528757606076981</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.06865401463535958</v>
+        <v>-0.06865441644900117</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.02926413919488979</v>
+        <v>-0.02926367153427367</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.01582358742165746</v>
+        <v>0.01582421110588461</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>0.03840855648540686</v>
+        <v>0.03840822879611538</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-0.1239060678845947</v>
+        <v>-0.1239059795941064</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-0.1069327976412153</v>
+        <v>-0.1069330985222697</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.03890979009329187</v>
+        <v>-0.03890986554285047</v>
       </c>
       <c r="S46" s="2" t="n">
-        <v>0.1305495556587275</v>
+        <v>0.130549644411553</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-0.0530232107916967</v>
+        <v>-0.05302341910845154</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-0.02904627084437672</v>
+        <v>-0.02904613058007199</v>
       </c>
       <c r="V46" s="2" t="n">
-        <v>0.07939783849645865</v>
+        <v>0.07939814657480349</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.07826396447099271</v>
+        <v>-0.07826401800909899</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.06566337459161542</v>
+        <v>-0.065663440529248</v>
       </c>
       <c r="Y46" s="2" t="n">
-        <v>0.04866934658033162</v>
+        <v>0.04866909890435567</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.0418277434795411</v>
+        <v>-0.04182736260898812</v>
       </c>
       <c r="AA46" s="2" t="n">
-        <v>0.1452340220236332</v>
+        <v>0.1452337442398941</v>
       </c>
       <c r="AB46" s="3" t="n">
         <v>-0.01144610937544011</v>
@@ -12089,67 +12031,67 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" s="2" t="n">
-        <v>0.09680869653677604</v>
+        <v>0.09680882886953457</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0.06547977568661789</v>
+        <v>0.06547997492752011</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>-0.2383411991478208</v>
+        <v>-0.2383410236434256</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.1061128581723583</v>
+        <v>0.1061122576617948</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>-0.03326473401149377</v>
+        <v>-0.03326484856533529</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>-0.01072121899980971</v>
+        <v>-0.01072068490331646</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.04289406213831337</v>
+        <v>0.04289362182263012</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>0.01611608274820342</v>
+        <v>0.01611598336572273</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>-0.06270664238157264</v>
+        <v>-0.06270625705937427</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>-0.0571019886313795</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>-0.1667126793462416</v>
+        <v>-0.1667127374920035</v>
       </c>
       <c r="S48" s="2" t="n">
-        <v>0.09096932267216107</v>
+        <v>0.09096925924111687</v>
       </c>
       <c r="T48" s="3" t="n">
-        <v>-0.05754562818614428</v>
+        <v>-0.0575455715870743</v>
       </c>
       <c r="U48" s="2" t="n">
-        <v>0.03865732843496716</v>
+        <v>0.03865733105847435</v>
       </c>
       <c r="V48" s="2" t="n">
-        <v>0.02873163068139784</v>
+        <v>0.0287318939181338</v>
       </c>
       <c r="W48" s="3" t="n">
-        <v>-0.01536458667448493</v>
+        <v>-0.01536483780663822</v>
       </c>
       <c r="X48" s="3" t="n">
-        <v>-0.1045396985515227</v>
+        <v>-0.1045395762828194</v>
       </c>
       <c r="Y48" s="2" t="n">
-        <v>0.08391722139183844</v>
+        <v>0.08391728738348059</v>
       </c>
       <c r="Z48" s="2" t="n">
-        <v>0.0135194239329619</v>
+        <v>0.01351942213596935</v>
       </c>
       <c r="AA48" s="2" t="n">
-        <v>0.1037131190367777</v>
+        <v>0.1037132365814728</v>
       </c>
       <c r="AB48" s="2" t="n">
-        <v>0.003610787781021862</v>
+        <v>0.00361054927735549</v>
       </c>
     </row>
     <row r="49">
@@ -12169,64 +12111,64 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" s="2" t="n">
-        <v>0.1078895978925289</v>
+        <v>0.1078895730454281</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0.1704240202890375</v>
+        <v>0.1704223911635359</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>-0.1409525009347972</v>
+        <v>-0.1409508325684445</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.2933020015045673</v>
+        <v>0.2933007454259831</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0.1791281861800305</v>
+        <v>0.1791287572268658</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0.0397024842150473</v>
+        <v>0.03970202153448543</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.04483101221416108</v>
+        <v>0.04483223705228556</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>-0.1259516709846942</v>
+        <v>-0.1259518780384696</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>-0.06935664780200324</v>
+        <v>-0.06935745170457219</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>-0.09404643241626032</v>
+        <v>-0.09404654432114967</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>-0.001015679696443228</v>
+        <v>-0.001014889601259839</v>
       </c>
       <c r="S49" s="2" t="n">
-        <v>0.09048807730720854</v>
+        <v>0.09048802617320817</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>-0.08845732469514012</v>
+        <v>-0.08845779705666479</v>
       </c>
       <c r="U49" s="2" t="n">
-        <v>0.001256811614239961</v>
+        <v>0.00125738010149079</v>
       </c>
       <c r="V49" s="2" t="n">
-        <v>0.09524119366010297</v>
+        <v>0.0952402311473417</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>-0.06169474894430316</v>
+        <v>-0.06169424973312732</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>-0.06458429511949282</v>
+        <v>-0.06458472283548167</v>
       </c>
       <c r="Y49" s="2" t="n">
-        <v>0.01201120215500207</v>
+        <v>0.01201155937171894</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>-0.0774905905608545</v>
+        <v>-0.07749075660227689</v>
       </c>
       <c r="AA49" s="2" t="n">
-        <v>0.09095736752589234</v>
+        <v>0.09095743654484334</v>
       </c>
       <c r="AB49" s="2" t="n">
         <v>0.06108000723250706</v>
@@ -12255,10 +12197,10 @@
         <v>0.06122965216823895</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0.06433009376613841</v>
+        <v>0.06433020376219512</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>-0.0800221164056707</v>
+        <v>-0.08002221148325006</v>
       </c>
       <c r="N50" s="2" t="n">
         <v>0.07055817519539653</v>
@@ -12273,13 +12215,13 @@
         <v>-0.09628832779398311</v>
       </c>
       <c r="R50" s="2" t="n">
-        <v>0.04107115699864905</v>
+        <v>0.04107122286298703</v>
       </c>
       <c r="S50" s="2" t="n">
-        <v>0.1109209337165984</v>
+        <v>0.1109207369012954</v>
       </c>
       <c r="T50" s="3" t="n">
-        <v>-0.0509118004431095</v>
+        <v>-0.05091169234368409</v>
       </c>
       <c r="U50" s="2" t="n">
         <v>0.04784142815277215</v>
@@ -12328,13 +12270,13 @@
         <v>0.01125449806882228</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.002365822939765394</v>
+        <v>0.002365744619411192</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0.006366714902314996</v>
+        <v>0.006366715399781508</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>-0.007095083970101057</v>
+        <v>-0.007095006879785482</v>
       </c>
       <c r="N51" s="2" t="n">
         <v>0.01349740936694088</v>
@@ -12897,7 +12839,7 @@
         <v>0.08550076663890249</v>
       </c>
       <c r="AB57" s="3" t="n">
-        <v>-0.0346838859609313</v>
+        <v>-0.03527600506161199</v>
       </c>
     </row>
     <row r="58">
@@ -13848,73 +13790,73 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>-0.04404117285930664</v>
+        <v>-0.0440414868239748</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>-0.2047952317118494</v>
+        <v>-0.2047954438816603</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.3074303023825018</v>
+        <v>0.3074303828631644</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0.1278147301915706</v>
+        <v>0.127816174106929</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.06304059046045007</v>
+        <v>0.06303968389334247</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>0.1569660182037411</v>
+        <v>0.1569661073407635</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0.05369919878332485</v>
+        <v>0.05369911760237334</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>-0.3698606038285306</v>
+        <v>-0.3698603844762647</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.2890466251358754</v>
+        <v>0.2890461764173833</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0.1742830135740145</v>
+        <v>0.1742828335437137</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.009685411547202927</v>
+        <v>0.009685413032081591</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.164513003328413</v>
+        <v>0.1645134838287512</v>
       </c>
       <c r="O69" s="2" t="n">
-        <v>0.3344977979180197</v>
+        <v>0.3344973195198802</v>
       </c>
       <c r="P69" s="2" t="n">
-        <v>0.1254933702065559</v>
+        <v>0.1254938710018763</v>
       </c>
       <c r="Q69" s="2" t="n">
-        <v>0.003550799472458621</v>
+        <v>0.00355053780243253</v>
       </c>
       <c r="R69" s="2" t="n">
-        <v>0.1281774443213572</v>
+        <v>0.1281771737177486</v>
       </c>
       <c r="S69" s="2" t="n">
-        <v>0.2121343726740526</v>
+        <v>0.2121344818826525</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>-0.05234810411322433</v>
+        <v>-0.05234785439344725</v>
       </c>
       <c r="U69" s="2" t="n">
-        <v>0.3066861885539829</v>
+        <v>0.3066861938902441</v>
       </c>
       <c r="V69" s="2" t="n">
-        <v>0.21076164047212</v>
+        <v>0.2107612908947332</v>
       </c>
       <c r="W69" s="2" t="n">
-        <v>0.2568186668401622</v>
+        <v>0.2568186041267984</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>-0.1952343727077388</v>
+        <v>-0.1952343989244965</v>
       </c>
       <c r="Y69" s="2" t="n">
-        <v>0.2604693832481693</v>
+        <v>0.2604695935706016</v>
       </c>
       <c r="Z69" s="2" t="n">
         <v>0.2381024370215845</v>
